--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128927950</v>
+        <v>128927732</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430233</v>
+        <v>430138</v>
       </c>
       <c r="R22" t="n">
-        <v>6817831</v>
+        <v>6817883</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,7 +2948,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927880</v>
+        <v>128927950</v>
       </c>
       <c r="B23" t="n">
         <v>79120</v>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430577</v>
+        <v>430233</v>
       </c>
       <c r="R23" t="n">
-        <v>6818221</v>
+        <v>6817831</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927868</v>
+        <v>128927880</v>
       </c>
       <c r="B24" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430089</v>
+        <v>430577</v>
       </c>
       <c r="R24" t="n">
-        <v>6817984</v>
+        <v>6818221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927978</v>
+        <v>128927868</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,21 +3153,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430082</v>
+        <v>430089</v>
       </c>
       <c r="R25" t="n">
-        <v>6818210</v>
+        <v>6817984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,7 +3221,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3240,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927843</v>
+        <v>128927978</v>
       </c>
       <c r="B26" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,21 +3250,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3275,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430626</v>
+        <v>430082</v>
       </c>
       <c r="R26" t="n">
-        <v>6818202</v>
+        <v>6818210</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,6 +3318,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927935</v>
+        <v>128927843</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430099</v>
+        <v>430626</v>
       </c>
       <c r="R27" t="n">
-        <v>6818154</v>
+        <v>6818202</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927963</v>
+        <v>128927935</v>
       </c>
       <c r="B28" t="n">
         <v>79120</v>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430064</v>
+        <v>430099</v>
       </c>
       <c r="R28" t="n">
-        <v>6818190</v>
+        <v>6818154</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927732</v>
+        <v>128927963</v>
       </c>
       <c r="B29" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,21 +3542,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430138</v>
+        <v>430064</v>
       </c>
       <c r="R29" t="n">
-        <v>6817883</v>
+        <v>6818190</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927821</v>
+        <v>128927721</v>
       </c>
       <c r="B30" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>429994</v>
+        <v>430060</v>
       </c>
       <c r="R30" t="n">
-        <v>6818158</v>
+        <v>6818156</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927770</v>
+        <v>128927726</v>
       </c>
       <c r="B31" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3736,42 +3736,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430455</v>
+        <v>430114</v>
       </c>
       <c r="R31" t="n">
-        <v>6818246</v>
+        <v>6817912</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3830,32 +3822,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128927834</v>
+        <v>128927821</v>
       </c>
       <c r="B32" t="n">
-        <v>58086</v>
+        <v>78878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3865,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430596</v>
+        <v>429994</v>
       </c>
       <c r="R32" t="n">
-        <v>6818184</v>
+        <v>6818158</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,10 +4016,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128927721</v>
+        <v>128927770</v>
       </c>
       <c r="B34" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,34 +4027,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>430060</v>
+        <v>430455</v>
       </c>
       <c r="R34" t="n">
-        <v>6818156</v>
+        <v>6818246</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128927726</v>
+        <v>128927834</v>
       </c>
       <c r="B35" t="n">
-        <v>79739</v>
+        <v>58086</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430114</v>
+        <v>430596</v>
       </c>
       <c r="R35" t="n">
-        <v>6817912</v>
+        <v>6818184</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128927895</v>
+        <v>128927743</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>430350</v>
+        <v>430211</v>
       </c>
       <c r="R36" t="n">
-        <v>6818053</v>
+        <v>6817980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128927871</v>
+        <v>128927813</v>
       </c>
       <c r="B37" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4326,21 +4326,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4353,7 +4353,7 @@
         <v>430145</v>
       </c>
       <c r="R37" t="n">
-        <v>6817833</v>
+        <v>6818165</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4412,7 +4412,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128927939</v>
+        <v>128927895</v>
       </c>
       <c r="B38" t="n">
         <v>79120</v>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>429903</v>
+        <v>430350</v>
       </c>
       <c r="R38" t="n">
-        <v>6818059</v>
+        <v>6818053</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4509,10 +4509,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128927973</v>
+        <v>128927871</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4520,37 +4520,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430073</v>
+        <v>430145</v>
       </c>
       <c r="R39" t="n">
-        <v>6818021</v>
+        <v>6817833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,7 +4588,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4610,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128927743</v>
+        <v>128927939</v>
       </c>
       <c r="B40" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,21 +4617,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4645,10 +4641,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>430211</v>
+        <v>429903</v>
       </c>
       <c r="R40" t="n">
-        <v>6817980</v>
+        <v>6818059</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4707,10 +4703,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128927773</v>
+        <v>128927973</v>
       </c>
       <c r="B41" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4718,31 +4714,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4750,10 +4741,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430251</v>
+        <v>430073</v>
       </c>
       <c r="R41" t="n">
-        <v>6818033</v>
+        <v>6818021</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4794,6 +4785,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4812,10 +4804,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128927813</v>
+        <v>128927773</v>
       </c>
       <c r="B42" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,34 +4815,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>430145</v>
+        <v>430251</v>
       </c>
       <c r="R42" t="n">
-        <v>6818165</v>
+        <v>6818033</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5689,10 +5689,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128927805</v>
+        <v>128927786</v>
       </c>
       <c r="B51" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,34 +5700,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430594</v>
+        <v>430078</v>
       </c>
       <c r="R51" t="n">
-        <v>6818187</v>
+        <v>6818213</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5760,6 +5768,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5786,7 +5799,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128927819</v>
+        <v>128927805</v>
       </c>
       <c r="B52" t="n">
         <v>78878</v>
@@ -5821,10 +5834,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>430033</v>
+        <v>430594</v>
       </c>
       <c r="R52" t="n">
-        <v>6818116</v>
+        <v>6818187</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5883,7 +5896,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128927799</v>
+        <v>128927819</v>
       </c>
       <c r="B53" t="n">
         <v>78878</v>
@@ -5918,10 +5931,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>430396</v>
+        <v>430033</v>
       </c>
       <c r="R53" t="n">
-        <v>6818052</v>
+        <v>6818116</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5980,10 +5993,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128927786</v>
+        <v>128927799</v>
       </c>
       <c r="B54" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5991,42 +6004,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>430078</v>
+        <v>430396</v>
       </c>
       <c r="R54" t="n">
-        <v>6818213</v>
+        <v>6818052</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6059,11 +6064,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6381,7 +6381,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128927944</v>
+        <v>128927970</v>
       </c>
       <c r="B58" t="n">
         <v>79120</v>
@@ -6410,19 +6410,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430531</v>
+        <v>429900</v>
       </c>
       <c r="R58" t="n">
-        <v>6818016</v>
+        <v>6818098</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6457,13 +6454,17 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6482,7 +6483,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927948</v>
+        <v>128927944</v>
       </c>
       <c r="B59" t="n">
         <v>79120</v>
@@ -6511,16 +6512,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430655</v>
+        <v>430531</v>
       </c>
       <c r="R59" t="n">
-        <v>6818216</v>
+        <v>6818016</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6561,6 +6565,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6579,7 +6584,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927882</v>
+        <v>128927948</v>
       </c>
       <c r="B60" t="n">
         <v>79120</v>
@@ -6614,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430526</v>
+        <v>430655</v>
       </c>
       <c r="R60" t="n">
-        <v>6818232</v>
+        <v>6818216</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6676,7 +6681,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128927929</v>
+        <v>128927882</v>
       </c>
       <c r="B61" t="n">
         <v>79120</v>
@@ -6711,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430208</v>
+        <v>430526</v>
       </c>
       <c r="R61" t="n">
-        <v>6817816</v>
+        <v>6818232</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6773,10 +6778,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128927855</v>
+        <v>128927929</v>
       </c>
       <c r="B62" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6784,21 +6789,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6808,10 +6813,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430113</v>
+        <v>430208</v>
       </c>
       <c r="R62" t="n">
-        <v>6818160</v>
+        <v>6817816</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6870,10 +6875,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128927815</v>
+        <v>128927855</v>
       </c>
       <c r="B63" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6881,21 +6886,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6905,10 +6910,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430061</v>
+        <v>430113</v>
       </c>
       <c r="R63" t="n">
-        <v>6818258</v>
+        <v>6818160</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7064,10 +7069,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128927970</v>
+        <v>128927815</v>
       </c>
       <c r="B65" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7075,21 +7080,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7099,10 +7104,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>429900</v>
+        <v>430061</v>
       </c>
       <c r="R65" t="n">
-        <v>6818098</v>
+        <v>6818258</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7135,11 +7140,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7166,10 +7166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128927893</v>
+        <v>128927790</v>
       </c>
       <c r="B66" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7177,34 +7177,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430286</v>
+        <v>430130</v>
       </c>
       <c r="R66" t="n">
-        <v>6818100</v>
+        <v>6817856</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7263,10 +7271,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128927974</v>
+        <v>128927751</v>
       </c>
       <c r="B67" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7274,34 +7282,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430091</v>
+        <v>430337</v>
       </c>
       <c r="R67" t="n">
-        <v>6818012</v>
+        <v>6818076</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7360,10 +7376,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128927825</v>
+        <v>128927893</v>
       </c>
       <c r="B68" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7371,21 +7387,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7395,10 +7411,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430024</v>
+        <v>430286</v>
       </c>
       <c r="R68" t="n">
-        <v>6818040</v>
+        <v>6818100</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7457,10 +7473,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128927790</v>
+        <v>128927974</v>
       </c>
       <c r="B69" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7468,42 +7484,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430130</v>
+        <v>430091</v>
       </c>
       <c r="R69" t="n">
-        <v>6817856</v>
+        <v>6818012</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7562,10 +7570,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128927751</v>
+        <v>128927825</v>
       </c>
       <c r="B70" t="n">
-        <v>57716</v>
+        <v>78878</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7573,42 +7581,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>430337</v>
+        <v>430024</v>
       </c>
       <c r="R70" t="n">
-        <v>6818076</v>
+        <v>6818040</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7667,10 +7667,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128927839</v>
+        <v>128927831</v>
       </c>
       <c r="B71" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,34 +7678,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430489</v>
+        <v>430126</v>
       </c>
       <c r="R71" t="n">
-        <v>6818084</v>
+        <v>6817835</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7746,6 +7749,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7764,7 +7768,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128927857</v>
+        <v>128927839</v>
       </c>
       <c r="B72" t="n">
         <v>78877</v>
@@ -7799,10 +7803,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>430051</v>
+        <v>430489</v>
       </c>
       <c r="R72" t="n">
-        <v>6818114</v>
+        <v>6818084</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7861,7 +7865,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128927852</v>
+        <v>128927857</v>
       </c>
       <c r="B73" t="n">
         <v>78877</v>
@@ -7896,10 +7900,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>430086</v>
+        <v>430051</v>
       </c>
       <c r="R73" t="n">
-        <v>6818279</v>
+        <v>6818114</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7958,10 +7962,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128927710</v>
+        <v>128927852</v>
       </c>
       <c r="B74" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7969,21 +7973,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7993,10 +7997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>430610</v>
+        <v>430086</v>
       </c>
       <c r="R74" t="n">
-        <v>6818230</v>
+        <v>6818279</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8055,10 +8059,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128927831</v>
+        <v>128927710</v>
       </c>
       <c r="B75" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8066,37 +8070,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>430126</v>
+        <v>430610</v>
       </c>
       <c r="R75" t="n">
-        <v>6817835</v>
+        <v>6818230</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8137,7 +8138,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8844,10 +8844,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128927885</v>
+        <v>128927725</v>
       </c>
       <c r="B83" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8855,21 +8855,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8879,10 +8879,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430366</v>
+        <v>430040</v>
       </c>
       <c r="R83" t="n">
-        <v>6818264</v>
+        <v>6818029</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8941,7 +8941,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128927947</v>
+        <v>128927885</v>
       </c>
       <c r="B84" t="n">
         <v>79120</v>
@@ -8976,10 +8976,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430568</v>
+        <v>430366</v>
       </c>
       <c r="R84" t="n">
-        <v>6818235</v>
+        <v>6818264</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9012,11 +9012,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9043,7 +9038,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128927912</v>
+        <v>128927947</v>
       </c>
       <c r="B85" t="n">
         <v>79120</v>
@@ -9078,10 +9073,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>430439</v>
+        <v>430568</v>
       </c>
       <c r="R85" t="n">
-        <v>6818230</v>
+        <v>6818235</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9114,6 +9109,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9140,10 +9140,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128927795</v>
+        <v>128927912</v>
       </c>
       <c r="B86" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9151,21 +9151,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430390</v>
+        <v>430439</v>
       </c>
       <c r="R86" t="n">
-        <v>6818205</v>
+        <v>6818230</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9237,10 +9237,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128927725</v>
+        <v>128927795</v>
       </c>
       <c r="B87" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9248,21 +9248,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>430040</v>
+        <v>430390</v>
       </c>
       <c r="R87" t="n">
-        <v>6818029</v>
+        <v>6818205</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9528,32 +9528,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128927794</v>
+        <v>128927891</v>
       </c>
       <c r="B90" t="n">
-        <v>97503</v>
+        <v>79120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>430535</v>
+        <v>430336</v>
       </c>
       <c r="R90" t="n">
-        <v>6818254</v>
+        <v>6818151</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128927810</v>
+        <v>128927884</v>
       </c>
       <c r="B91" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9636,21 +9636,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430215</v>
+        <v>430423</v>
       </c>
       <c r="R91" t="n">
-        <v>6818155</v>
+        <v>6818270</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128927714</v>
+        <v>128927864</v>
       </c>
       <c r="B92" t="n">
-        <v>79739</v>
+        <v>78877</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9733,21 +9733,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430630</v>
+        <v>429975</v>
       </c>
       <c r="R92" t="n">
-        <v>6818207</v>
+        <v>6818158</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128927803</v>
+        <v>128927965</v>
       </c>
       <c r="B93" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9830,21 +9830,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430580</v>
+        <v>430115</v>
       </c>
       <c r="R93" t="n">
-        <v>6818253</v>
+        <v>6818177</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9916,7 +9916,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128927891</v>
+        <v>128927932</v>
       </c>
       <c r="B94" t="n">
         <v>79120</v>
@@ -9945,16 +9945,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430336</v>
+        <v>430240</v>
       </c>
       <c r="R94" t="n">
-        <v>6818151</v>
+        <v>6817987</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9989,12 +9992,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10013,10 +10022,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128927980</v>
+        <v>128927975</v>
       </c>
       <c r="B95" t="n">
-        <v>78092</v>
+        <v>79120</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10024,21 +10033,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10048,10 +10057,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430081</v>
+        <v>430138</v>
       </c>
       <c r="R95" t="n">
-        <v>6818119</v>
+        <v>6817903</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10110,7 +10119,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128927884</v>
+        <v>128927943</v>
       </c>
       <c r="B96" t="n">
         <v>79120</v>
@@ -10145,10 +10154,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430423</v>
+        <v>430136</v>
       </c>
       <c r="R96" t="n">
-        <v>6818270</v>
+        <v>6817849</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10207,7 +10216,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128927864</v>
+        <v>128927851</v>
       </c>
       <c r="B97" t="n">
         <v>78877</v>
@@ -10242,10 +10251,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>429975</v>
+        <v>430135</v>
       </c>
       <c r="R97" t="n">
-        <v>6818158</v>
+        <v>6818172</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10304,10 +10313,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128927965</v>
+        <v>128927714</v>
       </c>
       <c r="B98" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10315,21 +10324,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10339,10 +10348,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430115</v>
+        <v>430630</v>
       </c>
       <c r="R98" t="n">
-        <v>6818177</v>
+        <v>6818207</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10401,10 +10410,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128927932</v>
+        <v>128927980</v>
       </c>
       <c r="B99" t="n">
-        <v>79120</v>
+        <v>78092</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10412,37 +10421,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430240</v>
+        <v>430081</v>
       </c>
       <c r="R99" t="n">
-        <v>6817987</v>
+        <v>6818119</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10477,18 +10483,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10507,10 +10507,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128927975</v>
+        <v>128927810</v>
       </c>
       <c r="B100" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10518,21 +10518,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430138</v>
+        <v>430215</v>
       </c>
       <c r="R100" t="n">
-        <v>6817903</v>
+        <v>6818155</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10604,10 +10604,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128927943</v>
+        <v>128927803</v>
       </c>
       <c r="B101" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10615,21 +10615,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>430136</v>
+        <v>430580</v>
       </c>
       <c r="R101" t="n">
-        <v>6817849</v>
+        <v>6818253</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10701,32 +10701,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128927851</v>
+        <v>128927794</v>
       </c>
       <c r="B102" t="n">
-        <v>78877</v>
+        <v>97503</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>430135</v>
+        <v>430535</v>
       </c>
       <c r="R102" t="n">
-        <v>6818172</v>
+        <v>6818254</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10798,32 +10798,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927827</v>
+        <v>128927836</v>
       </c>
       <c r="B103" t="n">
-        <v>78878</v>
+        <v>58086</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430057</v>
+        <v>430147</v>
       </c>
       <c r="R103" t="n">
-        <v>6818016</v>
+        <v>6817817</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927822</v>
+        <v>128927899</v>
       </c>
       <c r="B104" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10906,21 +10906,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>429973</v>
+        <v>430428</v>
       </c>
       <c r="R104" t="n">
-        <v>6818162</v>
+        <v>6818038</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10992,10 +10992,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927826</v>
+        <v>128927954</v>
       </c>
       <c r="B105" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11003,34 +11003,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430018</v>
+        <v>430166</v>
       </c>
       <c r="R105" t="n">
-        <v>6818046</v>
+        <v>6818134</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11065,12 +11068,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11089,10 +11098,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927796</v>
+        <v>128927888</v>
       </c>
       <c r="B106" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11100,21 +11109,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11124,10 +11133,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430323</v>
+        <v>430399</v>
       </c>
       <c r="R106" t="n">
-        <v>6818121</v>
+        <v>6818238</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11186,10 +11195,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927793</v>
+        <v>128927971</v>
       </c>
       <c r="B107" t="n">
-        <v>58146</v>
+        <v>79120</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11197,21 +11206,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11221,10 +11230,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430104</v>
+        <v>429925</v>
       </c>
       <c r="R107" t="n">
-        <v>6817933</v>
+        <v>6818065</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11283,32 +11292,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927836</v>
+        <v>128927949</v>
       </c>
       <c r="B108" t="n">
-        <v>58086</v>
+        <v>79120</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11318,10 +11327,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430147</v>
+        <v>430653</v>
       </c>
       <c r="R108" t="n">
-        <v>6817817</v>
+        <v>6818272</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11380,10 +11389,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927899</v>
+        <v>128927856</v>
       </c>
       <c r="B109" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11391,21 +11400,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11415,10 +11424,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430428</v>
+        <v>430060</v>
       </c>
       <c r="R109" t="n">
-        <v>6818038</v>
+        <v>6818160</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11477,10 +11486,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128927954</v>
+        <v>128927793</v>
       </c>
       <c r="B110" t="n">
-        <v>79120</v>
+        <v>58146</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11488,37 +11497,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430166</v>
+        <v>430104</v>
       </c>
       <c r="R110" t="n">
-        <v>6818134</v>
+        <v>6817933</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11553,18 +11559,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11583,10 +11583,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927888</v>
+        <v>128927827</v>
       </c>
       <c r="B111" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11594,21 +11594,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430399</v>
+        <v>430057</v>
       </c>
       <c r="R111" t="n">
-        <v>6818238</v>
+        <v>6818016</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927971</v>
+        <v>128927822</v>
       </c>
       <c r="B112" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11691,21 +11691,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>429925</v>
+        <v>429973</v>
       </c>
       <c r="R112" t="n">
-        <v>6818065</v>
+        <v>6818162</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,10 +11777,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927949</v>
+        <v>128927826</v>
       </c>
       <c r="B113" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11788,21 +11788,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430653</v>
+        <v>430018</v>
       </c>
       <c r="R113" t="n">
-        <v>6818272</v>
+        <v>6818046</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927856</v>
+        <v>128927796</v>
       </c>
       <c r="B114" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430060</v>
+        <v>430323</v>
       </c>
       <c r="R114" t="n">
-        <v>6818160</v>
+        <v>6818121</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13633,10 +13633,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128927777</v>
+        <v>128927720</v>
       </c>
       <c r="B132" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13644,42 +13644,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>429898</v>
+        <v>430112</v>
       </c>
       <c r="R132" t="n">
-        <v>6818099</v>
+        <v>6818160</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13738,10 +13730,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128927720</v>
+        <v>128927777</v>
       </c>
       <c r="B133" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13749,34 +13741,42 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430112</v>
+        <v>429898</v>
       </c>
       <c r="R133" t="n">
-        <v>6818160</v>
+        <v>6818099</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14045,37 +14045,43 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128927894</v>
+        <v>128927833</v>
       </c>
       <c r="B136" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -14083,10 +14089,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430321</v>
+        <v>430204</v>
       </c>
       <c r="R136" t="n">
-        <v>6818095</v>
+        <v>6817811</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14119,11 +14125,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14151,10 +14152,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128927900</v>
+        <v>128927781</v>
       </c>
       <c r="B137" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14162,34 +14163,42 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430467</v>
+        <v>430480</v>
       </c>
       <c r="R137" t="n">
-        <v>6818020</v>
+        <v>6817997</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14248,10 +14257,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128927889</v>
+        <v>128927788</v>
       </c>
       <c r="B138" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14259,34 +14268,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430385</v>
+        <v>430017</v>
       </c>
       <c r="R138" t="n">
-        <v>6818203</v>
+        <v>6818044</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14345,10 +14362,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128927863</v>
+        <v>128927775</v>
       </c>
       <c r="B139" t="n">
-        <v>78877</v>
+        <v>57713</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14356,34 +14373,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>429970</v>
+        <v>430083</v>
       </c>
       <c r="R139" t="n">
-        <v>6818162</v>
+        <v>6818224</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14442,10 +14467,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128927911</v>
+        <v>128927792</v>
       </c>
       <c r="B140" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14453,34 +14478,42 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430437</v>
+        <v>430150</v>
       </c>
       <c r="R140" t="n">
-        <v>6818227</v>
+        <v>6817814</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14539,10 +14572,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128927969</v>
+        <v>128927709</v>
       </c>
       <c r="B141" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14550,21 +14583,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14574,10 +14607,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>429947</v>
+        <v>430495</v>
       </c>
       <c r="R141" t="n">
-        <v>6818135</v>
+        <v>6818056</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14636,7 +14669,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128927956</v>
+        <v>128927894</v>
       </c>
       <c r="B142" t="n">
         <v>79120</v>
@@ -14665,16 +14698,19 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430119</v>
+        <v>430321</v>
       </c>
       <c r="R142" t="n">
-        <v>6818173</v>
+        <v>6818095</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14709,12 +14745,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14733,7 +14775,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128927925</v>
+        <v>128927900</v>
       </c>
       <c r="B143" t="n">
         <v>79120</v>
@@ -14768,10 +14810,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430683</v>
+        <v>430467</v>
       </c>
       <c r="R143" t="n">
-        <v>6818265</v>
+        <v>6818020</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14830,7 +14872,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128927972</v>
+        <v>128927889</v>
       </c>
       <c r="B144" t="n">
         <v>79120</v>
@@ -14859,19 +14901,16 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430018</v>
+        <v>430385</v>
       </c>
       <c r="R144" t="n">
-        <v>6818025</v>
+        <v>6818203</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14912,7 +14951,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -14931,7 +14969,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128927861</v>
+        <v>128927863</v>
       </c>
       <c r="B145" t="n">
         <v>78877</v>
@@ -14966,10 +15004,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>429989</v>
+        <v>429970</v>
       </c>
       <c r="R145" t="n">
-        <v>6818159</v>
+        <v>6818162</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15028,7 +15066,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128927926</v>
+        <v>128927911</v>
       </c>
       <c r="B146" t="n">
         <v>79120</v>
@@ -15063,10 +15101,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430701</v>
+        <v>430437</v>
       </c>
       <c r="R146" t="n">
-        <v>6818261</v>
+        <v>6818227</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15125,10 +15163,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128927824</v>
+        <v>128927969</v>
       </c>
       <c r="B147" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15136,21 +15174,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15160,10 +15198,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>429941</v>
+        <v>429947</v>
       </c>
       <c r="R147" t="n">
-        <v>6818056</v>
+        <v>6818135</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15222,10 +15260,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927748</v>
+        <v>128927956</v>
       </c>
       <c r="B148" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15233,21 +15271,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15257,10 +15295,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430202</v>
+        <v>430119</v>
       </c>
       <c r="R148" t="n">
-        <v>6818084</v>
+        <v>6818173</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15319,10 +15357,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927781</v>
+        <v>128927925</v>
       </c>
       <c r="B149" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15330,42 +15368,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430480</v>
+        <v>430683</v>
       </c>
       <c r="R149" t="n">
-        <v>6817997</v>
+        <v>6818265</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15424,10 +15454,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927788</v>
+        <v>128927972</v>
       </c>
       <c r="B150" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15435,31 +15465,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -15467,10 +15492,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430017</v>
+        <v>430018</v>
       </c>
       <c r="R150" t="n">
-        <v>6818044</v>
+        <v>6818025</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15511,6 +15536,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15529,54 +15555,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927833</v>
+        <v>128927861</v>
       </c>
       <c r="B151" t="n">
-        <v>8450</v>
+        <v>78877</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430204</v>
+        <v>429989</v>
       </c>
       <c r="R151" t="n">
-        <v>6817811</v>
+        <v>6818159</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15617,7 +15634,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15636,10 +15652,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128927709</v>
+        <v>128927926</v>
       </c>
       <c r="B152" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15647,21 +15663,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15671,10 +15687,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430495</v>
+        <v>430701</v>
       </c>
       <c r="R152" t="n">
-        <v>6818056</v>
+        <v>6818261</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15733,10 +15749,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128927775</v>
+        <v>128927824</v>
       </c>
       <c r="B153" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15744,42 +15760,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>430083</v>
+        <v>429941</v>
       </c>
       <c r="R153" t="n">
-        <v>6818224</v>
+        <v>6818056</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15838,10 +15846,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128927792</v>
+        <v>128927748</v>
       </c>
       <c r="B154" t="n">
-        <v>57713</v>
+        <v>79710</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15849,42 +15857,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430150</v>
+        <v>430202</v>
       </c>
       <c r="R154" t="n">
-        <v>6817814</v>
+        <v>6818084</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15943,10 +15943,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128927798</v>
+        <v>128927917</v>
       </c>
       <c r="B155" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15954,21 +15954,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15978,10 +15978,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>430315</v>
+        <v>430616</v>
       </c>
       <c r="R155" t="n">
-        <v>6818095</v>
+        <v>6818194</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16040,10 +16040,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128927828</v>
+        <v>128927903</v>
       </c>
       <c r="B156" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16051,21 +16051,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16078,10 +16078,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>430115</v>
+        <v>430437</v>
       </c>
       <c r="R156" t="n">
-        <v>6817902</v>
+        <v>6818119</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16114,6 +16114,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Måttligt/rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16141,10 +16146,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128927779</v>
+        <v>128927875</v>
       </c>
       <c r="B157" t="n">
-        <v>57713</v>
+        <v>78877</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16152,42 +16157,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430106</v>
+        <v>430127</v>
       </c>
       <c r="R157" t="n">
-        <v>6817957</v>
+        <v>6817846</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16246,10 +16243,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128927783</v>
+        <v>128927920</v>
       </c>
       <c r="B158" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16257,42 +16254,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430174</v>
+        <v>430637</v>
       </c>
       <c r="R158" t="n">
-        <v>6817923</v>
+        <v>6818260</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16351,10 +16340,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128927917</v>
+        <v>128927838</v>
       </c>
       <c r="B159" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16362,21 +16351,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16386,10 +16375,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430616</v>
+        <v>430439</v>
       </c>
       <c r="R159" t="n">
-        <v>6818194</v>
+        <v>6818031</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16448,10 +16437,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128927903</v>
+        <v>128927837</v>
       </c>
       <c r="B160" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16459,37 +16448,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430437</v>
+        <v>430360</v>
       </c>
       <c r="R160" t="n">
-        <v>6818119</v>
+        <v>6818057</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16524,18 +16510,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Måttligt/rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -16554,10 +16534,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128927875</v>
+        <v>128927951</v>
       </c>
       <c r="B161" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16565,34 +16545,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430127</v>
+        <v>430191</v>
       </c>
       <c r="R161" t="n">
-        <v>6817846</v>
+        <v>6817932</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16627,12 +16610,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Garnlav, måttligt inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -16651,7 +16640,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128927920</v>
+        <v>128927958</v>
       </c>
       <c r="B162" t="n">
         <v>79120</v>
@@ -16686,10 +16675,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430637</v>
+        <v>430048</v>
       </c>
       <c r="R162" t="n">
-        <v>6818260</v>
+        <v>6818232</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16748,7 +16737,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128927838</v>
+        <v>128927846</v>
       </c>
       <c r="B163" t="n">
         <v>78877</v>
@@ -16783,10 +16772,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430439</v>
+        <v>430241</v>
       </c>
       <c r="R163" t="n">
-        <v>6818031</v>
+        <v>6818085</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16845,10 +16834,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128927837</v>
+        <v>128927902</v>
       </c>
       <c r="B164" t="n">
-        <v>78877</v>
+        <v>79120</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16856,21 +16845,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16880,10 +16869,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430360</v>
+        <v>430530</v>
       </c>
       <c r="R164" t="n">
-        <v>6818057</v>
+        <v>6818025</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16942,10 +16931,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128927951</v>
+        <v>128927779</v>
       </c>
       <c r="B165" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16953,26 +16942,31 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -16980,10 +16974,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430191</v>
+        <v>430106</v>
       </c>
       <c r="R165" t="n">
-        <v>6817932</v>
+        <v>6817957</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17018,18 +17012,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Garnlav, måttligt inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17048,10 +17036,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128927958</v>
+        <v>128927783</v>
       </c>
       <c r="B166" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17059,34 +17047,42 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>430048</v>
+        <v>430174</v>
       </c>
       <c r="R166" t="n">
-        <v>6818232</v>
+        <v>6817923</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17145,10 +17141,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128927846</v>
+        <v>128927798</v>
       </c>
       <c r="B167" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17156,21 +17152,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17180,10 +17176,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430241</v>
+        <v>430315</v>
       </c>
       <c r="R167" t="n">
-        <v>6818085</v>
+        <v>6818095</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17242,10 +17238,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128927902</v>
+        <v>128927828</v>
       </c>
       <c r="B168" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17253,34 +17249,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430530</v>
+        <v>430115</v>
       </c>
       <c r="R168" t="n">
-        <v>6818025</v>
+        <v>6817902</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17321,6 +17320,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17339,10 +17339,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128927933</v>
+        <v>128927981</v>
       </c>
       <c r="B169" t="n">
-        <v>79120</v>
+        <v>78092</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17350,37 +17350,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>430220</v>
+        <v>430056</v>
       </c>
       <c r="R169" t="n">
-        <v>6818148</v>
+        <v>6818166</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17415,18 +17412,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -17445,10 +17436,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128927981</v>
+        <v>128927933</v>
       </c>
       <c r="B170" t="n">
-        <v>78092</v>
+        <v>79120</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17456,34 +17447,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430056</v>
+        <v>430220</v>
       </c>
       <c r="R170" t="n">
-        <v>6818166</v>
+        <v>6818148</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17518,12 +17512,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -17542,10 +17542,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128927904</v>
+        <v>128927737</v>
       </c>
       <c r="B171" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17553,34 +17553,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430405</v>
+        <v>430143</v>
       </c>
       <c r="R171" t="n">
-        <v>6818117</v>
+        <v>6817831</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17621,6 +17624,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -17639,32 +17643,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128927835</v>
+        <v>128927904</v>
       </c>
       <c r="B172" t="n">
-        <v>58086</v>
+        <v>79120</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17674,10 +17678,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430104</v>
+        <v>430405</v>
       </c>
       <c r="R172" t="n">
-        <v>6817960</v>
+        <v>6818117</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17736,10 +17740,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128927829</v>
+        <v>128927712</v>
       </c>
       <c r="B173" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17747,21 +17751,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17771,10 +17775,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430138</v>
+        <v>430596</v>
       </c>
       <c r="R173" t="n">
-        <v>6817883</v>
+        <v>6818190</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17833,32 +17837,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128927712</v>
+        <v>128927835</v>
       </c>
       <c r="B174" t="n">
-        <v>79739</v>
+        <v>58086</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17868,10 +17872,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430596</v>
+        <v>430104</v>
       </c>
       <c r="R174" t="n">
-        <v>6818190</v>
+        <v>6817960</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17930,10 +17934,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128927737</v>
+        <v>128927829</v>
       </c>
       <c r="B175" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17941,37 +17945,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430143</v>
+        <v>430138</v>
       </c>
       <c r="R175" t="n">
-        <v>6817831</v>
+        <v>6817883</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18012,7 +18013,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -18031,10 +18031,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128927898</v>
+        <v>128927750</v>
       </c>
       <c r="B176" t="n">
-        <v>79120</v>
+        <v>79710</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18042,21 +18042,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18066,10 +18066,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430384</v>
+        <v>430140</v>
       </c>
       <c r="R176" t="n">
-        <v>6818048</v>
+        <v>6817881</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18128,10 +18128,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128927848</v>
+        <v>128927741</v>
       </c>
       <c r="B177" t="n">
-        <v>78877</v>
+        <v>79710</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18139,21 +18139,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18163,10 +18163,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430174</v>
+        <v>430600</v>
       </c>
       <c r="R177" t="n">
-        <v>6818156</v>
+        <v>6818203</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18225,10 +18225,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128927968</v>
+        <v>128927812</v>
       </c>
       <c r="B178" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18236,21 +18236,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18260,10 +18260,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430067</v>
+        <v>430157</v>
       </c>
       <c r="R178" t="n">
-        <v>6818139</v>
+        <v>6818149</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18322,7 +18322,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128927952</v>
+        <v>128927898</v>
       </c>
       <c r="B179" t="n">
         <v>79120</v>
@@ -18357,10 +18357,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430190</v>
+        <v>430384</v>
       </c>
       <c r="R179" t="n">
-        <v>6817925</v>
+        <v>6818048</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18419,10 +18419,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128927945</v>
+        <v>128927848</v>
       </c>
       <c r="B180" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18430,21 +18430,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18454,10 +18454,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430404</v>
+        <v>430174</v>
       </c>
       <c r="R180" t="n">
-        <v>6818178</v>
+        <v>6818156</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18516,10 +18516,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128927750</v>
+        <v>128927968</v>
       </c>
       <c r="B181" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18527,21 +18527,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18551,10 +18551,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430140</v>
+        <v>430067</v>
       </c>
       <c r="R181" t="n">
-        <v>6817881</v>
+        <v>6818139</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18613,10 +18613,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128927723</v>
+        <v>128927952</v>
       </c>
       <c r="B182" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18624,21 +18624,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18648,10 +18648,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>429993</v>
+        <v>430190</v>
       </c>
       <c r="R182" t="n">
-        <v>6818157</v>
+        <v>6817925</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18710,10 +18710,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128927741</v>
+        <v>128927945</v>
       </c>
       <c r="B183" t="n">
-        <v>79710</v>
+        <v>79120</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18721,21 +18721,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18745,10 +18745,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430600</v>
+        <v>430404</v>
       </c>
       <c r="R183" t="n">
-        <v>6818203</v>
+        <v>6818178</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18807,53 +18807,45 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128927760</v>
+        <v>128927723</v>
       </c>
       <c r="B184" t="n">
-        <v>56907</v>
+        <v>79739</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430663</v>
+        <v>429993</v>
       </c>
       <c r="R184" t="n">
-        <v>6818259</v>
+        <v>6818157</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18912,45 +18904,53 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128927812</v>
+        <v>128927760</v>
       </c>
       <c r="B185" t="n">
-        <v>78878</v>
+        <v>56907</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430157</v>
+        <v>430663</v>
       </c>
       <c r="R185" t="n">
-        <v>6818149</v>
+        <v>6818259</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19802,10 +19802,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128927820</v>
+        <v>128927789</v>
       </c>
       <c r="B194" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19813,34 +19813,42 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430014</v>
+        <v>430089</v>
       </c>
       <c r="R194" t="n">
-        <v>6818142</v>
+        <v>6817965</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19873,6 +19881,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -19899,10 +19912,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128927818</v>
+        <v>128927728</v>
       </c>
       <c r="B195" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19910,21 +19923,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19934,10 +19947,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430048</v>
+        <v>430232</v>
       </c>
       <c r="R195" t="n">
-        <v>6818123</v>
+        <v>6818068</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19996,10 +20009,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128927789</v>
+        <v>128927731</v>
       </c>
       <c r="B196" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20007,42 +20020,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430089</v>
+        <v>430056</v>
       </c>
       <c r="R196" t="n">
-        <v>6817965</v>
+        <v>6818017</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20075,11 +20080,6 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20106,10 +20106,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128927731</v>
+        <v>128927820</v>
       </c>
       <c r="B197" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20117,21 +20117,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20141,10 +20141,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430056</v>
+        <v>430014</v>
       </c>
       <c r="R197" t="n">
-        <v>6818017</v>
+        <v>6818142</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20203,10 +20203,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128927728</v>
+        <v>128927818</v>
       </c>
       <c r="B198" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20214,21 +20214,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20238,10 +20238,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430232</v>
+        <v>430048</v>
       </c>
       <c r="R198" t="n">
-        <v>6818068</v>
+        <v>6818123</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20785,10 +20785,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128927755</v>
+        <v>128927715</v>
       </c>
       <c r="B204" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20796,42 +20796,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430480</v>
+        <v>430650</v>
       </c>
       <c r="R204" t="n">
-        <v>6818068</v>
+        <v>6818249</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20890,10 +20882,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128927809</v>
+        <v>128927717</v>
       </c>
       <c r="B205" t="n">
-        <v>78878</v>
+        <v>79739</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20901,21 +20893,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20925,10 +20917,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430222</v>
+        <v>430214</v>
       </c>
       <c r="R205" t="n">
-        <v>6818155</v>
+        <v>6817971</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20987,10 +20979,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128927814</v>
+        <v>128927755</v>
       </c>
       <c r="B206" t="n">
-        <v>78878</v>
+        <v>57716</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20998,34 +20990,42 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430138</v>
+        <v>430480</v>
       </c>
       <c r="R206" t="n">
-        <v>6818171</v>
+        <v>6818068</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21084,10 +21084,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128927717</v>
+        <v>128927809</v>
       </c>
       <c r="B207" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21095,21 +21095,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21119,10 +21119,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>430214</v>
+        <v>430222</v>
       </c>
       <c r="R207" t="n">
-        <v>6817971</v>
+        <v>6818155</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21181,10 +21181,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128927715</v>
+        <v>128927814</v>
       </c>
       <c r="B208" t="n">
-        <v>79739</v>
+        <v>78878</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21192,21 +21192,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>430650</v>
+        <v>430138</v>
       </c>
       <c r="R208" t="n">
-        <v>6818249</v>
+        <v>6818171</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21375,10 +21375,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128927830</v>
+        <v>128927860</v>
       </c>
       <c r="B210" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21386,21 +21386,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21410,10 +21410,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430167</v>
+        <v>430013</v>
       </c>
       <c r="R210" t="n">
-        <v>6817850</v>
+        <v>6818142</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21472,10 +21472,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128927808</v>
+        <v>128927941</v>
       </c>
       <c r="B211" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21483,21 +21483,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21507,10 +21507,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>430669</v>
+        <v>430078</v>
       </c>
       <c r="R211" t="n">
-        <v>6818242</v>
+        <v>6817995</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21569,10 +21569,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128927817</v>
+        <v>128927960</v>
       </c>
       <c r="B212" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21580,21 +21580,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21604,10 +21604,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430068</v>
+        <v>430089</v>
       </c>
       <c r="R212" t="n">
-        <v>6818152</v>
+        <v>6818238</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21666,10 +21666,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128927746</v>
+        <v>128927866</v>
       </c>
       <c r="B213" t="n">
-        <v>79710</v>
+        <v>78877</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21677,21 +21677,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21701,10 +21701,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>430232</v>
+        <v>429950</v>
       </c>
       <c r="R213" t="n">
-        <v>6818068</v>
+        <v>6818057</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21763,10 +21763,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128927860</v>
+        <v>128927753</v>
       </c>
       <c r="B214" t="n">
-        <v>78877</v>
+        <v>57716</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21774,34 +21774,42 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>430013</v>
+        <v>430514</v>
       </c>
       <c r="R214" t="n">
-        <v>6818142</v>
+        <v>6818047</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21860,10 +21868,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128927941</v>
+        <v>128927830</v>
       </c>
       <c r="B215" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21871,21 +21879,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21895,10 +21903,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>430078</v>
+        <v>430167</v>
       </c>
       <c r="R215" t="n">
-        <v>6817995</v>
+        <v>6817850</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21957,10 +21965,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128927960</v>
+        <v>128927808</v>
       </c>
       <c r="B216" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21968,21 +21976,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -21992,10 +22000,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>430089</v>
+        <v>430669</v>
       </c>
       <c r="R216" t="n">
-        <v>6818238</v>
+        <v>6818242</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22054,10 +22062,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128927866</v>
+        <v>128927817</v>
       </c>
       <c r="B217" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22065,21 +22073,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22089,10 +22097,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>429950</v>
+        <v>430068</v>
       </c>
       <c r="R217" t="n">
-        <v>6818057</v>
+        <v>6818152</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22151,10 +22159,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128927753</v>
+        <v>128927746</v>
       </c>
       <c r="B218" t="n">
-        <v>57716</v>
+        <v>79710</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22162,42 +22170,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>430514</v>
+        <v>430232</v>
       </c>
       <c r="R218" t="n">
-        <v>6818047</v>
+        <v>6818068</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22644,10 +22644,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128927800</v>
+        <v>128927771</v>
       </c>
       <c r="B223" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22655,26 +22655,31 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
@@ -22682,10 +22687,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430487</v>
+        <v>430658</v>
       </c>
       <c r="R223" t="n">
-        <v>6818080</v>
+        <v>6818274</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22726,7 +22731,6 @@
       <c r="AE223" t="b">
         <v>0</v>
       </c>
-      <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="b">
         <v>0</v>
       </c>
@@ -22745,10 +22749,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128927771</v>
+        <v>128927800</v>
       </c>
       <c r="B224" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22756,31 +22760,26 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
@@ -22788,10 +22787,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430658</v>
+        <v>430487</v>
       </c>
       <c r="R224" t="n">
-        <v>6818274</v>
+        <v>6818080</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22832,6 +22831,7 @@
       <c r="AE224" t="b">
         <v>0</v>
       </c>
+      <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
       </c>
@@ -22850,10 +22850,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128927850</v>
+        <v>128927730</v>
       </c>
       <c r="B225" t="n">
-        <v>78877</v>
+        <v>79739</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22861,21 +22861,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22885,10 +22885,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430159</v>
+        <v>430075</v>
       </c>
       <c r="R225" t="n">
-        <v>6818161</v>
+        <v>6818213</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22947,10 +22947,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128927890</v>
+        <v>128927850</v>
       </c>
       <c r="B226" t="n">
-        <v>79120</v>
+        <v>78877</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22958,21 +22958,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22982,10 +22982,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430348</v>
+        <v>430159</v>
       </c>
       <c r="R226" t="n">
-        <v>6818167</v>
+        <v>6818161</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23044,7 +23044,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128927915</v>
+        <v>128927890</v>
       </c>
       <c r="B227" t="n">
         <v>79120</v>
@@ -23073,19 +23073,16 @@
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430575</v>
+        <v>430348</v>
       </c>
       <c r="R227" t="n">
-        <v>6818234</v>
+        <v>6818167</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23126,7 +23123,6 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -23145,7 +23141,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128927923</v>
+        <v>128927915</v>
       </c>
       <c r="B228" t="n">
         <v>79120</v>
@@ -23174,16 +23170,19 @@
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430670</v>
+        <v>430575</v>
       </c>
       <c r="R228" t="n">
-        <v>6818263</v>
+        <v>6818234</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23224,6 +23223,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -23242,10 +23242,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128927730</v>
+        <v>128927923</v>
       </c>
       <c r="B229" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23253,21 +23253,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23277,10 +23277,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430075</v>
+        <v>430670</v>
       </c>
       <c r="R229" t="n">
-        <v>6818213</v>
+        <v>6818263</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128927732</v>
+        <v>128927950</v>
       </c>
       <c r="B22" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430138</v>
+        <v>430233</v>
       </c>
       <c r="R22" t="n">
-        <v>6817883</v>
+        <v>6817831</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927950</v>
+        <v>128927978</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430233</v>
+        <v>430082</v>
       </c>
       <c r="R23" t="n">
-        <v>6817831</v>
+        <v>6818210</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,6 +3027,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3045,10 +3046,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927880</v>
+        <v>128927935</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,10 +3081,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430577</v>
+        <v>430099</v>
       </c>
       <c r="R24" t="n">
-        <v>6818221</v>
+        <v>6818154</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3143,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927868</v>
+        <v>128927963</v>
       </c>
       <c r="B25" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,21 +3154,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430089</v>
+        <v>430064</v>
       </c>
       <c r="R25" t="n">
-        <v>6817984</v>
+        <v>6818190</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3240,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927978</v>
+        <v>128927880</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3274,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430082</v>
+        <v>430577</v>
       </c>
       <c r="R26" t="n">
-        <v>6818210</v>
+        <v>6818221</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3319,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927843</v>
+        <v>128927868</v>
       </c>
       <c r="B27" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430626</v>
+        <v>430089</v>
       </c>
       <c r="R27" t="n">
-        <v>6818202</v>
+        <v>6817984</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927935</v>
+        <v>128927843</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430099</v>
+        <v>430626</v>
       </c>
       <c r="R28" t="n">
-        <v>6818154</v>
+        <v>6818202</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927963</v>
+        <v>128927732</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,21 +3542,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430064</v>
+        <v>430138</v>
       </c>
       <c r="R29" t="n">
-        <v>6818190</v>
+        <v>6817883</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3631,7 +3631,7 @@
         <v>128927721</v>
       </c>
       <c r="B30" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>128927726</v>
       </c>
       <c r="B31" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128927821</v>
+        <v>128927770</v>
       </c>
       <c r="B32" t="n">
-        <v>78878</v>
+        <v>57717</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3833,34 +3833,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>429994</v>
+        <v>430455</v>
       </c>
       <c r="R32" t="n">
-        <v>6818158</v>
+        <v>6818246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3919,32 +3927,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128927802</v>
+        <v>128927834</v>
       </c>
       <c r="B33" t="n">
-        <v>78878</v>
+        <v>58090</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3954,10 +3962,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>430567</v>
+        <v>430596</v>
       </c>
       <c r="R33" t="n">
-        <v>6818243</v>
+        <v>6818184</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4016,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128927770</v>
+        <v>128927821</v>
       </c>
       <c r="B34" t="n">
-        <v>57713</v>
+        <v>78882</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4027,42 +4035,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>430455</v>
+        <v>429994</v>
       </c>
       <c r="R34" t="n">
-        <v>6818246</v>
+        <v>6818158</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128927834</v>
+        <v>128927802</v>
       </c>
       <c r="B35" t="n">
-        <v>58086</v>
+        <v>78882</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430596</v>
+        <v>430567</v>
       </c>
       <c r="R35" t="n">
-        <v>6818184</v>
+        <v>6818243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128927743</v>
+        <v>128927895</v>
       </c>
       <c r="B36" t="n">
-        <v>79710</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>430211</v>
+        <v>430350</v>
       </c>
       <c r="R36" t="n">
-        <v>6817980</v>
+        <v>6818053</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128927813</v>
+        <v>128927939</v>
       </c>
       <c r="B37" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4326,21 +4326,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>430145</v>
+        <v>429903</v>
       </c>
       <c r="R37" t="n">
-        <v>6818165</v>
+        <v>6818059</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128927895</v>
+        <v>128927973</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4441,16 +4441,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430350</v>
+        <v>430073</v>
       </c>
       <c r="R38" t="n">
-        <v>6818053</v>
+        <v>6818021</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4491,6 +4494,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4512,7 +4516,7 @@
         <v>128927871</v>
       </c>
       <c r="B39" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4606,10 +4610,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128927939</v>
+        <v>128927773</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4617,34 +4621,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>429903</v>
+        <v>430251</v>
       </c>
       <c r="R40" t="n">
-        <v>6818059</v>
+        <v>6818033</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4703,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128927973</v>
+        <v>128927743</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79714</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4714,37 +4726,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430073</v>
+        <v>430211</v>
       </c>
       <c r="R41" t="n">
-        <v>6818021</v>
+        <v>6817980</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4785,7 +4794,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4804,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128927773</v>
+        <v>128927813</v>
       </c>
       <c r="B42" t="n">
-        <v>57713</v>
+        <v>78882</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4815,42 +4823,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>430251</v>
+        <v>430145</v>
       </c>
       <c r="R42" t="n">
-        <v>6818033</v>
+        <v>6818165</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128927845</v>
+        <v>128927928</v>
       </c>
       <c r="B43" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430669</v>
+        <v>430293</v>
       </c>
       <c r="R43" t="n">
-        <v>6818249</v>
+        <v>6817871</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128927930</v>
+        <v>128927934</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430205</v>
+        <v>430088</v>
       </c>
       <c r="R44" t="n">
-        <v>6817961</v>
+        <v>6818186</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128927928</v>
+        <v>128927938</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430293</v>
+        <v>429959</v>
       </c>
       <c r="R45" t="n">
-        <v>6817871</v>
+        <v>6818128</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128927934</v>
+        <v>128927966</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430088</v>
+        <v>430071</v>
       </c>
       <c r="R46" t="n">
-        <v>6818186</v>
+        <v>6818124</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128927842</v>
+        <v>128927805</v>
       </c>
       <c r="B47" t="n">
-        <v>78877</v>
+        <v>78882</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430596</v>
+        <v>430594</v>
       </c>
       <c r="R47" t="n">
-        <v>6818186</v>
+        <v>6818187</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5394,10 +5394,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128927938</v>
+        <v>128927819</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5405,21 +5405,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>429959</v>
+        <v>430033</v>
       </c>
       <c r="R48" t="n">
-        <v>6818128</v>
+        <v>6818116</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128927976</v>
+        <v>128927799</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5502,37 +5502,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430149</v>
+        <v>430396</v>
       </c>
       <c r="R49" t="n">
-        <v>6817860</v>
+        <v>6818052</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5573,7 +5570,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5592,10 +5588,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128927966</v>
+        <v>128927806</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5603,21 +5599,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5627,10 +5623,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430071</v>
+        <v>430655</v>
       </c>
       <c r="R50" t="n">
-        <v>6818124</v>
+        <v>6818264</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5689,10 +5685,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128927786</v>
+        <v>128927845</v>
       </c>
       <c r="B51" t="n">
-        <v>57713</v>
+        <v>78881</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,42 +5696,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430078</v>
+        <v>430669</v>
       </c>
       <c r="R51" t="n">
-        <v>6818213</v>
+        <v>6818249</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5768,11 +5756,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5799,10 +5782,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128927805</v>
+        <v>128927930</v>
       </c>
       <c r="B52" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5810,21 +5793,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5834,10 +5817,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>430594</v>
+        <v>430205</v>
       </c>
       <c r="R52" t="n">
-        <v>6818187</v>
+        <v>6817961</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,10 +5879,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128927819</v>
+        <v>128927842</v>
       </c>
       <c r="B53" t="n">
-        <v>78878</v>
+        <v>78881</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5907,21 +5890,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5931,10 +5914,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>430033</v>
+        <v>430596</v>
       </c>
       <c r="R53" t="n">
-        <v>6818116</v>
+        <v>6818186</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5993,10 +5976,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128927799</v>
+        <v>128927976</v>
       </c>
       <c r="B54" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6004,34 +5987,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>430396</v>
+        <v>430149</v>
       </c>
       <c r="R54" t="n">
-        <v>6818052</v>
+        <v>6817860</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6072,6 +6058,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6090,10 +6077,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128927806</v>
+        <v>128927786</v>
       </c>
       <c r="B55" t="n">
-        <v>78878</v>
+        <v>57717</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6101,34 +6088,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>430655</v>
+        <v>430078</v>
       </c>
       <c r="R55" t="n">
-        <v>6818264</v>
+        <v>6818213</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6161,6 +6156,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6190,7 +6190,7 @@
         <v>128927937</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128927874</v>
+        <v>128927970</v>
       </c>
       <c r="B57" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6295,21 +6295,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>430154</v>
+        <v>429900</v>
       </c>
       <c r="R57" t="n">
-        <v>6817859</v>
+        <v>6818098</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6355,6 +6355,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,10 +6386,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128927970</v>
+        <v>128927944</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6410,16 +6415,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>429900</v>
+        <v>430531</v>
       </c>
       <c r="R58" t="n">
-        <v>6818098</v>
+        <v>6818016</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6454,17 +6462,13 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6483,10 +6487,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927944</v>
+        <v>128927948</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6512,19 +6516,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430531</v>
+        <v>430655</v>
       </c>
       <c r="R59" t="n">
-        <v>6818016</v>
+        <v>6818216</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6565,7 +6566,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927948</v>
+        <v>128927882</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430655</v>
+        <v>430526</v>
       </c>
       <c r="R60" t="n">
-        <v>6818216</v>
+        <v>6818232</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128927882</v>
+        <v>128927929</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430526</v>
+        <v>430208</v>
       </c>
       <c r="R61" t="n">
-        <v>6818232</v>
+        <v>6817816</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128927929</v>
+        <v>128927874</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430208</v>
+        <v>430154</v>
       </c>
       <c r="R62" t="n">
-        <v>6817816</v>
+        <v>6817859</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6878,7 +6878,7 @@
         <v>128927855</v>
       </c>
       <c r="B63" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>128927735</v>
       </c>
       <c r="B64" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>128927815</v>
       </c>
       <c r="B65" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128927790</v>
+        <v>128927893</v>
       </c>
       <c r="B66" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7177,42 +7177,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430130</v>
+        <v>430286</v>
       </c>
       <c r="R66" t="n">
-        <v>6817856</v>
+        <v>6818100</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,10 +7263,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128927751</v>
+        <v>128927790</v>
       </c>
       <c r="B67" t="n">
-        <v>57716</v>
+        <v>57717</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,16 +7274,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7304,7 +7296,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7314,10 +7306,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430337</v>
+        <v>430130</v>
       </c>
       <c r="R67" t="n">
-        <v>6818076</v>
+        <v>6817856</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7376,10 +7368,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128927893</v>
+        <v>128927974</v>
       </c>
       <c r="B68" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7411,10 +7403,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430286</v>
+        <v>430091</v>
       </c>
       <c r="R68" t="n">
-        <v>6818100</v>
+        <v>6818012</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7473,10 +7465,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128927974</v>
+        <v>128927751</v>
       </c>
       <c r="B69" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7484,34 +7476,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430091</v>
+        <v>430337</v>
       </c>
       <c r="R69" t="n">
-        <v>6818012</v>
+        <v>6818076</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,7 +7573,7 @@
         <v>128927825</v>
       </c>
       <c r="B70" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7667,10 +7667,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128927831</v>
+        <v>128927710</v>
       </c>
       <c r="B71" t="n">
-        <v>78878</v>
+        <v>79743</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,37 +7678,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430126</v>
+        <v>430610</v>
       </c>
       <c r="R71" t="n">
-        <v>6817835</v>
+        <v>6818230</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7749,7 +7746,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7771,7 +7767,7 @@
         <v>128927839</v>
       </c>
       <c r="B72" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7868,7 +7864,7 @@
         <v>128927857</v>
       </c>
       <c r="B73" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7965,7 +7961,7 @@
         <v>128927852</v>
       </c>
       <c r="B74" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8059,10 +8055,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128927710</v>
+        <v>128927831</v>
       </c>
       <c r="B75" t="n">
-        <v>79739</v>
+        <v>78882</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8070,34 +8066,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>430610</v>
+        <v>430126</v>
       </c>
       <c r="R75" t="n">
-        <v>6818230</v>
+        <v>6817835</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8138,6 +8137,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128927840</v>
+        <v>128927964</v>
       </c>
       <c r="B76" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8167,21 +8167,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430407</v>
+        <v>430099</v>
       </c>
       <c r="R76" t="n">
-        <v>6818114</v>
+        <v>6818174</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128927865</v>
+        <v>128927897</v>
       </c>
       <c r="B77" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>429935</v>
+        <v>430386</v>
       </c>
       <c r="R77" t="n">
-        <v>6818065</v>
+        <v>6818039</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8350,10 +8350,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128927924</v>
+        <v>128927912</v>
       </c>
       <c r="B78" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430671</v>
+        <v>430439</v>
       </c>
       <c r="R78" t="n">
-        <v>6818266</v>
+        <v>6818230</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128927964</v>
+        <v>128927840</v>
       </c>
       <c r="B79" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8458,21 +8458,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430099</v>
+        <v>430407</v>
       </c>
       <c r="R79" t="n">
-        <v>6818174</v>
+        <v>6818114</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8544,10 +8544,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128927897</v>
+        <v>128927865</v>
       </c>
       <c r="B80" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8555,21 +8555,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430386</v>
+        <v>429935</v>
       </c>
       <c r="R80" t="n">
-        <v>6818039</v>
+        <v>6818065</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8641,10 +8641,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128927955</v>
+        <v>128927924</v>
       </c>
       <c r="B81" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8670,19 +8670,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430129</v>
+        <v>430671</v>
       </c>
       <c r="R81" t="n">
-        <v>6818156</v>
+        <v>6818266</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8717,18 +8714,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30 m</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8747,10 +8738,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128927905</v>
+        <v>128927955</v>
       </c>
       <c r="B82" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8776,16 +8767,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430395</v>
+        <v>430129</v>
       </c>
       <c r="R82" t="n">
-        <v>6818138</v>
+        <v>6818156</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8820,12 +8814,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30 m</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8844,10 +8844,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128927725</v>
+        <v>128927905</v>
       </c>
       <c r="B83" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8855,21 +8855,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8879,10 +8879,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430040</v>
+        <v>430395</v>
       </c>
       <c r="R83" t="n">
-        <v>6818029</v>
+        <v>6818138</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
         <v>128927885</v>
       </c>
       <c r="B84" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>128927947</v>
       </c>
       <c r="B85" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9140,10 +9140,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128927912</v>
+        <v>128927725</v>
       </c>
       <c r="B86" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9151,21 +9151,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430439</v>
+        <v>430040</v>
       </c>
       <c r="R86" t="n">
-        <v>6818230</v>
+        <v>6818029</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9240,7 +9240,7 @@
         <v>128927795</v>
       </c>
       <c r="B87" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>128927811</v>
       </c>
       <c r="B88" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>128927832</v>
       </c>
       <c r="B89" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9528,10 +9528,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128927891</v>
+        <v>128927864</v>
       </c>
       <c r="B90" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9539,21 +9539,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>430336</v>
+        <v>429975</v>
       </c>
       <c r="R90" t="n">
-        <v>6818151</v>
+        <v>6818158</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128927884</v>
+        <v>128927965</v>
       </c>
       <c r="B91" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430423</v>
+        <v>430115</v>
       </c>
       <c r="R91" t="n">
-        <v>6818270</v>
+        <v>6818177</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128927864</v>
+        <v>128927932</v>
       </c>
       <c r="B92" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9733,34 +9733,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>429975</v>
+        <v>430240</v>
       </c>
       <c r="R92" t="n">
-        <v>6818158</v>
+        <v>6817987</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9795,12 +9798,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9819,10 +9828,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128927965</v>
+        <v>128927851</v>
       </c>
       <c r="B93" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9830,21 +9839,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9854,10 +9863,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430115</v>
+        <v>430135</v>
       </c>
       <c r="R93" t="n">
-        <v>6818177</v>
+        <v>6818172</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9916,10 +9925,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128927932</v>
+        <v>128927810</v>
       </c>
       <c r="B94" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9927,37 +9936,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430240</v>
+        <v>430215</v>
       </c>
       <c r="R94" t="n">
-        <v>6817987</v>
+        <v>6818155</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9992,18 +9998,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10022,10 +10022,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128927975</v>
+        <v>128927803</v>
       </c>
       <c r="B95" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10033,21 +10033,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10057,10 +10057,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430138</v>
+        <v>430580</v>
       </c>
       <c r="R95" t="n">
-        <v>6817903</v>
+        <v>6818253</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10119,10 +10119,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128927943</v>
+        <v>128927891</v>
       </c>
       <c r="B96" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10154,10 +10154,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430136</v>
+        <v>430336</v>
       </c>
       <c r="R96" t="n">
-        <v>6817849</v>
+        <v>6818151</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10216,10 +10216,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128927851</v>
+        <v>128927884</v>
       </c>
       <c r="B97" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10227,21 +10227,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430135</v>
+        <v>430423</v>
       </c>
       <c r="R97" t="n">
-        <v>6818172</v>
+        <v>6818270</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10313,10 +10313,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128927714</v>
+        <v>128927975</v>
       </c>
       <c r="B98" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10324,21 +10324,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430630</v>
+        <v>430138</v>
       </c>
       <c r="R98" t="n">
-        <v>6818207</v>
+        <v>6817903</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10410,10 +10410,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128927980</v>
+        <v>128927943</v>
       </c>
       <c r="B99" t="n">
-        <v>78092</v>
+        <v>79124</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10421,21 +10421,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430081</v>
+        <v>430136</v>
       </c>
       <c r="R99" t="n">
-        <v>6818119</v>
+        <v>6817849</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10507,10 +10507,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128927810</v>
+        <v>128927714</v>
       </c>
       <c r="B100" t="n">
-        <v>78878</v>
+        <v>79743</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10518,21 +10518,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430215</v>
+        <v>430630</v>
       </c>
       <c r="R100" t="n">
-        <v>6818155</v>
+        <v>6818207</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10604,10 +10604,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128927803</v>
+        <v>128927980</v>
       </c>
       <c r="B101" t="n">
-        <v>78878</v>
+        <v>78096</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10615,21 +10615,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>430580</v>
+        <v>430081</v>
       </c>
       <c r="R101" t="n">
-        <v>6818253</v>
+        <v>6818119</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10704,7 +10704,7 @@
         <v>128927794</v>
       </c>
       <c r="B102" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10798,32 +10798,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927836</v>
+        <v>128927888</v>
       </c>
       <c r="B103" t="n">
-        <v>58086</v>
+        <v>79124</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430147</v>
+        <v>430399</v>
       </c>
       <c r="R103" t="n">
-        <v>6817817</v>
+        <v>6818238</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927899</v>
+        <v>128927971</v>
       </c>
       <c r="B104" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430428</v>
+        <v>429925</v>
       </c>
       <c r="R104" t="n">
-        <v>6818038</v>
+        <v>6818065</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10992,10 +10992,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927954</v>
+        <v>128927949</v>
       </c>
       <c r="B105" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11021,19 +11021,16 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430166</v>
+        <v>430653</v>
       </c>
       <c r="R105" t="n">
-        <v>6818134</v>
+        <v>6818272</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11068,18 +11065,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11098,10 +11089,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927888</v>
+        <v>128927899</v>
       </c>
       <c r="B106" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11133,10 +11124,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430399</v>
+        <v>430428</v>
       </c>
       <c r="R106" t="n">
-        <v>6818238</v>
+        <v>6818038</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11195,10 +11186,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927971</v>
+        <v>128927954</v>
       </c>
       <c r="B107" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11224,16 +11215,19 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>429925</v>
+        <v>430166</v>
       </c>
       <c r="R107" t="n">
-        <v>6818065</v>
+        <v>6818134</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11268,12 +11262,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11292,10 +11292,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927949</v>
+        <v>128927856</v>
       </c>
       <c r="B108" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11303,21 +11303,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11327,10 +11327,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430653</v>
+        <v>430060</v>
       </c>
       <c r="R108" t="n">
-        <v>6818272</v>
+        <v>6818160</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11389,10 +11389,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927856</v>
+        <v>128927827</v>
       </c>
       <c r="B109" t="n">
-        <v>78877</v>
+        <v>78882</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11400,21 +11400,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11424,10 +11424,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430060</v>
+        <v>430057</v>
       </c>
       <c r="R109" t="n">
-        <v>6818160</v>
+        <v>6818016</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11486,10 +11486,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128927793</v>
+        <v>128927822</v>
       </c>
       <c r="B110" t="n">
-        <v>58146</v>
+        <v>78882</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11497,21 +11497,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103001</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430104</v>
+        <v>429973</v>
       </c>
       <c r="R110" t="n">
-        <v>6817933</v>
+        <v>6818162</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11583,10 +11583,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927827</v>
+        <v>128927826</v>
       </c>
       <c r="B111" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430057</v>
+        <v>430018</v>
       </c>
       <c r="R111" t="n">
-        <v>6818016</v>
+        <v>6818046</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927822</v>
+        <v>128927796</v>
       </c>
       <c r="B112" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>429973</v>
+        <v>430323</v>
       </c>
       <c r="R112" t="n">
-        <v>6818162</v>
+        <v>6818121</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,32 +11777,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927826</v>
+        <v>128927836</v>
       </c>
       <c r="B113" t="n">
-        <v>78878</v>
+        <v>58090</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430018</v>
+        <v>430147</v>
       </c>
       <c r="R113" t="n">
-        <v>6818046</v>
+        <v>6817817</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927796</v>
+        <v>128927793</v>
       </c>
       <c r="B114" t="n">
-        <v>78878</v>
+        <v>58150</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>103001</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430323</v>
+        <v>430104</v>
       </c>
       <c r="R114" t="n">
-        <v>6818121</v>
+        <v>6817933</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128927870</v>
+        <v>128927901</v>
       </c>
       <c r="B115" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>430164</v>
+        <v>430501</v>
       </c>
       <c r="R115" t="n">
-        <v>6817854</v>
+        <v>6818013</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12068,10 +12068,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128927858</v>
+        <v>128927870</v>
       </c>
       <c r="B116" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>430034</v>
+        <v>430164</v>
       </c>
       <c r="R116" t="n">
-        <v>6818117</v>
+        <v>6817854</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128927873</v>
+        <v>128927858</v>
       </c>
       <c r="B117" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>429998</v>
+        <v>430034</v>
       </c>
       <c r="R117" t="n">
-        <v>6818047</v>
+        <v>6818117</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,10 +12262,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128927901</v>
+        <v>128927873</v>
       </c>
       <c r="B118" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12273,21 +12273,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>430501</v>
+        <v>429998</v>
       </c>
       <c r="R118" t="n">
-        <v>6818013</v>
+        <v>6818047</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12362,7 +12362,7 @@
         <v>128927921</v>
       </c>
       <c r="B119" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>128927740</v>
       </c>
       <c r="B120" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>128927823</v>
       </c>
       <c r="B121" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128927953</v>
+        <v>128927907</v>
       </c>
       <c r="B122" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12679,19 +12679,16 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>430242</v>
+        <v>430394</v>
       </c>
       <c r="R122" t="n">
-        <v>6818048</v>
+        <v>6818166</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12726,18 +12723,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12756,10 +12747,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128927907</v>
+        <v>128927940</v>
       </c>
       <c r="B123" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12791,10 +12782,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430394</v>
+        <v>429952</v>
       </c>
       <c r="R123" t="n">
-        <v>6818166</v>
+        <v>6818061</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12853,10 +12844,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128927977</v>
+        <v>128927908</v>
       </c>
       <c r="B124" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12882,19 +12873,16 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430139</v>
+        <v>430425</v>
       </c>
       <c r="R124" t="n">
-        <v>6817862</v>
+        <v>6818197</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12935,7 +12923,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12954,10 +12941,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128927869</v>
+        <v>128927953</v>
       </c>
       <c r="B125" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,34 +12952,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>430138</v>
+        <v>430242</v>
       </c>
       <c r="R125" t="n">
-        <v>6817883</v>
+        <v>6818048</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13027,12 +13017,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13051,10 +13047,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128927940</v>
+        <v>128927977</v>
       </c>
       <c r="B126" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13080,16 +13076,19 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>429952</v>
+        <v>430139</v>
       </c>
       <c r="R126" t="n">
-        <v>6818061</v>
+        <v>6817862</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13130,6 +13129,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13148,10 +13148,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128927853</v>
+        <v>128927869</v>
       </c>
       <c r="B127" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430073</v>
+        <v>430138</v>
       </c>
       <c r="R127" t="n">
-        <v>6818201</v>
+        <v>6817883</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13245,10 +13245,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128927918</v>
+        <v>128927720</v>
       </c>
       <c r="B128" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13256,21 +13256,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430649</v>
+        <v>430112</v>
       </c>
       <c r="R128" t="n">
-        <v>6818232</v>
+        <v>6818160</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128927878</v>
+        <v>128927853</v>
       </c>
       <c r="B129" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13353,21 +13353,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430632</v>
+        <v>430073</v>
       </c>
       <c r="R129" t="n">
-        <v>6818282</v>
+        <v>6818201</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,10 +13439,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128927908</v>
+        <v>128927918</v>
       </c>
       <c r="B130" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>430425</v>
+        <v>430649</v>
       </c>
       <c r="R130" t="n">
-        <v>6818197</v>
+        <v>6818232</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13536,10 +13536,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128927886</v>
+        <v>128927878</v>
       </c>
       <c r="B131" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13571,10 +13571,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430424</v>
+        <v>430632</v>
       </c>
       <c r="R131" t="n">
-        <v>6818252</v>
+        <v>6818282</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13633,10 +13633,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128927720</v>
+        <v>128927886</v>
       </c>
       <c r="B132" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13644,21 +13644,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13668,10 +13668,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430112</v>
+        <v>430424</v>
       </c>
       <c r="R132" t="n">
-        <v>6818160</v>
+        <v>6818252</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13733,7 +13733,7 @@
         <v>128927777</v>
       </c>
       <c r="B133" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>128927784</v>
       </c>
       <c r="B134" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>128927769</v>
       </c>
       <c r="B135" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14045,54 +14045,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128927833</v>
+        <v>128927863</v>
       </c>
       <c r="B136" t="n">
-        <v>8450</v>
+        <v>78881</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430204</v>
+        <v>429970</v>
       </c>
       <c r="R136" t="n">
-        <v>6817811</v>
+        <v>6818162</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14133,7 +14124,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14152,10 +14142,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128927781</v>
+        <v>128927911</v>
       </c>
       <c r="B137" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14163,42 +14153,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430480</v>
+        <v>430437</v>
       </c>
       <c r="R137" t="n">
-        <v>6817997</v>
+        <v>6818227</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14257,10 +14239,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128927788</v>
+        <v>128927972</v>
       </c>
       <c r="B138" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14268,31 +14250,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -14300,10 +14277,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430017</v>
+        <v>430018</v>
       </c>
       <c r="R138" t="n">
-        <v>6818044</v>
+        <v>6818025</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14344,6 +14321,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14362,10 +14340,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128927775</v>
+        <v>128927861</v>
       </c>
       <c r="B139" t="n">
-        <v>57713</v>
+        <v>78881</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14373,42 +14351,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430083</v>
+        <v>429989</v>
       </c>
       <c r="R139" t="n">
-        <v>6818224</v>
+        <v>6818159</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14467,10 +14437,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128927792</v>
+        <v>128927894</v>
       </c>
       <c r="B140" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14478,31 +14448,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14510,10 +14475,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430150</v>
+        <v>430321</v>
       </c>
       <c r="R140" t="n">
-        <v>6817814</v>
+        <v>6818095</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14548,12 +14513,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14572,10 +14543,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128927709</v>
+        <v>128927900</v>
       </c>
       <c r="B141" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14583,21 +14554,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14607,10 +14578,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430495</v>
+        <v>430467</v>
       </c>
       <c r="R141" t="n">
-        <v>6818056</v>
+        <v>6818020</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14669,10 +14640,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128927894</v>
+        <v>128927889</v>
       </c>
       <c r="B142" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14698,19 +14669,16 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430321</v>
+        <v>430385</v>
       </c>
       <c r="R142" t="n">
-        <v>6818095</v>
+        <v>6818203</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14745,18 +14713,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14775,10 +14737,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128927900</v>
+        <v>128927969</v>
       </c>
       <c r="B143" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14810,10 +14772,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430467</v>
+        <v>429947</v>
       </c>
       <c r="R143" t="n">
-        <v>6818020</v>
+        <v>6818135</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14872,10 +14834,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128927889</v>
+        <v>128927956</v>
       </c>
       <c r="B144" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14907,10 +14869,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430385</v>
+        <v>430119</v>
       </c>
       <c r="R144" t="n">
-        <v>6818203</v>
+        <v>6818173</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14969,10 +14931,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128927863</v>
+        <v>128927925</v>
       </c>
       <c r="B145" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14980,21 +14942,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15004,10 +14966,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>429970</v>
+        <v>430683</v>
       </c>
       <c r="R145" t="n">
-        <v>6818162</v>
+        <v>6818265</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15066,10 +15028,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128927911</v>
+        <v>128927926</v>
       </c>
       <c r="B146" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15101,10 +15063,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430437</v>
+        <v>430701</v>
       </c>
       <c r="R146" t="n">
-        <v>6818227</v>
+        <v>6818261</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15163,10 +15125,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128927969</v>
+        <v>128927709</v>
       </c>
       <c r="B147" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15174,21 +15136,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15198,10 +15160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>429947</v>
+        <v>430495</v>
       </c>
       <c r="R147" t="n">
-        <v>6818135</v>
+        <v>6818056</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15260,10 +15222,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927956</v>
+        <v>128927781</v>
       </c>
       <c r="B148" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15271,34 +15233,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430119</v>
+        <v>430480</v>
       </c>
       <c r="R148" t="n">
-        <v>6818173</v>
+        <v>6817997</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15357,10 +15327,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927925</v>
+        <v>128927788</v>
       </c>
       <c r="B149" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15368,34 +15338,42 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430683</v>
+        <v>430017</v>
       </c>
       <c r="R149" t="n">
-        <v>6818265</v>
+        <v>6818044</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15454,10 +15432,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927972</v>
+        <v>128927775</v>
       </c>
       <c r="B150" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15465,26 +15443,31 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -15492,10 +15475,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430018</v>
+        <v>430083</v>
       </c>
       <c r="R150" t="n">
-        <v>6818025</v>
+        <v>6818224</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15536,7 +15519,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -15555,10 +15537,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927861</v>
+        <v>128927792</v>
       </c>
       <c r="B151" t="n">
-        <v>78877</v>
+        <v>57717</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15566,34 +15548,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>429989</v>
+        <v>430150</v>
       </c>
       <c r="R151" t="n">
-        <v>6818159</v>
+        <v>6817814</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15652,45 +15642,54 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128927926</v>
+        <v>128927833</v>
       </c>
       <c r="B152" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430701</v>
+        <v>430204</v>
       </c>
       <c r="R152" t="n">
-        <v>6818261</v>
+        <v>6817811</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15731,6 +15730,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15752,7 +15752,7 @@
         <v>128927824</v>
       </c>
       <c r="B153" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>128927748</v>
       </c>
       <c r="B154" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>128927917</v>
       </c>
       <c r="B155" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>128927903</v>
       </c>
       <c r="B156" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16146,10 +16146,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128927875</v>
+        <v>128927958</v>
       </c>
       <c r="B157" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16157,21 +16157,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16181,10 +16181,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430127</v>
+        <v>430048</v>
       </c>
       <c r="R157" t="n">
-        <v>6817846</v>
+        <v>6818232</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16243,10 +16243,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128927920</v>
+        <v>128927798</v>
       </c>
       <c r="B158" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16254,21 +16254,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16278,10 +16278,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430637</v>
+        <v>430315</v>
       </c>
       <c r="R158" t="n">
-        <v>6818260</v>
+        <v>6818095</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16340,10 +16340,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128927838</v>
+        <v>128927828</v>
       </c>
       <c r="B159" t="n">
-        <v>78877</v>
+        <v>78882</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16351,34 +16351,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430439</v>
+        <v>430115</v>
       </c>
       <c r="R159" t="n">
-        <v>6818031</v>
+        <v>6817902</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16419,6 +16422,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16437,10 +16441,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128927837</v>
+        <v>128927875</v>
       </c>
       <c r="B160" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16472,10 +16476,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430360</v>
+        <v>430127</v>
       </c>
       <c r="R160" t="n">
-        <v>6818057</v>
+        <v>6817846</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16534,10 +16538,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128927951</v>
+        <v>128927920</v>
       </c>
       <c r="B161" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16563,19 +16567,16 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430191</v>
+        <v>430637</v>
       </c>
       <c r="R161" t="n">
-        <v>6817932</v>
+        <v>6818260</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16610,18 +16611,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Garnlav, måttligt inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -16640,10 +16635,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128927958</v>
+        <v>128927838</v>
       </c>
       <c r="B162" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16651,21 +16646,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16675,10 +16670,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430048</v>
+        <v>430439</v>
       </c>
       <c r="R162" t="n">
-        <v>6818232</v>
+        <v>6818031</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16737,10 +16732,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128927846</v>
+        <v>128927837</v>
       </c>
       <c r="B163" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16772,10 +16767,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430241</v>
+        <v>430360</v>
       </c>
       <c r="R163" t="n">
-        <v>6818085</v>
+        <v>6818057</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16834,10 +16829,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128927902</v>
+        <v>128927951</v>
       </c>
       <c r="B164" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16863,16 +16858,19 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430530</v>
+        <v>430191</v>
       </c>
       <c r="R164" t="n">
-        <v>6818025</v>
+        <v>6817932</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16907,12 +16905,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Garnlav, måttligt inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -16931,10 +16935,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128927779</v>
+        <v>128927846</v>
       </c>
       <c r="B165" t="n">
-        <v>57713</v>
+        <v>78881</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16942,42 +16946,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430106</v>
+        <v>430241</v>
       </c>
       <c r="R165" t="n">
-        <v>6817957</v>
+        <v>6818085</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17036,10 +17032,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128927783</v>
+        <v>128927902</v>
       </c>
       <c r="B166" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17047,42 +17043,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>430174</v>
+        <v>430530</v>
       </c>
       <c r="R166" t="n">
-        <v>6817923</v>
+        <v>6818025</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17141,10 +17129,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128927798</v>
+        <v>128927779</v>
       </c>
       <c r="B167" t="n">
-        <v>78878</v>
+        <v>57717</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17152,34 +17140,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430315</v>
+        <v>430106</v>
       </c>
       <c r="R167" t="n">
-        <v>6818095</v>
+        <v>6817957</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17238,10 +17234,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128927828</v>
+        <v>128927783</v>
       </c>
       <c r="B168" t="n">
-        <v>78878</v>
+        <v>57717</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17249,26 +17245,31 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -17276,10 +17277,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430115</v>
+        <v>430174</v>
       </c>
       <c r="R168" t="n">
-        <v>6817902</v>
+        <v>6817923</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17320,7 +17321,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17339,10 +17339,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128927981</v>
+        <v>128927829</v>
       </c>
       <c r="B169" t="n">
-        <v>78092</v>
+        <v>78882</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17350,21 +17350,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17374,10 +17374,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>430056</v>
+        <v>430138</v>
       </c>
       <c r="R169" t="n">
-        <v>6818166</v>
+        <v>6817883</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17436,10 +17436,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128927933</v>
+        <v>128927904</v>
       </c>
       <c r="B170" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17465,19 +17465,16 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430220</v>
+        <v>430405</v>
       </c>
       <c r="R170" t="n">
-        <v>6818148</v>
+        <v>6818117</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17512,18 +17509,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -17542,10 +17533,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128927737</v>
+        <v>128927933</v>
       </c>
       <c r="B171" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17553,21 +17544,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17580,10 +17571,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430143</v>
+        <v>430220</v>
       </c>
       <c r="R171" t="n">
-        <v>6817831</v>
+        <v>6818148</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17616,6 +17607,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17643,10 +17639,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128927904</v>
+        <v>128927981</v>
       </c>
       <c r="B172" t="n">
-        <v>79120</v>
+        <v>78096</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17654,21 +17650,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17678,10 +17674,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430405</v>
+        <v>430056</v>
       </c>
       <c r="R172" t="n">
-        <v>6818117</v>
+        <v>6818166</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17743,7 +17739,7 @@
         <v>128927712</v>
       </c>
       <c r="B173" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17837,45 +17833,48 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128927835</v>
+        <v>128927737</v>
       </c>
       <c r="B174" t="n">
-        <v>58086</v>
+        <v>79743</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430104</v>
+        <v>430143</v>
       </c>
       <c r="R174" t="n">
-        <v>6817960</v>
+        <v>6817831</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17916,6 +17915,7 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -17934,32 +17934,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128927829</v>
+        <v>128927835</v>
       </c>
       <c r="B175" t="n">
-        <v>78878</v>
+        <v>58090</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17969,10 +17969,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430138</v>
+        <v>430104</v>
       </c>
       <c r="R175" t="n">
-        <v>6817883</v>
+        <v>6817960</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18031,10 +18031,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128927750</v>
+        <v>128927848</v>
       </c>
       <c r="B176" t="n">
-        <v>79710</v>
+        <v>78881</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18042,21 +18042,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18066,10 +18066,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430140</v>
+        <v>430174</v>
       </c>
       <c r="R176" t="n">
-        <v>6817881</v>
+        <v>6818156</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18128,10 +18128,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128927741</v>
+        <v>128927952</v>
       </c>
       <c r="B177" t="n">
-        <v>79710</v>
+        <v>79124</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18139,21 +18139,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18163,10 +18163,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430600</v>
+        <v>430190</v>
       </c>
       <c r="R177" t="n">
-        <v>6818203</v>
+        <v>6817925</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18225,10 +18225,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128927812</v>
+        <v>128927945</v>
       </c>
       <c r="B178" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18236,21 +18236,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18260,10 +18260,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430157</v>
+        <v>430404</v>
       </c>
       <c r="R178" t="n">
-        <v>6818149</v>
+        <v>6818178</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18322,10 +18322,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128927898</v>
+        <v>128927723</v>
       </c>
       <c r="B179" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18333,21 +18333,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18357,10 +18357,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430384</v>
+        <v>429993</v>
       </c>
       <c r="R179" t="n">
-        <v>6818048</v>
+        <v>6818157</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18419,10 +18419,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128927848</v>
+        <v>128927750</v>
       </c>
       <c r="B180" t="n">
-        <v>78877</v>
+        <v>79714</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18430,21 +18430,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18454,10 +18454,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430174</v>
+        <v>430140</v>
       </c>
       <c r="R180" t="n">
-        <v>6818156</v>
+        <v>6817881</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18516,10 +18516,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128927968</v>
+        <v>128927741</v>
       </c>
       <c r="B181" t="n">
-        <v>79120</v>
+        <v>79714</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18527,21 +18527,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18551,10 +18551,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430067</v>
+        <v>430600</v>
       </c>
       <c r="R181" t="n">
-        <v>6818139</v>
+        <v>6818203</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18613,10 +18613,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128927952</v>
+        <v>128927812</v>
       </c>
       <c r="B182" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18624,21 +18624,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18648,10 +18648,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430190</v>
+        <v>430157</v>
       </c>
       <c r="R182" t="n">
-        <v>6817925</v>
+        <v>6818149</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18710,10 +18710,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128927945</v>
+        <v>128927898</v>
       </c>
       <c r="B183" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18745,10 +18745,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430404</v>
+        <v>430384</v>
       </c>
       <c r="R183" t="n">
-        <v>6818178</v>
+        <v>6818048</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18807,10 +18807,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128927723</v>
+        <v>128927968</v>
       </c>
       <c r="B184" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18818,21 +18818,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18842,10 +18842,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>429993</v>
+        <v>430067</v>
       </c>
       <c r="R184" t="n">
-        <v>6818157</v>
+        <v>6818139</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18907,7 +18907,7 @@
         <v>128927760</v>
       </c>
       <c r="B185" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>128927762</v>
       </c>
       <c r="B186" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19114,10 +19114,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128927910</v>
+        <v>128927820</v>
       </c>
       <c r="B187" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19125,21 +19125,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19149,10 +19149,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430430</v>
+        <v>430014</v>
       </c>
       <c r="R187" t="n">
-        <v>6818202</v>
+        <v>6818142</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19211,10 +19211,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128927847</v>
+        <v>128927818</v>
       </c>
       <c r="B188" t="n">
-        <v>78877</v>
+        <v>78882</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19222,21 +19222,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19246,10 +19246,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430227</v>
+        <v>430048</v>
       </c>
       <c r="R188" t="n">
-        <v>6818154</v>
+        <v>6818123</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19308,10 +19308,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128927892</v>
+        <v>128927910</v>
       </c>
       <c r="B189" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19343,10 +19343,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430304</v>
+        <v>430430</v>
       </c>
       <c r="R189" t="n">
-        <v>6818124</v>
+        <v>6818202</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19405,10 +19405,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128927872</v>
+        <v>128927962</v>
       </c>
       <c r="B190" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19416,21 +19416,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19440,10 +19440,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430227</v>
+        <v>430069</v>
       </c>
       <c r="R190" t="n">
-        <v>6818015</v>
+        <v>6818225</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19502,10 +19502,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128927906</v>
+        <v>128927847</v>
       </c>
       <c r="B191" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19513,37 +19513,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430401</v>
+        <v>430227</v>
       </c>
       <c r="R191" t="n">
-        <v>6818157</v>
+        <v>6818154</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19578,18 +19575,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
-        </is>
-      </c>
       <c r="AD191" t="b">
         <v>0</v>
       </c>
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -19608,10 +19599,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128927922</v>
+        <v>128927892</v>
       </c>
       <c r="B192" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19643,10 +19634,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430668</v>
+        <v>430304</v>
       </c>
       <c r="R192" t="n">
-        <v>6818241</v>
+        <v>6818124</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19705,10 +19696,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128927962</v>
+        <v>128927872</v>
       </c>
       <c r="B193" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19716,21 +19707,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19740,10 +19731,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430069</v>
+        <v>430227</v>
       </c>
       <c r="R193" t="n">
-        <v>6818225</v>
+        <v>6818015</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19802,10 +19793,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128927789</v>
+        <v>128927906</v>
       </c>
       <c r="B194" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19813,31 +19804,26 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
@@ -19845,10 +19831,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430089</v>
+        <v>430401</v>
       </c>
       <c r="R194" t="n">
-        <v>6817965</v>
+        <v>6818157</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19885,7 +19871,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -19894,6 +19880,7 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -19912,10 +19899,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128927728</v>
+        <v>128927922</v>
       </c>
       <c r="B195" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19923,21 +19910,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19947,10 +19934,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430232</v>
+        <v>430668</v>
       </c>
       <c r="R195" t="n">
-        <v>6818068</v>
+        <v>6818241</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20009,10 +19996,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128927731</v>
+        <v>128927728</v>
       </c>
       <c r="B196" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20044,10 +20031,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430056</v>
+        <v>430232</v>
       </c>
       <c r="R196" t="n">
-        <v>6818017</v>
+        <v>6818068</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20106,10 +20093,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128927820</v>
+        <v>128927731</v>
       </c>
       <c r="B197" t="n">
-        <v>78878</v>
+        <v>79743</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20117,21 +20104,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20141,10 +20128,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430014</v>
+        <v>430056</v>
       </c>
       <c r="R197" t="n">
-        <v>6818142</v>
+        <v>6818017</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20203,10 +20190,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128927818</v>
+        <v>128927789</v>
       </c>
       <c r="B198" t="n">
-        <v>78878</v>
+        <v>57717</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20214,34 +20201,42 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430048</v>
+        <v>430089</v>
       </c>
       <c r="R198" t="n">
-        <v>6818123</v>
+        <v>6817965</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20274,6 +20269,11 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20303,7 +20303,7 @@
         <v>128927913</v>
       </c>
       <c r="B199" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20397,10 +20397,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128927841</v>
+        <v>128927936</v>
       </c>
       <c r="B200" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20408,21 +20408,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20432,10 +20432,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430569</v>
+        <v>430084</v>
       </c>
       <c r="R200" t="n">
-        <v>6818243</v>
+        <v>6818157</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20494,10 +20494,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128927936</v>
+        <v>128927961</v>
       </c>
       <c r="B201" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20529,10 +20529,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430084</v>
+        <v>430086</v>
       </c>
       <c r="R201" t="n">
-        <v>6818157</v>
+        <v>6818236</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20591,10 +20591,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128927961</v>
+        <v>128927942</v>
       </c>
       <c r="B202" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20626,10 +20626,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430086</v>
+        <v>430087</v>
       </c>
       <c r="R202" t="n">
-        <v>6818236</v>
+        <v>6817971</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20688,10 +20688,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128927942</v>
+        <v>128927715</v>
       </c>
       <c r="B203" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20699,21 +20699,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20723,10 +20723,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430087</v>
+        <v>430650</v>
       </c>
       <c r="R203" t="n">
-        <v>6817971</v>
+        <v>6818249</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20785,10 +20785,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128927715</v>
+        <v>128927717</v>
       </c>
       <c r="B204" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20820,10 +20820,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430650</v>
+        <v>430214</v>
       </c>
       <c r="R204" t="n">
-        <v>6818249</v>
+        <v>6817971</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20882,10 +20882,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128927717</v>
+        <v>128927841</v>
       </c>
       <c r="B205" t="n">
-        <v>79739</v>
+        <v>78881</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20893,21 +20893,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430214</v>
+        <v>430569</v>
       </c>
       <c r="R205" t="n">
-        <v>6817971</v>
+        <v>6818243</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20982,7 +20982,7 @@
         <v>128927755</v>
       </c>
       <c r="B206" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>128927809</v>
       </c>
       <c r="B207" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>128927814</v>
       </c>
       <c r="B208" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>128927816</v>
       </c>
       <c r="B209" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>128927860</v>
       </c>
       <c r="B210" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>128927941</v>
       </c>
       <c r="B211" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>128927960</v>
       </c>
       <c r="B212" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>128927866</v>
       </c>
       <c r="B213" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>128927753</v>
       </c>
       <c r="B214" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>128927830</v>
       </c>
       <c r="B215" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>128927808</v>
       </c>
       <c r="B216" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22062,10 +22062,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128927817</v>
+        <v>128927746</v>
       </c>
       <c r="B217" t="n">
-        <v>78878</v>
+        <v>79714</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22073,21 +22073,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22097,10 +22097,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>430068</v>
+        <v>430232</v>
       </c>
       <c r="R217" t="n">
-        <v>6818152</v>
+        <v>6818068</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22159,10 +22159,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128927746</v>
+        <v>128927817</v>
       </c>
       <c r="B218" t="n">
-        <v>79710</v>
+        <v>78882</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22170,21 +22170,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22194,10 +22194,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>430232</v>
+        <v>430068</v>
       </c>
       <c r="R218" t="n">
-        <v>6818068</v>
+        <v>6818152</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22259,7 +22259,7 @@
         <v>128927967</v>
       </c>
       <c r="B219" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>128927867</v>
       </c>
       <c r="B220" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22450,10 +22450,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128927881</v>
+        <v>128927771</v>
       </c>
       <c r="B221" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22461,34 +22461,42 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430536</v>
+        <v>430658</v>
       </c>
       <c r="R221" t="n">
-        <v>6818208</v>
+        <v>6818274</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22547,10 +22555,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128927916</v>
+        <v>128927881</v>
       </c>
       <c r="B222" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22582,10 +22590,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430580</v>
+        <v>430536</v>
       </c>
       <c r="R222" t="n">
-        <v>6818221</v>
+        <v>6818208</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22644,10 +22652,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128927771</v>
+        <v>128927916</v>
       </c>
       <c r="B223" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22655,42 +22663,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430658</v>
+        <v>430580</v>
       </c>
       <c r="R223" t="n">
-        <v>6818274</v>
+        <v>6818221</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22752,7 +22752,7 @@
         <v>128927800</v>
       </c>
       <c r="B224" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22850,10 +22850,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128927730</v>
+        <v>128927915</v>
       </c>
       <c r="B225" t="n">
-        <v>79739</v>
+        <v>79124</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22861,34 +22861,37 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430075</v>
+        <v>430575</v>
       </c>
       <c r="R225" t="n">
-        <v>6818213</v>
+        <v>6818234</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22929,6 +22932,7 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
+      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
       </c>
@@ -22947,10 +22951,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128927850</v>
+        <v>128927923</v>
       </c>
       <c r="B226" t="n">
-        <v>78877</v>
+        <v>79124</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22958,21 +22962,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22982,10 +22986,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430159</v>
+        <v>430670</v>
       </c>
       <c r="R226" t="n">
-        <v>6818161</v>
+        <v>6818263</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23044,10 +23048,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128927890</v>
+        <v>128927850</v>
       </c>
       <c r="B227" t="n">
-        <v>79120</v>
+        <v>78881</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23055,21 +23059,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23079,10 +23083,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430348</v>
+        <v>430159</v>
       </c>
       <c r="R227" t="n">
-        <v>6818167</v>
+        <v>6818161</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23141,10 +23145,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128927915</v>
+        <v>128927890</v>
       </c>
       <c r="B228" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23170,19 +23174,16 @@
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430575</v>
+        <v>430348</v>
       </c>
       <c r="R228" t="n">
-        <v>6818234</v>
+        <v>6818167</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23223,7 +23224,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -23242,10 +23242,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128927923</v>
+        <v>128927730</v>
       </c>
       <c r="B229" t="n">
-        <v>79120</v>
+        <v>79743</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23253,21 +23253,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23277,10 +23277,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430670</v>
+        <v>430075</v>
       </c>
       <c r="R229" t="n">
-        <v>6818263</v>
+        <v>6818213</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128927950</v>
+        <v>128927732</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430233</v>
+        <v>430138</v>
       </c>
       <c r="R22" t="n">
-        <v>6817831</v>
+        <v>6817883</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927978</v>
+        <v>128927868</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430082</v>
+        <v>430089</v>
       </c>
       <c r="R23" t="n">
-        <v>6818210</v>
+        <v>6817984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,7 +3027,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3046,10 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927935</v>
+        <v>128927843</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3081,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430099</v>
+        <v>430626</v>
       </c>
       <c r="R24" t="n">
-        <v>6818154</v>
+        <v>6818202</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927963</v>
+        <v>128927721</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3154,21 +3153,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3178,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430064</v>
+        <v>430060</v>
       </c>
       <c r="R25" t="n">
-        <v>6818190</v>
+        <v>6818156</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927880</v>
+        <v>128927726</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,21 +3250,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3275,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430577</v>
+        <v>430114</v>
       </c>
       <c r="R26" t="n">
-        <v>6818221</v>
+        <v>6817912</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,10 +3336,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927868</v>
+        <v>128927950</v>
       </c>
       <c r="B27" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3348,21 +3347,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3372,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430089</v>
+        <v>430233</v>
       </c>
       <c r="R27" t="n">
-        <v>6817984</v>
+        <v>6817831</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927843</v>
+        <v>128927880</v>
       </c>
       <c r="B28" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3445,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3469,10 +3468,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430626</v>
+        <v>430577</v>
       </c>
       <c r="R28" t="n">
-        <v>6818202</v>
+        <v>6818221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927732</v>
+        <v>128927978</v>
       </c>
       <c r="B29" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,21 +3541,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3566,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430138</v>
+        <v>430082</v>
       </c>
       <c r="R29" t="n">
-        <v>6817883</v>
+        <v>6818210</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,6 +3609,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927721</v>
+        <v>128927935</v>
       </c>
       <c r="B30" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430060</v>
+        <v>430099</v>
       </c>
       <c r="R30" t="n">
-        <v>6818156</v>
+        <v>6818154</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927726</v>
+        <v>128927963</v>
       </c>
       <c r="B31" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3736,21 +3736,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430114</v>
+        <v>430064</v>
       </c>
       <c r="R31" t="n">
-        <v>6817912</v>
+        <v>6818190</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128927895</v>
+        <v>128927871</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>430350</v>
+        <v>430145</v>
       </c>
       <c r="R36" t="n">
-        <v>6818053</v>
+        <v>6817833</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4315,7 +4315,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128927939</v>
+        <v>128927895</v>
       </c>
       <c r="B37" t="n">
         <v>79124</v>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>429903</v>
+        <v>430350</v>
       </c>
       <c r="R37" t="n">
-        <v>6818059</v>
+        <v>6818053</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4412,7 +4412,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128927973</v>
+        <v>128927939</v>
       </c>
       <c r="B38" t="n">
         <v>79124</v>
@@ -4441,19 +4441,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430073</v>
+        <v>429903</v>
       </c>
       <c r="R38" t="n">
-        <v>6818021</v>
+        <v>6818059</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4494,7 +4491,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4513,10 +4509,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128927871</v>
+        <v>128927973</v>
       </c>
       <c r="B39" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4524,34 +4520,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430145</v>
+        <v>430073</v>
       </c>
       <c r="R39" t="n">
-        <v>6817833</v>
+        <v>6818021</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4592,6 +4591,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128927928</v>
+        <v>128927845</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430293</v>
+        <v>430669</v>
       </c>
       <c r="R43" t="n">
-        <v>6817871</v>
+        <v>6818249</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128927934</v>
+        <v>128927842</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430088</v>
+        <v>430596</v>
       </c>
       <c r="R44" t="n">
         <v>6818186</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128927938</v>
+        <v>128927786</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5114,34 +5114,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>429959</v>
+        <v>430078</v>
       </c>
       <c r="R45" t="n">
-        <v>6818128</v>
+        <v>6818213</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5174,6 +5182,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5200,7 +5213,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128927966</v>
+        <v>128927930</v>
       </c>
       <c r="B46" t="n">
         <v>79124</v>
@@ -5235,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430071</v>
+        <v>430205</v>
       </c>
       <c r="R46" t="n">
-        <v>6818124</v>
+        <v>6817961</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,10 +5310,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128927805</v>
+        <v>128927928</v>
       </c>
       <c r="B47" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5308,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5332,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430594</v>
+        <v>430293</v>
       </c>
       <c r="R47" t="n">
-        <v>6818187</v>
+        <v>6817871</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5394,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128927819</v>
+        <v>128927934</v>
       </c>
       <c r="B48" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5405,21 +5418,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5429,10 +5442,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430033</v>
+        <v>430088</v>
       </c>
       <c r="R48" t="n">
-        <v>6818116</v>
+        <v>6818186</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5491,10 +5504,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128927799</v>
+        <v>128927938</v>
       </c>
       <c r="B49" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5502,21 +5515,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5526,10 +5539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430396</v>
+        <v>429959</v>
       </c>
       <c r="R49" t="n">
-        <v>6818052</v>
+        <v>6818128</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5588,10 +5601,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128927806</v>
+        <v>128927976</v>
       </c>
       <c r="B50" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5599,34 +5612,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430655</v>
+        <v>430149</v>
       </c>
       <c r="R50" t="n">
-        <v>6818264</v>
+        <v>6817860</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5667,6 +5683,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5685,10 +5702,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128927845</v>
+        <v>128927966</v>
       </c>
       <c r="B51" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5696,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5720,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430669</v>
+        <v>430071</v>
       </c>
       <c r="R51" t="n">
-        <v>6818249</v>
+        <v>6818124</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128927930</v>
+        <v>128927805</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5793,21 +5810,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5817,10 +5834,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>430205</v>
+        <v>430594</v>
       </c>
       <c r="R52" t="n">
-        <v>6817961</v>
+        <v>6818187</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5879,10 +5896,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128927842</v>
+        <v>128927819</v>
       </c>
       <c r="B53" t="n">
-        <v>78881</v>
+        <v>78882</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5890,21 +5907,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5914,10 +5931,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>430596</v>
+        <v>430033</v>
       </c>
       <c r="R53" t="n">
-        <v>6818186</v>
+        <v>6818116</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5976,10 +5993,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128927976</v>
+        <v>128927799</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5987,37 +6004,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>430149</v>
+        <v>430396</v>
       </c>
       <c r="R54" t="n">
-        <v>6817860</v>
+        <v>6818052</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6058,7 +6072,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6077,10 +6090,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128927786</v>
+        <v>128927806</v>
       </c>
       <c r="B55" t="n">
-        <v>57717</v>
+        <v>78882</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6088,42 +6101,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>430078</v>
+        <v>430655</v>
       </c>
       <c r="R55" t="n">
-        <v>6818213</v>
+        <v>6818264</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6156,11 +6161,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6187,7 +6187,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128927937</v>
+        <v>128927970</v>
       </c>
       <c r="B56" t="n">
         <v>79124</v>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>430011</v>
+        <v>429900</v>
       </c>
       <c r="R56" t="n">
-        <v>6818137</v>
+        <v>6818098</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6258,6 +6258,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6284,7 +6289,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128927970</v>
+        <v>128927944</v>
       </c>
       <c r="B57" t="n">
         <v>79124</v>
@@ -6313,16 +6318,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>429900</v>
+        <v>430531</v>
       </c>
       <c r="R57" t="n">
-        <v>6818098</v>
+        <v>6818016</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6357,17 +6365,13 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6386,7 +6390,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128927944</v>
+        <v>128927948</v>
       </c>
       <c r="B58" t="n">
         <v>79124</v>
@@ -6415,19 +6419,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430531</v>
+        <v>430655</v>
       </c>
       <c r="R58" t="n">
-        <v>6818016</v>
+        <v>6818216</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6468,7 +6469,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927948</v>
+        <v>128927882</v>
       </c>
       <c r="B59" t="n">
         <v>79124</v>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430655</v>
+        <v>430526</v>
       </c>
       <c r="R59" t="n">
-        <v>6818216</v>
+        <v>6818232</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927882</v>
+        <v>128927929</v>
       </c>
       <c r="B60" t="n">
         <v>79124</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430526</v>
+        <v>430208</v>
       </c>
       <c r="R60" t="n">
-        <v>6818232</v>
+        <v>6817816</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128927929</v>
+        <v>128927815</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,21 +6692,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430208</v>
+        <v>430061</v>
       </c>
       <c r="R61" t="n">
-        <v>6817816</v>
+        <v>6818258</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6875,10 +6875,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128927855</v>
+        <v>128927735</v>
       </c>
       <c r="B63" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6886,21 +6886,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430113</v>
+        <v>430132</v>
       </c>
       <c r="R63" t="n">
-        <v>6818160</v>
+        <v>6817858</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6972,10 +6972,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128927735</v>
+        <v>128927937</v>
       </c>
       <c r="B64" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430132</v>
+        <v>430011</v>
       </c>
       <c r="R64" t="n">
-        <v>6817858</v>
+        <v>6818137</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128927815</v>
+        <v>128927855</v>
       </c>
       <c r="B65" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430061</v>
+        <v>430113</v>
       </c>
       <c r="R65" t="n">
-        <v>6818258</v>
+        <v>6818160</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128927893</v>
+        <v>128927825</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7177,21 +7177,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430286</v>
+        <v>430024</v>
       </c>
       <c r="R66" t="n">
-        <v>6818100</v>
+        <v>6818040</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128927790</v>
+        <v>128927893</v>
       </c>
       <c r="B67" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7274,42 +7274,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430130</v>
+        <v>430286</v>
       </c>
       <c r="R67" t="n">
-        <v>6817856</v>
+        <v>6818100</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7465,10 +7457,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128927751</v>
+        <v>128927790</v>
       </c>
       <c r="B69" t="n">
-        <v>57720</v>
+        <v>57717</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7476,16 +7468,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7498,7 +7490,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -7508,10 +7500,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430337</v>
+        <v>430130</v>
       </c>
       <c r="R69" t="n">
-        <v>6818076</v>
+        <v>6817856</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,10 +7562,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128927825</v>
+        <v>128927751</v>
       </c>
       <c r="B70" t="n">
-        <v>78882</v>
+        <v>57720</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7581,34 +7573,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>430024</v>
+        <v>430337</v>
       </c>
       <c r="R70" t="n">
-        <v>6818040</v>
+        <v>6818076</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8156,7 +8156,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128927964</v>
+        <v>128927924</v>
       </c>
       <c r="B76" t="n">
         <v>79124</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430099</v>
+        <v>430671</v>
       </c>
       <c r="R76" t="n">
-        <v>6818174</v>
+        <v>6818266</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8253,7 +8253,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128927897</v>
+        <v>128927964</v>
       </c>
       <c r="B77" t="n">
         <v>79124</v>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430386</v>
+        <v>430099</v>
       </c>
       <c r="R77" t="n">
-        <v>6818039</v>
+        <v>6818174</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128927912</v>
+        <v>128927897</v>
       </c>
       <c r="B78" t="n">
         <v>79124</v>
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430439</v>
+        <v>430386</v>
       </c>
       <c r="R78" t="n">
-        <v>6818230</v>
+        <v>6818039</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128927840</v>
+        <v>128927955</v>
       </c>
       <c r="B79" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8458,34 +8458,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430407</v>
+        <v>430129</v>
       </c>
       <c r="R79" t="n">
-        <v>6818114</v>
+        <v>6818156</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8520,12 +8523,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30 m</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8544,10 +8553,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128927865</v>
+        <v>128927905</v>
       </c>
       <c r="B80" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8555,21 +8564,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8579,10 +8588,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>429935</v>
+        <v>430395</v>
       </c>
       <c r="R80" t="n">
-        <v>6818065</v>
+        <v>6818138</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8641,7 +8650,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128927924</v>
+        <v>128927885</v>
       </c>
       <c r="B81" t="n">
         <v>79124</v>
@@ -8676,10 +8685,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430671</v>
+        <v>430366</v>
       </c>
       <c r="R81" t="n">
-        <v>6818266</v>
+        <v>6818264</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8738,7 +8747,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128927955</v>
+        <v>128927947</v>
       </c>
       <c r="B82" t="n">
         <v>79124</v>
@@ -8767,19 +8776,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430129</v>
+        <v>430568</v>
       </c>
       <c r="R82" t="n">
-        <v>6818156</v>
+        <v>6818235</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8816,7 +8822,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Gott om garnlav inom en radie av 30 m</t>
+          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8825,7 +8831,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8844,7 +8849,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128927905</v>
+        <v>128927912</v>
       </c>
       <c r="B83" t="n">
         <v>79124</v>
@@ -8879,10 +8884,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430395</v>
+        <v>430439</v>
       </c>
       <c r="R83" t="n">
-        <v>6818138</v>
+        <v>6818230</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8941,10 +8946,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128927885</v>
+        <v>128927795</v>
       </c>
       <c r="B84" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8952,21 +8957,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8976,10 +8981,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430366</v>
+        <v>430390</v>
       </c>
       <c r="R84" t="n">
-        <v>6818264</v>
+        <v>6818205</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9038,10 +9043,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128927947</v>
+        <v>128927811</v>
       </c>
       <c r="B85" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9049,21 +9054,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9073,10 +9078,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>430568</v>
+        <v>430176</v>
       </c>
       <c r="R85" t="n">
-        <v>6818235</v>
+        <v>6818150</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9109,11 +9114,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9140,10 +9140,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128927725</v>
+        <v>128927832</v>
       </c>
       <c r="B86" t="n">
-        <v>79743</v>
+        <v>78882</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9151,21 +9151,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430040</v>
+        <v>430153</v>
       </c>
       <c r="R86" t="n">
-        <v>6818029</v>
+        <v>6817822</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9237,10 +9237,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128927795</v>
+        <v>128927840</v>
       </c>
       <c r="B87" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9248,21 +9248,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>430390</v>
+        <v>430407</v>
       </c>
       <c r="R87" t="n">
-        <v>6818205</v>
+        <v>6818114</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9334,10 +9334,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128927811</v>
+        <v>128927865</v>
       </c>
       <c r="B88" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9345,21 +9345,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>430176</v>
+        <v>429935</v>
       </c>
       <c r="R88" t="n">
-        <v>6818150</v>
+        <v>6818065</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128927832</v>
+        <v>128927725</v>
       </c>
       <c r="B89" t="n">
-        <v>78882</v>
+        <v>79743</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>430153</v>
+        <v>430040</v>
       </c>
       <c r="R89" t="n">
-        <v>6817822</v>
+        <v>6818029</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9528,10 +9528,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128927864</v>
+        <v>128927980</v>
       </c>
       <c r="B90" t="n">
-        <v>78881</v>
+        <v>78096</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9539,21 +9539,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>429975</v>
+        <v>430081</v>
       </c>
       <c r="R90" t="n">
-        <v>6818158</v>
+        <v>6818119</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128927965</v>
+        <v>128927864</v>
       </c>
       <c r="B91" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9636,21 +9636,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430115</v>
+        <v>429975</v>
       </c>
       <c r="R91" t="n">
-        <v>6818177</v>
+        <v>6818158</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128927932</v>
+        <v>128927714</v>
       </c>
       <c r="B92" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9733,37 +9733,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430240</v>
+        <v>430630</v>
       </c>
       <c r="R92" t="n">
-        <v>6817987</v>
+        <v>6818207</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9798,18 +9795,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9925,10 +9916,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128927810</v>
+        <v>128927891</v>
       </c>
       <c r="B94" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9936,21 +9927,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9960,10 +9951,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430215</v>
+        <v>430336</v>
       </c>
       <c r="R94" t="n">
-        <v>6818155</v>
+        <v>6818151</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10022,10 +10013,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128927803</v>
+        <v>128927884</v>
       </c>
       <c r="B95" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10033,21 +10024,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10057,10 +10048,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430580</v>
+        <v>430423</v>
       </c>
       <c r="R95" t="n">
-        <v>6818253</v>
+        <v>6818270</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10119,7 +10110,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128927891</v>
+        <v>128927965</v>
       </c>
       <c r="B96" t="n">
         <v>79124</v>
@@ -10154,10 +10145,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430336</v>
+        <v>430115</v>
       </c>
       <c r="R96" t="n">
-        <v>6818151</v>
+        <v>6818177</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10216,7 +10207,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128927884</v>
+        <v>128927932</v>
       </c>
       <c r="B97" t="n">
         <v>79124</v>
@@ -10245,16 +10236,19 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430423</v>
+        <v>430240</v>
       </c>
       <c r="R97" t="n">
-        <v>6818270</v>
+        <v>6817987</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10289,12 +10283,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10507,32 +10507,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128927714</v>
+        <v>128927794</v>
       </c>
       <c r="B100" t="n">
-        <v>79743</v>
+        <v>97507</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430630</v>
+        <v>430535</v>
       </c>
       <c r="R100" t="n">
-        <v>6818207</v>
+        <v>6818254</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10604,10 +10604,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128927980</v>
+        <v>128927810</v>
       </c>
       <c r="B101" t="n">
-        <v>78096</v>
+        <v>78882</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10615,21 +10615,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>430081</v>
+        <v>430215</v>
       </c>
       <c r="R101" t="n">
-        <v>6818119</v>
+        <v>6818155</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10701,32 +10701,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128927794</v>
+        <v>128927803</v>
       </c>
       <c r="B102" t="n">
-        <v>97507</v>
+        <v>78882</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>430535</v>
+        <v>430580</v>
       </c>
       <c r="R102" t="n">
-        <v>6818254</v>
+        <v>6818253</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10798,32 +10798,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927888</v>
+        <v>128927836</v>
       </c>
       <c r="B103" t="n">
-        <v>79124</v>
+        <v>58090</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430399</v>
+        <v>430147</v>
       </c>
       <c r="R103" t="n">
-        <v>6818238</v>
+        <v>6817817</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927971</v>
+        <v>128927856</v>
       </c>
       <c r="B104" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10906,21 +10906,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>429925</v>
+        <v>430060</v>
       </c>
       <c r="R104" t="n">
-        <v>6818065</v>
+        <v>6818160</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10992,7 +10992,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927949</v>
+        <v>128927899</v>
       </c>
       <c r="B105" t="n">
         <v>79124</v>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430653</v>
+        <v>430428</v>
       </c>
       <c r="R105" t="n">
-        <v>6818272</v>
+        <v>6818038</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11089,7 +11089,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927899</v>
+        <v>128927954</v>
       </c>
       <c r="B106" t="n">
         <v>79124</v>
@@ -11118,16 +11118,19 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430428</v>
+        <v>430166</v>
       </c>
       <c r="R106" t="n">
-        <v>6818038</v>
+        <v>6818134</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11162,12 +11165,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11186,7 +11195,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927954</v>
+        <v>128927888</v>
       </c>
       <c r="B107" t="n">
         <v>79124</v>
@@ -11215,19 +11224,16 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430166</v>
+        <v>430399</v>
       </c>
       <c r="R107" t="n">
-        <v>6818134</v>
+        <v>6818238</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11262,18 +11268,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11292,10 +11292,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927856</v>
+        <v>128927971</v>
       </c>
       <c r="B108" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11303,21 +11303,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11327,10 +11327,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430060</v>
+        <v>429925</v>
       </c>
       <c r="R108" t="n">
-        <v>6818160</v>
+        <v>6818065</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11389,10 +11389,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927827</v>
+        <v>128927949</v>
       </c>
       <c r="B109" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11400,21 +11400,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11424,10 +11424,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430057</v>
+        <v>430653</v>
       </c>
       <c r="R109" t="n">
-        <v>6818016</v>
+        <v>6818272</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11486,10 +11486,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128927822</v>
+        <v>128927793</v>
       </c>
       <c r="B110" t="n">
-        <v>78882</v>
+        <v>58150</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11497,21 +11497,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>103001</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>429973</v>
+        <v>430104</v>
       </c>
       <c r="R110" t="n">
-        <v>6818162</v>
+        <v>6817933</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11583,7 +11583,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927826</v>
+        <v>128927827</v>
       </c>
       <c r="B111" t="n">
         <v>78882</v>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430018</v>
+        <v>430057</v>
       </c>
       <c r="R111" t="n">
-        <v>6818046</v>
+        <v>6818016</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11680,7 +11680,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927796</v>
+        <v>128927822</v>
       </c>
       <c r="B112" t="n">
         <v>78882</v>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>430323</v>
+        <v>429973</v>
       </c>
       <c r="R112" t="n">
-        <v>6818121</v>
+        <v>6818162</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,32 +11777,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927836</v>
+        <v>128927826</v>
       </c>
       <c r="B113" t="n">
-        <v>58090</v>
+        <v>78882</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430147</v>
+        <v>430018</v>
       </c>
       <c r="R113" t="n">
-        <v>6817817</v>
+        <v>6818046</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927793</v>
+        <v>128927796</v>
       </c>
       <c r="B114" t="n">
-        <v>58150</v>
+        <v>78882</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103001</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430104</v>
+        <v>430323</v>
       </c>
       <c r="R114" t="n">
-        <v>6817933</v>
+        <v>6818121</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128927901</v>
+        <v>128927858</v>
       </c>
       <c r="B115" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>430501</v>
+        <v>430034</v>
       </c>
       <c r="R115" t="n">
-        <v>6818013</v>
+        <v>6818117</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12068,7 +12068,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128927870</v>
+        <v>128927873</v>
       </c>
       <c r="B116" t="n">
         <v>78881</v>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>430164</v>
+        <v>429998</v>
       </c>
       <c r="R116" t="n">
-        <v>6817854</v>
+        <v>6818047</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12165,7 +12165,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128927858</v>
+        <v>128927870</v>
       </c>
       <c r="B117" t="n">
         <v>78881</v>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430034</v>
+        <v>430164</v>
       </c>
       <c r="R117" t="n">
-        <v>6818117</v>
+        <v>6817854</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,10 +12262,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128927873</v>
+        <v>128927901</v>
       </c>
       <c r="B118" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12273,21 +12273,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>429998</v>
+        <v>430501</v>
       </c>
       <c r="R118" t="n">
-        <v>6818047</v>
+        <v>6818013</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128927907</v>
+        <v>128927869</v>
       </c>
       <c r="B122" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12661,21 +12661,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12685,10 +12685,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>430394</v>
+        <v>430138</v>
       </c>
       <c r="R122" t="n">
-        <v>6818166</v>
+        <v>6817883</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12747,10 +12747,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128927940</v>
+        <v>128927720</v>
       </c>
       <c r="B123" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12758,21 +12758,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12782,10 +12782,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>429952</v>
+        <v>430112</v>
       </c>
       <c r="R123" t="n">
-        <v>6818061</v>
+        <v>6818160</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128927908</v>
+        <v>128927853</v>
       </c>
       <c r="B124" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12855,21 +12855,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12879,10 +12879,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430425</v>
+        <v>430073</v>
       </c>
       <c r="R124" t="n">
-        <v>6818197</v>
+        <v>6818201</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13047,7 +13047,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128927977</v>
+        <v>128927907</v>
       </c>
       <c r="B126" t="n">
         <v>79124</v>
@@ -13076,19 +13076,16 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430139</v>
+        <v>430394</v>
       </c>
       <c r="R126" t="n">
-        <v>6817862</v>
+        <v>6818166</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13129,7 +13126,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13148,10 +13144,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128927869</v>
+        <v>128927977</v>
       </c>
       <c r="B127" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13159,34 +13155,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430138</v>
+        <v>430139</v>
       </c>
       <c r="R127" t="n">
-        <v>6817883</v>
+        <v>6817862</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13227,6 +13226,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13245,10 +13245,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128927720</v>
+        <v>128927940</v>
       </c>
       <c r="B128" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13256,21 +13256,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430112</v>
+        <v>429952</v>
       </c>
       <c r="R128" t="n">
-        <v>6818160</v>
+        <v>6818061</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128927853</v>
+        <v>128927918</v>
       </c>
       <c r="B129" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13353,21 +13353,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430073</v>
+        <v>430649</v>
       </c>
       <c r="R129" t="n">
-        <v>6818201</v>
+        <v>6818232</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128927918</v>
+        <v>128927878</v>
       </c>
       <c r="B130" t="n">
         <v>79124</v>
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>430649</v>
+        <v>430632</v>
       </c>
       <c r="R130" t="n">
-        <v>6818232</v>
+        <v>6818282</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13536,7 +13536,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128927878</v>
+        <v>128927908</v>
       </c>
       <c r="B131" t="n">
         <v>79124</v>
@@ -13571,10 +13571,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430632</v>
+        <v>430425</v>
       </c>
       <c r="R131" t="n">
-        <v>6818282</v>
+        <v>6818197</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14045,10 +14045,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128927863</v>
+        <v>128927894</v>
       </c>
       <c r="B136" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14056,34 +14056,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>429970</v>
+        <v>430321</v>
       </c>
       <c r="R136" t="n">
-        <v>6818162</v>
+        <v>6818095</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14118,12 +14121,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14142,7 +14151,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128927911</v>
+        <v>128927900</v>
       </c>
       <c r="B137" t="n">
         <v>79124</v>
@@ -14177,10 +14186,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430437</v>
+        <v>430467</v>
       </c>
       <c r="R137" t="n">
-        <v>6818227</v>
+        <v>6818020</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14239,7 +14248,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128927972</v>
+        <v>128927889</v>
       </c>
       <c r="B138" t="n">
         <v>79124</v>
@@ -14268,19 +14277,16 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430018</v>
+        <v>430385</v>
       </c>
       <c r="R138" t="n">
-        <v>6818025</v>
+        <v>6818203</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14321,7 +14327,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14340,10 +14345,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128927861</v>
+        <v>128927911</v>
       </c>
       <c r="B139" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14351,21 +14356,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14375,10 +14380,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>429989</v>
+        <v>430437</v>
       </c>
       <c r="R139" t="n">
-        <v>6818159</v>
+        <v>6818227</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14437,7 +14442,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128927894</v>
+        <v>128927969</v>
       </c>
       <c r="B140" t="n">
         <v>79124</v>
@@ -14466,19 +14471,16 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430321</v>
+        <v>429947</v>
       </c>
       <c r="R140" t="n">
-        <v>6818095</v>
+        <v>6818135</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14513,18 +14515,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14543,7 +14539,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128927900</v>
+        <v>128927956</v>
       </c>
       <c r="B141" t="n">
         <v>79124</v>
@@ -14578,10 +14574,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430467</v>
+        <v>430119</v>
       </c>
       <c r="R141" t="n">
-        <v>6818020</v>
+        <v>6818173</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14640,7 +14636,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128927889</v>
+        <v>128927925</v>
       </c>
       <c r="B142" t="n">
         <v>79124</v>
@@ -14675,10 +14671,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430385</v>
+        <v>430683</v>
       </c>
       <c r="R142" t="n">
-        <v>6818203</v>
+        <v>6818265</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14737,7 +14733,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128927969</v>
+        <v>128927972</v>
       </c>
       <c r="B143" t="n">
         <v>79124</v>
@@ -14766,16 +14762,19 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>429947</v>
+        <v>430018</v>
       </c>
       <c r="R143" t="n">
-        <v>6818135</v>
+        <v>6818025</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14816,6 +14815,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14834,7 +14834,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128927956</v>
+        <v>128927926</v>
       </c>
       <c r="B144" t="n">
         <v>79124</v>
@@ -14869,10 +14869,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430119</v>
+        <v>430701</v>
       </c>
       <c r="R144" t="n">
-        <v>6818173</v>
+        <v>6818261</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14931,10 +14931,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128927925</v>
+        <v>128927781</v>
       </c>
       <c r="B145" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14942,34 +14942,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430683</v>
+        <v>430480</v>
       </c>
       <c r="R145" t="n">
-        <v>6818265</v>
+        <v>6817997</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15028,10 +15036,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128927926</v>
+        <v>128927788</v>
       </c>
       <c r="B146" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15039,34 +15047,42 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430701</v>
+        <v>430017</v>
       </c>
       <c r="R146" t="n">
-        <v>6818261</v>
+        <v>6818044</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15125,10 +15141,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128927709</v>
+        <v>128927775</v>
       </c>
       <c r="B147" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15136,34 +15152,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430495</v>
+        <v>430083</v>
       </c>
       <c r="R147" t="n">
-        <v>6818056</v>
+        <v>6818224</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15222,7 +15246,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927781</v>
+        <v>128927792</v>
       </c>
       <c r="B148" t="n">
         <v>57717</v>
@@ -15255,7 +15279,7 @@
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -15265,10 +15289,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430480</v>
+        <v>430150</v>
       </c>
       <c r="R148" t="n">
-        <v>6817997</v>
+        <v>6817814</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15327,10 +15351,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927788</v>
+        <v>128927863</v>
       </c>
       <c r="B149" t="n">
-        <v>57717</v>
+        <v>78881</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15338,42 +15362,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430017</v>
+        <v>429970</v>
       </c>
       <c r="R149" t="n">
-        <v>6818044</v>
+        <v>6818162</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15432,10 +15448,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927775</v>
+        <v>128927709</v>
       </c>
       <c r="B150" t="n">
-        <v>57717</v>
+        <v>79743</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15443,42 +15459,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430083</v>
+        <v>430495</v>
       </c>
       <c r="R150" t="n">
-        <v>6818224</v>
+        <v>6818056</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15537,10 +15545,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927792</v>
+        <v>128927861</v>
       </c>
       <c r="B151" t="n">
-        <v>57717</v>
+        <v>78881</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15548,42 +15556,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430150</v>
+        <v>429989</v>
       </c>
       <c r="R151" t="n">
-        <v>6817814</v>
+        <v>6818159</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16146,7 +16146,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128927958</v>
+        <v>128927920</v>
       </c>
       <c r="B157" t="n">
         <v>79124</v>
@@ -16181,10 +16181,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430048</v>
+        <v>430637</v>
       </c>
       <c r="R157" t="n">
-        <v>6818232</v>
+        <v>6818260</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16243,10 +16243,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128927798</v>
+        <v>128927951</v>
       </c>
       <c r="B158" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16254,34 +16254,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430315</v>
+        <v>430191</v>
       </c>
       <c r="R158" t="n">
-        <v>6818095</v>
+        <v>6817932</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16316,12 +16319,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Garnlav, måttligt inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -16340,10 +16349,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128927828</v>
+        <v>128927958</v>
       </c>
       <c r="B159" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16351,37 +16360,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430115</v>
+        <v>430048</v>
       </c>
       <c r="R159" t="n">
-        <v>6817902</v>
+        <v>6818232</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16422,7 +16428,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -16441,10 +16446,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128927875</v>
+        <v>128927902</v>
       </c>
       <c r="B160" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16452,21 +16457,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16476,10 +16481,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430127</v>
+        <v>430530</v>
       </c>
       <c r="R160" t="n">
-        <v>6817846</v>
+        <v>6818025</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16538,10 +16543,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128927920</v>
+        <v>128927875</v>
       </c>
       <c r="B161" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16549,21 +16554,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16573,10 +16578,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430637</v>
+        <v>430127</v>
       </c>
       <c r="R161" t="n">
-        <v>6818260</v>
+        <v>6817846</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16829,10 +16834,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128927951</v>
+        <v>128927846</v>
       </c>
       <c r="B164" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16840,37 +16845,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430191</v>
+        <v>430241</v>
       </c>
       <c r="R164" t="n">
-        <v>6817932</v>
+        <v>6818085</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16905,18 +16907,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Garnlav, måttligt inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -16935,10 +16931,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128927846</v>
+        <v>128927779</v>
       </c>
       <c r="B165" t="n">
-        <v>78881</v>
+        <v>57717</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16946,34 +16942,42 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430241</v>
+        <v>430106</v>
       </c>
       <c r="R165" t="n">
-        <v>6818085</v>
+        <v>6817957</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17032,10 +17036,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128927902</v>
+        <v>128927783</v>
       </c>
       <c r="B166" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17043,34 +17047,42 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>430530</v>
+        <v>430174</v>
       </c>
       <c r="R166" t="n">
-        <v>6818025</v>
+        <v>6817923</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17129,10 +17141,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128927779</v>
+        <v>128927798</v>
       </c>
       <c r="B167" t="n">
-        <v>57717</v>
+        <v>78882</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17140,42 +17152,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430106</v>
+        <v>430315</v>
       </c>
       <c r="R167" t="n">
-        <v>6817957</v>
+        <v>6818095</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17234,10 +17238,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128927783</v>
+        <v>128927828</v>
       </c>
       <c r="B168" t="n">
-        <v>57717</v>
+        <v>78882</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17245,31 +17249,26 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -17277,10 +17276,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430174</v>
+        <v>430115</v>
       </c>
       <c r="R168" t="n">
-        <v>6817923</v>
+        <v>6817902</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17321,6 +17320,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17436,10 +17436,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128927904</v>
+        <v>128927737</v>
       </c>
       <c r="B170" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17447,34 +17447,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430405</v>
+        <v>430143</v>
       </c>
       <c r="R170" t="n">
-        <v>6818117</v>
+        <v>6817831</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17515,6 +17518,7 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -17533,10 +17537,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128927933</v>
+        <v>128927981</v>
       </c>
       <c r="B171" t="n">
-        <v>79124</v>
+        <v>78096</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17544,37 +17548,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430220</v>
+        <v>430056</v>
       </c>
       <c r="R171" t="n">
-        <v>6818148</v>
+        <v>6818166</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17609,18 +17610,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -17639,10 +17634,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128927981</v>
+        <v>128927712</v>
       </c>
       <c r="B172" t="n">
-        <v>78096</v>
+        <v>79743</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17650,21 +17645,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17674,10 +17669,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430056</v>
+        <v>430596</v>
       </c>
       <c r="R172" t="n">
-        <v>6818166</v>
+        <v>6818190</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17736,10 +17731,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128927712</v>
+        <v>128927933</v>
       </c>
       <c r="B173" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17747,34 +17742,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430596</v>
+        <v>430220</v>
       </c>
       <c r="R173" t="n">
-        <v>6818190</v>
+        <v>6818148</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17809,12 +17807,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -17833,10 +17837,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128927737</v>
+        <v>128927904</v>
       </c>
       <c r="B174" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17844,37 +17848,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430143</v>
+        <v>430405</v>
       </c>
       <c r="R174" t="n">
-        <v>6817831</v>
+        <v>6818117</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17915,7 +17916,6 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -18031,10 +18031,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128927848</v>
+        <v>128927723</v>
       </c>
       <c r="B176" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18042,21 +18042,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18066,10 +18066,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430174</v>
+        <v>429993</v>
       </c>
       <c r="R176" t="n">
-        <v>6818156</v>
+        <v>6818157</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18128,10 +18128,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128927952</v>
+        <v>128927848</v>
       </c>
       <c r="B177" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18139,21 +18139,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18163,10 +18163,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430190</v>
+        <v>430174</v>
       </c>
       <c r="R177" t="n">
-        <v>6817925</v>
+        <v>6818156</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18225,7 +18225,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128927945</v>
+        <v>128927898</v>
       </c>
       <c r="B178" t="n">
         <v>79124</v>
@@ -18260,10 +18260,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430404</v>
+        <v>430384</v>
       </c>
       <c r="R178" t="n">
-        <v>6818178</v>
+        <v>6818048</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18322,10 +18322,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128927723</v>
+        <v>128927968</v>
       </c>
       <c r="B179" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18333,21 +18333,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18357,10 +18357,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>429993</v>
+        <v>430067</v>
       </c>
       <c r="R179" t="n">
-        <v>6818157</v>
+        <v>6818139</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18419,10 +18419,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128927750</v>
+        <v>128927952</v>
       </c>
       <c r="B180" t="n">
-        <v>79714</v>
+        <v>79124</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18430,21 +18430,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18454,10 +18454,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430140</v>
+        <v>430190</v>
       </c>
       <c r="R180" t="n">
-        <v>6817881</v>
+        <v>6817925</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18516,10 +18516,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128927741</v>
+        <v>128927945</v>
       </c>
       <c r="B181" t="n">
-        <v>79714</v>
+        <v>79124</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18527,21 +18527,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18551,10 +18551,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430600</v>
+        <v>430404</v>
       </c>
       <c r="R181" t="n">
-        <v>6818203</v>
+        <v>6818178</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18613,45 +18613,53 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128927812</v>
+        <v>128927760</v>
       </c>
       <c r="B182" t="n">
-        <v>78882</v>
+        <v>56910</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430157</v>
+        <v>430663</v>
       </c>
       <c r="R182" t="n">
-        <v>6818149</v>
+        <v>6818259</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18710,45 +18718,53 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128927898</v>
+        <v>128927762</v>
       </c>
       <c r="B183" t="n">
-        <v>79124</v>
+        <v>56910</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430384</v>
+        <v>430394</v>
       </c>
       <c r="R183" t="n">
-        <v>6818048</v>
+        <v>6818168</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18807,10 +18823,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128927968</v>
+        <v>128927750</v>
       </c>
       <c r="B184" t="n">
-        <v>79124</v>
+        <v>79714</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18818,21 +18834,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18842,10 +18858,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430067</v>
+        <v>430140</v>
       </c>
       <c r="R184" t="n">
-        <v>6818139</v>
+        <v>6817881</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18904,53 +18920,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128927760</v>
+        <v>128927741</v>
       </c>
       <c r="B185" t="n">
-        <v>56910</v>
+        <v>79714</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430663</v>
+        <v>430600</v>
       </c>
       <c r="R185" t="n">
-        <v>6818259</v>
+        <v>6818203</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19009,53 +19017,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128927762</v>
+        <v>128927812</v>
       </c>
       <c r="B186" t="n">
-        <v>56910</v>
+        <v>78882</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430394</v>
+        <v>430157</v>
       </c>
       <c r="R186" t="n">
-        <v>6818168</v>
+        <v>6818149</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19114,10 +19114,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128927820</v>
+        <v>128927731</v>
       </c>
       <c r="B187" t="n">
-        <v>78882</v>
+        <v>79743</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19125,21 +19125,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19149,10 +19149,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430014</v>
+        <v>430056</v>
       </c>
       <c r="R187" t="n">
-        <v>6818142</v>
+        <v>6818017</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19211,10 +19211,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128927818</v>
+        <v>128927847</v>
       </c>
       <c r="B188" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19222,21 +19222,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19246,10 +19246,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430048</v>
+        <v>430227</v>
       </c>
       <c r="R188" t="n">
-        <v>6818123</v>
+        <v>6818154</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19308,10 +19308,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128927910</v>
+        <v>128927872</v>
       </c>
       <c r="B189" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19319,21 +19319,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19343,10 +19343,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430430</v>
+        <v>430227</v>
       </c>
       <c r="R189" t="n">
-        <v>6818202</v>
+        <v>6818015</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19405,10 +19405,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128927962</v>
+        <v>128927728</v>
       </c>
       <c r="B190" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19416,21 +19416,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19440,10 +19440,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430069</v>
+        <v>430232</v>
       </c>
       <c r="R190" t="n">
-        <v>6818225</v>
+        <v>6818068</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19502,10 +19502,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128927847</v>
+        <v>128927910</v>
       </c>
       <c r="B191" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19513,21 +19513,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19537,10 +19537,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430227</v>
+        <v>430430</v>
       </c>
       <c r="R191" t="n">
-        <v>6818154</v>
+        <v>6818202</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19696,10 +19696,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128927872</v>
+        <v>128927906</v>
       </c>
       <c r="B193" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19707,34 +19707,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430227</v>
+        <v>430401</v>
       </c>
       <c r="R193" t="n">
-        <v>6818015</v>
+        <v>6818157</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19769,12 +19772,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -19793,7 +19802,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128927906</v>
+        <v>128927922</v>
       </c>
       <c r="B194" t="n">
         <v>79124</v>
@@ -19822,19 +19831,16 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430401</v>
+        <v>430668</v>
       </c>
       <c r="R194" t="n">
-        <v>6818157</v>
+        <v>6818241</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19869,18 +19875,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
-        </is>
-      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -19899,7 +19899,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128927922</v>
+        <v>128927962</v>
       </c>
       <c r="B195" t="n">
         <v>79124</v>
@@ -19934,10 +19934,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430668</v>
+        <v>430069</v>
       </c>
       <c r="R195" t="n">
-        <v>6818241</v>
+        <v>6818225</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19996,10 +19996,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128927728</v>
+        <v>128927789</v>
       </c>
       <c r="B196" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20007,34 +20007,42 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430232</v>
+        <v>430089</v>
       </c>
       <c r="R196" t="n">
-        <v>6818068</v>
+        <v>6817965</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20067,6 +20075,11 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20093,10 +20106,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128927731</v>
+        <v>128927820</v>
       </c>
       <c r="B197" t="n">
-        <v>79743</v>
+        <v>78882</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20104,21 +20117,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20128,10 +20141,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430056</v>
+        <v>430014</v>
       </c>
       <c r="R197" t="n">
-        <v>6818017</v>
+        <v>6818142</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20190,10 +20203,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128927789</v>
+        <v>128927818</v>
       </c>
       <c r="B198" t="n">
-        <v>57717</v>
+        <v>78882</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20201,42 +20214,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430089</v>
+        <v>430048</v>
       </c>
       <c r="R198" t="n">
-        <v>6817965</v>
+        <v>6818123</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20269,11 +20274,6 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20300,10 +20300,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128927913</v>
+        <v>128927841</v>
       </c>
       <c r="B199" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20311,21 +20311,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20335,10 +20335,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430484</v>
+        <v>430569</v>
       </c>
       <c r="R199" t="n">
-        <v>6818253</v>
+        <v>6818243</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20397,10 +20397,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128927936</v>
+        <v>128927755</v>
       </c>
       <c r="B200" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20408,34 +20408,42 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430084</v>
+        <v>430480</v>
       </c>
       <c r="R200" t="n">
-        <v>6818157</v>
+        <v>6818068</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20494,10 +20502,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128927961</v>
+        <v>128927717</v>
       </c>
       <c r="B201" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20505,21 +20513,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20529,10 +20537,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430086</v>
+        <v>430214</v>
       </c>
       <c r="R201" t="n">
-        <v>6818236</v>
+        <v>6817971</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20591,10 +20599,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128927942</v>
+        <v>128927715</v>
       </c>
       <c r="B202" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20602,21 +20610,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20626,10 +20634,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430087</v>
+        <v>430650</v>
       </c>
       <c r="R202" t="n">
-        <v>6817971</v>
+        <v>6818249</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20688,10 +20696,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128927715</v>
+        <v>128927913</v>
       </c>
       <c r="B203" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20699,21 +20707,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20723,10 +20731,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430650</v>
+        <v>430484</v>
       </c>
       <c r="R203" t="n">
-        <v>6818249</v>
+        <v>6818253</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20785,10 +20793,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128927717</v>
+        <v>128927936</v>
       </c>
       <c r="B204" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20796,21 +20804,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20820,10 +20828,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430214</v>
+        <v>430084</v>
       </c>
       <c r="R204" t="n">
-        <v>6817971</v>
+        <v>6818157</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20882,10 +20890,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128927841</v>
+        <v>128927961</v>
       </c>
       <c r="B205" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20893,21 +20901,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20917,10 +20925,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430569</v>
+        <v>430086</v>
       </c>
       <c r="R205" t="n">
-        <v>6818243</v>
+        <v>6818236</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20979,10 +20987,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128927755</v>
+        <v>128927942</v>
       </c>
       <c r="B206" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20990,42 +20998,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430480</v>
+        <v>430087</v>
       </c>
       <c r="R206" t="n">
-        <v>6818068</v>
+        <v>6817971</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21472,10 +21472,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128927941</v>
+        <v>128927866</v>
       </c>
       <c r="B211" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21483,21 +21483,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21507,10 +21507,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>430078</v>
+        <v>429950</v>
       </c>
       <c r="R211" t="n">
-        <v>6817995</v>
+        <v>6818057</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21569,7 +21569,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128927960</v>
+        <v>128927941</v>
       </c>
       <c r="B212" t="n">
         <v>79124</v>
@@ -21604,10 +21604,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430089</v>
+        <v>430078</v>
       </c>
       <c r="R212" t="n">
-        <v>6818238</v>
+        <v>6817995</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21666,10 +21666,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128927866</v>
+        <v>128927960</v>
       </c>
       <c r="B213" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21677,21 +21677,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21701,10 +21701,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>429950</v>
+        <v>430089</v>
       </c>
       <c r="R213" t="n">
-        <v>6818057</v>
+        <v>6818238</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22062,10 +22062,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128927746</v>
+        <v>128927817</v>
       </c>
       <c r="B217" t="n">
-        <v>79714</v>
+        <v>78882</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22073,21 +22073,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22097,10 +22097,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>430232</v>
+        <v>430068</v>
       </c>
       <c r="R217" t="n">
-        <v>6818068</v>
+        <v>6818152</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22159,10 +22159,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128927817</v>
+        <v>128927746</v>
       </c>
       <c r="B218" t="n">
-        <v>78882</v>
+        <v>79714</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22170,21 +22170,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22194,10 +22194,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>430068</v>
+        <v>430232</v>
       </c>
       <c r="R218" t="n">
-        <v>6818152</v>
+        <v>6818068</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22353,10 +22353,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128927867</v>
+        <v>128927881</v>
       </c>
       <c r="B220" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22364,21 +22364,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22388,10 +22388,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430006</v>
+        <v>430536</v>
       </c>
       <c r="R220" t="n">
-        <v>6818034</v>
+        <v>6818208</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22450,10 +22450,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128927771</v>
+        <v>128927916</v>
       </c>
       <c r="B221" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22461,42 +22461,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430658</v>
+        <v>430580</v>
       </c>
       <c r="R221" t="n">
-        <v>6818274</v>
+        <v>6818221</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22555,10 +22547,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128927881</v>
+        <v>128927771</v>
       </c>
       <c r="B222" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22566,34 +22558,42 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430536</v>
+        <v>430658</v>
       </c>
       <c r="R222" t="n">
-        <v>6818208</v>
+        <v>6818274</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22652,10 +22652,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128927916</v>
+        <v>128927867</v>
       </c>
       <c r="B223" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22663,21 +22663,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22687,10 +22687,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430580</v>
+        <v>430006</v>
       </c>
       <c r="R223" t="n">
-        <v>6818221</v>
+        <v>6818034</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22850,10 +22850,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128927915</v>
+        <v>128927850</v>
       </c>
       <c r="B225" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22861,37 +22861,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430575</v>
+        <v>430159</v>
       </c>
       <c r="R225" t="n">
-        <v>6818234</v>
+        <v>6818161</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22932,7 +22929,6 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
-      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
       </c>
@@ -22951,10 +22947,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128927923</v>
+        <v>128927730</v>
       </c>
       <c r="B226" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22962,21 +22958,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22986,10 +22982,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430670</v>
+        <v>430075</v>
       </c>
       <c r="R226" t="n">
-        <v>6818263</v>
+        <v>6818213</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23048,10 +23044,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128927850</v>
+        <v>128927890</v>
       </c>
       <c r="B227" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23059,21 +23055,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23083,10 +23079,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430159</v>
+        <v>430348</v>
       </c>
       <c r="R227" t="n">
-        <v>6818161</v>
+        <v>6818167</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23145,7 +23141,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128927890</v>
+        <v>128927915</v>
       </c>
       <c r="B228" t="n">
         <v>79124</v>
@@ -23174,16 +23170,19 @@
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430348</v>
+        <v>430575</v>
       </c>
       <c r="R228" t="n">
-        <v>6818167</v>
+        <v>6818234</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23224,6 +23223,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -23242,10 +23242,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128927730</v>
+        <v>128927923</v>
       </c>
       <c r="B229" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23253,21 +23253,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23277,10 +23277,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430075</v>
+        <v>430670</v>
       </c>
       <c r="R229" t="n">
-        <v>6818213</v>
+        <v>6818263</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128927732</v>
+        <v>128927950</v>
       </c>
       <c r="B22" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430138</v>
+        <v>430233</v>
       </c>
       <c r="R22" t="n">
-        <v>6817883</v>
+        <v>6817831</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927868</v>
+        <v>128927880</v>
       </c>
       <c r="B23" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430089</v>
+        <v>430577</v>
       </c>
       <c r="R23" t="n">
-        <v>6817984</v>
+        <v>6818221</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927843</v>
+        <v>128927978</v>
       </c>
       <c r="B24" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430626</v>
+        <v>430082</v>
       </c>
       <c r="R24" t="n">
-        <v>6818202</v>
+        <v>6818210</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,6 +3124,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3142,10 +3143,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927721</v>
+        <v>128927935</v>
       </c>
       <c r="B25" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,21 +3154,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430060</v>
+        <v>430099</v>
       </c>
       <c r="R25" t="n">
-        <v>6818156</v>
+        <v>6818154</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3240,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927726</v>
+        <v>128927963</v>
       </c>
       <c r="B26" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3250,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3274,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430114</v>
+        <v>430064</v>
       </c>
       <c r="R26" t="n">
-        <v>6817912</v>
+        <v>6818190</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,10 +3337,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927950</v>
+        <v>128927732</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3347,21 +3348,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3372,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430233</v>
+        <v>430138</v>
       </c>
       <c r="R27" t="n">
-        <v>6817831</v>
+        <v>6817883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927880</v>
+        <v>128927868</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3445,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3468,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430577</v>
+        <v>430089</v>
       </c>
       <c r="R28" t="n">
-        <v>6818221</v>
+        <v>6817984</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927978</v>
+        <v>128927843</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,21 +3542,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3565,10 +3566,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430082</v>
+        <v>430626</v>
       </c>
       <c r="R29" t="n">
-        <v>6818210</v>
+        <v>6818202</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3609,7 +3610,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927935</v>
+        <v>128927721</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430099</v>
+        <v>430060</v>
       </c>
       <c r="R30" t="n">
-        <v>6818154</v>
+        <v>6818156</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927963</v>
+        <v>128927726</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3736,21 +3736,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430064</v>
+        <v>430114</v>
       </c>
       <c r="R31" t="n">
-        <v>6818190</v>
+        <v>6817912</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128927871</v>
+        <v>128927939</v>
       </c>
       <c r="B36" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>430145</v>
+        <v>429903</v>
       </c>
       <c r="R36" t="n">
-        <v>6817833</v>
+        <v>6818059</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128927939</v>
+        <v>128927871</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4423,21 +4423,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>429903</v>
+        <v>430145</v>
       </c>
       <c r="R38" t="n">
-        <v>6818059</v>
+        <v>6817833</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128927743</v>
+        <v>128927813</v>
       </c>
       <c r="B41" t="n">
-        <v>79714</v>
+        <v>78882</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430211</v>
+        <v>430145</v>
       </c>
       <c r="R41" t="n">
-        <v>6817980</v>
+        <v>6818165</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128927813</v>
+        <v>128927743</v>
       </c>
       <c r="B42" t="n">
-        <v>78882</v>
+        <v>79714</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>430145</v>
+        <v>430211</v>
       </c>
       <c r="R42" t="n">
-        <v>6818165</v>
+        <v>6817980</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128927845</v>
+        <v>128927930</v>
       </c>
       <c r="B43" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430669</v>
+        <v>430205</v>
       </c>
       <c r="R43" t="n">
-        <v>6818249</v>
+        <v>6817961</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128927842</v>
+        <v>128927928</v>
       </c>
       <c r="B44" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,21 +5017,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430596</v>
+        <v>430293</v>
       </c>
       <c r="R44" t="n">
-        <v>6818186</v>
+        <v>6817871</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128927786</v>
+        <v>128927934</v>
       </c>
       <c r="B45" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5114,42 +5114,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430078</v>
+        <v>430088</v>
       </c>
       <c r="R45" t="n">
-        <v>6818213</v>
+        <v>6818186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5182,11 +5174,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5213,7 +5200,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128927930</v>
+        <v>128927938</v>
       </c>
       <c r="B46" t="n">
         <v>79124</v>
@@ -5248,10 +5235,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430205</v>
+        <v>429959</v>
       </c>
       <c r="R46" t="n">
-        <v>6817961</v>
+        <v>6818128</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5310,7 +5297,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128927928</v>
+        <v>128927976</v>
       </c>
       <c r="B47" t="n">
         <v>79124</v>
@@ -5339,16 +5326,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430293</v>
+        <v>430149</v>
       </c>
       <c r="R47" t="n">
-        <v>6817871</v>
+        <v>6817860</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,6 +5379,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5407,7 +5398,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128927934</v>
+        <v>128927966</v>
       </c>
       <c r="B48" t="n">
         <v>79124</v>
@@ -5442,10 +5433,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430088</v>
+        <v>430071</v>
       </c>
       <c r="R48" t="n">
-        <v>6818186</v>
+        <v>6818124</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5504,10 +5495,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128927938</v>
+        <v>128927845</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5515,21 +5506,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5539,10 +5530,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>429959</v>
+        <v>430669</v>
       </c>
       <c r="R49" t="n">
-        <v>6818128</v>
+        <v>6818249</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5601,10 +5592,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128927976</v>
+        <v>128927842</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5612,37 +5603,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430149</v>
+        <v>430596</v>
       </c>
       <c r="R50" t="n">
-        <v>6817860</v>
+        <v>6818186</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5683,7 +5671,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5702,10 +5689,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128927966</v>
+        <v>128927786</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,34 +5700,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430071</v>
+        <v>430078</v>
       </c>
       <c r="R51" t="n">
-        <v>6818124</v>
+        <v>6818213</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5773,6 +5768,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128927799</v>
+        <v>128927806</v>
       </c>
       <c r="B54" t="n">
         <v>78882</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>430396</v>
+        <v>430655</v>
       </c>
       <c r="R54" t="n">
-        <v>6818052</v>
+        <v>6818264</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128927806</v>
+        <v>128927799</v>
       </c>
       <c r="B55" t="n">
         <v>78882</v>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>430655</v>
+        <v>430396</v>
       </c>
       <c r="R55" t="n">
-        <v>6818264</v>
+        <v>6818052</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6187,10 +6187,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128927970</v>
+        <v>128927874</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>429900</v>
+        <v>430154</v>
       </c>
       <c r="R56" t="n">
-        <v>6818098</v>
+        <v>6817859</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6258,11 +6258,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6289,10 +6284,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128927944</v>
+        <v>128927735</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6300,37 +6295,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>430531</v>
+        <v>430132</v>
       </c>
       <c r="R57" t="n">
-        <v>6818016</v>
+        <v>6817858</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6371,7 +6363,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6390,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128927948</v>
+        <v>128927855</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6401,21 +6392,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6425,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430655</v>
+        <v>430113</v>
       </c>
       <c r="R58" t="n">
-        <v>6818216</v>
+        <v>6818160</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6487,7 +6478,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927882</v>
+        <v>128927937</v>
       </c>
       <c r="B59" t="n">
         <v>79124</v>
@@ -6522,10 +6513,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430526</v>
+        <v>430011</v>
       </c>
       <c r="R59" t="n">
-        <v>6818232</v>
+        <v>6818137</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6584,7 +6575,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927929</v>
+        <v>128927970</v>
       </c>
       <c r="B60" t="n">
         <v>79124</v>
@@ -6619,10 +6610,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430208</v>
+        <v>429900</v>
       </c>
       <c r="R60" t="n">
-        <v>6817816</v>
+        <v>6818098</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6655,6 +6646,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6681,10 +6677,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128927815</v>
+        <v>128927944</v>
       </c>
       <c r="B61" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,34 +6688,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430061</v>
+        <v>430531</v>
       </c>
       <c r="R61" t="n">
-        <v>6818258</v>
+        <v>6818016</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6760,6 +6759,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128927874</v>
+        <v>128927948</v>
       </c>
       <c r="B62" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430154</v>
+        <v>430655</v>
       </c>
       <c r="R62" t="n">
-        <v>6817859</v>
+        <v>6818216</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6875,10 +6875,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128927735</v>
+        <v>128927882</v>
       </c>
       <c r="B63" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6886,21 +6886,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430132</v>
+        <v>430526</v>
       </c>
       <c r="R63" t="n">
-        <v>6817858</v>
+        <v>6818232</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6972,7 +6972,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128927937</v>
+        <v>128927929</v>
       </c>
       <c r="B64" t="n">
         <v>79124</v>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430011</v>
+        <v>430208</v>
       </c>
       <c r="R64" t="n">
-        <v>6818137</v>
+        <v>6817816</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128927855</v>
+        <v>128927815</v>
       </c>
       <c r="B65" t="n">
-        <v>78881</v>
+        <v>78882</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430113</v>
+        <v>430061</v>
       </c>
       <c r="R65" t="n">
-        <v>6818160</v>
+        <v>6818258</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128927825</v>
+        <v>128927893</v>
       </c>
       <c r="B66" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7177,21 +7177,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430024</v>
+        <v>430286</v>
       </c>
       <c r="R66" t="n">
-        <v>6818040</v>
+        <v>6818100</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7263,7 +7263,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128927893</v>
+        <v>128927974</v>
       </c>
       <c r="B67" t="n">
         <v>79124</v>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430286</v>
+        <v>430091</v>
       </c>
       <c r="R67" t="n">
-        <v>6818100</v>
+        <v>6818012</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128927974</v>
+        <v>128927790</v>
       </c>
       <c r="B68" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7371,34 +7371,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430091</v>
+        <v>430130</v>
       </c>
       <c r="R68" t="n">
-        <v>6818012</v>
+        <v>6817856</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7457,10 +7465,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128927790</v>
+        <v>128927751</v>
       </c>
       <c r="B69" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7468,16 +7476,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7490,7 +7498,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -7500,10 +7508,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430130</v>
+        <v>430337</v>
       </c>
       <c r="R69" t="n">
-        <v>6817856</v>
+        <v>6818076</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7562,10 +7570,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128927751</v>
+        <v>128927825</v>
       </c>
       <c r="B70" t="n">
-        <v>57720</v>
+        <v>78882</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7573,42 +7581,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>430337</v>
+        <v>430024</v>
       </c>
       <c r="R70" t="n">
-        <v>6818076</v>
+        <v>6818040</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128927924</v>
+        <v>128927840</v>
       </c>
       <c r="B76" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8167,21 +8167,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430671</v>
+        <v>430407</v>
       </c>
       <c r="R76" t="n">
-        <v>6818266</v>
+        <v>6818114</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128927964</v>
+        <v>128927865</v>
       </c>
       <c r="B77" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430099</v>
+        <v>429935</v>
       </c>
       <c r="R77" t="n">
-        <v>6818174</v>
+        <v>6818065</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128927897</v>
+        <v>128927964</v>
       </c>
       <c r="B78" t="n">
         <v>79124</v>
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430386</v>
+        <v>430099</v>
       </c>
       <c r="R78" t="n">
-        <v>6818039</v>
+        <v>6818174</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128927955</v>
+        <v>128927725</v>
       </c>
       <c r="B79" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8458,37 +8458,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430129</v>
+        <v>430040</v>
       </c>
       <c r="R79" t="n">
-        <v>6818156</v>
+        <v>6818029</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8523,18 +8520,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30 m</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8553,10 +8544,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128927905</v>
+        <v>128927811</v>
       </c>
       <c r="B80" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8564,21 +8555,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8588,10 +8579,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430395</v>
+        <v>430176</v>
       </c>
       <c r="R80" t="n">
-        <v>6818138</v>
+        <v>6818150</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8650,10 +8641,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128927885</v>
+        <v>128927795</v>
       </c>
       <c r="B81" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8661,21 +8652,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8685,10 +8676,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430366</v>
+        <v>430390</v>
       </c>
       <c r="R81" t="n">
-        <v>6818264</v>
+        <v>6818205</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8747,10 +8738,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128927947</v>
+        <v>128927832</v>
       </c>
       <c r="B82" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8758,21 +8749,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8782,10 +8773,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430568</v>
+        <v>430153</v>
       </c>
       <c r="R82" t="n">
-        <v>6818235</v>
+        <v>6817822</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8818,11 +8809,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8849,7 +8835,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128927912</v>
+        <v>128927924</v>
       </c>
       <c r="B83" t="n">
         <v>79124</v>
@@ -8884,10 +8870,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430439</v>
+        <v>430671</v>
       </c>
       <c r="R83" t="n">
-        <v>6818230</v>
+        <v>6818266</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8946,10 +8932,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128927795</v>
+        <v>128927897</v>
       </c>
       <c r="B84" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8957,21 +8943,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8981,10 +8967,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430390</v>
+        <v>430386</v>
       </c>
       <c r="R84" t="n">
-        <v>6818205</v>
+        <v>6818039</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9043,10 +9029,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128927811</v>
+        <v>128927955</v>
       </c>
       <c r="B85" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9054,34 +9040,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>430176</v>
+        <v>430129</v>
       </c>
       <c r="R85" t="n">
-        <v>6818150</v>
+        <v>6818156</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9116,12 +9105,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30 m</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9140,10 +9135,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128927832</v>
+        <v>128927905</v>
       </c>
       <c r="B86" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9151,21 +9146,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9175,10 +9170,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430153</v>
+        <v>430395</v>
       </c>
       <c r="R86" t="n">
-        <v>6817822</v>
+        <v>6818138</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9237,10 +9232,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128927840</v>
+        <v>128927885</v>
       </c>
       <c r="B87" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9248,21 +9243,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9272,10 +9267,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>430407</v>
+        <v>430366</v>
       </c>
       <c r="R87" t="n">
-        <v>6818114</v>
+        <v>6818264</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9334,10 +9329,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128927865</v>
+        <v>128927947</v>
       </c>
       <c r="B88" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9345,21 +9340,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9369,10 +9364,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>429935</v>
+        <v>430568</v>
       </c>
       <c r="R88" t="n">
-        <v>6818065</v>
+        <v>6818235</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9405,6 +9400,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9431,10 +9431,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128927725</v>
+        <v>128927912</v>
       </c>
       <c r="B89" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>430040</v>
+        <v>430439</v>
       </c>
       <c r="R89" t="n">
-        <v>6818029</v>
+        <v>6818230</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128927864</v>
+        <v>128927891</v>
       </c>
       <c r="B91" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9636,21 +9636,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>429975</v>
+        <v>430336</v>
       </c>
       <c r="R91" t="n">
-        <v>6818158</v>
+        <v>6818151</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128927714</v>
+        <v>128927884</v>
       </c>
       <c r="B92" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9733,21 +9733,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430630</v>
+        <v>430423</v>
       </c>
       <c r="R92" t="n">
-        <v>6818207</v>
+        <v>6818270</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128927851</v>
+        <v>128927965</v>
       </c>
       <c r="B93" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9830,21 +9830,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430135</v>
+        <v>430115</v>
       </c>
       <c r="R93" t="n">
-        <v>6818172</v>
+        <v>6818177</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9916,7 +9916,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128927891</v>
+        <v>128927975</v>
       </c>
       <c r="B94" t="n">
         <v>79124</v>
@@ -9951,10 +9951,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430336</v>
+        <v>430138</v>
       </c>
       <c r="R94" t="n">
-        <v>6818151</v>
+        <v>6817903</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10013,7 +10013,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128927884</v>
+        <v>128927943</v>
       </c>
       <c r="B95" t="n">
         <v>79124</v>
@@ -10048,10 +10048,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430423</v>
+        <v>430136</v>
       </c>
       <c r="R95" t="n">
-        <v>6818270</v>
+        <v>6817849</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10110,10 +10110,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128927965</v>
+        <v>128927864</v>
       </c>
       <c r="B96" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10121,21 +10121,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10145,10 +10145,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430115</v>
+        <v>429975</v>
       </c>
       <c r="R96" t="n">
-        <v>6818177</v>
+        <v>6818158</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10207,10 +10207,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128927932</v>
+        <v>128927714</v>
       </c>
       <c r="B97" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10218,37 +10218,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430240</v>
+        <v>430630</v>
       </c>
       <c r="R97" t="n">
-        <v>6817987</v>
+        <v>6818207</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10283,18 +10280,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10313,7 +10304,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128927975</v>
+        <v>128927932</v>
       </c>
       <c r="B98" t="n">
         <v>79124</v>
@@ -10342,16 +10333,19 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430138</v>
+        <v>430240</v>
       </c>
       <c r="R98" t="n">
-        <v>6817903</v>
+        <v>6817987</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10386,12 +10380,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10410,10 +10410,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128927943</v>
+        <v>128927851</v>
       </c>
       <c r="B99" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10421,21 +10421,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430136</v>
+        <v>430135</v>
       </c>
       <c r="R99" t="n">
-        <v>6817849</v>
+        <v>6818172</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10507,32 +10507,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128927794</v>
+        <v>128927803</v>
       </c>
       <c r="B100" t="n">
-        <v>97507</v>
+        <v>78882</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430535</v>
+        <v>430580</v>
       </c>
       <c r="R100" t="n">
-        <v>6818254</v>
+        <v>6818253</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10701,32 +10701,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128927803</v>
+        <v>128927794</v>
       </c>
       <c r="B102" t="n">
-        <v>78882</v>
+        <v>97507</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>430580</v>
+        <v>430535</v>
       </c>
       <c r="R102" t="n">
-        <v>6818253</v>
+        <v>6818254</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10798,32 +10798,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927836</v>
+        <v>128927793</v>
       </c>
       <c r="B103" t="n">
-        <v>58090</v>
+        <v>58150</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430147</v>
+        <v>430104</v>
       </c>
       <c r="R103" t="n">
-        <v>6817817</v>
+        <v>6817933</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927856</v>
+        <v>128927796</v>
       </c>
       <c r="B104" t="n">
-        <v>78881</v>
+        <v>78882</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10906,21 +10906,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430060</v>
+        <v>430323</v>
       </c>
       <c r="R104" t="n">
-        <v>6818160</v>
+        <v>6818121</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10992,10 +10992,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927899</v>
+        <v>128927826</v>
       </c>
       <c r="B105" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11003,21 +11003,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430428</v>
+        <v>430018</v>
       </c>
       <c r="R105" t="n">
-        <v>6818038</v>
+        <v>6818046</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11089,10 +11089,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927954</v>
+        <v>128927822</v>
       </c>
       <c r="B106" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11100,37 +11100,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430166</v>
+        <v>429973</v>
       </c>
       <c r="R106" t="n">
-        <v>6818134</v>
+        <v>6818162</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11165,18 +11162,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11195,10 +11186,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927888</v>
+        <v>128927827</v>
       </c>
       <c r="B107" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11206,21 +11197,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11230,10 +11221,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430399</v>
+        <v>430057</v>
       </c>
       <c r="R107" t="n">
-        <v>6818238</v>
+        <v>6818016</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11292,7 +11283,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927971</v>
+        <v>128927899</v>
       </c>
       <c r="B108" t="n">
         <v>79124</v>
@@ -11327,10 +11318,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>429925</v>
+        <v>430428</v>
       </c>
       <c r="R108" t="n">
-        <v>6818065</v>
+        <v>6818038</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11389,7 +11380,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927949</v>
+        <v>128927954</v>
       </c>
       <c r="B109" t="n">
         <v>79124</v>
@@ -11418,16 +11409,19 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430653</v>
+        <v>430166</v>
       </c>
       <c r="R109" t="n">
-        <v>6818272</v>
+        <v>6818134</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11462,12 +11456,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11486,10 +11486,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128927793</v>
+        <v>128927888</v>
       </c>
       <c r="B110" t="n">
-        <v>58150</v>
+        <v>79124</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11497,21 +11497,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430104</v>
+        <v>430399</v>
       </c>
       <c r="R110" t="n">
-        <v>6817933</v>
+        <v>6818238</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11583,10 +11583,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927827</v>
+        <v>128927971</v>
       </c>
       <c r="B111" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11594,21 +11594,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430057</v>
+        <v>429925</v>
       </c>
       <c r="R111" t="n">
-        <v>6818016</v>
+        <v>6818065</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927822</v>
+        <v>128927949</v>
       </c>
       <c r="B112" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11691,21 +11691,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>429973</v>
+        <v>430653</v>
       </c>
       <c r="R112" t="n">
-        <v>6818162</v>
+        <v>6818272</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,10 +11777,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927826</v>
+        <v>128927856</v>
       </c>
       <c r="B113" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11788,21 +11788,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430018</v>
+        <v>430060</v>
       </c>
       <c r="R113" t="n">
-        <v>6818046</v>
+        <v>6818160</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,32 +11874,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927796</v>
+        <v>128927836</v>
       </c>
       <c r="B114" t="n">
-        <v>78882</v>
+        <v>58090</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430323</v>
+        <v>430147</v>
       </c>
       <c r="R114" t="n">
-        <v>6818121</v>
+        <v>6817817</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128927858</v>
+        <v>128927823</v>
       </c>
       <c r="B115" t="n">
-        <v>78881</v>
+        <v>78882</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>430034</v>
+        <v>429975</v>
       </c>
       <c r="R115" t="n">
-        <v>6818117</v>
+        <v>6818162</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12068,10 +12068,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128927873</v>
+        <v>128927740</v>
       </c>
       <c r="B116" t="n">
-        <v>78881</v>
+        <v>79714</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12079,21 +12079,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>429998</v>
+        <v>430401</v>
       </c>
       <c r="R116" t="n">
-        <v>6818047</v>
+        <v>6818062</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128927870</v>
+        <v>128927901</v>
       </c>
       <c r="B117" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12176,21 +12176,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430164</v>
+        <v>430501</v>
       </c>
       <c r="R117" t="n">
-        <v>6817854</v>
+        <v>6818013</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128927901</v>
+        <v>128927921</v>
       </c>
       <c r="B118" t="n">
         <v>79124</v>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>430501</v>
+        <v>430664</v>
       </c>
       <c r="R118" t="n">
-        <v>6818013</v>
+        <v>6818275</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12359,10 +12359,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128927921</v>
+        <v>128927870</v>
       </c>
       <c r="B119" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12370,21 +12370,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12394,10 +12394,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>430664</v>
+        <v>430164</v>
       </c>
       <c r="R119" t="n">
-        <v>6818275</v>
+        <v>6817854</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12456,10 +12456,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128927740</v>
+        <v>128927858</v>
       </c>
       <c r="B120" t="n">
-        <v>79714</v>
+        <v>78881</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12467,21 +12467,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12491,10 +12491,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>430401</v>
+        <v>430034</v>
       </c>
       <c r="R120" t="n">
-        <v>6818062</v>
+        <v>6818117</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12553,10 +12553,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128927823</v>
+        <v>128927873</v>
       </c>
       <c r="B121" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12564,21 +12564,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12588,10 +12588,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>429975</v>
+        <v>429998</v>
       </c>
       <c r="R121" t="n">
-        <v>6818162</v>
+        <v>6818047</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128927869</v>
+        <v>128927953</v>
       </c>
       <c r="B122" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12661,34 +12661,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>430138</v>
+        <v>430242</v>
       </c>
       <c r="R122" t="n">
-        <v>6817883</v>
+        <v>6818048</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12723,12 +12726,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12747,10 +12756,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128927720</v>
+        <v>128927907</v>
       </c>
       <c r="B123" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12758,21 +12767,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12782,10 +12791,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430112</v>
+        <v>430394</v>
       </c>
       <c r="R123" t="n">
-        <v>6818160</v>
+        <v>6818166</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12844,10 +12853,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128927853</v>
+        <v>128927977</v>
       </c>
       <c r="B124" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12855,34 +12864,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430073</v>
+        <v>430139</v>
       </c>
       <c r="R124" t="n">
-        <v>6818201</v>
+        <v>6817862</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12923,6 +12935,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12941,7 +12954,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128927953</v>
+        <v>128927940</v>
       </c>
       <c r="B125" t="n">
         <v>79124</v>
@@ -12970,19 +12983,16 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>430242</v>
+        <v>429952</v>
       </c>
       <c r="R125" t="n">
-        <v>6818048</v>
+        <v>6818061</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13017,18 +13027,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13047,7 +13051,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128927907</v>
+        <v>128927918</v>
       </c>
       <c r="B126" t="n">
         <v>79124</v>
@@ -13082,10 +13086,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430394</v>
+        <v>430649</v>
       </c>
       <c r="R126" t="n">
-        <v>6818166</v>
+        <v>6818232</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13144,7 +13148,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128927977</v>
+        <v>128927878</v>
       </c>
       <c r="B127" t="n">
         <v>79124</v>
@@ -13173,19 +13177,16 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430139</v>
+        <v>430632</v>
       </c>
       <c r="R127" t="n">
-        <v>6817862</v>
+        <v>6818282</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13226,7 +13227,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13245,7 +13245,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128927940</v>
+        <v>128927908</v>
       </c>
       <c r="B128" t="n">
         <v>79124</v>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>429952</v>
+        <v>430425</v>
       </c>
       <c r="R128" t="n">
-        <v>6818061</v>
+        <v>6818197</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,7 +13342,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128927918</v>
+        <v>128927886</v>
       </c>
       <c r="B129" t="n">
         <v>79124</v>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430649</v>
+        <v>430424</v>
       </c>
       <c r="R129" t="n">
-        <v>6818232</v>
+        <v>6818252</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,10 +13439,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128927878</v>
+        <v>128927869</v>
       </c>
       <c r="B130" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13450,21 +13450,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>430632</v>
+        <v>430138</v>
       </c>
       <c r="R130" t="n">
-        <v>6818282</v>
+        <v>6817883</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13536,10 +13536,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128927908</v>
+        <v>128927720</v>
       </c>
       <c r="B131" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13547,21 +13547,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13571,10 +13571,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430425</v>
+        <v>430112</v>
       </c>
       <c r="R131" t="n">
-        <v>6818197</v>
+        <v>6818160</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13633,10 +13633,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128927886</v>
+        <v>128927853</v>
       </c>
       <c r="B132" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13644,21 +13644,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13668,10 +13668,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430424</v>
+        <v>430073</v>
       </c>
       <c r="R132" t="n">
-        <v>6818252</v>
+        <v>6818201</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14636,7 +14636,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128927925</v>
+        <v>128927972</v>
       </c>
       <c r="B142" t="n">
         <v>79124</v>
@@ -14665,16 +14665,19 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430683</v>
+        <v>430018</v>
       </c>
       <c r="R142" t="n">
-        <v>6818265</v>
+        <v>6818025</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14715,6 +14718,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14733,7 +14737,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128927972</v>
+        <v>128927926</v>
       </c>
       <c r="B143" t="n">
         <v>79124</v>
@@ -14762,19 +14766,16 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430018</v>
+        <v>430701</v>
       </c>
       <c r="R143" t="n">
-        <v>6818025</v>
+        <v>6818261</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14815,7 +14816,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14834,7 +14834,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128927926</v>
+        <v>128927925</v>
       </c>
       <c r="B144" t="n">
         <v>79124</v>
@@ -14869,10 +14869,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430701</v>
+        <v>430683</v>
       </c>
       <c r="R144" t="n">
-        <v>6818261</v>
+        <v>6818265</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14931,10 +14931,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128927781</v>
+        <v>128927861</v>
       </c>
       <c r="B145" t="n">
-        <v>57717</v>
+        <v>78881</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14942,42 +14942,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430480</v>
+        <v>429989</v>
       </c>
       <c r="R145" t="n">
-        <v>6817997</v>
+        <v>6818159</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15036,7 +15028,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128927788</v>
+        <v>128927781</v>
       </c>
       <c r="B146" t="n">
         <v>57717</v>
@@ -15069,7 +15061,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -15079,10 +15071,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430017</v>
+        <v>430480</v>
       </c>
       <c r="R146" t="n">
-        <v>6818044</v>
+        <v>6817997</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15141,7 +15133,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128927775</v>
+        <v>128927788</v>
       </c>
       <c r="B147" t="n">
         <v>57717</v>
@@ -15174,7 +15166,7 @@
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -15184,10 +15176,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430083</v>
+        <v>430017</v>
       </c>
       <c r="R147" t="n">
-        <v>6818224</v>
+        <v>6818044</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15246,7 +15238,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927792</v>
+        <v>128927775</v>
       </c>
       <c r="B148" t="n">
         <v>57717</v>
@@ -15279,7 +15271,7 @@
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -15289,10 +15281,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430150</v>
+        <v>430083</v>
       </c>
       <c r="R148" t="n">
-        <v>6817814</v>
+        <v>6818224</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15351,10 +15343,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927863</v>
+        <v>128927792</v>
       </c>
       <c r="B149" t="n">
-        <v>78881</v>
+        <v>57717</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15362,34 +15354,42 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>429970</v>
+        <v>430150</v>
       </c>
       <c r="R149" t="n">
-        <v>6818162</v>
+        <v>6817814</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15448,10 +15448,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927709</v>
+        <v>128927863</v>
       </c>
       <c r="B150" t="n">
-        <v>79743</v>
+        <v>78881</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15459,21 +15459,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15483,10 +15483,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430495</v>
+        <v>429970</v>
       </c>
       <c r="R150" t="n">
-        <v>6818056</v>
+        <v>6818162</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15545,10 +15545,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927861</v>
+        <v>128927709</v>
       </c>
       <c r="B151" t="n">
-        <v>78881</v>
+        <v>79743</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15556,21 +15556,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15580,10 +15580,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>429989</v>
+        <v>430495</v>
       </c>
       <c r="R151" t="n">
-        <v>6818159</v>
+        <v>6818056</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17141,7 +17141,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128927798</v>
+        <v>128927828</v>
       </c>
       <c r="B167" t="n">
         <v>78882</v>
@@ -17170,16 +17170,19 @@
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430315</v>
+        <v>430115</v>
       </c>
       <c r="R167" t="n">
-        <v>6818095</v>
+        <v>6817902</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17220,6 +17223,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17238,7 +17242,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128927828</v>
+        <v>128927798</v>
       </c>
       <c r="B168" t="n">
         <v>78882</v>
@@ -17267,19 +17271,16 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430115</v>
+        <v>430315</v>
       </c>
       <c r="R168" t="n">
-        <v>6817902</v>
+        <v>6818095</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17320,7 +17321,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17339,10 +17339,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128927829</v>
+        <v>128927933</v>
       </c>
       <c r="B169" t="n">
-        <v>78882</v>
+        <v>79124</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17350,34 +17350,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>430138</v>
+        <v>430220</v>
       </c>
       <c r="R169" t="n">
-        <v>6817883</v>
+        <v>6818148</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17412,12 +17415,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -17436,10 +17445,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128927737</v>
+        <v>128927981</v>
       </c>
       <c r="B170" t="n">
-        <v>79743</v>
+        <v>78096</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17447,37 +17456,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430143</v>
+        <v>430056</v>
       </c>
       <c r="R170" t="n">
-        <v>6817831</v>
+        <v>6818166</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17518,7 +17524,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -17537,32 +17542,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128927981</v>
+        <v>128927835</v>
       </c>
       <c r="B171" t="n">
-        <v>78096</v>
+        <v>58090</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6487</v>
+        <v>103015</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17572,10 +17577,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430056</v>
+        <v>430104</v>
       </c>
       <c r="R171" t="n">
-        <v>6818166</v>
+        <v>6817960</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17634,10 +17639,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128927712</v>
+        <v>128927829</v>
       </c>
       <c r="B172" t="n">
-        <v>79743</v>
+        <v>78882</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17645,21 +17650,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17669,10 +17674,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430596</v>
+        <v>430138</v>
       </c>
       <c r="R172" t="n">
-        <v>6818190</v>
+        <v>6817883</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17731,10 +17736,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128927933</v>
+        <v>128927737</v>
       </c>
       <c r="B173" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17742,21 +17747,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17769,10 +17774,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430220</v>
+        <v>430143</v>
       </c>
       <c r="R173" t="n">
-        <v>6818148</v>
+        <v>6817831</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17805,11 +17810,6 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -17934,32 +17934,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128927835</v>
+        <v>128927712</v>
       </c>
       <c r="B175" t="n">
-        <v>58090</v>
+        <v>79743</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17969,10 +17969,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430104</v>
+        <v>430596</v>
       </c>
       <c r="R175" t="n">
-        <v>6817960</v>
+        <v>6818190</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18031,10 +18031,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128927723</v>
+        <v>128927812</v>
       </c>
       <c r="B176" t="n">
-        <v>79743</v>
+        <v>78882</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18042,21 +18042,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18066,10 +18066,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>429993</v>
+        <v>430157</v>
       </c>
       <c r="R176" t="n">
-        <v>6818157</v>
+        <v>6818149</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18128,10 +18128,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128927848</v>
+        <v>128927750</v>
       </c>
       <c r="B177" t="n">
-        <v>78881</v>
+        <v>79714</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18139,21 +18139,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18163,10 +18163,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430174</v>
+        <v>430140</v>
       </c>
       <c r="R177" t="n">
-        <v>6818156</v>
+        <v>6817881</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18225,10 +18225,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128927898</v>
+        <v>128927741</v>
       </c>
       <c r="B178" t="n">
-        <v>79124</v>
+        <v>79714</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18236,21 +18236,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18260,10 +18260,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430384</v>
+        <v>430600</v>
       </c>
       <c r="R178" t="n">
-        <v>6818048</v>
+        <v>6818203</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18322,7 +18322,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128927968</v>
+        <v>128927898</v>
       </c>
       <c r="B179" t="n">
         <v>79124</v>
@@ -18357,10 +18357,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430067</v>
+        <v>430384</v>
       </c>
       <c r="R179" t="n">
-        <v>6818139</v>
+        <v>6818048</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18613,53 +18613,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128927760</v>
+        <v>128927723</v>
       </c>
       <c r="B182" t="n">
-        <v>56910</v>
+        <v>79743</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430663</v>
+        <v>429993</v>
       </c>
       <c r="R182" t="n">
-        <v>6818259</v>
+        <v>6818157</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18718,53 +18710,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128927762</v>
+        <v>128927848</v>
       </c>
       <c r="B183" t="n">
-        <v>56910</v>
+        <v>78881</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430394</v>
+        <v>430174</v>
       </c>
       <c r="R183" t="n">
-        <v>6818168</v>
+        <v>6818156</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18823,10 +18807,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128927750</v>
+        <v>128927968</v>
       </c>
       <c r="B184" t="n">
-        <v>79714</v>
+        <v>79124</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18834,21 +18818,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18858,10 +18842,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430140</v>
+        <v>430067</v>
       </c>
       <c r="R184" t="n">
-        <v>6817881</v>
+        <v>6818139</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18920,45 +18904,53 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128927741</v>
+        <v>128927760</v>
       </c>
       <c r="B185" t="n">
-        <v>79714</v>
+        <v>56910</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430600</v>
+        <v>430663</v>
       </c>
       <c r="R185" t="n">
-        <v>6818203</v>
+        <v>6818259</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19017,45 +19009,53 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128927812</v>
+        <v>128927762</v>
       </c>
       <c r="B186" t="n">
-        <v>78882</v>
+        <v>56910</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430157</v>
+        <v>430394</v>
       </c>
       <c r="R186" t="n">
-        <v>6818149</v>
+        <v>6818168</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19114,10 +19114,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128927731</v>
+        <v>128927910</v>
       </c>
       <c r="B187" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19125,21 +19125,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19149,10 +19149,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430056</v>
+        <v>430430</v>
       </c>
       <c r="R187" t="n">
-        <v>6818017</v>
+        <v>6818202</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19211,10 +19211,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128927847</v>
+        <v>128927892</v>
       </c>
       <c r="B188" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19222,21 +19222,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19246,10 +19246,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430227</v>
+        <v>430304</v>
       </c>
       <c r="R188" t="n">
-        <v>6818154</v>
+        <v>6818124</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19308,10 +19308,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128927872</v>
+        <v>128927906</v>
       </c>
       <c r="B189" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19319,34 +19319,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430227</v>
+        <v>430401</v>
       </c>
       <c r="R189" t="n">
-        <v>6818015</v>
+        <v>6818157</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19381,12 +19384,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
+        </is>
+      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -19405,10 +19414,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128927728</v>
+        <v>128927922</v>
       </c>
       <c r="B190" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19416,21 +19425,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19440,10 +19449,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430232</v>
+        <v>430668</v>
       </c>
       <c r="R190" t="n">
-        <v>6818068</v>
+        <v>6818241</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19502,7 +19511,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128927910</v>
+        <v>128927962</v>
       </c>
       <c r="B191" t="n">
         <v>79124</v>
@@ -19537,10 +19546,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430430</v>
+        <v>430069</v>
       </c>
       <c r="R191" t="n">
-        <v>6818202</v>
+        <v>6818225</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19599,10 +19608,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128927892</v>
+        <v>128927820</v>
       </c>
       <c r="B192" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19610,21 +19619,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19634,10 +19643,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430304</v>
+        <v>430014</v>
       </c>
       <c r="R192" t="n">
-        <v>6818124</v>
+        <v>6818142</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19696,10 +19705,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128927906</v>
+        <v>128927818</v>
       </c>
       <c r="B193" t="n">
-        <v>79124</v>
+        <v>78882</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19707,37 +19716,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430401</v>
+        <v>430048</v>
       </c>
       <c r="R193" t="n">
-        <v>6818157</v>
+        <v>6818123</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19772,18 +19778,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -19802,10 +19802,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128927922</v>
+        <v>128927731</v>
       </c>
       <c r="B194" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19813,21 +19813,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19837,10 +19837,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430668</v>
+        <v>430056</v>
       </c>
       <c r="R194" t="n">
-        <v>6818241</v>
+        <v>6818017</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19899,10 +19899,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128927962</v>
+        <v>128927847</v>
       </c>
       <c r="B195" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19910,21 +19910,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19934,10 +19934,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430069</v>
+        <v>430227</v>
       </c>
       <c r="R195" t="n">
-        <v>6818225</v>
+        <v>6818154</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19996,10 +19996,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128927789</v>
+        <v>128927872</v>
       </c>
       <c r="B196" t="n">
-        <v>57717</v>
+        <v>78881</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20007,42 +20007,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430089</v>
+        <v>430227</v>
       </c>
       <c r="R196" t="n">
-        <v>6817965</v>
+        <v>6818015</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20075,11 +20067,6 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20106,10 +20093,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128927820</v>
+        <v>128927728</v>
       </c>
       <c r="B197" t="n">
-        <v>78882</v>
+        <v>79743</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20117,21 +20104,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20141,10 +20128,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430014</v>
+        <v>430232</v>
       </c>
       <c r="R197" t="n">
-        <v>6818142</v>
+        <v>6818068</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20203,10 +20190,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128927818</v>
+        <v>128927789</v>
       </c>
       <c r="B198" t="n">
-        <v>78882</v>
+        <v>57717</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20214,34 +20201,42 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430048</v>
+        <v>430089</v>
       </c>
       <c r="R198" t="n">
-        <v>6818123</v>
+        <v>6817965</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20274,6 +20269,11 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20300,10 +20300,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128927841</v>
+        <v>128927913</v>
       </c>
       <c r="B199" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20311,21 +20311,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20335,10 +20335,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430569</v>
+        <v>430484</v>
       </c>
       <c r="R199" t="n">
-        <v>6818243</v>
+        <v>6818253</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20397,10 +20397,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128927755</v>
+        <v>128927936</v>
       </c>
       <c r="B200" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20408,42 +20408,34 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430480</v>
+        <v>430084</v>
       </c>
       <c r="R200" t="n">
-        <v>6818068</v>
+        <v>6818157</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20502,10 +20494,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128927717</v>
+        <v>128927961</v>
       </c>
       <c r="B201" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20513,21 +20505,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20537,10 +20529,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430214</v>
+        <v>430086</v>
       </c>
       <c r="R201" t="n">
-        <v>6817971</v>
+        <v>6818236</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20599,10 +20591,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128927715</v>
+        <v>128927942</v>
       </c>
       <c r="B202" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20610,21 +20602,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20634,10 +20626,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430650</v>
+        <v>430087</v>
       </c>
       <c r="R202" t="n">
-        <v>6818249</v>
+        <v>6817971</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20696,10 +20688,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128927913</v>
+        <v>128927841</v>
       </c>
       <c r="B203" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20707,21 +20699,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20731,10 +20723,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430484</v>
+        <v>430569</v>
       </c>
       <c r="R203" t="n">
-        <v>6818253</v>
+        <v>6818243</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20793,10 +20785,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128927936</v>
+        <v>128927717</v>
       </c>
       <c r="B204" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20804,21 +20796,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20828,10 +20820,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430084</v>
+        <v>430214</v>
       </c>
       <c r="R204" t="n">
-        <v>6818157</v>
+        <v>6817971</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20890,10 +20882,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128927961</v>
+        <v>128927715</v>
       </c>
       <c r="B205" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20901,21 +20893,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20925,10 +20917,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430086</v>
+        <v>430650</v>
       </c>
       <c r="R205" t="n">
-        <v>6818236</v>
+        <v>6818249</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20987,10 +20979,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128927942</v>
+        <v>128927755</v>
       </c>
       <c r="B206" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20998,34 +20990,42 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430087</v>
+        <v>430480</v>
       </c>
       <c r="R206" t="n">
-        <v>6817971</v>
+        <v>6818068</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21084,7 +21084,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128927809</v>
+        <v>128927816</v>
       </c>
       <c r="B207" t="n">
         <v>78882</v>
@@ -21119,10 +21119,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>430222</v>
+        <v>430086</v>
       </c>
       <c r="R207" t="n">
-        <v>6818155</v>
+        <v>6818278</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21278,7 +21278,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128927816</v>
+        <v>128927809</v>
       </c>
       <c r="B209" t="n">
         <v>78882</v>
@@ -21313,10 +21313,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>430086</v>
+        <v>430222</v>
       </c>
       <c r="R209" t="n">
-        <v>6818278</v>
+        <v>6818155</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21375,10 +21375,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128927860</v>
+        <v>128927941</v>
       </c>
       <c r="B210" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21386,21 +21386,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21410,10 +21410,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430013</v>
+        <v>430078</v>
       </c>
       <c r="R210" t="n">
-        <v>6818142</v>
+        <v>6817995</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21472,10 +21472,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128927866</v>
+        <v>128927960</v>
       </c>
       <c r="B211" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21483,21 +21483,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21507,10 +21507,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>429950</v>
+        <v>430089</v>
       </c>
       <c r="R211" t="n">
-        <v>6818057</v>
+        <v>6818238</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21569,10 +21569,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128927941</v>
+        <v>128927860</v>
       </c>
       <c r="B212" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21580,21 +21580,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21604,10 +21604,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430078</v>
+        <v>430013</v>
       </c>
       <c r="R212" t="n">
-        <v>6817995</v>
+        <v>6818142</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21666,10 +21666,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128927960</v>
+        <v>128927866</v>
       </c>
       <c r="B213" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21677,21 +21677,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21701,10 +21701,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>430089</v>
+        <v>429950</v>
       </c>
       <c r="R213" t="n">
-        <v>6818238</v>
+        <v>6818057</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21965,7 +21965,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128927808</v>
+        <v>128927817</v>
       </c>
       <c r="B216" t="n">
         <v>78882</v>
@@ -22000,10 +22000,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>430669</v>
+        <v>430068</v>
       </c>
       <c r="R216" t="n">
-        <v>6818242</v>
+        <v>6818152</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22062,7 +22062,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128927817</v>
+        <v>128927808</v>
       </c>
       <c r="B217" t="n">
         <v>78882</v>
@@ -22097,10 +22097,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>430068</v>
+        <v>430669</v>
       </c>
       <c r="R217" t="n">
-        <v>6818152</v>
+        <v>6818242</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22547,10 +22547,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128927771</v>
+        <v>128927867</v>
       </c>
       <c r="B222" t="n">
-        <v>57717</v>
+        <v>78881</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22558,42 +22558,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430658</v>
+        <v>430006</v>
       </c>
       <c r="R222" t="n">
-        <v>6818274</v>
+        <v>6818034</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22652,10 +22644,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128927867</v>
+        <v>128927771</v>
       </c>
       <c r="B223" t="n">
-        <v>78881</v>
+        <v>57717</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22663,34 +22655,42 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430006</v>
+        <v>430658</v>
       </c>
       <c r="R223" t="n">
-        <v>6818034</v>
+        <v>6818274</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22850,10 +22850,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128927850</v>
+        <v>128927890</v>
       </c>
       <c r="B225" t="n">
-        <v>78881</v>
+        <v>79124</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22861,21 +22861,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22885,10 +22885,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430159</v>
+        <v>430348</v>
       </c>
       <c r="R225" t="n">
-        <v>6818161</v>
+        <v>6818167</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22947,10 +22947,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128927730</v>
+        <v>128927915</v>
       </c>
       <c r="B226" t="n">
-        <v>79743</v>
+        <v>79124</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22958,34 +22958,37 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430075</v>
+        <v>430575</v>
       </c>
       <c r="R226" t="n">
-        <v>6818213</v>
+        <v>6818234</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23026,6 +23029,7 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
+      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
@@ -23044,7 +23048,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128927890</v>
+        <v>128927923</v>
       </c>
       <c r="B227" t="n">
         <v>79124</v>
@@ -23079,10 +23083,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430348</v>
+        <v>430670</v>
       </c>
       <c r="R227" t="n">
-        <v>6818167</v>
+        <v>6818263</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23141,10 +23145,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128927915</v>
+        <v>128927850</v>
       </c>
       <c r="B228" t="n">
-        <v>79124</v>
+        <v>78881</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23152,37 +23156,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430575</v>
+        <v>430159</v>
       </c>
       <c r="R228" t="n">
-        <v>6818234</v>
+        <v>6818161</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23223,7 +23224,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -23242,10 +23242,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128927923</v>
+        <v>128927730</v>
       </c>
       <c r="B229" t="n">
-        <v>79124</v>
+        <v>79743</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23253,21 +23253,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23277,10 +23277,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430670</v>
+        <v>430075</v>
       </c>
       <c r="R229" t="n">
-        <v>6818263</v>
+        <v>6818213</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2854,7 +2854,7 @@
         <v>128927950</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927880</v>
+        <v>128927978</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430577</v>
+        <v>430082</v>
       </c>
       <c r="R23" t="n">
-        <v>6818221</v>
+        <v>6818210</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3027,6 +3027,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3045,10 +3046,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927978</v>
+        <v>128927935</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,10 +3081,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430082</v>
+        <v>430099</v>
       </c>
       <c r="R24" t="n">
-        <v>6818210</v>
+        <v>6818154</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3125,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3143,32 +3143,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927935</v>
+        <v>128927834</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>58093</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430099</v>
+        <v>430596</v>
       </c>
       <c r="R25" t="n">
-        <v>6818154</v>
+        <v>6818184</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,10 +3240,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927963</v>
+        <v>128927821</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430064</v>
+        <v>429994</v>
       </c>
       <c r="R26" t="n">
-        <v>6818190</v>
+        <v>6818158</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927732</v>
+        <v>128927802</v>
       </c>
       <c r="B27" t="n">
-        <v>79743</v>
+        <v>78787</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430138</v>
+        <v>430567</v>
       </c>
       <c r="R27" t="n">
-        <v>6817883</v>
+        <v>6818243</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927868</v>
+        <v>128927732</v>
       </c>
       <c r="B28" t="n">
-        <v>78881</v>
+        <v>79648</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430089</v>
+        <v>430138</v>
       </c>
       <c r="R28" t="n">
-        <v>6817984</v>
+        <v>6817883</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927843</v>
+        <v>128927868</v>
       </c>
       <c r="B29" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430626</v>
+        <v>430089</v>
       </c>
       <c r="R29" t="n">
-        <v>6818202</v>
+        <v>6817984</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927721</v>
+        <v>128927843</v>
       </c>
       <c r="B30" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430060</v>
+        <v>430626</v>
       </c>
       <c r="R30" t="n">
-        <v>6818156</v>
+        <v>6818202</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927726</v>
+        <v>128927721</v>
       </c>
       <c r="B31" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430114</v>
+        <v>430060</v>
       </c>
       <c r="R31" t="n">
-        <v>6817912</v>
+        <v>6818156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128927770</v>
+        <v>128927726</v>
       </c>
       <c r="B32" t="n">
-        <v>57717</v>
+        <v>79648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3833,42 +3833,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430455</v>
+        <v>430114</v>
       </c>
       <c r="R32" t="n">
-        <v>6818246</v>
+        <v>6817912</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,27 +3919,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128927834</v>
+        <v>128927770</v>
       </c>
       <c r="B33" t="n">
-        <v>58090</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3956,16 +3948,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>430596</v>
+        <v>430455</v>
       </c>
       <c r="R33" t="n">
-        <v>6818184</v>
+        <v>6818246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128927821</v>
+        <v>128927880</v>
       </c>
       <c r="B34" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>429994</v>
+        <v>430577</v>
       </c>
       <c r="R34" t="n">
-        <v>6818158</v>
+        <v>6818221</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128927802</v>
+        <v>128927963</v>
       </c>
       <c r="B35" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4132,21 +4132,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430567</v>
+        <v>430064</v>
       </c>
       <c r="R35" t="n">
-        <v>6818243</v>
+        <v>6818190</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128927939</v>
+        <v>128927743</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>429903</v>
+        <v>430211</v>
       </c>
       <c r="R36" t="n">
-        <v>6818059</v>
+        <v>6817980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128927895</v>
+        <v>128927813</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4326,21 +4326,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>430350</v>
+        <v>430145</v>
       </c>
       <c r="R37" t="n">
-        <v>6818053</v>
+        <v>6818165</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128927871</v>
+        <v>128927895</v>
       </c>
       <c r="B38" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4423,21 +4423,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430145</v>
+        <v>430350</v>
       </c>
       <c r="R38" t="n">
-        <v>6817833</v>
+        <v>6818053</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4509,10 +4509,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128927973</v>
+        <v>128927939</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4538,19 +4538,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430073</v>
+        <v>429903</v>
       </c>
       <c r="R39" t="n">
-        <v>6818021</v>
+        <v>6818059</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,7 +4588,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4610,10 +4606,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128927773</v>
+        <v>128927973</v>
       </c>
       <c r="B40" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,31 +4617,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4653,10 +4644,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>430251</v>
+        <v>430073</v>
       </c>
       <c r="R40" t="n">
-        <v>6818033</v>
+        <v>6818021</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4697,6 +4688,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4715,10 +4707,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128927813</v>
+        <v>128927871</v>
       </c>
       <c r="B41" t="n">
-        <v>78882</v>
+        <v>78786</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4718,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4753,7 +4745,7 @@
         <v>430145</v>
       </c>
       <c r="R41" t="n">
-        <v>6818165</v>
+        <v>6817833</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4812,10 +4804,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128927743</v>
+        <v>128927773</v>
       </c>
       <c r="B42" t="n">
-        <v>79714</v>
+        <v>57720</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,34 +4815,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>430211</v>
+        <v>430251</v>
       </c>
       <c r="R42" t="n">
-        <v>6817980</v>
+        <v>6818033</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4912,7 +4912,7 @@
         <v>128927930</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128927928</v>
+        <v>128927786</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,34 +5017,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430293</v>
+        <v>430078</v>
       </c>
       <c r="R44" t="n">
-        <v>6817871</v>
+        <v>6818213</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5077,6 +5085,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5103,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128927934</v>
+        <v>128927928</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5138,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430088</v>
+        <v>430293</v>
       </c>
       <c r="R45" t="n">
-        <v>6818186</v>
+        <v>6817871</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5200,10 +5213,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128927938</v>
+        <v>128927934</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5235,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>429959</v>
+        <v>430088</v>
       </c>
       <c r="R46" t="n">
-        <v>6818128</v>
+        <v>6818186</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,10 +5310,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128927976</v>
+        <v>128927938</v>
       </c>
       <c r="B47" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5326,19 +5339,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430149</v>
+        <v>429959</v>
       </c>
       <c r="R47" t="n">
-        <v>6817860</v>
+        <v>6818128</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5379,7 +5389,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5398,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128927966</v>
+        <v>128927976</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5427,16 +5436,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430071</v>
+        <v>430149</v>
       </c>
       <c r="R48" t="n">
-        <v>6818124</v>
+        <v>6817860</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5477,6 +5489,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5495,10 +5508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128927845</v>
+        <v>128927966</v>
       </c>
       <c r="B49" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5506,21 +5519,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5530,10 +5543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430669</v>
+        <v>430071</v>
       </c>
       <c r="R49" t="n">
-        <v>6818249</v>
+        <v>6818124</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5592,10 +5605,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128927842</v>
+        <v>128927845</v>
       </c>
       <c r="B50" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5627,10 +5640,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430596</v>
+        <v>430669</v>
       </c>
       <c r="R50" t="n">
-        <v>6818186</v>
+        <v>6818249</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5689,10 +5702,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128927786</v>
+        <v>128927842</v>
       </c>
       <c r="B51" t="n">
-        <v>57717</v>
+        <v>78786</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,42 +5713,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430078</v>
+        <v>430596</v>
       </c>
       <c r="R51" t="n">
-        <v>6818213</v>
+        <v>6818186</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5768,11 +5773,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5802,7 +5802,7 @@
         <v>128927805</v>
       </c>
       <c r="B52" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>128927819</v>
       </c>
       <c r="B53" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5993,10 +5993,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128927806</v>
+        <v>128927799</v>
       </c>
       <c r="B54" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>430655</v>
+        <v>430396</v>
       </c>
       <c r="R54" t="n">
-        <v>6818264</v>
+        <v>6818052</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,10 +6090,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128927799</v>
+        <v>128927806</v>
       </c>
       <c r="B55" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>430396</v>
+        <v>430655</v>
       </c>
       <c r="R55" t="n">
-        <v>6818052</v>
+        <v>6818264</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6187,10 +6187,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128927874</v>
+        <v>128927937</v>
       </c>
       <c r="B56" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>430154</v>
+        <v>430011</v>
       </c>
       <c r="R56" t="n">
-        <v>6817859</v>
+        <v>6818137</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128927735</v>
+        <v>128927970</v>
       </c>
       <c r="B57" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6295,21 +6295,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>430132</v>
+        <v>429900</v>
       </c>
       <c r="R57" t="n">
-        <v>6817858</v>
+        <v>6818098</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6355,6 +6355,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,10 +6386,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128927855</v>
+        <v>128927944</v>
       </c>
       <c r="B58" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,34 +6397,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430113</v>
+        <v>430531</v>
       </c>
       <c r="R58" t="n">
-        <v>6818160</v>
+        <v>6818016</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6460,6 +6468,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6478,10 +6487,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927937</v>
+        <v>128927948</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430011</v>
+        <v>430655</v>
       </c>
       <c r="R59" t="n">
-        <v>6818137</v>
+        <v>6818216</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6575,10 +6584,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927970</v>
+        <v>128927882</v>
       </c>
       <c r="B60" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6610,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>429900</v>
+        <v>430526</v>
       </c>
       <c r="R60" t="n">
-        <v>6818098</v>
+        <v>6818232</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6646,11 +6655,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6677,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128927944</v>
+        <v>128927929</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6706,19 +6710,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430531</v>
+        <v>430208</v>
       </c>
       <c r="R61" t="n">
-        <v>6818016</v>
+        <v>6817816</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6759,7 +6760,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128927948</v>
+        <v>128927874</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430655</v>
+        <v>430154</v>
       </c>
       <c r="R62" t="n">
-        <v>6818216</v>
+        <v>6817859</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6875,10 +6875,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128927882</v>
+        <v>128927735</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6886,21 +6886,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430526</v>
+        <v>430132</v>
       </c>
       <c r="R63" t="n">
-        <v>6818232</v>
+        <v>6817858</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6972,10 +6972,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128927929</v>
+        <v>128927855</v>
       </c>
       <c r="B64" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430208</v>
+        <v>430113</v>
       </c>
       <c r="R64" t="n">
-        <v>6817816</v>
+        <v>6818160</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7072,7 +7072,7 @@
         <v>128927815</v>
       </c>
       <c r="B65" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>128927893</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>128927974</v>
       </c>
       <c r="B67" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128927790</v>
+        <v>128927825</v>
       </c>
       <c r="B68" t="n">
-        <v>57717</v>
+        <v>78787</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7371,42 +7371,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430130</v>
+        <v>430024</v>
       </c>
       <c r="R68" t="n">
-        <v>6817856</v>
+        <v>6818040</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7465,7 +7457,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128927751</v>
+        <v>128927790</v>
       </c>
       <c r="B69" t="n">
         <v>57720</v>
@@ -7476,16 +7468,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7498,7 +7490,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -7508,10 +7500,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430337</v>
+        <v>430130</v>
       </c>
       <c r="R69" t="n">
-        <v>6818076</v>
+        <v>6817856</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,10 +7562,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128927825</v>
+        <v>128927751</v>
       </c>
       <c r="B70" t="n">
-        <v>78882</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7581,34 +7573,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>430024</v>
+        <v>430337</v>
       </c>
       <c r="R70" t="n">
-        <v>6818040</v>
+        <v>6818076</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7670,7 +7670,7 @@
         <v>128927710</v>
       </c>
       <c r="B71" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>128927839</v>
       </c>
       <c r="B72" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>128927857</v>
       </c>
       <c r="B73" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>128927852</v>
       </c>
       <c r="B74" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>128927831</v>
       </c>
       <c r="B75" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128927840</v>
+        <v>128927924</v>
       </c>
       <c r="B76" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8167,21 +8167,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430407</v>
+        <v>430671</v>
       </c>
       <c r="R76" t="n">
-        <v>6818114</v>
+        <v>6818266</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128927865</v>
+        <v>128927964</v>
       </c>
       <c r="B77" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>429935</v>
+        <v>430099</v>
       </c>
       <c r="R77" t="n">
-        <v>6818065</v>
+        <v>6818174</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8350,10 +8350,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128927964</v>
+        <v>128927897</v>
       </c>
       <c r="B78" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430099</v>
+        <v>430386</v>
       </c>
       <c r="R78" t="n">
-        <v>6818174</v>
+        <v>6818039</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128927725</v>
+        <v>128927955</v>
       </c>
       <c r="B79" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8458,34 +8458,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430040</v>
+        <v>430129</v>
       </c>
       <c r="R79" t="n">
-        <v>6818029</v>
+        <v>6818156</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8520,12 +8523,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30 m</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8544,10 +8553,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128927811</v>
+        <v>128927905</v>
       </c>
       <c r="B80" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8555,21 +8564,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8579,10 +8588,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430176</v>
+        <v>430395</v>
       </c>
       <c r="R80" t="n">
-        <v>6818150</v>
+        <v>6818138</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8641,10 +8650,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128927795</v>
+        <v>128927885</v>
       </c>
       <c r="B81" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8652,21 +8661,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8676,10 +8685,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430390</v>
+        <v>430366</v>
       </c>
       <c r="R81" t="n">
-        <v>6818205</v>
+        <v>6818264</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8738,10 +8747,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128927832</v>
+        <v>128927947</v>
       </c>
       <c r="B82" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8749,21 +8758,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8773,10 +8782,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430153</v>
+        <v>430568</v>
       </c>
       <c r="R82" t="n">
-        <v>6817822</v>
+        <v>6818235</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8809,6 +8818,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8835,10 +8849,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128927924</v>
+        <v>128927912</v>
       </c>
       <c r="B83" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8870,10 +8884,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430671</v>
+        <v>430439</v>
       </c>
       <c r="R83" t="n">
-        <v>6818266</v>
+        <v>6818230</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8932,10 +8946,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128927897</v>
+        <v>128927840</v>
       </c>
       <c r="B84" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8943,21 +8957,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8967,10 +8981,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430386</v>
+        <v>430407</v>
       </c>
       <c r="R84" t="n">
-        <v>6818039</v>
+        <v>6818114</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9029,10 +9043,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128927955</v>
+        <v>128927865</v>
       </c>
       <c r="B85" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9040,37 +9054,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>430129</v>
+        <v>429935</v>
       </c>
       <c r="R85" t="n">
-        <v>6818156</v>
+        <v>6818065</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9105,18 +9116,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30 m</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9135,10 +9140,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128927905</v>
+        <v>128927725</v>
       </c>
       <c r="B86" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9146,21 +9151,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9170,10 +9175,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430395</v>
+        <v>430040</v>
       </c>
       <c r="R86" t="n">
-        <v>6818138</v>
+        <v>6818029</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9232,10 +9237,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128927885</v>
+        <v>128927795</v>
       </c>
       <c r="B87" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9243,21 +9248,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9267,10 +9272,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>430366</v>
+        <v>430390</v>
       </c>
       <c r="R87" t="n">
-        <v>6818264</v>
+        <v>6818205</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9329,10 +9334,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128927947</v>
+        <v>128927811</v>
       </c>
       <c r="B88" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9340,21 +9345,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9364,10 +9369,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>430568</v>
+        <v>430176</v>
       </c>
       <c r="R88" t="n">
-        <v>6818235</v>
+        <v>6818150</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9400,11 +9405,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9431,10 +9431,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128927912</v>
+        <v>128927832</v>
       </c>
       <c r="B89" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>430439</v>
+        <v>430153</v>
       </c>
       <c r="R89" t="n">
-        <v>6818230</v>
+        <v>6817822</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9528,10 +9528,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128927980</v>
+        <v>128927891</v>
       </c>
       <c r="B90" t="n">
-        <v>78096</v>
+        <v>79029</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9539,21 +9539,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>430081</v>
+        <v>430336</v>
       </c>
       <c r="R90" t="n">
-        <v>6818119</v>
+        <v>6818151</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128927891</v>
+        <v>128927884</v>
       </c>
       <c r="B91" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430336</v>
+        <v>430423</v>
       </c>
       <c r="R91" t="n">
-        <v>6818151</v>
+        <v>6818270</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128927884</v>
+        <v>128927965</v>
       </c>
       <c r="B92" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430423</v>
+        <v>430115</v>
       </c>
       <c r="R92" t="n">
-        <v>6818270</v>
+        <v>6818177</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128927965</v>
+        <v>128927932</v>
       </c>
       <c r="B93" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9848,16 +9848,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430115</v>
+        <v>430240</v>
       </c>
       <c r="R93" t="n">
-        <v>6818177</v>
+        <v>6817987</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9892,12 +9895,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9919,7 +9928,7 @@
         <v>128927975</v>
       </c>
       <c r="B94" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10016,7 +10025,7 @@
         <v>128927943</v>
       </c>
       <c r="B95" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10110,10 +10119,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128927864</v>
+        <v>128927980</v>
       </c>
       <c r="B96" t="n">
-        <v>78881</v>
+        <v>78037</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10121,21 +10130,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10145,10 +10154,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>429975</v>
+        <v>430081</v>
       </c>
       <c r="R96" t="n">
-        <v>6818158</v>
+        <v>6818119</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10207,10 +10216,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128927714</v>
+        <v>128927864</v>
       </c>
       <c r="B97" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10218,21 +10227,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10242,10 +10251,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430630</v>
+        <v>429975</v>
       </c>
       <c r="R97" t="n">
-        <v>6818207</v>
+        <v>6818158</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10304,10 +10313,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128927932</v>
+        <v>128927714</v>
       </c>
       <c r="B98" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10315,37 +10324,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430240</v>
+        <v>430630</v>
       </c>
       <c r="R98" t="n">
-        <v>6817987</v>
+        <v>6818207</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10380,18 +10386,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>128927851</v>
       </c>
       <c r="B99" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10507,10 +10507,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128927803</v>
+        <v>128927810</v>
       </c>
       <c r="B100" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430580</v>
+        <v>430215</v>
       </c>
       <c r="R100" t="n">
-        <v>6818253</v>
+        <v>6818155</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10604,10 +10604,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128927810</v>
+        <v>128927803</v>
       </c>
       <c r="B101" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>430215</v>
+        <v>430580</v>
       </c>
       <c r="R101" t="n">
-        <v>6818155</v>
+        <v>6818253</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10704,7 +10704,7 @@
         <v>128927794</v>
       </c>
       <c r="B102" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927793</v>
+        <v>128927899</v>
       </c>
       <c r="B103" t="n">
-        <v>58150</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430104</v>
+        <v>430428</v>
       </c>
       <c r="R103" t="n">
-        <v>6817933</v>
+        <v>6818038</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927796</v>
+        <v>128927954</v>
       </c>
       <c r="B104" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10906,34 +10906,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430323</v>
+        <v>430166</v>
       </c>
       <c r="R104" t="n">
-        <v>6818121</v>
+        <v>6818134</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10968,12 +10971,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -10992,10 +11001,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927826</v>
+        <v>128927888</v>
       </c>
       <c r="B105" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11003,21 +11012,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11027,10 +11036,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430018</v>
+        <v>430399</v>
       </c>
       <c r="R105" t="n">
-        <v>6818046</v>
+        <v>6818238</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11089,10 +11098,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927822</v>
+        <v>128927971</v>
       </c>
       <c r="B106" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11100,21 +11109,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11124,10 +11133,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>429973</v>
+        <v>429925</v>
       </c>
       <c r="R106" t="n">
-        <v>6818162</v>
+        <v>6818065</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11186,10 +11195,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927827</v>
+        <v>128927949</v>
       </c>
       <c r="B107" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11197,21 +11206,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11221,10 +11230,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430057</v>
+        <v>430653</v>
       </c>
       <c r="R107" t="n">
-        <v>6818016</v>
+        <v>6818272</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11283,10 +11292,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927899</v>
+        <v>128927793</v>
       </c>
       <c r="B108" t="n">
-        <v>79124</v>
+        <v>58153</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11294,21 +11303,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11318,10 +11327,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430428</v>
+        <v>430104</v>
       </c>
       <c r="R108" t="n">
-        <v>6818038</v>
+        <v>6817933</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11380,10 +11389,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927954</v>
+        <v>128927827</v>
       </c>
       <c r="B109" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11391,37 +11400,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430166</v>
+        <v>430057</v>
       </c>
       <c r="R109" t="n">
-        <v>6818134</v>
+        <v>6818016</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11456,18 +11462,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11486,10 +11486,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128927888</v>
+        <v>128927822</v>
       </c>
       <c r="B110" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11497,21 +11497,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430399</v>
+        <v>429973</v>
       </c>
       <c r="R110" t="n">
-        <v>6818238</v>
+        <v>6818162</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11583,10 +11583,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927971</v>
+        <v>128927826</v>
       </c>
       <c r="B111" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11594,21 +11594,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>429925</v>
+        <v>430018</v>
       </c>
       <c r="R111" t="n">
-        <v>6818065</v>
+        <v>6818046</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927949</v>
+        <v>128927796</v>
       </c>
       <c r="B112" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11691,21 +11691,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>430653</v>
+        <v>430323</v>
       </c>
       <c r="R112" t="n">
-        <v>6818272</v>
+        <v>6818121</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,32 +11777,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927856</v>
+        <v>128927836</v>
       </c>
       <c r="B113" t="n">
-        <v>78881</v>
+        <v>58093</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430060</v>
+        <v>430147</v>
       </c>
       <c r="R113" t="n">
-        <v>6818160</v>
+        <v>6817817</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,32 +11874,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927836</v>
+        <v>128927856</v>
       </c>
       <c r="B114" t="n">
-        <v>58090</v>
+        <v>78786</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430147</v>
+        <v>430060</v>
       </c>
       <c r="R114" t="n">
-        <v>6817817</v>
+        <v>6818160</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128927823</v>
+        <v>128927901</v>
       </c>
       <c r="B115" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>429975</v>
+        <v>430501</v>
       </c>
       <c r="R115" t="n">
-        <v>6818162</v>
+        <v>6818013</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12071,7 +12071,7 @@
         <v>128927740</v>
       </c>
       <c r="B116" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128927901</v>
+        <v>128927823</v>
       </c>
       <c r="B117" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12176,21 +12176,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430501</v>
+        <v>429975</v>
       </c>
       <c r="R117" t="n">
-        <v>6818013</v>
+        <v>6818162</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,10 +12262,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128927921</v>
+        <v>128927870</v>
       </c>
       <c r="B118" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12273,21 +12273,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>430664</v>
+        <v>430164</v>
       </c>
       <c r="R118" t="n">
-        <v>6818275</v>
+        <v>6817854</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12359,10 +12359,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128927870</v>
+        <v>128927858</v>
       </c>
       <c r="B119" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12394,10 +12394,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>430164</v>
+        <v>430034</v>
       </c>
       <c r="R119" t="n">
-        <v>6817854</v>
+        <v>6818117</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12456,10 +12456,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128927858</v>
+        <v>128927873</v>
       </c>
       <c r="B120" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12491,10 +12491,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>430034</v>
+        <v>429998</v>
       </c>
       <c r="R120" t="n">
-        <v>6818117</v>
+        <v>6818047</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12553,10 +12553,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128927873</v>
+        <v>128927921</v>
       </c>
       <c r="B121" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12564,21 +12564,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12588,10 +12588,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>429998</v>
+        <v>430664</v>
       </c>
       <c r="R121" t="n">
-        <v>6818047</v>
+        <v>6818275</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128927953</v>
+        <v>128927769</v>
       </c>
       <c r="B122" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12661,26 +12661,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -12688,10 +12693,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>430242</v>
+        <v>430485</v>
       </c>
       <c r="R122" t="n">
-        <v>6818048</v>
+        <v>6818017</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12726,18 +12731,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12756,10 +12755,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128927907</v>
+        <v>128927953</v>
       </c>
       <c r="B123" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12785,16 +12784,19 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430394</v>
+        <v>430242</v>
       </c>
       <c r="R123" t="n">
-        <v>6818166</v>
+        <v>6818048</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12829,12 +12831,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -12853,10 +12861,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128927977</v>
+        <v>128927907</v>
       </c>
       <c r="B124" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12882,19 +12890,16 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430139</v>
+        <v>430394</v>
       </c>
       <c r="R124" t="n">
-        <v>6817862</v>
+        <v>6818166</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12935,7 +12940,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12954,10 +12958,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128927940</v>
+        <v>128927977</v>
       </c>
       <c r="B125" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12983,16 +12987,19 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>429952</v>
+        <v>430139</v>
       </c>
       <c r="R125" t="n">
-        <v>6818061</v>
+        <v>6817862</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13033,6 +13040,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13051,10 +13059,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128927918</v>
+        <v>128927940</v>
       </c>
       <c r="B126" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13086,10 +13094,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430649</v>
+        <v>429952</v>
       </c>
       <c r="R126" t="n">
-        <v>6818232</v>
+        <v>6818061</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13148,10 +13156,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128927878</v>
+        <v>128927918</v>
       </c>
       <c r="B127" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13183,10 +13191,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430632</v>
+        <v>430649</v>
       </c>
       <c r="R127" t="n">
-        <v>6818282</v>
+        <v>6818232</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13245,10 +13253,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128927908</v>
+        <v>128927878</v>
       </c>
       <c r="B128" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13280,10 +13288,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430425</v>
+        <v>430632</v>
       </c>
       <c r="R128" t="n">
-        <v>6818197</v>
+        <v>6818282</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,10 +13350,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128927886</v>
+        <v>128927908</v>
       </c>
       <c r="B129" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13377,10 +13385,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430424</v>
+        <v>430425</v>
       </c>
       <c r="R129" t="n">
-        <v>6818252</v>
+        <v>6818197</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,10 +13447,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128927869</v>
+        <v>128927886</v>
       </c>
       <c r="B130" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13450,21 +13458,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13474,10 +13482,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>430138</v>
+        <v>430424</v>
       </c>
       <c r="R130" t="n">
-        <v>6817883</v>
+        <v>6818252</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13536,10 +13544,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128927720</v>
+        <v>128927869</v>
       </c>
       <c r="B131" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13547,21 +13555,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13571,10 +13579,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430112</v>
+        <v>430138</v>
       </c>
       <c r="R131" t="n">
-        <v>6818160</v>
+        <v>6817883</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13633,10 +13641,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128927853</v>
+        <v>128927720</v>
       </c>
       <c r="B132" t="n">
-        <v>78881</v>
+        <v>79648</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13644,21 +13652,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13668,10 +13676,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430073</v>
+        <v>430112</v>
       </c>
       <c r="R132" t="n">
-        <v>6818201</v>
+        <v>6818160</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13730,10 +13738,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128927777</v>
+        <v>128927853</v>
       </c>
       <c r="B133" t="n">
-        <v>57717</v>
+        <v>78786</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13741,42 +13749,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>429898</v>
+        <v>430073</v>
       </c>
       <c r="R133" t="n">
-        <v>6818099</v>
+        <v>6818201</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13835,10 +13835,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128927784</v>
+        <v>128927777</v>
       </c>
       <c r="B134" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
@@ -13878,10 +13878,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430201</v>
+        <v>429898</v>
       </c>
       <c r="R134" t="n">
-        <v>6818093</v>
+        <v>6818099</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13940,10 +13940,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128927769</v>
+        <v>128927784</v>
       </c>
       <c r="B135" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -13983,10 +13983,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430485</v>
+        <v>430201</v>
       </c>
       <c r="R135" t="n">
-        <v>6818017</v>
+        <v>6818093</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14048,7 +14048,7 @@
         <v>128927894</v>
       </c>
       <c r="B136" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>128927900</v>
       </c>
       <c r="B137" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>128927889</v>
       </c>
       <c r="B138" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14345,10 +14345,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128927911</v>
+        <v>128927969</v>
       </c>
       <c r="B139" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14380,10 +14380,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430437</v>
+        <v>429947</v>
       </c>
       <c r="R139" t="n">
-        <v>6818227</v>
+        <v>6818135</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14442,10 +14442,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128927969</v>
+        <v>128927956</v>
       </c>
       <c r="B140" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14477,10 +14477,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>429947</v>
+        <v>430119</v>
       </c>
       <c r="R140" t="n">
-        <v>6818135</v>
+        <v>6818173</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14539,10 +14539,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128927956</v>
+        <v>128927925</v>
       </c>
       <c r="B141" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14574,10 +14574,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430119</v>
+        <v>430683</v>
       </c>
       <c r="R141" t="n">
-        <v>6818173</v>
+        <v>6818265</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14639,7 +14639,7 @@
         <v>128927972</v>
       </c>
       <c r="B142" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14737,10 +14737,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128927926</v>
+        <v>128927781</v>
       </c>
       <c r="B143" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14748,34 +14748,42 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430701</v>
+        <v>430480</v>
       </c>
       <c r="R143" t="n">
-        <v>6818261</v>
+        <v>6817997</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14834,10 +14842,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128927925</v>
+        <v>128927788</v>
       </c>
       <c r="B144" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14845,34 +14853,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430683</v>
+        <v>430017</v>
       </c>
       <c r="R144" t="n">
-        <v>6818265</v>
+        <v>6818044</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14931,10 +14947,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128927861</v>
+        <v>128927775</v>
       </c>
       <c r="B145" t="n">
-        <v>78881</v>
+        <v>57720</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14942,34 +14958,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>429989</v>
+        <v>430083</v>
       </c>
       <c r="R145" t="n">
-        <v>6818159</v>
+        <v>6818224</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15028,10 +15052,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128927781</v>
+        <v>128927792</v>
       </c>
       <c r="B146" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15061,7 +15085,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
@@ -15071,10 +15095,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430480</v>
+        <v>430150</v>
       </c>
       <c r="R146" t="n">
-        <v>6817997</v>
+        <v>6817814</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15133,10 +15157,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128927788</v>
+        <v>128927863</v>
       </c>
       <c r="B147" t="n">
-        <v>57717</v>
+        <v>78786</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15144,42 +15168,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430017</v>
+        <v>429970</v>
       </c>
       <c r="R147" t="n">
-        <v>6818044</v>
+        <v>6818162</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15238,10 +15254,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927775</v>
+        <v>128927911</v>
       </c>
       <c r="B148" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15249,42 +15265,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430083</v>
+        <v>430437</v>
       </c>
       <c r="R148" t="n">
-        <v>6818224</v>
+        <v>6818227</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15343,10 +15351,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927792</v>
+        <v>128927709</v>
       </c>
       <c r="B149" t="n">
-        <v>57717</v>
+        <v>79648</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15354,42 +15362,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430150</v>
+        <v>430495</v>
       </c>
       <c r="R149" t="n">
-        <v>6817814</v>
+        <v>6818056</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15448,10 +15448,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927863</v>
+        <v>128927861</v>
       </c>
       <c r="B150" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15483,10 +15483,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>429970</v>
+        <v>429989</v>
       </c>
       <c r="R150" t="n">
-        <v>6818162</v>
+        <v>6818159</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15545,10 +15545,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927709</v>
+        <v>128927926</v>
       </c>
       <c r="B151" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15556,21 +15556,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15580,10 +15580,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430495</v>
+        <v>430701</v>
       </c>
       <c r="R151" t="n">
-        <v>6818056</v>
+        <v>6818261</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15752,7 +15752,7 @@
         <v>128927824</v>
       </c>
       <c r="B153" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>128927748</v>
       </c>
       <c r="B154" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>128927917</v>
       </c>
       <c r="B155" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>128927903</v>
       </c>
       <c r="B156" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>128927920</v>
       </c>
       <c r="B157" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>128927951</v>
       </c>
       <c r="B158" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>128927958</v>
       </c>
       <c r="B159" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16446,10 +16446,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128927902</v>
+        <v>128927798</v>
       </c>
       <c r="B160" t="n">
-        <v>79124</v>
+        <v>78787</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16457,21 +16457,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16481,10 +16481,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430530</v>
+        <v>430315</v>
       </c>
       <c r="R160" t="n">
-        <v>6818025</v>
+        <v>6818095</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16543,10 +16543,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128927875</v>
+        <v>128927828</v>
       </c>
       <c r="B161" t="n">
-        <v>78881</v>
+        <v>78787</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16554,34 +16554,37 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430127</v>
+        <v>430115</v>
       </c>
       <c r="R161" t="n">
-        <v>6817846</v>
+        <v>6817902</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16622,6 +16625,7 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -16640,10 +16644,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128927838</v>
+        <v>128927875</v>
       </c>
       <c r="B162" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16675,10 +16679,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430439</v>
+        <v>430127</v>
       </c>
       <c r="R162" t="n">
-        <v>6818031</v>
+        <v>6817846</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16737,10 +16741,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128927837</v>
+        <v>128927838</v>
       </c>
       <c r="B163" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16772,10 +16776,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430360</v>
+        <v>430439</v>
       </c>
       <c r="R163" t="n">
-        <v>6818057</v>
+        <v>6818031</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16834,10 +16838,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128927846</v>
+        <v>128927837</v>
       </c>
       <c r="B164" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16869,10 +16873,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430241</v>
+        <v>430360</v>
       </c>
       <c r="R164" t="n">
-        <v>6818085</v>
+        <v>6818057</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16931,10 +16935,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128927779</v>
+        <v>128927846</v>
       </c>
       <c r="B165" t="n">
-        <v>57717</v>
+        <v>78786</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16942,42 +16946,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430106</v>
+        <v>430241</v>
       </c>
       <c r="R165" t="n">
-        <v>6817957</v>
+        <v>6818085</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17036,10 +17032,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128927783</v>
+        <v>128927902</v>
       </c>
       <c r="B166" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17047,42 +17043,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>430174</v>
+        <v>430530</v>
       </c>
       <c r="R166" t="n">
-        <v>6817923</v>
+        <v>6818025</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17141,10 +17129,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128927828</v>
+        <v>128927779</v>
       </c>
       <c r="B167" t="n">
-        <v>78882</v>
+        <v>57720</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17152,26 +17140,31 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
@@ -17179,10 +17172,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430115</v>
+        <v>430106</v>
       </c>
       <c r="R167" t="n">
-        <v>6817902</v>
+        <v>6817957</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17223,7 +17216,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17242,10 +17234,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128927798</v>
+        <v>128927783</v>
       </c>
       <c r="B168" t="n">
-        <v>78882</v>
+        <v>57720</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17253,34 +17245,42 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430315</v>
+        <v>430174</v>
       </c>
       <c r="R168" t="n">
-        <v>6818095</v>
+        <v>6817923</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17342,7 +17342,7 @@
         <v>128927933</v>
       </c>
       <c r="B169" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17445,10 +17445,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128927981</v>
+        <v>128927904</v>
       </c>
       <c r="B170" t="n">
-        <v>78096</v>
+        <v>79029</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17456,21 +17456,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17480,10 +17480,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430056</v>
+        <v>430405</v>
       </c>
       <c r="R170" t="n">
-        <v>6818166</v>
+        <v>6818117</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17542,45 +17542,48 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128927835</v>
+        <v>128927737</v>
       </c>
       <c r="B171" t="n">
-        <v>58090</v>
+        <v>79648</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430104</v>
+        <v>430143</v>
       </c>
       <c r="R171" t="n">
-        <v>6817960</v>
+        <v>6817831</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17621,6 +17624,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -17639,10 +17643,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128927829</v>
+        <v>128927981</v>
       </c>
       <c r="B172" t="n">
-        <v>78882</v>
+        <v>78037</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17650,21 +17654,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17674,10 +17678,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430138</v>
+        <v>430056</v>
       </c>
       <c r="R172" t="n">
-        <v>6817883</v>
+        <v>6818166</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17736,10 +17740,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128927737</v>
+        <v>128927712</v>
       </c>
       <c r="B173" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17765,19 +17769,16 @@
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430143</v>
+        <v>430596</v>
       </c>
       <c r="R173" t="n">
-        <v>6817831</v>
+        <v>6818190</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17818,7 +17819,6 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -17837,32 +17837,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128927904</v>
+        <v>128927835</v>
       </c>
       <c r="B174" t="n">
-        <v>79124</v>
+        <v>58093</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17872,10 +17872,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430405</v>
+        <v>430104</v>
       </c>
       <c r="R174" t="n">
-        <v>6818117</v>
+        <v>6817960</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17934,10 +17934,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128927712</v>
+        <v>128927829</v>
       </c>
       <c r="B175" t="n">
-        <v>79743</v>
+        <v>78787</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17945,21 +17945,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17969,10 +17969,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430596</v>
+        <v>430138</v>
       </c>
       <c r="R175" t="n">
-        <v>6818190</v>
+        <v>6817883</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18031,10 +18031,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128927812</v>
+        <v>128927898</v>
       </c>
       <c r="B176" t="n">
-        <v>78882</v>
+        <v>79029</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18042,21 +18042,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18066,10 +18066,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430157</v>
+        <v>430384</v>
       </c>
       <c r="R176" t="n">
-        <v>6818149</v>
+        <v>6818048</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18128,10 +18128,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128927750</v>
+        <v>128927968</v>
       </c>
       <c r="B177" t="n">
-        <v>79714</v>
+        <v>79029</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18139,21 +18139,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18163,10 +18163,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430140</v>
+        <v>430067</v>
       </c>
       <c r="R177" t="n">
-        <v>6817881</v>
+        <v>6818139</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18225,10 +18225,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128927741</v>
+        <v>128927952</v>
       </c>
       <c r="B178" t="n">
-        <v>79714</v>
+        <v>79029</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18236,21 +18236,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18260,10 +18260,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430600</v>
+        <v>430190</v>
       </c>
       <c r="R178" t="n">
-        <v>6818203</v>
+        <v>6817925</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18322,10 +18322,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128927898</v>
+        <v>128927945</v>
       </c>
       <c r="B179" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18357,10 +18357,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430384</v>
+        <v>430404</v>
       </c>
       <c r="R179" t="n">
-        <v>6818048</v>
+        <v>6818178</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18419,10 +18419,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128927952</v>
+        <v>128927723</v>
       </c>
       <c r="B180" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18430,21 +18430,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18454,10 +18454,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430190</v>
+        <v>429993</v>
       </c>
       <c r="R180" t="n">
-        <v>6817925</v>
+        <v>6818157</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18516,10 +18516,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128927945</v>
+        <v>128927848</v>
       </c>
       <c r="B181" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18527,21 +18527,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18551,10 +18551,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430404</v>
+        <v>430174</v>
       </c>
       <c r="R181" t="n">
-        <v>6818178</v>
+        <v>6818156</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18613,45 +18613,53 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128927723</v>
+        <v>128927762</v>
       </c>
       <c r="B182" t="n">
-        <v>79743</v>
+        <v>56913</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>429993</v>
+        <v>430394</v>
       </c>
       <c r="R182" t="n">
-        <v>6818157</v>
+        <v>6818168</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18710,45 +18718,53 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128927848</v>
+        <v>128927760</v>
       </c>
       <c r="B183" t="n">
-        <v>78881</v>
+        <v>56913</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430174</v>
+        <v>430663</v>
       </c>
       <c r="R183" t="n">
-        <v>6818156</v>
+        <v>6818259</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18807,10 +18823,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128927968</v>
+        <v>128927741</v>
       </c>
       <c r="B184" t="n">
-        <v>79124</v>
+        <v>79619</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18818,21 +18834,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18842,10 +18858,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430067</v>
+        <v>430600</v>
       </c>
       <c r="R184" t="n">
-        <v>6818139</v>
+        <v>6818203</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18904,53 +18920,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128927760</v>
+        <v>128927750</v>
       </c>
       <c r="B185" t="n">
-        <v>56910</v>
+        <v>79619</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430663</v>
+        <v>430140</v>
       </c>
       <c r="R185" t="n">
-        <v>6818259</v>
+        <v>6817881</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19009,53 +19017,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128927762</v>
+        <v>128927812</v>
       </c>
       <c r="B186" t="n">
-        <v>56910</v>
+        <v>78787</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430394</v>
+        <v>430157</v>
       </c>
       <c r="R186" t="n">
-        <v>6818168</v>
+        <v>6818149</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19117,7 +19117,7 @@
         <v>128927910</v>
       </c>
       <c r="B187" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>128927892</v>
       </c>
       <c r="B188" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>128927906</v>
       </c>
       <c r="B189" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>128927922</v>
       </c>
       <c r="B190" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>128927962</v>
       </c>
       <c r="B191" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19608,10 +19608,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128927820</v>
+        <v>128927789</v>
       </c>
       <c r="B192" t="n">
-        <v>78882</v>
+        <v>57720</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19619,34 +19619,42 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430014</v>
+        <v>430089</v>
       </c>
       <c r="R192" t="n">
-        <v>6818142</v>
+        <v>6817965</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19679,6 +19687,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -19705,10 +19718,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128927818</v>
+        <v>128927731</v>
       </c>
       <c r="B193" t="n">
-        <v>78882</v>
+        <v>79648</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19716,21 +19729,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19740,10 +19753,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430048</v>
+        <v>430056</v>
       </c>
       <c r="R193" t="n">
-        <v>6818123</v>
+        <v>6818017</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19802,10 +19815,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128927731</v>
+        <v>128927847</v>
       </c>
       <c r="B194" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19813,21 +19826,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19837,10 +19850,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430056</v>
+        <v>430227</v>
       </c>
       <c r="R194" t="n">
-        <v>6818017</v>
+        <v>6818154</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19899,10 +19912,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128927847</v>
+        <v>128927872</v>
       </c>
       <c r="B195" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19937,7 +19950,7 @@
         <v>430227</v>
       </c>
       <c r="R195" t="n">
-        <v>6818154</v>
+        <v>6818015</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19996,10 +20009,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128927872</v>
+        <v>128927728</v>
       </c>
       <c r="B196" t="n">
-        <v>78881</v>
+        <v>79648</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20007,21 +20020,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20031,10 +20044,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430227</v>
+        <v>430232</v>
       </c>
       <c r="R196" t="n">
-        <v>6818015</v>
+        <v>6818068</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20093,10 +20106,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128927728</v>
+        <v>128927820</v>
       </c>
       <c r="B197" t="n">
-        <v>79743</v>
+        <v>78787</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20104,21 +20117,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20128,10 +20141,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430232</v>
+        <v>430014</v>
       </c>
       <c r="R197" t="n">
-        <v>6818068</v>
+        <v>6818142</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20190,10 +20203,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128927789</v>
+        <v>128927818</v>
       </c>
       <c r="B198" t="n">
-        <v>57717</v>
+        <v>78787</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20201,42 +20214,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430089</v>
+        <v>430048</v>
       </c>
       <c r="R198" t="n">
-        <v>6817965</v>
+        <v>6818123</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20269,11 +20274,6 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20300,10 +20300,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128927913</v>
+        <v>128927755</v>
       </c>
       <c r="B199" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20311,34 +20311,42 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430484</v>
+        <v>430480</v>
       </c>
       <c r="R199" t="n">
-        <v>6818253</v>
+        <v>6818068</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20397,10 +20405,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128927936</v>
+        <v>128927913</v>
       </c>
       <c r="B200" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20432,10 +20440,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430084</v>
+        <v>430484</v>
       </c>
       <c r="R200" t="n">
-        <v>6818157</v>
+        <v>6818253</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20494,10 +20502,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128927961</v>
+        <v>128927936</v>
       </c>
       <c r="B201" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20529,10 +20537,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430086</v>
+        <v>430084</v>
       </c>
       <c r="R201" t="n">
-        <v>6818236</v>
+        <v>6818157</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20591,10 +20599,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128927942</v>
+        <v>128927961</v>
       </c>
       <c r="B202" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20626,10 +20634,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430087</v>
+        <v>430086</v>
       </c>
       <c r="R202" t="n">
-        <v>6817971</v>
+        <v>6818236</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20688,10 +20696,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128927841</v>
+        <v>128927942</v>
       </c>
       <c r="B203" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20699,21 +20707,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20723,10 +20731,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430569</v>
+        <v>430087</v>
       </c>
       <c r="R203" t="n">
-        <v>6818243</v>
+        <v>6817971</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20785,10 +20793,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128927717</v>
+        <v>128927841</v>
       </c>
       <c r="B204" t="n">
-        <v>79743</v>
+        <v>78786</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20796,21 +20804,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20820,10 +20828,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430214</v>
+        <v>430569</v>
       </c>
       <c r="R204" t="n">
-        <v>6817971</v>
+        <v>6818243</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20882,10 +20890,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128927715</v>
+        <v>128927717</v>
       </c>
       <c r="B205" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20917,10 +20925,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430650</v>
+        <v>430214</v>
       </c>
       <c r="R205" t="n">
-        <v>6818249</v>
+        <v>6817971</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20979,10 +20987,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128927755</v>
+        <v>128927715</v>
       </c>
       <c r="B206" t="n">
-        <v>57720</v>
+        <v>79648</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20990,42 +20998,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430480</v>
+        <v>430650</v>
       </c>
       <c r="R206" t="n">
-        <v>6818068</v>
+        <v>6818249</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21084,10 +21084,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128927816</v>
+        <v>128927809</v>
       </c>
       <c r="B207" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21119,10 +21119,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>430086</v>
+        <v>430222</v>
       </c>
       <c r="R207" t="n">
-        <v>6818278</v>
+        <v>6818155</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21184,7 +21184,7 @@
         <v>128927814</v>
       </c>
       <c r="B208" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21278,10 +21278,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128927809</v>
+        <v>128927816</v>
       </c>
       <c r="B209" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21313,10 +21313,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>430222</v>
+        <v>430086</v>
       </c>
       <c r="R209" t="n">
-        <v>6818155</v>
+        <v>6818278</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21378,7 +21378,7 @@
         <v>128927941</v>
       </c>
       <c r="B210" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>128927960</v>
       </c>
       <c r="B211" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>128927860</v>
       </c>
       <c r="B212" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>128927866</v>
       </c>
       <c r="B213" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>128927753</v>
       </c>
       <c r="B214" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>128927830</v>
       </c>
       <c r="B215" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21965,10 +21965,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128927817</v>
+        <v>128927808</v>
       </c>
       <c r="B216" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22000,10 +22000,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>430068</v>
+        <v>430669</v>
       </c>
       <c r="R216" t="n">
-        <v>6818152</v>
+        <v>6818242</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22062,10 +22062,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128927808</v>
+        <v>128927817</v>
       </c>
       <c r="B217" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22097,10 +22097,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>430669</v>
+        <v>430068</v>
       </c>
       <c r="R217" t="n">
-        <v>6818242</v>
+        <v>6818152</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22162,7 +22162,7 @@
         <v>128927746</v>
       </c>
       <c r="B218" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22256,10 +22256,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128927967</v>
+        <v>128927771</v>
       </c>
       <c r="B219" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22267,34 +22267,42 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430084</v>
+        <v>430658</v>
       </c>
       <c r="R219" t="n">
-        <v>6818144</v>
+        <v>6818274</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22353,10 +22361,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128927881</v>
+        <v>128927967</v>
       </c>
       <c r="B220" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22388,10 +22396,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430536</v>
+        <v>430084</v>
       </c>
       <c r="R220" t="n">
-        <v>6818208</v>
+        <v>6818144</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22450,10 +22458,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128927916</v>
+        <v>128927881</v>
       </c>
       <c r="B221" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22485,10 +22493,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430580</v>
+        <v>430536</v>
       </c>
       <c r="R221" t="n">
-        <v>6818221</v>
+        <v>6818208</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22547,10 +22555,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128927867</v>
+        <v>128927916</v>
       </c>
       <c r="B222" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22558,21 +22566,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22582,10 +22590,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430006</v>
+        <v>430580</v>
       </c>
       <c r="R222" t="n">
-        <v>6818034</v>
+        <v>6818221</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22644,10 +22652,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128927771</v>
+        <v>128927867</v>
       </c>
       <c r="B223" t="n">
-        <v>57717</v>
+        <v>78786</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22655,42 +22663,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430658</v>
+        <v>430006</v>
       </c>
       <c r="R223" t="n">
-        <v>6818274</v>
+        <v>6818034</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22752,7 +22752,7 @@
         <v>128927800</v>
       </c>
       <c r="B224" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22850,10 +22850,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128927890</v>
+        <v>128927730</v>
       </c>
       <c r="B225" t="n">
-        <v>79124</v>
+        <v>79648</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22861,21 +22861,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22885,10 +22885,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430348</v>
+        <v>430075</v>
       </c>
       <c r="R225" t="n">
-        <v>6818167</v>
+        <v>6818213</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22947,10 +22947,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128927915</v>
+        <v>128927850</v>
       </c>
       <c r="B226" t="n">
-        <v>79124</v>
+        <v>78786</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22958,37 +22958,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430575</v>
+        <v>430159</v>
       </c>
       <c r="R226" t="n">
-        <v>6818234</v>
+        <v>6818161</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23029,7 +23026,6 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
-      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
@@ -23048,10 +23044,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128927923</v>
+        <v>128927890</v>
       </c>
       <c r="B227" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23083,10 +23079,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430670</v>
+        <v>430348</v>
       </c>
       <c r="R227" t="n">
-        <v>6818263</v>
+        <v>6818167</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23145,10 +23141,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128927850</v>
+        <v>128927915</v>
       </c>
       <c r="B228" t="n">
-        <v>78881</v>
+        <v>79029</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23156,34 +23152,37 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430159</v>
+        <v>430575</v>
       </c>
       <c r="R228" t="n">
-        <v>6818161</v>
+        <v>6818234</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23224,6 +23223,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -23242,10 +23242,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128927730</v>
+        <v>128927923</v>
       </c>
       <c r="B229" t="n">
-        <v>79743</v>
+        <v>79029</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23253,21 +23253,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23277,10 +23277,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430075</v>
+        <v>430670</v>
       </c>
       <c r="R229" t="n">
-        <v>6818213</v>
+        <v>6818263</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128927732</v>
+        <v>128927978</v>
       </c>
       <c r="B22" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430138</v>
+        <v>430082</v>
       </c>
       <c r="R22" t="n">
-        <v>6817883</v>
+        <v>6818210</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,6 +2930,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2948,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927950</v>
+        <v>128927843</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,21 +2960,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430233</v>
+        <v>430626</v>
       </c>
       <c r="R23" t="n">
-        <v>6817831</v>
+        <v>6818202</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,10 +3046,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927880</v>
+        <v>128927721</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,21 +3057,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3081,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430577</v>
+        <v>430060</v>
       </c>
       <c r="R24" t="n">
-        <v>6818221</v>
+        <v>6818156</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3143,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927868</v>
+        <v>128927935</v>
       </c>
       <c r="B25" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,21 +3154,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3178,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430089</v>
+        <v>430099</v>
       </c>
       <c r="R25" t="n">
-        <v>6817984</v>
+        <v>6818154</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3240,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927978</v>
+        <v>128927726</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3250,21 +3251,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3274,10 +3275,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430082</v>
+        <v>430114</v>
       </c>
       <c r="R26" t="n">
-        <v>6818210</v>
+        <v>6817912</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3319,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927843</v>
+        <v>128927963</v>
       </c>
       <c r="B27" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430626</v>
+        <v>430064</v>
       </c>
       <c r="R27" t="n">
-        <v>6818202</v>
+        <v>6818190</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927721</v>
+        <v>128927770</v>
       </c>
       <c r="B28" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3445,34 +3445,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430060</v>
+        <v>430455</v>
       </c>
       <c r="R28" t="n">
-        <v>6818156</v>
+        <v>6818246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927935</v>
+        <v>128927821</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,21 +3550,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3566,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430099</v>
+        <v>429994</v>
       </c>
       <c r="R29" t="n">
-        <v>6818154</v>
+        <v>6818158</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,10 +3636,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927726</v>
+        <v>128927802</v>
       </c>
       <c r="B30" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3639,21 +3647,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3663,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430114</v>
+        <v>430567</v>
       </c>
       <c r="R30" t="n">
-        <v>6817912</v>
+        <v>6818243</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927963</v>
+        <v>128927732</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3736,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430064</v>
+        <v>430138</v>
       </c>
       <c r="R31" t="n">
-        <v>6818190</v>
+        <v>6817883</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128927770</v>
+        <v>128927950</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3833,42 +3841,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430455</v>
+        <v>430233</v>
       </c>
       <c r="R32" t="n">
-        <v>6818246</v>
+        <v>6817831</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,32 +3927,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128927834</v>
+        <v>128927880</v>
       </c>
       <c r="B33" t="n">
-        <v>58093</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>430596</v>
+        <v>430577</v>
       </c>
       <c r="R33" t="n">
-        <v>6818184</v>
+        <v>6818221</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128927821</v>
+        <v>128927868</v>
       </c>
       <c r="B34" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>429994</v>
+        <v>430089</v>
       </c>
       <c r="R34" t="n">
-        <v>6818158</v>
+        <v>6817984</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128927802</v>
+        <v>128927834</v>
       </c>
       <c r="B35" t="n">
-        <v>78792</v>
+        <v>58093</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430567</v>
+        <v>430596</v>
       </c>
       <c r="R35" t="n">
-        <v>6818243</v>
+        <v>6818184</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128927893</v>
+        <v>128927790</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7177,34 +7177,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430286</v>
+        <v>430130</v>
       </c>
       <c r="R66" t="n">
-        <v>6818100</v>
+        <v>6817856</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7263,10 +7271,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128927974</v>
+        <v>128927751</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7274,34 +7282,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430091</v>
+        <v>430337</v>
       </c>
       <c r="R67" t="n">
-        <v>6818012</v>
+        <v>6818076</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7360,10 +7376,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128927825</v>
+        <v>128927893</v>
       </c>
       <c r="B68" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7371,21 +7387,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7395,10 +7411,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430024</v>
+        <v>430286</v>
       </c>
       <c r="R68" t="n">
-        <v>6818040</v>
+        <v>6818100</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7457,10 +7473,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128927751</v>
+        <v>128927974</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7468,42 +7484,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430337</v>
+        <v>430091</v>
       </c>
       <c r="R69" t="n">
-        <v>6818076</v>
+        <v>6818012</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7562,10 +7570,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128927790</v>
+        <v>128927825</v>
       </c>
       <c r="B70" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7573,42 +7581,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>430130</v>
+        <v>430024</v>
       </c>
       <c r="R70" t="n">
-        <v>6817856</v>
+        <v>6818040</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -10798,10 +10798,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927899</v>
+        <v>128927793</v>
       </c>
       <c r="B103" t="n">
-        <v>79034</v>
+        <v>58153</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430428</v>
+        <v>430104</v>
       </c>
       <c r="R103" t="n">
-        <v>6818038</v>
+        <v>6817933</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,7 +10895,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927954</v>
+        <v>128927899</v>
       </c>
       <c r="B104" t="n">
         <v>79034</v>
@@ -10924,19 +10924,16 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430166</v>
+        <v>430428</v>
       </c>
       <c r="R104" t="n">
-        <v>6818134</v>
+        <v>6818038</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10971,18 +10968,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11001,7 +10992,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927888</v>
+        <v>128927954</v>
       </c>
       <c r="B105" t="n">
         <v>79034</v>
@@ -11030,16 +11021,19 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430399</v>
+        <v>430166</v>
       </c>
       <c r="R105" t="n">
-        <v>6818238</v>
+        <v>6818134</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11074,12 +11068,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11098,7 +11098,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927971</v>
+        <v>128927888</v>
       </c>
       <c r="B106" t="n">
         <v>79034</v>
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>429925</v>
+        <v>430399</v>
       </c>
       <c r="R106" t="n">
-        <v>6818065</v>
+        <v>6818238</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11195,7 +11195,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927949</v>
+        <v>128927971</v>
       </c>
       <c r="B107" t="n">
         <v>79034</v>
@@ -11230,10 +11230,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430653</v>
+        <v>429925</v>
       </c>
       <c r="R107" t="n">
-        <v>6818272</v>
+        <v>6818065</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11292,10 +11292,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927856</v>
+        <v>128927949</v>
       </c>
       <c r="B108" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11303,21 +11303,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11327,10 +11327,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430060</v>
+        <v>430653</v>
       </c>
       <c r="R108" t="n">
-        <v>6818160</v>
+        <v>6818272</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11389,32 +11389,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927836</v>
+        <v>128927856</v>
       </c>
       <c r="B109" t="n">
-        <v>58093</v>
+        <v>78791</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11424,10 +11424,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430147</v>
+        <v>430060</v>
       </c>
       <c r="R109" t="n">
-        <v>6817817</v>
+        <v>6818160</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11486,32 +11486,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128927827</v>
+        <v>128927836</v>
       </c>
       <c r="B110" t="n">
-        <v>78792</v>
+        <v>58093</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430057</v>
+        <v>430147</v>
       </c>
       <c r="R110" t="n">
-        <v>6818016</v>
+        <v>6817817</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11583,7 +11583,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927822</v>
+        <v>128927827</v>
       </c>
       <c r="B111" t="n">
         <v>78792</v>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>429973</v>
+        <v>430057</v>
       </c>
       <c r="R111" t="n">
-        <v>6818162</v>
+        <v>6818016</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11680,7 +11680,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927826</v>
+        <v>128927822</v>
       </c>
       <c r="B112" t="n">
         <v>78792</v>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>430018</v>
+        <v>429973</v>
       </c>
       <c r="R112" t="n">
-        <v>6818046</v>
+        <v>6818162</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,7 +11777,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927796</v>
+        <v>128927826</v>
       </c>
       <c r="B113" t="n">
         <v>78792</v>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430323</v>
+        <v>430018</v>
       </c>
       <c r="R113" t="n">
-        <v>6818121</v>
+        <v>6818046</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927793</v>
+        <v>128927796</v>
       </c>
       <c r="B114" t="n">
-        <v>58153</v>
+        <v>78792</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103001</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430104</v>
+        <v>430323</v>
       </c>
       <c r="R114" t="n">
-        <v>6817933</v>
+        <v>6818121</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128927901</v>
+        <v>128927873</v>
       </c>
       <c r="B117" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12176,21 +12176,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430501</v>
+        <v>429998</v>
       </c>
       <c r="R117" t="n">
-        <v>6818013</v>
+        <v>6818047</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128927921</v>
+        <v>128927901</v>
       </c>
       <c r="B118" t="n">
         <v>79034</v>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>430664</v>
+        <v>430501</v>
       </c>
       <c r="R118" t="n">
-        <v>6818275</v>
+        <v>6818013</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12359,10 +12359,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128927873</v>
+        <v>128927921</v>
       </c>
       <c r="B119" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12370,21 +12370,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12394,10 +12394,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>429998</v>
+        <v>430664</v>
       </c>
       <c r="R119" t="n">
-        <v>6818047</v>
+        <v>6818275</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14045,7 +14045,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128927969</v>
+        <v>128927889</v>
       </c>
       <c r="B136" t="n">
         <v>79034</v>
@@ -14080,10 +14080,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>429947</v>
+        <v>430385</v>
       </c>
       <c r="R136" t="n">
-        <v>6818135</v>
+        <v>6818203</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14142,10 +14142,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128927709</v>
+        <v>128927781</v>
       </c>
       <c r="B137" t="n">
-        <v>79653</v>
+        <v>57720</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14153,34 +14153,42 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430495</v>
+        <v>430480</v>
       </c>
       <c r="R137" t="n">
-        <v>6818056</v>
+        <v>6817997</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14239,10 +14247,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128927925</v>
+        <v>128927788</v>
       </c>
       <c r="B138" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14250,34 +14258,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430683</v>
+        <v>430017</v>
       </c>
       <c r="R138" t="n">
-        <v>6818265</v>
+        <v>6818044</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14336,10 +14352,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128927972</v>
+        <v>128927775</v>
       </c>
       <c r="B139" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14347,26 +14363,31 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14374,10 +14395,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430018</v>
+        <v>430083</v>
       </c>
       <c r="R139" t="n">
-        <v>6818025</v>
+        <v>6818224</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14418,7 +14439,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14437,10 +14457,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128927894</v>
+        <v>128927792</v>
       </c>
       <c r="B140" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14448,26 +14468,31 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14475,10 +14500,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430321</v>
+        <v>430150</v>
       </c>
       <c r="R140" t="n">
-        <v>6818095</v>
+        <v>6817814</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14513,18 +14538,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14543,10 +14562,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128927900</v>
+        <v>128927824</v>
       </c>
       <c r="B141" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14554,21 +14573,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14578,10 +14597,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430467</v>
+        <v>429941</v>
       </c>
       <c r="R141" t="n">
-        <v>6818020</v>
+        <v>6818056</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14640,10 +14659,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128927889</v>
+        <v>128927748</v>
       </c>
       <c r="B142" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14651,21 +14670,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14675,10 +14694,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430385</v>
+        <v>430202</v>
       </c>
       <c r="R142" t="n">
-        <v>6818203</v>
+        <v>6818084</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14737,10 +14756,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128927863</v>
+        <v>128927894</v>
       </c>
       <c r="B143" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14748,34 +14767,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>429970</v>
+        <v>430321</v>
       </c>
       <c r="R143" t="n">
-        <v>6818162</v>
+        <v>6818095</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14810,12 +14832,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14834,7 +14862,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128927911</v>
+        <v>128927900</v>
       </c>
       <c r="B144" t="n">
         <v>79034</v>
@@ -14869,10 +14897,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430437</v>
+        <v>430467</v>
       </c>
       <c r="R144" t="n">
-        <v>6818227</v>
+        <v>6818020</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14931,10 +14959,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128927956</v>
+        <v>128927863</v>
       </c>
       <c r="B145" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14942,21 +14970,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14966,10 +14994,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430119</v>
+        <v>429970</v>
       </c>
       <c r="R145" t="n">
-        <v>6818173</v>
+        <v>6818162</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15028,10 +15056,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128927861</v>
+        <v>128927911</v>
       </c>
       <c r="B146" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15039,21 +15067,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15063,10 +15091,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>429989</v>
+        <v>430437</v>
       </c>
       <c r="R146" t="n">
-        <v>6818159</v>
+        <v>6818227</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15125,7 +15153,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128927926</v>
+        <v>128927969</v>
       </c>
       <c r="B147" t="n">
         <v>79034</v>
@@ -15160,10 +15188,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430701</v>
+        <v>429947</v>
       </c>
       <c r="R147" t="n">
-        <v>6818261</v>
+        <v>6818135</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15222,10 +15250,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927781</v>
+        <v>128927709</v>
       </c>
       <c r="B148" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15233,42 +15261,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430480</v>
+        <v>430495</v>
       </c>
       <c r="R148" t="n">
-        <v>6817997</v>
+        <v>6818056</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15327,10 +15347,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927788</v>
+        <v>128927956</v>
       </c>
       <c r="B149" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15338,42 +15358,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430017</v>
+        <v>430119</v>
       </c>
       <c r="R149" t="n">
-        <v>6818044</v>
+        <v>6818173</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15432,10 +15444,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927775</v>
+        <v>128927925</v>
       </c>
       <c r="B150" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15443,42 +15455,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430083</v>
+        <v>430683</v>
       </c>
       <c r="R150" t="n">
-        <v>6818224</v>
+        <v>6818265</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15537,10 +15541,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927792</v>
+        <v>128927972</v>
       </c>
       <c r="B151" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15548,31 +15552,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -15580,10 +15579,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430150</v>
+        <v>430018</v>
       </c>
       <c r="R151" t="n">
-        <v>6817814</v>
+        <v>6818025</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15624,6 +15623,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15642,54 +15642,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128927833</v>
+        <v>128927861</v>
       </c>
       <c r="B152" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430204</v>
+        <v>429989</v>
       </c>
       <c r="R152" t="n">
-        <v>6817811</v>
+        <v>6818159</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15730,7 +15721,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15749,10 +15739,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128927824</v>
+        <v>128927926</v>
       </c>
       <c r="B153" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15760,21 +15750,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15784,10 +15774,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>429941</v>
+        <v>430701</v>
       </c>
       <c r="R153" t="n">
-        <v>6818056</v>
+        <v>6818261</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15846,45 +15836,54 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128927748</v>
+        <v>128927833</v>
       </c>
       <c r="B154" t="n">
-        <v>79624</v>
+        <v>8450</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430202</v>
+        <v>430204</v>
       </c>
       <c r="R154" t="n">
-        <v>6818084</v>
+        <v>6817811</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15925,6 +15924,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -15943,10 +15943,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128927779</v>
+        <v>128927798</v>
       </c>
       <c r="B155" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15954,42 +15954,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>430106</v>
+        <v>430315</v>
       </c>
       <c r="R155" t="n">
-        <v>6817957</v>
+        <v>6818095</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16048,10 +16040,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128927783</v>
+        <v>128927828</v>
       </c>
       <c r="B156" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16059,31 +16051,26 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -16091,10 +16078,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>430174</v>
+        <v>430115</v>
       </c>
       <c r="R156" t="n">
-        <v>6817923</v>
+        <v>6817902</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16135,6 +16122,7 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17141,10 +17129,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128927798</v>
+        <v>128927779</v>
       </c>
       <c r="B167" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17152,34 +17140,42 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430315</v>
+        <v>430106</v>
       </c>
       <c r="R167" t="n">
-        <v>6818095</v>
+        <v>6817957</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17238,10 +17234,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128927828</v>
+        <v>128927783</v>
       </c>
       <c r="B168" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17249,26 +17245,31 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -17276,10 +17277,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430115</v>
+        <v>430174</v>
       </c>
       <c r="R168" t="n">
-        <v>6817902</v>
+        <v>6817923</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17320,7 +17321,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17837,32 +17837,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128927835</v>
+        <v>128927829</v>
       </c>
       <c r="B174" t="n">
-        <v>58093</v>
+        <v>78792</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17872,10 +17872,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430104</v>
+        <v>430138</v>
       </c>
       <c r="R174" t="n">
-        <v>6817960</v>
+        <v>6817883</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17934,32 +17934,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128927829</v>
+        <v>128927835</v>
       </c>
       <c r="B175" t="n">
-        <v>78792</v>
+        <v>58093</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17969,10 +17969,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430138</v>
+        <v>430104</v>
       </c>
       <c r="R175" t="n">
-        <v>6817883</v>
+        <v>6817960</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19114,10 +19114,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128927910</v>
+        <v>128927789</v>
       </c>
       <c r="B187" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19125,34 +19125,42 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430430</v>
+        <v>430089</v>
       </c>
       <c r="R187" t="n">
-        <v>6818202</v>
+        <v>6817965</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19185,6 +19193,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19211,10 +19224,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128927847</v>
+        <v>128927910</v>
       </c>
       <c r="B188" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19222,21 +19235,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19246,10 +19259,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430227</v>
+        <v>430430</v>
       </c>
       <c r="R188" t="n">
-        <v>6818154</v>
+        <v>6818202</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19308,10 +19321,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128927892</v>
+        <v>128927731</v>
       </c>
       <c r="B189" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19319,21 +19332,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19343,10 +19356,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430304</v>
+        <v>430056</v>
       </c>
       <c r="R189" t="n">
-        <v>6818124</v>
+        <v>6818017</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19405,10 +19418,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128927728</v>
+        <v>128927847</v>
       </c>
       <c r="B190" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19416,21 +19429,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19440,10 +19453,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430232</v>
+        <v>430227</v>
       </c>
       <c r="R190" t="n">
-        <v>6818068</v>
+        <v>6818154</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19502,10 +19515,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128927731</v>
+        <v>128927892</v>
       </c>
       <c r="B191" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19513,21 +19526,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19537,10 +19550,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430056</v>
+        <v>430304</v>
       </c>
       <c r="R191" t="n">
-        <v>6818017</v>
+        <v>6818124</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19696,10 +19709,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128927906</v>
+        <v>128927728</v>
       </c>
       <c r="B193" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19707,37 +19720,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430401</v>
+        <v>430232</v>
       </c>
       <c r="R193" t="n">
-        <v>6818157</v>
+        <v>6818068</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19772,18 +19782,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -19802,7 +19806,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128927922</v>
+        <v>128927906</v>
       </c>
       <c r="B194" t="n">
         <v>79034</v>
@@ -19831,16 +19835,19 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430668</v>
+        <v>430401</v>
       </c>
       <c r="R194" t="n">
-        <v>6818241</v>
+        <v>6818157</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19875,12 +19882,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
+        </is>
+      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -19899,7 +19912,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128927962</v>
+        <v>128927922</v>
       </c>
       <c r="B195" t="n">
         <v>79034</v>
@@ -19934,10 +19947,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430069</v>
+        <v>430668</v>
       </c>
       <c r="R195" t="n">
-        <v>6818225</v>
+        <v>6818241</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19996,10 +20009,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128927789</v>
+        <v>128927962</v>
       </c>
       <c r="B196" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20007,42 +20020,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430089</v>
+        <v>430069</v>
       </c>
       <c r="R196" t="n">
-        <v>6817965</v>
+        <v>6818225</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20075,11 +20080,6 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22256,10 +22256,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128927967</v>
+        <v>128927800</v>
       </c>
       <c r="B219" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22267,34 +22267,37 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430084</v>
+        <v>430487</v>
       </c>
       <c r="R219" t="n">
-        <v>6818144</v>
+        <v>6818080</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22335,6 +22338,7 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -22353,10 +22357,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128927867</v>
+        <v>128927967</v>
       </c>
       <c r="B220" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22364,21 +22368,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22388,10 +22392,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430006</v>
+        <v>430084</v>
       </c>
       <c r="R220" t="n">
-        <v>6818034</v>
+        <v>6818144</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22450,10 +22454,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128927881</v>
+        <v>128927867</v>
       </c>
       <c r="B221" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22461,21 +22465,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22485,10 +22489,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430536</v>
+        <v>430006</v>
       </c>
       <c r="R221" t="n">
-        <v>6818208</v>
+        <v>6818034</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22547,7 +22551,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128927916</v>
+        <v>128927881</v>
       </c>
       <c r="B222" t="n">
         <v>79034</v>
@@ -22582,10 +22586,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430580</v>
+        <v>430536</v>
       </c>
       <c r="R222" t="n">
-        <v>6818221</v>
+        <v>6818208</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22644,10 +22648,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128927800</v>
+        <v>128927916</v>
       </c>
       <c r="B223" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22655,37 +22659,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430487</v>
+        <v>430580</v>
       </c>
       <c r="R223" t="n">
-        <v>6818080</v>
+        <v>6818221</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22726,7 +22727,6 @@
       <c r="AE223" t="b">
         <v>0</v>
       </c>
-      <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128927978</v>
+        <v>128927732</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430082</v>
+        <v>430138</v>
       </c>
       <c r="R22" t="n">
-        <v>6818210</v>
+        <v>6817883</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2930,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2949,7 +2948,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927843</v>
+        <v>128927868</v>
       </c>
       <c r="B23" t="n">
         <v>78791</v>
@@ -2984,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430626</v>
+        <v>430089</v>
       </c>
       <c r="R23" t="n">
-        <v>6818202</v>
+        <v>6817984</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3046,10 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927721</v>
+        <v>128927843</v>
       </c>
       <c r="B24" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3081,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430060</v>
+        <v>430626</v>
       </c>
       <c r="R24" t="n">
-        <v>6818156</v>
+        <v>6818202</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927935</v>
+        <v>128927721</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3154,21 +3153,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3178,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430099</v>
+        <v>430060</v>
       </c>
       <c r="R25" t="n">
-        <v>6818154</v>
+        <v>6818156</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3337,7 +3336,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927963</v>
+        <v>128927950</v>
       </c>
       <c r="B27" t="n">
         <v>79034</v>
@@ -3372,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430064</v>
+        <v>430233</v>
       </c>
       <c r="R27" t="n">
-        <v>6818190</v>
+        <v>6817831</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927770</v>
+        <v>128927880</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3445,42 +3444,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430455</v>
+        <v>430577</v>
       </c>
       <c r="R28" t="n">
-        <v>6818246</v>
+        <v>6818221</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927821</v>
+        <v>128927978</v>
       </c>
       <c r="B29" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3550,21 +3541,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3574,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>429994</v>
+        <v>430082</v>
       </c>
       <c r="R29" t="n">
-        <v>6818158</v>
+        <v>6818210</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,6 +3609,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3636,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927802</v>
+        <v>128927935</v>
       </c>
       <c r="B30" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3647,21 +3639,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3671,10 +3663,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430567</v>
+        <v>430099</v>
       </c>
       <c r="R30" t="n">
-        <v>6818243</v>
+        <v>6818154</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3733,10 +3725,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927732</v>
+        <v>128927963</v>
       </c>
       <c r="B31" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3744,21 +3736,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430138</v>
+        <v>430064</v>
       </c>
       <c r="R31" t="n">
-        <v>6817883</v>
+        <v>6818190</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3830,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128927950</v>
+        <v>128927770</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3841,34 +3833,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430233</v>
+        <v>430455</v>
       </c>
       <c r="R32" t="n">
-        <v>6817831</v>
+        <v>6818246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,32 +3927,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128927880</v>
+        <v>128927834</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>58093</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>430577</v>
+        <v>430596</v>
       </c>
       <c r="R33" t="n">
-        <v>6818221</v>
+        <v>6818184</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128927868</v>
+        <v>128927821</v>
       </c>
       <c r="B34" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>430089</v>
+        <v>429994</v>
       </c>
       <c r="R34" t="n">
-        <v>6817984</v>
+        <v>6818158</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128927834</v>
+        <v>128927802</v>
       </c>
       <c r="B35" t="n">
-        <v>58093</v>
+        <v>78792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430596</v>
+        <v>430567</v>
       </c>
       <c r="R35" t="n">
-        <v>6818184</v>
+        <v>6818243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128927871</v>
+        <v>128927939</v>
       </c>
       <c r="B37" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4326,21 +4326,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>430145</v>
+        <v>429903</v>
       </c>
       <c r="R37" t="n">
-        <v>6817833</v>
+        <v>6818059</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4412,7 +4412,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128927939</v>
+        <v>128927973</v>
       </c>
       <c r="B38" t="n">
         <v>79034</v>
@@ -4441,16 +4441,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>429903</v>
+        <v>430073</v>
       </c>
       <c r="R38" t="n">
-        <v>6818059</v>
+        <v>6818021</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4491,6 +4494,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4509,10 +4513,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128927973</v>
+        <v>128927871</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4520,37 +4524,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430073</v>
+        <v>430145</v>
       </c>
       <c r="R39" t="n">
-        <v>6818021</v>
+        <v>6817833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4591,7 +4592,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4610,10 +4610,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128927743</v>
+        <v>128927773</v>
       </c>
       <c r="B40" t="n">
-        <v>79624</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,34 +4621,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>430211</v>
+        <v>430251</v>
       </c>
       <c r="R40" t="n">
-        <v>6817980</v>
+        <v>6818033</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4707,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128927813</v>
+        <v>128927743</v>
       </c>
       <c r="B41" t="n">
-        <v>78792</v>
+        <v>79624</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4718,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4742,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430145</v>
+        <v>430211</v>
       </c>
       <c r="R41" t="n">
-        <v>6818165</v>
+        <v>6817980</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4804,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128927773</v>
+        <v>128927813</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4815,42 +4823,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>430251</v>
+        <v>430145</v>
       </c>
       <c r="R42" t="n">
-        <v>6818033</v>
+        <v>6818165</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128927845</v>
+        <v>128927930</v>
       </c>
       <c r="B43" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430669</v>
+        <v>430205</v>
       </c>
       <c r="R43" t="n">
-        <v>6818249</v>
+        <v>6817961</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128927930</v>
+        <v>128927928</v>
       </c>
       <c r="B44" t="n">
         <v>79034</v>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430205</v>
+        <v>430293</v>
       </c>
       <c r="R44" t="n">
-        <v>6817961</v>
+        <v>6817871</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,7 +5103,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128927928</v>
+        <v>128927934</v>
       </c>
       <c r="B45" t="n">
         <v>79034</v>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430293</v>
+        <v>430088</v>
       </c>
       <c r="R45" t="n">
-        <v>6817871</v>
+        <v>6818186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5200,7 +5200,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128927934</v>
+        <v>128927938</v>
       </c>
       <c r="B46" t="n">
         <v>79034</v>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430088</v>
+        <v>429959</v>
       </c>
       <c r="R46" t="n">
-        <v>6818186</v>
+        <v>6818128</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128927842</v>
+        <v>128927976</v>
       </c>
       <c r="B47" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5308,34 +5308,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430596</v>
+        <v>430149</v>
       </c>
       <c r="R47" t="n">
-        <v>6818186</v>
+        <v>6817860</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5376,6 +5379,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5394,7 +5398,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128927938</v>
+        <v>128927966</v>
       </c>
       <c r="B48" t="n">
         <v>79034</v>
@@ -5429,10 +5433,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>429959</v>
+        <v>430071</v>
       </c>
       <c r="R48" t="n">
-        <v>6818128</v>
+        <v>6818124</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5491,10 +5495,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128927976</v>
+        <v>128927845</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5502,37 +5506,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430149</v>
+        <v>430669</v>
       </c>
       <c r="R49" t="n">
-        <v>6817860</v>
+        <v>6818249</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5573,7 +5574,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128927966</v>
+        <v>128927842</v>
       </c>
       <c r="B50" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430071</v>
+        <v>430596</v>
       </c>
       <c r="R50" t="n">
-        <v>6818124</v>
+        <v>6818186</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128927874</v>
+        <v>128927970</v>
       </c>
       <c r="B57" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6295,21 +6295,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>430154</v>
+        <v>429900</v>
       </c>
       <c r="R57" t="n">
-        <v>6817859</v>
+        <v>6818098</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6355,6 +6355,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,7 +6386,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128927970</v>
+        <v>128927944</v>
       </c>
       <c r="B58" t="n">
         <v>79034</v>
@@ -6410,16 +6415,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>429900</v>
+        <v>430531</v>
       </c>
       <c r="R58" t="n">
-        <v>6818098</v>
+        <v>6818016</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6454,17 +6462,13 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6483,7 +6487,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927944</v>
+        <v>128927948</v>
       </c>
       <c r="B59" t="n">
         <v>79034</v>
@@ -6512,19 +6516,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430531</v>
+        <v>430655</v>
       </c>
       <c r="R59" t="n">
-        <v>6818016</v>
+        <v>6818216</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6565,7 +6566,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6584,7 +6584,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927948</v>
+        <v>128927882</v>
       </c>
       <c r="B60" t="n">
         <v>79034</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430655</v>
+        <v>430526</v>
       </c>
       <c r="R60" t="n">
-        <v>6818216</v>
+        <v>6818232</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128927735</v>
+        <v>128927929</v>
       </c>
       <c r="B61" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,21 +6692,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430132</v>
+        <v>430208</v>
       </c>
       <c r="R61" t="n">
-        <v>6817858</v>
+        <v>6817816</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128927882</v>
+        <v>128927874</v>
       </c>
       <c r="B62" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430526</v>
+        <v>430154</v>
       </c>
       <c r="R62" t="n">
-        <v>6818232</v>
+        <v>6817859</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6875,10 +6875,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128927929</v>
+        <v>128927735</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6886,21 +6886,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430208</v>
+        <v>430132</v>
       </c>
       <c r="R63" t="n">
-        <v>6817816</v>
+        <v>6817858</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128927790</v>
+        <v>128927893</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7177,42 +7177,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430130</v>
+        <v>430286</v>
       </c>
       <c r="R66" t="n">
-        <v>6817856</v>
+        <v>6818100</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,10 +7263,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128927751</v>
+        <v>128927974</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,42 +7274,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430337</v>
+        <v>430091</v>
       </c>
       <c r="R67" t="n">
-        <v>6818076</v>
+        <v>6818012</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7376,10 +7360,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128927893</v>
+        <v>128927790</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7387,34 +7371,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430286</v>
+        <v>430130</v>
       </c>
       <c r="R68" t="n">
-        <v>6818100</v>
+        <v>6817856</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7473,10 +7465,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128927974</v>
+        <v>128927751</v>
       </c>
       <c r="B69" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7484,34 +7476,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430091</v>
+        <v>430337</v>
       </c>
       <c r="R69" t="n">
-        <v>6818012</v>
+        <v>6818076</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7667,10 +7667,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128927831</v>
+        <v>128927710</v>
       </c>
       <c r="B71" t="n">
-        <v>78792</v>
+        <v>79653</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,37 +7678,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430126</v>
+        <v>430610</v>
       </c>
       <c r="R71" t="n">
-        <v>6817835</v>
+        <v>6818230</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7749,7 +7746,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7768,10 +7764,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128927710</v>
+        <v>128927839</v>
       </c>
       <c r="B72" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7779,21 +7775,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7803,10 +7799,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>430610</v>
+        <v>430489</v>
       </c>
       <c r="R72" t="n">
-        <v>6818230</v>
+        <v>6818084</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7865,7 +7861,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128927839</v>
+        <v>128927857</v>
       </c>
       <c r="B73" t="n">
         <v>78791</v>
@@ -7900,10 +7896,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>430489</v>
+        <v>430051</v>
       </c>
       <c r="R73" t="n">
-        <v>6818084</v>
+        <v>6818114</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7962,7 +7958,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128927857</v>
+        <v>128927852</v>
       </c>
       <c r="B74" t="n">
         <v>78791</v>
@@ -7997,10 +7993,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>430051</v>
+        <v>430086</v>
       </c>
       <c r="R74" t="n">
-        <v>6818114</v>
+        <v>6818279</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8059,10 +8055,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128927852</v>
+        <v>128927831</v>
       </c>
       <c r="B75" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8070,34 +8066,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>430086</v>
+        <v>430126</v>
       </c>
       <c r="R75" t="n">
-        <v>6818279</v>
+        <v>6817835</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8138,6 +8137,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128927840</v>
+        <v>128927924</v>
       </c>
       <c r="B76" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8167,21 +8167,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430407</v>
+        <v>430671</v>
       </c>
       <c r="R76" t="n">
-        <v>6818114</v>
+        <v>6818266</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128927865</v>
+        <v>128927964</v>
       </c>
       <c r="B77" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>429935</v>
+        <v>430099</v>
       </c>
       <c r="R77" t="n">
-        <v>6818065</v>
+        <v>6818174</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128927924</v>
+        <v>128927897</v>
       </c>
       <c r="B78" t="n">
         <v>79034</v>
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430671</v>
+        <v>430386</v>
       </c>
       <c r="R78" t="n">
-        <v>6818266</v>
+        <v>6818039</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8447,7 +8447,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128927964</v>
+        <v>128927955</v>
       </c>
       <c r="B79" t="n">
         <v>79034</v>
@@ -8476,16 +8476,19 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430099</v>
+        <v>430129</v>
       </c>
       <c r="R79" t="n">
-        <v>6818174</v>
+        <v>6818156</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8520,12 +8523,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30 m</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8544,7 +8553,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128927897</v>
+        <v>128927905</v>
       </c>
       <c r="B80" t="n">
         <v>79034</v>
@@ -8579,10 +8588,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430386</v>
+        <v>430395</v>
       </c>
       <c r="R80" t="n">
-        <v>6818039</v>
+        <v>6818138</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8641,7 +8650,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128927955</v>
+        <v>128927885</v>
       </c>
       <c r="B81" t="n">
         <v>79034</v>
@@ -8670,19 +8679,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430129</v>
+        <v>430366</v>
       </c>
       <c r="R81" t="n">
-        <v>6818156</v>
+        <v>6818264</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8717,18 +8723,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30 m</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8747,7 +8747,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128927905</v>
+        <v>128927947</v>
       </c>
       <c r="B82" t="n">
         <v>79034</v>
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430395</v>
+        <v>430568</v>
       </c>
       <c r="R82" t="n">
-        <v>6818138</v>
+        <v>6818235</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8818,6 +8818,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8844,10 +8849,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128927725</v>
+        <v>128927912</v>
       </c>
       <c r="B83" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8855,21 +8860,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8879,10 +8884,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430040</v>
+        <v>430439</v>
       </c>
       <c r="R83" t="n">
-        <v>6818029</v>
+        <v>6818230</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8941,10 +8946,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128927885</v>
+        <v>128927840</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8952,21 +8957,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8976,10 +8981,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430366</v>
+        <v>430407</v>
       </c>
       <c r="R84" t="n">
-        <v>6818264</v>
+        <v>6818114</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9038,10 +9043,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128927947</v>
+        <v>128927865</v>
       </c>
       <c r="B85" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9049,21 +9054,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9073,10 +9078,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>430568</v>
+        <v>429935</v>
       </c>
       <c r="R85" t="n">
-        <v>6818235</v>
+        <v>6818065</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9109,11 +9114,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9140,10 +9140,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128927912</v>
+        <v>128927725</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9151,21 +9151,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430439</v>
+        <v>430040</v>
       </c>
       <c r="R86" t="n">
-        <v>6818230</v>
+        <v>6818029</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9531,7 +9531,7 @@
         <v>128927794</v>
       </c>
       <c r="B90" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128927810</v>
+        <v>128927891</v>
       </c>
       <c r="B91" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9636,21 +9636,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430215</v>
+        <v>430336</v>
       </c>
       <c r="R91" t="n">
-        <v>6818155</v>
+        <v>6818151</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128927803</v>
+        <v>128927884</v>
       </c>
       <c r="B92" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9733,21 +9733,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430580</v>
+        <v>430423</v>
       </c>
       <c r="R92" t="n">
-        <v>6818253</v>
+        <v>6818270</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9819,7 +9819,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128927891</v>
+        <v>128927965</v>
       </c>
       <c r="B93" t="n">
         <v>79034</v>
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430336</v>
+        <v>430115</v>
       </c>
       <c r="R93" t="n">
-        <v>6818151</v>
+        <v>6818177</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9916,7 +9916,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128927884</v>
+        <v>128927932</v>
       </c>
       <c r="B94" t="n">
         <v>79034</v>
@@ -9945,16 +9945,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430423</v>
+        <v>430240</v>
       </c>
       <c r="R94" t="n">
-        <v>6818270</v>
+        <v>6817987</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9989,12 +9992,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10013,10 +10022,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128927864</v>
+        <v>128927975</v>
       </c>
       <c r="B95" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10024,21 +10033,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10048,10 +10057,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>429975</v>
+        <v>430138</v>
       </c>
       <c r="R95" t="n">
-        <v>6818158</v>
+        <v>6817903</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10110,10 +10119,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128927714</v>
+        <v>128927943</v>
       </c>
       <c r="B96" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10121,21 +10130,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10145,10 +10154,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430630</v>
+        <v>430136</v>
       </c>
       <c r="R96" t="n">
-        <v>6818207</v>
+        <v>6817849</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10207,10 +10216,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128927965</v>
+        <v>128927980</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>78042</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10218,21 +10227,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10242,10 +10251,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430115</v>
+        <v>430081</v>
       </c>
       <c r="R97" t="n">
-        <v>6818177</v>
+        <v>6818119</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10304,10 +10313,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128927932</v>
+        <v>128927864</v>
       </c>
       <c r="B98" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10315,37 +10324,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430240</v>
+        <v>429975</v>
       </c>
       <c r="R98" t="n">
-        <v>6817987</v>
+        <v>6818158</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10380,18 +10386,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10410,10 +10410,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128927975</v>
+        <v>128927714</v>
       </c>
       <c r="B99" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10421,21 +10421,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430138</v>
+        <v>430630</v>
       </c>
       <c r="R99" t="n">
-        <v>6817903</v>
+        <v>6818207</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10507,10 +10507,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128927943</v>
+        <v>128927851</v>
       </c>
       <c r="B100" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10518,21 +10518,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430136</v>
+        <v>430135</v>
       </c>
       <c r="R100" t="n">
-        <v>6817849</v>
+        <v>6818172</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10604,10 +10604,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128927851</v>
+        <v>128927810</v>
       </c>
       <c r="B101" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10615,21 +10615,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>430135</v>
+        <v>430215</v>
       </c>
       <c r="R101" t="n">
-        <v>6818172</v>
+        <v>6818155</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10701,10 +10701,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128927980</v>
+        <v>128927803</v>
       </c>
       <c r="B102" t="n">
-        <v>78042</v>
+        <v>78792</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10712,21 +10712,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>430081</v>
+        <v>430580</v>
       </c>
       <c r="R102" t="n">
-        <v>6818119</v>
+        <v>6818253</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10798,10 +10798,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927793</v>
+        <v>128927856</v>
       </c>
       <c r="B103" t="n">
-        <v>58153</v>
+        <v>78791</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103001</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430104</v>
+        <v>430060</v>
       </c>
       <c r="R103" t="n">
-        <v>6817933</v>
+        <v>6818160</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11389,10 +11389,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927856</v>
+        <v>128927793</v>
       </c>
       <c r="B109" t="n">
-        <v>78791</v>
+        <v>58153</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11400,21 +11400,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>103001</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11424,10 +11424,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430060</v>
+        <v>430104</v>
       </c>
       <c r="R109" t="n">
-        <v>6818160</v>
+        <v>6817933</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128927870</v>
+        <v>128927740</v>
       </c>
       <c r="B115" t="n">
-        <v>78791</v>
+        <v>79624</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>430164</v>
+        <v>430401</v>
       </c>
       <c r="R115" t="n">
-        <v>6817854</v>
+        <v>6818062</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12068,10 +12068,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128927858</v>
+        <v>128927823</v>
       </c>
       <c r="B116" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12079,21 +12079,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>430034</v>
+        <v>429975</v>
       </c>
       <c r="R116" t="n">
-        <v>6818117</v>
+        <v>6818162</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128927873</v>
+        <v>128927901</v>
       </c>
       <c r="B117" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12176,21 +12176,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>429998</v>
+        <v>430501</v>
       </c>
       <c r="R117" t="n">
-        <v>6818047</v>
+        <v>6818013</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128927901</v>
+        <v>128927921</v>
       </c>
       <c r="B118" t="n">
         <v>79034</v>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>430501</v>
+        <v>430664</v>
       </c>
       <c r="R118" t="n">
-        <v>6818013</v>
+        <v>6818275</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12359,10 +12359,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128927921</v>
+        <v>128927870</v>
       </c>
       <c r="B119" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12370,21 +12370,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12394,10 +12394,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>430664</v>
+        <v>430164</v>
       </c>
       <c r="R119" t="n">
-        <v>6818275</v>
+        <v>6817854</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12456,10 +12456,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128927740</v>
+        <v>128927858</v>
       </c>
       <c r="B120" t="n">
-        <v>79624</v>
+        <v>78791</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12467,21 +12467,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12491,10 +12491,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>430401</v>
+        <v>430034</v>
       </c>
       <c r="R120" t="n">
-        <v>6818062</v>
+        <v>6818117</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12553,10 +12553,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128927823</v>
+        <v>128927873</v>
       </c>
       <c r="B121" t="n">
-        <v>78792</v>
+        <v>78791</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12564,21 +12564,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12588,10 +12588,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>429975</v>
+        <v>429998</v>
       </c>
       <c r="R121" t="n">
-        <v>6818162</v>
+        <v>6818047</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12954,10 +12954,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128927869</v>
+        <v>128927940</v>
       </c>
       <c r="B125" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,21 +12965,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12989,10 +12989,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>430138</v>
+        <v>429952</v>
       </c>
       <c r="R125" t="n">
-        <v>6817883</v>
+        <v>6818061</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13051,10 +13051,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128927720</v>
+        <v>128927918</v>
       </c>
       <c r="B126" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13062,21 +13062,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13086,10 +13086,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430112</v>
+        <v>430649</v>
       </c>
       <c r="R126" t="n">
-        <v>6818160</v>
+        <v>6818232</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13148,7 +13148,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128927940</v>
+        <v>128927878</v>
       </c>
       <c r="B127" t="n">
         <v>79034</v>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>429952</v>
+        <v>430632</v>
       </c>
       <c r="R127" t="n">
-        <v>6818061</v>
+        <v>6818282</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13245,10 +13245,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128927853</v>
+        <v>128927908</v>
       </c>
       <c r="B128" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13256,21 +13256,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430073</v>
+        <v>430425</v>
       </c>
       <c r="R128" t="n">
-        <v>6818201</v>
+        <v>6818197</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,7 +13342,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128927918</v>
+        <v>128927886</v>
       </c>
       <c r="B129" t="n">
         <v>79034</v>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430649</v>
+        <v>430424</v>
       </c>
       <c r="R129" t="n">
-        <v>6818232</v>
+        <v>6818252</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,10 +13439,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128927878</v>
+        <v>128927777</v>
       </c>
       <c r="B130" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13450,34 +13450,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>430632</v>
+        <v>429898</v>
       </c>
       <c r="R130" t="n">
-        <v>6818282</v>
+        <v>6818099</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13536,10 +13544,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128927908</v>
+        <v>128927784</v>
       </c>
       <c r="B131" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13547,34 +13555,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430425</v>
+        <v>430201</v>
       </c>
       <c r="R131" t="n">
-        <v>6818197</v>
+        <v>6818093</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13633,10 +13649,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128927886</v>
+        <v>128927769</v>
       </c>
       <c r="B132" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13644,34 +13660,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430424</v>
+        <v>430485</v>
       </c>
       <c r="R132" t="n">
-        <v>6818252</v>
+        <v>6818017</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13730,10 +13754,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128927777</v>
+        <v>128927869</v>
       </c>
       <c r="B133" t="n">
-        <v>57720</v>
+        <v>78791</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13741,42 +13765,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>429898</v>
+        <v>430138</v>
       </c>
       <c r="R133" t="n">
-        <v>6818099</v>
+        <v>6817883</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13835,10 +13851,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128927784</v>
+        <v>128927720</v>
       </c>
       <c r="B134" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13846,42 +13862,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430201</v>
+        <v>430112</v>
       </c>
       <c r="R134" t="n">
-        <v>6818093</v>
+        <v>6818160</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13940,10 +13948,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128927769</v>
+        <v>128927853</v>
       </c>
       <c r="B135" t="n">
-        <v>57720</v>
+        <v>78791</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13951,42 +13959,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430485</v>
+        <v>430073</v>
       </c>
       <c r="R135" t="n">
-        <v>6818017</v>
+        <v>6818201</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14045,7 +14045,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128927889</v>
+        <v>128927894</v>
       </c>
       <c r="B136" t="n">
         <v>79034</v>
@@ -14074,16 +14074,19 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430385</v>
+        <v>430321</v>
       </c>
       <c r="R136" t="n">
-        <v>6818203</v>
+        <v>6818095</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14118,12 +14121,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14142,10 +14151,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128927781</v>
+        <v>128927900</v>
       </c>
       <c r="B137" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14153,42 +14162,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430480</v>
+        <v>430467</v>
       </c>
       <c r="R137" t="n">
-        <v>6817997</v>
+        <v>6818020</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14247,10 +14248,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128927788</v>
+        <v>128927889</v>
       </c>
       <c r="B138" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14258,42 +14259,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430017</v>
+        <v>430385</v>
       </c>
       <c r="R138" t="n">
-        <v>6818044</v>
+        <v>6818203</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14352,10 +14345,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128927775</v>
+        <v>128927911</v>
       </c>
       <c r="B139" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14363,42 +14356,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430083</v>
+        <v>430437</v>
       </c>
       <c r="R139" t="n">
-        <v>6818224</v>
+        <v>6818227</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14457,10 +14442,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128927792</v>
+        <v>128927969</v>
       </c>
       <c r="B140" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14468,42 +14453,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430150</v>
+        <v>429947</v>
       </c>
       <c r="R140" t="n">
-        <v>6817814</v>
+        <v>6818135</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14562,10 +14539,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128927824</v>
+        <v>128927956</v>
       </c>
       <c r="B141" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14573,21 +14550,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14597,10 +14574,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>429941</v>
+        <v>430119</v>
       </c>
       <c r="R141" t="n">
-        <v>6818056</v>
+        <v>6818173</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14659,10 +14636,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128927748</v>
+        <v>128927925</v>
       </c>
       <c r="B142" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14670,21 +14647,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14694,10 +14671,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430202</v>
+        <v>430683</v>
       </c>
       <c r="R142" t="n">
-        <v>6818084</v>
+        <v>6818265</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14756,7 +14733,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128927894</v>
+        <v>128927972</v>
       </c>
       <c r="B143" t="n">
         <v>79034</v>
@@ -14794,10 +14771,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430321</v>
+        <v>430018</v>
       </c>
       <c r="R143" t="n">
-        <v>6818095</v>
+        <v>6818025</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14830,11 +14807,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14862,7 +14834,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128927900</v>
+        <v>128927926</v>
       </c>
       <c r="B144" t="n">
         <v>79034</v>
@@ -14897,10 +14869,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430467</v>
+        <v>430701</v>
       </c>
       <c r="R144" t="n">
-        <v>6818020</v>
+        <v>6818261</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15056,10 +15028,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128927911</v>
+        <v>128927709</v>
       </c>
       <c r="B146" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15067,21 +15039,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15091,10 +15063,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430437</v>
+        <v>430495</v>
       </c>
       <c r="R146" t="n">
-        <v>6818227</v>
+        <v>6818056</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15153,10 +15125,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128927969</v>
+        <v>128927861</v>
       </c>
       <c r="B147" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15164,21 +15136,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15188,10 +15160,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>429947</v>
+        <v>429989</v>
       </c>
       <c r="R147" t="n">
-        <v>6818135</v>
+        <v>6818159</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15250,45 +15222,54 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927709</v>
+        <v>128927833</v>
       </c>
       <c r="B148" t="n">
-        <v>79653</v>
+        <v>8450</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430495</v>
+        <v>430204</v>
       </c>
       <c r="R148" t="n">
-        <v>6818056</v>
+        <v>6817811</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15329,6 +15310,7 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -15347,10 +15329,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927956</v>
+        <v>128927781</v>
       </c>
       <c r="B149" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15358,34 +15340,42 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430119</v>
+        <v>430480</v>
       </c>
       <c r="R149" t="n">
-        <v>6818173</v>
+        <v>6817997</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15444,10 +15434,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927925</v>
+        <v>128927788</v>
       </c>
       <c r="B150" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15455,34 +15445,42 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430683</v>
+        <v>430017</v>
       </c>
       <c r="R150" t="n">
-        <v>6818265</v>
+        <v>6818044</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15541,10 +15539,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927972</v>
+        <v>128927775</v>
       </c>
       <c r="B151" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15552,26 +15550,31 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -15579,10 +15582,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430018</v>
+        <v>430083</v>
       </c>
       <c r="R151" t="n">
-        <v>6818025</v>
+        <v>6818224</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15623,7 +15626,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -15642,10 +15644,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128927861</v>
+        <v>128927792</v>
       </c>
       <c r="B152" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15653,34 +15655,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>429989</v>
+        <v>430150</v>
       </c>
       <c r="R152" t="n">
-        <v>6818159</v>
+        <v>6817814</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15739,10 +15749,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128927926</v>
+        <v>128927824</v>
       </c>
       <c r="B153" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15750,21 +15760,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15774,10 +15784,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>430701</v>
+        <v>429941</v>
       </c>
       <c r="R153" t="n">
-        <v>6818261</v>
+        <v>6818056</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15836,54 +15846,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128927833</v>
+        <v>128927748</v>
       </c>
       <c r="B154" t="n">
-        <v>8450</v>
+        <v>79624</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430204</v>
+        <v>430202</v>
       </c>
       <c r="R154" t="n">
-        <v>6817811</v>
+        <v>6818084</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15924,7 +15925,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -15943,10 +15943,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128927798</v>
+        <v>128927917</v>
       </c>
       <c r="B155" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15954,21 +15954,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15978,10 +15978,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>430315</v>
+        <v>430616</v>
       </c>
       <c r="R155" t="n">
-        <v>6818095</v>
+        <v>6818194</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16040,10 +16040,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128927828</v>
+        <v>128927903</v>
       </c>
       <c r="B156" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16051,21 +16051,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16078,10 +16078,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>430115</v>
+        <v>430437</v>
       </c>
       <c r="R156" t="n">
-        <v>6817902</v>
+        <v>6818119</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16114,6 +16114,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Måttligt/rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16141,7 +16146,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128927917</v>
+        <v>128927920</v>
       </c>
       <c r="B157" t="n">
         <v>79034</v>
@@ -16176,10 +16181,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430616</v>
+        <v>430637</v>
       </c>
       <c r="R157" t="n">
-        <v>6818194</v>
+        <v>6818260</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16238,7 +16243,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128927903</v>
+        <v>128927951</v>
       </c>
       <c r="B158" t="n">
         <v>79034</v>
@@ -16276,10 +16281,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430437</v>
+        <v>430191</v>
       </c>
       <c r="R158" t="n">
-        <v>6818119</v>
+        <v>6817932</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16316,7 +16321,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Måttligt/rikligt med garnlav inom en radie av 40m</t>
+          <t>Garnlav, måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16344,10 +16349,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128927875</v>
+        <v>128927958</v>
       </c>
       <c r="B159" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16355,21 +16360,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16379,10 +16384,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430127</v>
+        <v>430048</v>
       </c>
       <c r="R159" t="n">
-        <v>6817846</v>
+        <v>6818232</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16441,7 +16446,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128927920</v>
+        <v>128927902</v>
       </c>
       <c r="B160" t="n">
         <v>79034</v>
@@ -16476,10 +16481,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430637</v>
+        <v>430530</v>
       </c>
       <c r="R160" t="n">
-        <v>6818260</v>
+        <v>6818025</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16538,7 +16543,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128927838</v>
+        <v>128927875</v>
       </c>
       <c r="B161" t="n">
         <v>78791</v>
@@ -16573,10 +16578,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430439</v>
+        <v>430127</v>
       </c>
       <c r="R161" t="n">
-        <v>6818031</v>
+        <v>6817846</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16635,7 +16640,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128927837</v>
+        <v>128927838</v>
       </c>
       <c r="B162" t="n">
         <v>78791</v>
@@ -16670,10 +16675,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430360</v>
+        <v>430439</v>
       </c>
       <c r="R162" t="n">
-        <v>6818057</v>
+        <v>6818031</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16732,10 +16737,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128927951</v>
+        <v>128927837</v>
       </c>
       <c r="B163" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16743,37 +16748,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430191</v>
+        <v>430360</v>
       </c>
       <c r="R163" t="n">
-        <v>6817932</v>
+        <v>6818057</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16808,18 +16810,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Garnlav, måttligt inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -16838,10 +16834,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128927958</v>
+        <v>128927846</v>
       </c>
       <c r="B164" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16849,21 +16845,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16873,10 +16869,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430048</v>
+        <v>430241</v>
       </c>
       <c r="R164" t="n">
-        <v>6818232</v>
+        <v>6818085</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16935,10 +16931,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128927846</v>
+        <v>128927779</v>
       </c>
       <c r="B165" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16946,34 +16942,42 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430241</v>
+        <v>430106</v>
       </c>
       <c r="R165" t="n">
-        <v>6818085</v>
+        <v>6817957</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17032,10 +17036,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128927902</v>
+        <v>128927783</v>
       </c>
       <c r="B166" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17043,34 +17047,42 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>430530</v>
+        <v>430174</v>
       </c>
       <c r="R166" t="n">
-        <v>6818025</v>
+        <v>6817923</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17129,10 +17141,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128927779</v>
+        <v>128927798</v>
       </c>
       <c r="B167" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17140,42 +17152,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430106</v>
+        <v>430315</v>
       </c>
       <c r="R167" t="n">
-        <v>6817957</v>
+        <v>6818095</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17234,10 +17238,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128927783</v>
+        <v>128927828</v>
       </c>
       <c r="B168" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17245,31 +17249,26 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -17277,10 +17276,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430174</v>
+        <v>430115</v>
       </c>
       <c r="R168" t="n">
-        <v>6817923</v>
+        <v>6817902</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17321,6 +17320,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17339,48 +17339,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128927933</v>
+        <v>128927835</v>
       </c>
       <c r="B169" t="n">
-        <v>79034</v>
+        <v>58093</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>430220</v>
+        <v>430104</v>
       </c>
       <c r="R169" t="n">
-        <v>6818148</v>
+        <v>6817960</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17415,18 +17412,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -17445,10 +17436,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128927737</v>
+        <v>128927829</v>
       </c>
       <c r="B170" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17456,37 +17447,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430143</v>
+        <v>430138</v>
       </c>
       <c r="R170" t="n">
-        <v>6817831</v>
+        <v>6817883</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17527,7 +17515,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -17546,10 +17533,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128927904</v>
+        <v>128927737</v>
       </c>
       <c r="B171" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17557,34 +17544,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430405</v>
+        <v>430143</v>
       </c>
       <c r="R171" t="n">
-        <v>6818117</v>
+        <v>6817831</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17625,6 +17615,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -17643,10 +17634,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128927712</v>
+        <v>128927981</v>
       </c>
       <c r="B172" t="n">
-        <v>79653</v>
+        <v>78042</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17654,21 +17645,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17678,10 +17669,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430596</v>
+        <v>430056</v>
       </c>
       <c r="R172" t="n">
-        <v>6818190</v>
+        <v>6818166</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17740,10 +17731,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128927981</v>
+        <v>128927712</v>
       </c>
       <c r="B173" t="n">
-        <v>78042</v>
+        <v>79653</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17751,21 +17742,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17775,10 +17766,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430056</v>
+        <v>430596</v>
       </c>
       <c r="R173" t="n">
-        <v>6818166</v>
+        <v>6818190</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17837,10 +17828,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128927829</v>
+        <v>128927933</v>
       </c>
       <c r="B174" t="n">
-        <v>78792</v>
+        <v>79034</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17848,34 +17839,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430138</v>
+        <v>430220</v>
       </c>
       <c r="R174" t="n">
-        <v>6817883</v>
+        <v>6818148</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17910,12 +17904,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -17934,32 +17934,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128927835</v>
+        <v>128927904</v>
       </c>
       <c r="B175" t="n">
-        <v>58093</v>
+        <v>79034</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17969,10 +17969,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430104</v>
+        <v>430405</v>
       </c>
       <c r="R175" t="n">
-        <v>6817960</v>
+        <v>6818117</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18031,53 +18031,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128927762</v>
+        <v>128927898</v>
       </c>
       <c r="B176" t="n">
-        <v>56913</v>
+        <v>79034</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430394</v>
+        <v>430384</v>
       </c>
       <c r="R176" t="n">
-        <v>6818168</v>
+        <v>6818048</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18136,53 +18128,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128927760</v>
+        <v>128927968</v>
       </c>
       <c r="B177" t="n">
-        <v>56913</v>
+        <v>79034</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430663</v>
+        <v>430067</v>
       </c>
       <c r="R177" t="n">
-        <v>6818259</v>
+        <v>6818139</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18241,7 +18225,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128927898</v>
+        <v>128927952</v>
       </c>
       <c r="B178" t="n">
         <v>79034</v>
@@ -18276,10 +18260,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430384</v>
+        <v>430190</v>
       </c>
       <c r="R178" t="n">
-        <v>6818048</v>
+        <v>6817925</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18338,10 +18322,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128927723</v>
+        <v>128927945</v>
       </c>
       <c r="B179" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18349,21 +18333,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18373,10 +18357,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>429993</v>
+        <v>430404</v>
       </c>
       <c r="R179" t="n">
-        <v>6818157</v>
+        <v>6818178</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18435,10 +18419,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128927848</v>
+        <v>128927750</v>
       </c>
       <c r="B180" t="n">
-        <v>78791</v>
+        <v>79624</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18446,21 +18430,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18470,10 +18454,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430174</v>
+        <v>430140</v>
       </c>
       <c r="R180" t="n">
-        <v>6818156</v>
+        <v>6817881</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18532,10 +18516,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128927968</v>
+        <v>128927741</v>
       </c>
       <c r="B181" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18543,21 +18527,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18567,10 +18551,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430067</v>
+        <v>430600</v>
       </c>
       <c r="R181" t="n">
-        <v>6818139</v>
+        <v>6818203</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18629,10 +18613,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128927952</v>
+        <v>128927812</v>
       </c>
       <c r="B182" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18640,21 +18624,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18664,10 +18648,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430190</v>
+        <v>430157</v>
       </c>
       <c r="R182" t="n">
-        <v>6817925</v>
+        <v>6818149</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18726,10 +18710,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128927945</v>
+        <v>128927723</v>
       </c>
       <c r="B183" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18737,21 +18721,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18761,10 +18745,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430404</v>
+        <v>429993</v>
       </c>
       <c r="R183" t="n">
-        <v>6818178</v>
+        <v>6818157</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18823,10 +18807,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128927750</v>
+        <v>128927848</v>
       </c>
       <c r="B184" t="n">
-        <v>79624</v>
+        <v>78791</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18834,21 +18818,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18858,10 +18842,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430140</v>
+        <v>430174</v>
       </c>
       <c r="R184" t="n">
-        <v>6817881</v>
+        <v>6818156</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18920,45 +18904,53 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128927741</v>
+        <v>128927760</v>
       </c>
       <c r="B185" t="n">
-        <v>79624</v>
+        <v>56913</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430600</v>
+        <v>430663</v>
       </c>
       <c r="R185" t="n">
-        <v>6818203</v>
+        <v>6818259</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19017,45 +19009,53 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128927812</v>
+        <v>128927762</v>
       </c>
       <c r="B186" t="n">
-        <v>78792</v>
+        <v>56913</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430157</v>
+        <v>430394</v>
       </c>
       <c r="R186" t="n">
-        <v>6818149</v>
+        <v>6818168</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19114,10 +19114,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128927789</v>
+        <v>128927731</v>
       </c>
       <c r="B187" t="n">
-        <v>57720</v>
+        <v>79653</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19125,42 +19125,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430089</v>
+        <v>430056</v>
       </c>
       <c r="R187" t="n">
-        <v>6817965</v>
+        <v>6818017</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19193,11 +19185,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19224,10 +19211,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128927910</v>
+        <v>128927847</v>
       </c>
       <c r="B188" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19235,21 +19222,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19259,10 +19246,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430430</v>
+        <v>430227</v>
       </c>
       <c r="R188" t="n">
-        <v>6818202</v>
+        <v>6818154</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19321,10 +19308,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128927731</v>
+        <v>128927872</v>
       </c>
       <c r="B189" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19332,21 +19319,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19356,10 +19343,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430056</v>
+        <v>430227</v>
       </c>
       <c r="R189" t="n">
-        <v>6818017</v>
+        <v>6818015</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19418,10 +19405,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128927847</v>
+        <v>128927728</v>
       </c>
       <c r="B190" t="n">
-        <v>78791</v>
+        <v>79653</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19429,21 +19416,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19453,10 +19440,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430227</v>
+        <v>430232</v>
       </c>
       <c r="R190" t="n">
-        <v>6818154</v>
+        <v>6818068</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19515,7 +19502,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128927892</v>
+        <v>128927910</v>
       </c>
       <c r="B191" t="n">
         <v>79034</v>
@@ -19550,10 +19537,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430304</v>
+        <v>430430</v>
       </c>
       <c r="R191" t="n">
-        <v>6818124</v>
+        <v>6818202</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19612,10 +19599,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128927872</v>
+        <v>128927892</v>
       </c>
       <c r="B192" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19623,21 +19610,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19647,10 +19634,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430227</v>
+        <v>430304</v>
       </c>
       <c r="R192" t="n">
-        <v>6818015</v>
+        <v>6818124</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19709,10 +19696,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128927728</v>
+        <v>128927906</v>
       </c>
       <c r="B193" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19720,34 +19707,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430232</v>
+        <v>430401</v>
       </c>
       <c r="R193" t="n">
-        <v>6818068</v>
+        <v>6818157</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19782,12 +19772,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -19806,7 +19802,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128927906</v>
+        <v>128927922</v>
       </c>
       <c r="B194" t="n">
         <v>79034</v>
@@ -19835,19 +19831,16 @@
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430401</v>
+        <v>430668</v>
       </c>
       <c r="R194" t="n">
-        <v>6818157</v>
+        <v>6818241</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19882,18 +19875,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
-        </is>
-      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
@@ -19912,7 +19899,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128927922</v>
+        <v>128927962</v>
       </c>
       <c r="B195" t="n">
         <v>79034</v>
@@ -19947,10 +19934,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430668</v>
+        <v>430069</v>
       </c>
       <c r="R195" t="n">
-        <v>6818241</v>
+        <v>6818225</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20009,10 +19996,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128927962</v>
+        <v>128927789</v>
       </c>
       <c r="B196" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20020,34 +20007,42 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430069</v>
+        <v>430089</v>
       </c>
       <c r="R196" t="n">
-        <v>6818225</v>
+        <v>6817965</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20080,6 +20075,11 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20502,10 +20502,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128927841</v>
+        <v>128927936</v>
       </c>
       <c r="B201" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20513,21 +20513,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20537,10 +20537,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430569</v>
+        <v>430084</v>
       </c>
       <c r="R201" t="n">
-        <v>6818243</v>
+        <v>6818157</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20599,7 +20599,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128927936</v>
+        <v>128927961</v>
       </c>
       <c r="B202" t="n">
         <v>79034</v>
@@ -20634,10 +20634,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430084</v>
+        <v>430086</v>
       </c>
       <c r="R202" t="n">
-        <v>6818157</v>
+        <v>6818236</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20696,10 +20696,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128927717</v>
+        <v>128927942</v>
       </c>
       <c r="B203" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20707,21 +20707,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20731,7 +20731,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430214</v>
+        <v>430087</v>
       </c>
       <c r="R203" t="n">
         <v>6817971</v>
@@ -20793,10 +20793,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128927715</v>
+        <v>128927841</v>
       </c>
       <c r="B204" t="n">
-        <v>79653</v>
+        <v>78791</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20804,21 +20804,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20828,10 +20828,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430650</v>
+        <v>430569</v>
       </c>
       <c r="R204" t="n">
-        <v>6818249</v>
+        <v>6818243</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20890,10 +20890,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128927961</v>
+        <v>128927717</v>
       </c>
       <c r="B205" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20901,21 +20901,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430086</v>
+        <v>430214</v>
       </c>
       <c r="R205" t="n">
-        <v>6818236</v>
+        <v>6817971</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20987,10 +20987,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128927942</v>
+        <v>128927715</v>
       </c>
       <c r="B206" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20998,21 +20998,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21022,10 +21022,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430087</v>
+        <v>430650</v>
       </c>
       <c r="R206" t="n">
-        <v>6817971</v>
+        <v>6818249</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21375,10 +21375,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128927753</v>
+        <v>128927941</v>
       </c>
       <c r="B210" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21386,42 +21386,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430514</v>
+        <v>430078</v>
       </c>
       <c r="R210" t="n">
-        <v>6818047</v>
+        <v>6817995</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21577,7 +21569,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128927866</v>
+        <v>128927860</v>
       </c>
       <c r="B212" t="n">
         <v>78791</v>
@@ -21612,10 +21604,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>429950</v>
+        <v>430013</v>
       </c>
       <c r="R212" t="n">
-        <v>6818057</v>
+        <v>6818142</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21674,7 +21666,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128927860</v>
+        <v>128927866</v>
       </c>
       <c r="B213" t="n">
         <v>78791</v>
@@ -21709,10 +21701,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>430013</v>
+        <v>429950</v>
       </c>
       <c r="R213" t="n">
-        <v>6818142</v>
+        <v>6818057</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21771,10 +21763,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128927941</v>
+        <v>128927753</v>
       </c>
       <c r="B214" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21782,34 +21774,42 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>430078</v>
+        <v>430514</v>
       </c>
       <c r="R214" t="n">
-        <v>6817995</v>
+        <v>6818047</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22454,10 +22454,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128927867</v>
+        <v>128927881</v>
       </c>
       <c r="B221" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22465,21 +22465,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -22489,10 +22489,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430006</v>
+        <v>430536</v>
       </c>
       <c r="R221" t="n">
-        <v>6818034</v>
+        <v>6818208</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22551,7 +22551,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128927881</v>
+        <v>128927916</v>
       </c>
       <c r="B222" t="n">
         <v>79034</v>
@@ -22586,10 +22586,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430536</v>
+        <v>430580</v>
       </c>
       <c r="R222" t="n">
-        <v>6818208</v>
+        <v>6818221</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22648,10 +22648,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128927916</v>
+        <v>128927867</v>
       </c>
       <c r="B223" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22659,21 +22659,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22683,10 +22683,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430580</v>
+        <v>430006</v>
       </c>
       <c r="R223" t="n">
-        <v>6818221</v>
+        <v>6818034</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22850,10 +22850,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128927850</v>
+        <v>128927890</v>
       </c>
       <c r="B225" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22861,21 +22861,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22885,10 +22885,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430159</v>
+        <v>430348</v>
       </c>
       <c r="R225" t="n">
-        <v>6818161</v>
+        <v>6818167</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22947,7 +22947,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128927890</v>
+        <v>128927915</v>
       </c>
       <c r="B226" t="n">
         <v>79034</v>
@@ -22976,16 +22976,19 @@
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430348</v>
+        <v>430575</v>
       </c>
       <c r="R226" t="n">
-        <v>6818167</v>
+        <v>6818234</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23026,6 +23029,7 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
+      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
@@ -23044,10 +23048,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128927730</v>
+        <v>128927923</v>
       </c>
       <c r="B227" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23055,21 +23059,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23079,10 +23083,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430075</v>
+        <v>430670</v>
       </c>
       <c r="R227" t="n">
-        <v>6818213</v>
+        <v>6818263</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23141,10 +23145,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128927915</v>
+        <v>128927850</v>
       </c>
       <c r="B228" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23152,37 +23156,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430575</v>
+        <v>430159</v>
       </c>
       <c r="R228" t="n">
-        <v>6818234</v>
+        <v>6818161</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23223,7 +23224,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -23242,10 +23242,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128927923</v>
+        <v>128927730</v>
       </c>
       <c r="B229" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23253,21 +23253,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23277,10 +23277,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430670</v>
+        <v>430075</v>
       </c>
       <c r="R229" t="n">
-        <v>6818263</v>
+        <v>6818213</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128927732</v>
+        <v>128927821</v>
       </c>
       <c r="B22" t="n">
-        <v>79653</v>
+        <v>78793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430138</v>
+        <v>429994</v>
       </c>
       <c r="R22" t="n">
-        <v>6817883</v>
+        <v>6818158</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927868</v>
+        <v>128927802</v>
       </c>
       <c r="B23" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430089</v>
+        <v>430567</v>
       </c>
       <c r="R23" t="n">
-        <v>6817984</v>
+        <v>6818243</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927843</v>
+        <v>128927935</v>
       </c>
       <c r="B24" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430626</v>
+        <v>430099</v>
       </c>
       <c r="R24" t="n">
-        <v>6818202</v>
+        <v>6818154</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927721</v>
+        <v>128927963</v>
       </c>
       <c r="B25" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,21 +3153,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430060</v>
+        <v>430064</v>
       </c>
       <c r="R25" t="n">
-        <v>6818156</v>
+        <v>6818190</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927726</v>
+        <v>128927732</v>
       </c>
       <c r="B26" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430114</v>
+        <v>430138</v>
       </c>
       <c r="R26" t="n">
-        <v>6817912</v>
+        <v>6817883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927950</v>
+        <v>128927721</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3347,21 +3347,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430233</v>
+        <v>430060</v>
       </c>
       <c r="R27" t="n">
-        <v>6817831</v>
+        <v>6818156</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927880</v>
+        <v>128927726</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430577</v>
+        <v>430114</v>
       </c>
       <c r="R28" t="n">
-        <v>6818221</v>
+        <v>6817912</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927978</v>
+        <v>128927770</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,34 +3541,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430082</v>
+        <v>430455</v>
       </c>
       <c r="R29" t="n">
-        <v>6818210</v>
+        <v>6818246</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3609,7 +3617,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3628,10 +3635,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927935</v>
+        <v>128927950</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3663,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430099</v>
+        <v>430233</v>
       </c>
       <c r="R30" t="n">
-        <v>6818154</v>
+        <v>6817831</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,10 +3732,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927963</v>
+        <v>128927880</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3760,10 +3767,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430064</v>
+        <v>430577</v>
       </c>
       <c r="R31" t="n">
-        <v>6818190</v>
+        <v>6818221</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,10 +3829,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128927770</v>
+        <v>128927868</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3833,42 +3840,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430455</v>
+        <v>430089</v>
       </c>
       <c r="R32" t="n">
-        <v>6818246</v>
+        <v>6817984</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,32 +3926,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128927834</v>
+        <v>128927978</v>
       </c>
       <c r="B33" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3962,10 +3961,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>430596</v>
+        <v>430082</v>
       </c>
       <c r="R33" t="n">
-        <v>6818184</v>
+        <v>6818210</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4006,6 +4005,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128927821</v>
+        <v>128927843</v>
       </c>
       <c r="B34" t="n">
         <v>78792</v>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>429994</v>
+        <v>430626</v>
       </c>
       <c r="R34" t="n">
-        <v>6818158</v>
+        <v>6818202</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128927802</v>
+        <v>128927834</v>
       </c>
       <c r="B35" t="n">
-        <v>78792</v>
+        <v>58093</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430567</v>
+        <v>430596</v>
       </c>
       <c r="R35" t="n">
-        <v>6818243</v>
+        <v>6818184</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128927895</v>
+        <v>128927871</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>430350</v>
+        <v>430145</v>
       </c>
       <c r="R36" t="n">
-        <v>6818053</v>
+        <v>6817833</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128927939</v>
+        <v>128927773</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4326,34 +4326,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>429903</v>
+        <v>430251</v>
       </c>
       <c r="R37" t="n">
-        <v>6818059</v>
+        <v>6818033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4412,10 +4420,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128927973</v>
+        <v>128927895</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4441,19 +4449,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430073</v>
+        <v>430350</v>
       </c>
       <c r="R38" t="n">
-        <v>6818021</v>
+        <v>6818053</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4494,7 +4499,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4513,10 +4517,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128927871</v>
+        <v>128927939</v>
       </c>
       <c r="B39" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4524,21 +4528,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4548,10 +4552,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430145</v>
+        <v>429903</v>
       </c>
       <c r="R39" t="n">
-        <v>6817833</v>
+        <v>6818059</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4610,10 +4614,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128927773</v>
+        <v>128927973</v>
       </c>
       <c r="B40" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,31 +4625,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4653,10 +4652,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>430251</v>
+        <v>430073</v>
       </c>
       <c r="R40" t="n">
-        <v>6818033</v>
+        <v>6818021</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4697,6 +4696,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128927743</v>
+        <v>128927813</v>
       </c>
       <c r="B41" t="n">
-        <v>79624</v>
+        <v>78793</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430211</v>
+        <v>430145</v>
       </c>
       <c r="R41" t="n">
-        <v>6817980</v>
+        <v>6818165</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128927813</v>
+        <v>128927743</v>
       </c>
       <c r="B42" t="n">
-        <v>78792</v>
+        <v>79625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>430145</v>
+        <v>430211</v>
       </c>
       <c r="R42" t="n">
-        <v>6818165</v>
+        <v>6817980</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128927930</v>
+        <v>128927845</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430205</v>
+        <v>430669</v>
       </c>
       <c r="R43" t="n">
-        <v>6817961</v>
+        <v>6818249</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128927928</v>
+        <v>128927930</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430293</v>
+        <v>430205</v>
       </c>
       <c r="R44" t="n">
-        <v>6817871</v>
+        <v>6817961</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128927934</v>
+        <v>128927928</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430088</v>
+        <v>430293</v>
       </c>
       <c r="R45" t="n">
-        <v>6818186</v>
+        <v>6817871</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128927938</v>
+        <v>128927934</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>429959</v>
+        <v>430088</v>
       </c>
       <c r="R46" t="n">
-        <v>6818128</v>
+        <v>6818186</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128927976</v>
+        <v>128927938</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5326,19 +5326,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430149</v>
+        <v>429959</v>
       </c>
       <c r="R47" t="n">
-        <v>6817860</v>
+        <v>6818128</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5379,7 +5376,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5398,10 +5394,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128927966</v>
+        <v>128927976</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5427,16 +5423,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430071</v>
+        <v>430149</v>
       </c>
       <c r="R48" t="n">
-        <v>6818124</v>
+        <v>6817860</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5477,6 +5476,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5495,10 +5495,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128927845</v>
+        <v>128927966</v>
       </c>
       <c r="B49" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430669</v>
+        <v>430071</v>
       </c>
       <c r="R49" t="n">
-        <v>6818249</v>
+        <v>6818124</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,7 +5595,7 @@
         <v>128927842</v>
       </c>
       <c r="B50" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>128927805</v>
       </c>
       <c r="B52" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>128927819</v>
       </c>
       <c r="B53" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>128927799</v>
       </c>
       <c r="B54" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>128927806</v>
       </c>
       <c r="B55" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>128927937</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128927970</v>
+        <v>128927874</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6295,21 +6295,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>429900</v>
+        <v>430154</v>
       </c>
       <c r="R57" t="n">
-        <v>6818098</v>
+        <v>6817859</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6355,11 +6355,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6386,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128927944</v>
+        <v>128927970</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6415,19 +6410,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430531</v>
+        <v>429900</v>
       </c>
       <c r="R58" t="n">
-        <v>6818016</v>
+        <v>6818098</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6462,13 +6454,17 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6487,10 +6483,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927948</v>
+        <v>128927944</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6516,16 +6512,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430655</v>
+        <v>430531</v>
       </c>
       <c r="R59" t="n">
-        <v>6818216</v>
+        <v>6818016</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6566,6 +6565,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927882</v>
+        <v>128927948</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430526</v>
+        <v>430655</v>
       </c>
       <c r="R60" t="n">
-        <v>6818232</v>
+        <v>6818216</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128927929</v>
+        <v>128927882</v>
       </c>
       <c r="B61" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430208</v>
+        <v>430526</v>
       </c>
       <c r="R61" t="n">
-        <v>6817816</v>
+        <v>6818232</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128927874</v>
+        <v>128927929</v>
       </c>
       <c r="B62" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430154</v>
+        <v>430208</v>
       </c>
       <c r="R62" t="n">
-        <v>6817859</v>
+        <v>6817816</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6875,10 +6875,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128927735</v>
+        <v>128927855</v>
       </c>
       <c r="B63" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6886,21 +6886,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430132</v>
+        <v>430113</v>
       </c>
       <c r="R63" t="n">
-        <v>6817858</v>
+        <v>6818160</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6972,10 +6972,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128927855</v>
+        <v>128927815</v>
       </c>
       <c r="B64" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430113</v>
+        <v>430061</v>
       </c>
       <c r="R64" t="n">
-        <v>6818160</v>
+        <v>6818258</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128927815</v>
+        <v>128927735</v>
       </c>
       <c r="B65" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430061</v>
+        <v>430132</v>
       </c>
       <c r="R65" t="n">
-        <v>6818258</v>
+        <v>6817858</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128927893</v>
+        <v>128927790</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7177,34 +7177,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430286</v>
+        <v>430130</v>
       </c>
       <c r="R66" t="n">
-        <v>6818100</v>
+        <v>6817856</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7263,10 +7271,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128927974</v>
+        <v>128927893</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7298,10 +7306,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430091</v>
+        <v>430286</v>
       </c>
       <c r="R67" t="n">
-        <v>6818012</v>
+        <v>6818100</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7360,10 +7368,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128927790</v>
+        <v>128927974</v>
       </c>
       <c r="B68" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7371,42 +7379,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430130</v>
+        <v>430091</v>
       </c>
       <c r="R68" t="n">
-        <v>6817856</v>
+        <v>6818012</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7573,7 +7573,7 @@
         <v>128927825</v>
       </c>
       <c r="B70" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7667,10 +7667,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128927710</v>
+        <v>128927857</v>
       </c>
       <c r="B71" t="n">
-        <v>79653</v>
+        <v>78792</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,21 +7678,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430610</v>
+        <v>430051</v>
       </c>
       <c r="R71" t="n">
-        <v>6818230</v>
+        <v>6818114</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,10 +7764,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128927839</v>
+        <v>128927710</v>
       </c>
       <c r="B72" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7775,21 +7775,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>430489</v>
+        <v>430610</v>
       </c>
       <c r="R72" t="n">
-        <v>6818084</v>
+        <v>6818230</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7861,10 +7861,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128927857</v>
+        <v>128927839</v>
       </c>
       <c r="B73" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>430051</v>
+        <v>430489</v>
       </c>
       <c r="R73" t="n">
-        <v>6818114</v>
+        <v>6818084</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
         <v>128927852</v>
       </c>
       <c r="B74" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>128927831</v>
       </c>
       <c r="B75" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>128927924</v>
       </c>
       <c r="B76" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>128927964</v>
       </c>
       <c r="B77" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>128927897</v>
       </c>
       <c r="B78" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>128927955</v>
       </c>
       <c r="B79" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>128927905</v>
       </c>
       <c r="B80" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>128927885</v>
       </c>
       <c r="B81" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>128927947</v>
       </c>
       <c r="B82" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>128927912</v>
       </c>
       <c r="B83" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8946,10 +8946,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128927840</v>
+        <v>128927795</v>
       </c>
       <c r="B84" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8957,21 +8957,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430407</v>
+        <v>430390</v>
       </c>
       <c r="R84" t="n">
-        <v>6818114</v>
+        <v>6818205</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9043,10 +9043,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128927865</v>
+        <v>128927811</v>
       </c>
       <c r="B85" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9054,21 +9054,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>429935</v>
+        <v>430176</v>
       </c>
       <c r="R85" t="n">
-        <v>6818065</v>
+        <v>6818150</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9140,10 +9140,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128927725</v>
+        <v>128927832</v>
       </c>
       <c r="B86" t="n">
-        <v>79653</v>
+        <v>78793</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9151,21 +9151,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430040</v>
+        <v>430153</v>
       </c>
       <c r="R86" t="n">
-        <v>6818029</v>
+        <v>6817822</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9237,7 +9237,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128927795</v>
+        <v>128927840</v>
       </c>
       <c r="B87" t="n">
         <v>78792</v>
@@ -9248,21 +9248,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>430390</v>
+        <v>430407</v>
       </c>
       <c r="R87" t="n">
-        <v>6818205</v>
+        <v>6818114</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128927811</v>
+        <v>128927865</v>
       </c>
       <c r="B88" t="n">
         <v>78792</v>
@@ -9345,21 +9345,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>430176</v>
+        <v>429935</v>
       </c>
       <c r="R88" t="n">
-        <v>6818150</v>
+        <v>6818065</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128927832</v>
+        <v>128927725</v>
       </c>
       <c r="B89" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>430153</v>
+        <v>430040</v>
       </c>
       <c r="R89" t="n">
-        <v>6817822</v>
+        <v>6818029</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9531,7 +9531,7 @@
         <v>128927794</v>
       </c>
       <c r="B90" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128927891</v>
+        <v>128927980</v>
       </c>
       <c r="B91" t="n">
-        <v>79034</v>
+        <v>78043</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9636,21 +9636,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430336</v>
+        <v>430081</v>
       </c>
       <c r="R91" t="n">
-        <v>6818151</v>
+        <v>6818119</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128927884</v>
+        <v>128927891</v>
       </c>
       <c r="B92" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430423</v>
+        <v>430336</v>
       </c>
       <c r="R92" t="n">
-        <v>6818270</v>
+        <v>6818151</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128927965</v>
+        <v>128927884</v>
       </c>
       <c r="B93" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430115</v>
+        <v>430423</v>
       </c>
       <c r="R93" t="n">
-        <v>6818177</v>
+        <v>6818270</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9916,10 +9916,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128927932</v>
+        <v>128927965</v>
       </c>
       <c r="B94" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9945,19 +9945,16 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430240</v>
+        <v>430115</v>
       </c>
       <c r="R94" t="n">
-        <v>6817987</v>
+        <v>6818177</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9992,18 +9989,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10022,10 +10013,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128927975</v>
+        <v>128927932</v>
       </c>
       <c r="B95" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10051,16 +10042,19 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430138</v>
+        <v>430240</v>
       </c>
       <c r="R95" t="n">
-        <v>6817903</v>
+        <v>6817987</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10095,12 +10089,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10119,10 +10119,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128927943</v>
+        <v>128927975</v>
       </c>
       <c r="B96" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10154,10 +10154,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430136</v>
+        <v>430138</v>
       </c>
       <c r="R96" t="n">
-        <v>6817849</v>
+        <v>6817903</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10216,10 +10216,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128927980</v>
+        <v>128927943</v>
       </c>
       <c r="B97" t="n">
-        <v>78042</v>
+        <v>79035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10227,21 +10227,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430081</v>
+        <v>430136</v>
       </c>
       <c r="R97" t="n">
-        <v>6818119</v>
+        <v>6817849</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10316,7 +10316,7 @@
         <v>128927864</v>
       </c>
       <c r="B98" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>128927714</v>
       </c>
       <c r="B99" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>128927851</v>
       </c>
       <c r="B100" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>128927810</v>
       </c>
       <c r="B101" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>128927803</v>
       </c>
       <c r="B102" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927856</v>
+        <v>128927899</v>
       </c>
       <c r="B103" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430060</v>
+        <v>430428</v>
       </c>
       <c r="R103" t="n">
-        <v>6818160</v>
+        <v>6818038</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927899</v>
+        <v>128927954</v>
       </c>
       <c r="B104" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10924,16 +10924,19 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430428</v>
+        <v>430166</v>
       </c>
       <c r="R104" t="n">
-        <v>6818038</v>
+        <v>6818134</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10968,12 +10971,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -10992,10 +11001,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927954</v>
+        <v>128927888</v>
       </c>
       <c r="B105" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11021,19 +11030,16 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430166</v>
+        <v>430399</v>
       </c>
       <c r="R105" t="n">
-        <v>6818134</v>
+        <v>6818238</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11068,18 +11074,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11098,10 +11098,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927888</v>
+        <v>128927971</v>
       </c>
       <c r="B106" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11133,10 +11133,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430399</v>
+        <v>429925</v>
       </c>
       <c r="R106" t="n">
-        <v>6818238</v>
+        <v>6818065</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11195,10 +11195,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927971</v>
+        <v>128927949</v>
       </c>
       <c r="B107" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11230,10 +11230,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>429925</v>
+        <v>430653</v>
       </c>
       <c r="R107" t="n">
-        <v>6818065</v>
+        <v>6818272</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11292,10 +11292,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927949</v>
+        <v>128927856</v>
       </c>
       <c r="B108" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11303,21 +11303,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11327,10 +11327,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430653</v>
+        <v>430060</v>
       </c>
       <c r="R108" t="n">
-        <v>6818272</v>
+        <v>6818160</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11583,10 +11583,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927827</v>
+        <v>128927826</v>
       </c>
       <c r="B111" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430057</v>
+        <v>430018</v>
       </c>
       <c r="R111" t="n">
-        <v>6818016</v>
+        <v>6818046</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927822</v>
+        <v>128927796</v>
       </c>
       <c r="B112" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>429973</v>
+        <v>430323</v>
       </c>
       <c r="R112" t="n">
-        <v>6818162</v>
+        <v>6818121</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,10 +11777,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927826</v>
+        <v>128927827</v>
       </c>
       <c r="B113" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430018</v>
+        <v>430057</v>
       </c>
       <c r="R113" t="n">
-        <v>6818046</v>
+        <v>6818016</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927796</v>
+        <v>128927822</v>
       </c>
       <c r="B114" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430323</v>
+        <v>429973</v>
       </c>
       <c r="R114" t="n">
-        <v>6818121</v>
+        <v>6818162</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128927740</v>
+        <v>128927870</v>
       </c>
       <c r="B115" t="n">
-        <v>79624</v>
+        <v>78792</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11982,21 +11982,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>430401</v>
+        <v>430164</v>
       </c>
       <c r="R115" t="n">
-        <v>6818062</v>
+        <v>6817854</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12068,7 +12068,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128927823</v>
+        <v>128927858</v>
       </c>
       <c r="B116" t="n">
         <v>78792</v>
@@ -12079,21 +12079,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>429975</v>
+        <v>430034</v>
       </c>
       <c r="R116" t="n">
-        <v>6818162</v>
+        <v>6818117</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128927901</v>
+        <v>128927740</v>
       </c>
       <c r="B117" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12176,21 +12176,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430501</v>
+        <v>430401</v>
       </c>
       <c r="R117" t="n">
-        <v>6818013</v>
+        <v>6818062</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,10 +12262,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128927921</v>
+        <v>128927873</v>
       </c>
       <c r="B118" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12273,21 +12273,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>430664</v>
+        <v>429998</v>
       </c>
       <c r="R118" t="n">
-        <v>6818275</v>
+        <v>6818047</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12359,10 +12359,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128927870</v>
+        <v>128927901</v>
       </c>
       <c r="B119" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12370,21 +12370,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12394,10 +12394,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>430164</v>
+        <v>430501</v>
       </c>
       <c r="R119" t="n">
-        <v>6817854</v>
+        <v>6818013</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12456,10 +12456,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128927858</v>
+        <v>128927921</v>
       </c>
       <c r="B120" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12467,21 +12467,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12491,10 +12491,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>430034</v>
+        <v>430664</v>
       </c>
       <c r="R120" t="n">
-        <v>6818117</v>
+        <v>6818275</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12553,10 +12553,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128927873</v>
+        <v>128927823</v>
       </c>
       <c r="B121" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12564,21 +12564,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12588,10 +12588,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>429998</v>
+        <v>429975</v>
       </c>
       <c r="R121" t="n">
-        <v>6818047</v>
+        <v>6818162</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128927953</v>
+        <v>128927720</v>
       </c>
       <c r="B122" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12661,37 +12661,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>430242</v>
+        <v>430112</v>
       </c>
       <c r="R122" t="n">
-        <v>6818048</v>
+        <v>6818160</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12726,18 +12723,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12756,10 +12747,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128927907</v>
+        <v>128927853</v>
       </c>
       <c r="B123" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12767,21 +12758,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12791,10 +12782,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430394</v>
+        <v>430073</v>
       </c>
       <c r="R123" t="n">
-        <v>6818166</v>
+        <v>6818201</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12853,10 +12844,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128927977</v>
+        <v>128927777</v>
       </c>
       <c r="B124" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12864,26 +12855,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -12891,10 +12887,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430139</v>
+        <v>429898</v>
       </c>
       <c r="R124" t="n">
-        <v>6817862</v>
+        <v>6818099</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12935,7 +12931,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12954,10 +12949,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128927940</v>
+        <v>128927784</v>
       </c>
       <c r="B125" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,34 +12960,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>429952</v>
+        <v>430201</v>
       </c>
       <c r="R125" t="n">
-        <v>6818061</v>
+        <v>6818093</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13051,10 +13054,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128927918</v>
+        <v>128927769</v>
       </c>
       <c r="B126" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13062,34 +13065,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430649</v>
+        <v>430485</v>
       </c>
       <c r="R126" t="n">
-        <v>6818232</v>
+        <v>6818017</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13148,10 +13159,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128927878</v>
+        <v>128927953</v>
       </c>
       <c r="B127" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13177,16 +13188,19 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430632</v>
+        <v>430242</v>
       </c>
       <c r="R127" t="n">
-        <v>6818282</v>
+        <v>6818048</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13221,12 +13235,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13245,10 +13265,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128927908</v>
+        <v>128927907</v>
       </c>
       <c r="B128" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13280,10 +13300,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430425</v>
+        <v>430394</v>
       </c>
       <c r="R128" t="n">
-        <v>6818197</v>
+        <v>6818166</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,10 +13362,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128927886</v>
+        <v>128927977</v>
       </c>
       <c r="B129" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13371,16 +13391,19 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430424</v>
+        <v>430139</v>
       </c>
       <c r="R129" t="n">
-        <v>6818252</v>
+        <v>6817862</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13421,6 +13444,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13439,10 +13463,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128927777</v>
+        <v>128927869</v>
       </c>
       <c r="B130" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13450,42 +13474,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>429898</v>
+        <v>430138</v>
       </c>
       <c r="R130" t="n">
-        <v>6818099</v>
+        <v>6817883</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13544,10 +13560,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128927784</v>
+        <v>128927940</v>
       </c>
       <c r="B131" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13555,42 +13571,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430201</v>
+        <v>429952</v>
       </c>
       <c r="R131" t="n">
-        <v>6818093</v>
+        <v>6818061</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13649,10 +13657,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128927769</v>
+        <v>128927918</v>
       </c>
       <c r="B132" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13660,42 +13668,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430485</v>
+        <v>430649</v>
       </c>
       <c r="R132" t="n">
-        <v>6818017</v>
+        <v>6818232</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13754,10 +13754,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128927869</v>
+        <v>128927878</v>
       </c>
       <c r="B133" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13765,21 +13765,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13789,10 +13789,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430138</v>
+        <v>430632</v>
       </c>
       <c r="R133" t="n">
-        <v>6817883</v>
+        <v>6818282</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13851,10 +13851,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128927720</v>
+        <v>128927908</v>
       </c>
       <c r="B134" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13862,21 +13862,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13886,10 +13886,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430112</v>
+        <v>430425</v>
       </c>
       <c r="R134" t="n">
-        <v>6818160</v>
+        <v>6818197</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13948,10 +13948,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128927853</v>
+        <v>128927886</v>
       </c>
       <c r="B135" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13959,21 +13959,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13983,10 +13983,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430073</v>
+        <v>430424</v>
       </c>
       <c r="R135" t="n">
-        <v>6818201</v>
+        <v>6818252</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14048,7 +14048,7 @@
         <v>128927894</v>
       </c>
       <c r="B136" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>128927900</v>
       </c>
       <c r="B137" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>128927889</v>
       </c>
       <c r="B138" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>128927911</v>
       </c>
       <c r="B139" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>128927969</v>
       </c>
       <c r="B140" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>128927956</v>
       </c>
       <c r="B141" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>128927925</v>
       </c>
       <c r="B142" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>128927972</v>
       </c>
       <c r="B143" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>128927926</v>
       </c>
       <c r="B144" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>128927863</v>
       </c>
       <c r="B145" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>128927709</v>
       </c>
       <c r="B146" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>128927861</v>
       </c>
       <c r="B147" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15222,41 +15222,40 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927833</v>
+        <v>128927781</v>
       </c>
       <c r="B148" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
@@ -15266,10 +15265,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430204</v>
+        <v>430480</v>
       </c>
       <c r="R148" t="n">
-        <v>6817811</v>
+        <v>6817997</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15310,7 +15309,6 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -15329,7 +15327,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927781</v>
+        <v>128927788</v>
       </c>
       <c r="B149" t="n">
         <v>57720</v>
@@ -15362,7 +15360,7 @@
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
@@ -15372,10 +15370,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430480</v>
+        <v>430017</v>
       </c>
       <c r="R149" t="n">
-        <v>6817997</v>
+        <v>6818044</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15434,7 +15432,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927788</v>
+        <v>128927775</v>
       </c>
       <c r="B150" t="n">
         <v>57720</v>
@@ -15467,7 +15465,7 @@
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -15477,10 +15475,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430017</v>
+        <v>430083</v>
       </c>
       <c r="R150" t="n">
-        <v>6818044</v>
+        <v>6818224</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15539,7 +15537,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927775</v>
+        <v>128927792</v>
       </c>
       <c r="B151" t="n">
         <v>57720</v>
@@ -15572,7 +15570,7 @@
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -15582,10 +15580,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430083</v>
+        <v>430150</v>
       </c>
       <c r="R151" t="n">
-        <v>6818224</v>
+        <v>6817814</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15644,40 +15642,41 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128927792</v>
+        <v>128927833</v>
       </c>
       <c r="B152" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -15687,10 +15686,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430150</v>
+        <v>430204</v>
       </c>
       <c r="R152" t="n">
-        <v>6817814</v>
+        <v>6817811</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15731,6 +15730,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15752,7 +15752,7 @@
         <v>128927824</v>
       </c>
       <c r="B153" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>128927748</v>
       </c>
       <c r="B154" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>128927917</v>
       </c>
       <c r="B155" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>128927903</v>
       </c>
       <c r="B156" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16146,10 +16146,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128927920</v>
+        <v>128927875</v>
       </c>
       <c r="B157" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16157,21 +16157,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16181,10 +16181,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430637</v>
+        <v>430127</v>
       </c>
       <c r="R157" t="n">
-        <v>6818260</v>
+        <v>6817846</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16243,10 +16243,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128927951</v>
+        <v>128927920</v>
       </c>
       <c r="B158" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16272,19 +16272,16 @@
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430191</v>
+        <v>430637</v>
       </c>
       <c r="R158" t="n">
-        <v>6817932</v>
+        <v>6818260</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16319,18 +16316,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Garnlav, måttligt inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -16349,10 +16340,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128927958</v>
+        <v>128927838</v>
       </c>
       <c r="B159" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16360,21 +16351,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16384,10 +16375,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430048</v>
+        <v>430439</v>
       </c>
       <c r="R159" t="n">
-        <v>6818232</v>
+        <v>6818031</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16446,10 +16437,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128927902</v>
+        <v>128927951</v>
       </c>
       <c r="B160" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16475,16 +16466,19 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430530</v>
+        <v>430191</v>
       </c>
       <c r="R160" t="n">
-        <v>6818025</v>
+        <v>6817932</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16519,12 +16513,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Garnlav, måttligt inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -16543,10 +16543,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128927875</v>
+        <v>128927958</v>
       </c>
       <c r="B161" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16554,21 +16554,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16578,10 +16578,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430127</v>
+        <v>430048</v>
       </c>
       <c r="R161" t="n">
-        <v>6817846</v>
+        <v>6818232</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16640,10 +16640,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128927838</v>
+        <v>128927902</v>
       </c>
       <c r="B162" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16651,21 +16651,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16675,10 +16675,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430439</v>
+        <v>430530</v>
       </c>
       <c r="R162" t="n">
-        <v>6818031</v>
+        <v>6818025</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16740,7 +16740,7 @@
         <v>128927837</v>
       </c>
       <c r="B163" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>128927846</v>
       </c>
       <c r="B164" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>128927798</v>
       </c>
       <c r="B167" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>128927828</v>
       </c>
       <c r="B168" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17339,32 +17339,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128927835</v>
+        <v>128927981</v>
       </c>
       <c r="B169" t="n">
-        <v>58093</v>
+        <v>78043</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>103015</v>
+        <v>6487</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17374,10 +17374,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>430104</v>
+        <v>430056</v>
       </c>
       <c r="R169" t="n">
-        <v>6817960</v>
+        <v>6818166</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17436,10 +17436,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128927829</v>
+        <v>128927933</v>
       </c>
       <c r="B170" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17447,34 +17447,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430138</v>
+        <v>430220</v>
       </c>
       <c r="R170" t="n">
-        <v>6817883</v>
+        <v>6818148</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17509,12 +17512,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -17533,10 +17542,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128927737</v>
+        <v>128927904</v>
       </c>
       <c r="B171" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17544,37 +17553,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430143</v>
+        <v>430405</v>
       </c>
       <c r="R171" t="n">
-        <v>6817831</v>
+        <v>6818117</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17615,7 +17621,6 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -17634,10 +17639,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128927981</v>
+        <v>128927737</v>
       </c>
       <c r="B172" t="n">
-        <v>78042</v>
+        <v>79654</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17645,34 +17650,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430056</v>
+        <v>430143</v>
       </c>
       <c r="R172" t="n">
-        <v>6818166</v>
+        <v>6817831</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17713,6 +17721,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -17734,7 +17743,7 @@
         <v>128927712</v>
       </c>
       <c r="B173" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17828,10 +17837,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128927933</v>
+        <v>128927829</v>
       </c>
       <c r="B174" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17839,37 +17848,34 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430220</v>
+        <v>430138</v>
       </c>
       <c r="R174" t="n">
-        <v>6818148</v>
+        <v>6817883</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17904,18 +17910,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -17934,32 +17934,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128927904</v>
+        <v>128927835</v>
       </c>
       <c r="B175" t="n">
-        <v>79034</v>
+        <v>58093</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17969,10 +17969,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430405</v>
+        <v>430104</v>
       </c>
       <c r="R175" t="n">
-        <v>6818117</v>
+        <v>6817960</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18031,45 +18031,53 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128927898</v>
+        <v>128927762</v>
       </c>
       <c r="B176" t="n">
-        <v>79034</v>
+        <v>56913</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430384</v>
+        <v>430394</v>
       </c>
       <c r="R176" t="n">
-        <v>6818048</v>
+        <v>6818168</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18128,45 +18136,53 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128927968</v>
+        <v>128927760</v>
       </c>
       <c r="B177" t="n">
-        <v>79034</v>
+        <v>56913</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430067</v>
+        <v>430663</v>
       </c>
       <c r="R177" t="n">
-        <v>6818139</v>
+        <v>6818259</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18225,10 +18241,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128927952</v>
+        <v>128927750</v>
       </c>
       <c r="B178" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18236,21 +18252,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18260,10 +18276,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430190</v>
+        <v>430140</v>
       </c>
       <c r="R178" t="n">
-        <v>6817925</v>
+        <v>6817881</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18322,10 +18338,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128927945</v>
+        <v>128927741</v>
       </c>
       <c r="B179" t="n">
-        <v>79034</v>
+        <v>79625</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18333,21 +18349,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18357,10 +18373,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430404</v>
+        <v>430600</v>
       </c>
       <c r="R179" t="n">
-        <v>6818178</v>
+        <v>6818203</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18419,10 +18435,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128927750</v>
+        <v>128927898</v>
       </c>
       <c r="B180" t="n">
-        <v>79624</v>
+        <v>79035</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18430,21 +18446,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18454,10 +18470,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430140</v>
+        <v>430384</v>
       </c>
       <c r="R180" t="n">
-        <v>6817881</v>
+        <v>6818048</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18516,10 +18532,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128927741</v>
+        <v>128927968</v>
       </c>
       <c r="B181" t="n">
-        <v>79624</v>
+        <v>79035</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18527,21 +18543,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18551,10 +18567,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430600</v>
+        <v>430067</v>
       </c>
       <c r="R181" t="n">
-        <v>6818203</v>
+        <v>6818139</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18613,10 +18629,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128927812</v>
+        <v>128927952</v>
       </c>
       <c r="B182" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18624,21 +18640,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18648,10 +18664,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430157</v>
+        <v>430190</v>
       </c>
       <c r="R182" t="n">
-        <v>6818149</v>
+        <v>6817925</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18710,10 +18726,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128927723</v>
+        <v>128927945</v>
       </c>
       <c r="B183" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18721,21 +18737,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18745,10 +18761,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>429993</v>
+        <v>430404</v>
       </c>
       <c r="R183" t="n">
-        <v>6818157</v>
+        <v>6818178</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18807,10 +18823,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128927848</v>
+        <v>128927723</v>
       </c>
       <c r="B184" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18818,21 +18834,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18842,10 +18858,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430174</v>
+        <v>429993</v>
       </c>
       <c r="R184" t="n">
-        <v>6818156</v>
+        <v>6818157</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18904,53 +18920,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128927760</v>
+        <v>128927848</v>
       </c>
       <c r="B185" t="n">
-        <v>56913</v>
+        <v>78792</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430663</v>
+        <v>430174</v>
       </c>
       <c r="R185" t="n">
-        <v>6818259</v>
+        <v>6818156</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19009,53 +19017,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128927762</v>
+        <v>128927812</v>
       </c>
       <c r="B186" t="n">
-        <v>56913</v>
+        <v>78793</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430394</v>
+        <v>430157</v>
       </c>
       <c r="R186" t="n">
-        <v>6818168</v>
+        <v>6818149</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19114,10 +19114,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128927731</v>
+        <v>128927910</v>
       </c>
       <c r="B187" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19125,21 +19125,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19149,10 +19149,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430056</v>
+        <v>430430</v>
       </c>
       <c r="R187" t="n">
-        <v>6818017</v>
+        <v>6818202</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19214,7 +19214,7 @@
         <v>128927847</v>
       </c>
       <c r="B188" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19308,10 +19308,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128927872</v>
+        <v>128927892</v>
       </c>
       <c r="B189" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19319,21 +19319,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19343,10 +19343,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430227</v>
+        <v>430304</v>
       </c>
       <c r="R189" t="n">
-        <v>6818015</v>
+        <v>6818124</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19405,10 +19405,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128927728</v>
+        <v>128927906</v>
       </c>
       <c r="B190" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19416,34 +19416,37 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430232</v>
+        <v>430401</v>
       </c>
       <c r="R190" t="n">
-        <v>6818068</v>
+        <v>6818157</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19478,12 +19481,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
+        </is>
+      </c>
       <c r="AD190" t="b">
         <v>0</v>
       </c>
       <c r="AE190" t="b">
         <v>0</v>
       </c>
+      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
@@ -19502,10 +19511,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128927910</v>
+        <v>128927922</v>
       </c>
       <c r="B191" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19537,10 +19546,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430430</v>
+        <v>430668</v>
       </c>
       <c r="R191" t="n">
-        <v>6818202</v>
+        <v>6818241</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19599,10 +19608,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128927892</v>
+        <v>128927962</v>
       </c>
       <c r="B192" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19634,10 +19643,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430304</v>
+        <v>430069</v>
       </c>
       <c r="R192" t="n">
-        <v>6818124</v>
+        <v>6818225</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19696,10 +19705,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128927906</v>
+        <v>128927731</v>
       </c>
       <c r="B193" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19707,37 +19716,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430401</v>
+        <v>430056</v>
       </c>
       <c r="R193" t="n">
-        <v>6818157</v>
+        <v>6818017</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19772,18 +19778,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -19802,10 +19802,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128927922</v>
+        <v>128927872</v>
       </c>
       <c r="B194" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19813,21 +19813,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19837,10 +19837,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430668</v>
+        <v>430227</v>
       </c>
       <c r="R194" t="n">
-        <v>6818241</v>
+        <v>6818015</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19899,10 +19899,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128927962</v>
+        <v>128927728</v>
       </c>
       <c r="B195" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19910,21 +19910,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19934,10 +19934,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430069</v>
+        <v>430232</v>
       </c>
       <c r="R195" t="n">
-        <v>6818225</v>
+        <v>6818068</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -19996,10 +19996,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128927789</v>
+        <v>128927820</v>
       </c>
       <c r="B196" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20007,42 +20007,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430089</v>
+        <v>430014</v>
       </c>
       <c r="R196" t="n">
-        <v>6817965</v>
+        <v>6818142</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20075,11 +20067,6 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20106,10 +20093,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128927820</v>
+        <v>128927818</v>
       </c>
       <c r="B197" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20141,10 +20128,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430014</v>
+        <v>430048</v>
       </c>
       <c r="R197" t="n">
-        <v>6818142</v>
+        <v>6818123</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20203,10 +20190,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128927818</v>
+        <v>128927789</v>
       </c>
       <c r="B198" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20214,34 +20201,42 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430048</v>
+        <v>430089</v>
       </c>
       <c r="R198" t="n">
-        <v>6818123</v>
+        <v>6817965</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20274,6 +20269,11 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20300,10 +20300,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128927755</v>
+        <v>128927913</v>
       </c>
       <c r="B199" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20311,42 +20311,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430480</v>
+        <v>430484</v>
       </c>
       <c r="R199" t="n">
-        <v>6818068</v>
+        <v>6818253</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20405,10 +20397,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128927913</v>
+        <v>128927841</v>
       </c>
       <c r="B200" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20416,21 +20408,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20440,10 +20432,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430484</v>
+        <v>430569</v>
       </c>
       <c r="R200" t="n">
-        <v>6818253</v>
+        <v>6818243</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20505,7 +20497,7 @@
         <v>128927936</v>
       </c>
       <c r="B201" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20599,10 +20591,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128927961</v>
+        <v>128927942</v>
       </c>
       <c r="B202" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20634,10 +20626,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430086</v>
+        <v>430087</v>
       </c>
       <c r="R202" t="n">
-        <v>6818236</v>
+        <v>6817971</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20696,10 +20688,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128927942</v>
+        <v>128927717</v>
       </c>
       <c r="B203" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20707,21 +20699,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20731,7 +20723,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430087</v>
+        <v>430214</v>
       </c>
       <c r="R203" t="n">
         <v>6817971</v>
@@ -20793,10 +20785,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128927841</v>
+        <v>128927715</v>
       </c>
       <c r="B204" t="n">
-        <v>78791</v>
+        <v>79654</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20804,21 +20796,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20828,10 +20820,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430569</v>
+        <v>430650</v>
       </c>
       <c r="R204" t="n">
-        <v>6818243</v>
+        <v>6818249</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20890,10 +20882,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128927717</v>
+        <v>128927755</v>
       </c>
       <c r="B205" t="n">
-        <v>79653</v>
+        <v>57723</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20901,34 +20893,42 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430214</v>
+        <v>430480</v>
       </c>
       <c r="R205" t="n">
-        <v>6817971</v>
+        <v>6818068</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20987,10 +20987,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128927715</v>
+        <v>128927961</v>
       </c>
       <c r="B206" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20998,21 +20998,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21022,10 +21022,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430650</v>
+        <v>430086</v>
       </c>
       <c r="R206" t="n">
-        <v>6818249</v>
+        <v>6818236</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21087,7 +21087,7 @@
         <v>128927809</v>
       </c>
       <c r="B207" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>128927814</v>
       </c>
       <c r="B208" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>128927816</v>
       </c>
       <c r="B209" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21375,10 +21375,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128927941</v>
+        <v>128927830</v>
       </c>
       <c r="B210" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21386,21 +21386,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21410,10 +21410,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430078</v>
+        <v>430167</v>
       </c>
       <c r="R210" t="n">
-        <v>6817995</v>
+        <v>6817850</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21472,10 +21472,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128927960</v>
+        <v>128927808</v>
       </c>
       <c r="B211" t="n">
-        <v>79034</v>
+        <v>78793</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21483,21 +21483,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21507,10 +21507,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>430089</v>
+        <v>430669</v>
       </c>
       <c r="R211" t="n">
-        <v>6818238</v>
+        <v>6818242</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21569,10 +21569,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128927860</v>
+        <v>128927817</v>
       </c>
       <c r="B212" t="n">
-        <v>78791</v>
+        <v>78793</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21580,21 +21580,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21604,10 +21604,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430013</v>
+        <v>430068</v>
       </c>
       <c r="R212" t="n">
-        <v>6818142</v>
+        <v>6818152</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21666,10 +21666,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128927866</v>
+        <v>128927746</v>
       </c>
       <c r="B213" t="n">
-        <v>78791</v>
+        <v>79625</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21677,21 +21677,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21701,10 +21701,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>429950</v>
+        <v>430232</v>
       </c>
       <c r="R213" t="n">
-        <v>6818057</v>
+        <v>6818068</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21763,10 +21763,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128927753</v>
+        <v>128927860</v>
       </c>
       <c r="B214" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21774,42 +21774,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>430514</v>
+        <v>430013</v>
       </c>
       <c r="R214" t="n">
-        <v>6818047</v>
+        <v>6818142</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21868,10 +21860,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128927830</v>
+        <v>128927941</v>
       </c>
       <c r="B215" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21879,21 +21871,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21903,10 +21895,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>430167</v>
+        <v>430078</v>
       </c>
       <c r="R215" t="n">
-        <v>6817850</v>
+        <v>6817995</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21965,10 +21957,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128927808</v>
+        <v>128927960</v>
       </c>
       <c r="B216" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21976,21 +21968,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22000,10 +21992,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>430669</v>
+        <v>430089</v>
       </c>
       <c r="R216" t="n">
-        <v>6818242</v>
+        <v>6818238</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22062,7 +22054,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128927817</v>
+        <v>128927866</v>
       </c>
       <c r="B217" t="n">
         <v>78792</v>
@@ -22073,21 +22065,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22097,10 +22089,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>430068</v>
+        <v>429950</v>
       </c>
       <c r="R217" t="n">
-        <v>6818152</v>
+        <v>6818057</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22159,10 +22151,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128927746</v>
+        <v>128927753</v>
       </c>
       <c r="B218" t="n">
-        <v>79624</v>
+        <v>57723</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22170,34 +22162,42 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>430232</v>
+        <v>430514</v>
       </c>
       <c r="R218" t="n">
-        <v>6818068</v>
+        <v>6818047</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22256,10 +22256,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128927800</v>
+        <v>128927967</v>
       </c>
       <c r="B219" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22267,37 +22267,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430487</v>
+        <v>430084</v>
       </c>
       <c r="R219" t="n">
-        <v>6818080</v>
+        <v>6818144</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22338,7 +22335,6 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -22357,10 +22353,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128927967</v>
+        <v>128927881</v>
       </c>
       <c r="B220" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22392,10 +22388,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430084</v>
+        <v>430536</v>
       </c>
       <c r="R220" t="n">
-        <v>6818144</v>
+        <v>6818208</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22454,10 +22450,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128927881</v>
+        <v>128927916</v>
       </c>
       <c r="B221" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -22489,10 +22485,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430536</v>
+        <v>430580</v>
       </c>
       <c r="R221" t="n">
-        <v>6818208</v>
+        <v>6818221</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22551,10 +22547,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128927916</v>
+        <v>128927867</v>
       </c>
       <c r="B222" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22562,21 +22558,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -22586,10 +22582,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430580</v>
+        <v>430006</v>
       </c>
       <c r="R222" t="n">
-        <v>6818221</v>
+        <v>6818034</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22648,10 +22644,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128927867</v>
+        <v>128927771</v>
       </c>
       <c r="B223" t="n">
-        <v>78791</v>
+        <v>57720</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22659,34 +22655,42 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430006</v>
+        <v>430658</v>
       </c>
       <c r="R223" t="n">
-        <v>6818034</v>
+        <v>6818274</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22745,10 +22749,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128927771</v>
+        <v>128927800</v>
       </c>
       <c r="B224" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22756,31 +22760,26 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
@@ -22788,10 +22787,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430658</v>
+        <v>430487</v>
       </c>
       <c r="R224" t="n">
-        <v>6818274</v>
+        <v>6818080</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22832,6 +22831,7 @@
       <c r="AE224" t="b">
         <v>0</v>
       </c>
+      <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
       </c>
@@ -22853,7 +22853,7 @@
         <v>128927890</v>
       </c>
       <c r="B225" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>128927915</v>
       </c>
       <c r="B226" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>128927923</v>
       </c>
       <c r="B227" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>128927850</v>
       </c>
       <c r="B228" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>128927730</v>
       </c>
       <c r="B229" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128927821</v>
+        <v>128927732</v>
       </c>
       <c r="B22" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>429994</v>
+        <v>430138</v>
       </c>
       <c r="R22" t="n">
-        <v>6818158</v>
+        <v>6817883</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927802</v>
+        <v>128927950</v>
       </c>
       <c r="B23" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430567</v>
+        <v>430233</v>
       </c>
       <c r="R23" t="n">
-        <v>6818243</v>
+        <v>6817831</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927935</v>
+        <v>128927880</v>
       </c>
       <c r="B24" t="n">
         <v>79035</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430099</v>
+        <v>430577</v>
       </c>
       <c r="R24" t="n">
-        <v>6818154</v>
+        <v>6818221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927963</v>
+        <v>128927868</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,21 +3153,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430064</v>
+        <v>430089</v>
       </c>
       <c r="R25" t="n">
-        <v>6818190</v>
+        <v>6817984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927732</v>
+        <v>128927978</v>
       </c>
       <c r="B26" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430138</v>
+        <v>430082</v>
       </c>
       <c r="R26" t="n">
-        <v>6817883</v>
+        <v>6818210</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,6 +3318,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3336,10 +3337,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927721</v>
+        <v>128927843</v>
       </c>
       <c r="B27" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3347,21 +3348,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3372,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430060</v>
+        <v>430626</v>
       </c>
       <c r="R27" t="n">
-        <v>6818156</v>
+        <v>6818202</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,7 +3434,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927726</v>
+        <v>128927721</v>
       </c>
       <c r="B28" t="n">
         <v>79654</v>
@@ -3468,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430114</v>
+        <v>430060</v>
       </c>
       <c r="R28" t="n">
-        <v>6817912</v>
+        <v>6818156</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927770</v>
+        <v>128927935</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,42 +3542,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430455</v>
+        <v>430099</v>
       </c>
       <c r="R29" t="n">
-        <v>6818246</v>
+        <v>6818154</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927950</v>
+        <v>128927726</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3646,21 +3639,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3670,10 +3663,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430233</v>
+        <v>430114</v>
       </c>
       <c r="R30" t="n">
-        <v>6817831</v>
+        <v>6817912</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,32 +3725,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927880</v>
+        <v>128927834</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3767,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430577</v>
+        <v>430596</v>
       </c>
       <c r="R31" t="n">
-        <v>6818221</v>
+        <v>6818184</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3829,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128927868</v>
+        <v>128927770</v>
       </c>
       <c r="B32" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,34 +3833,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430089</v>
+        <v>430455</v>
       </c>
       <c r="R32" t="n">
-        <v>6817984</v>
+        <v>6818246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3926,7 +3927,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128927978</v>
+        <v>128927963</v>
       </c>
       <c r="B33" t="n">
         <v>79035</v>
@@ -3961,10 +3962,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>430082</v>
+        <v>430064</v>
       </c>
       <c r="R33" t="n">
-        <v>6818210</v>
+        <v>6818190</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4005,7 +4006,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128927843</v>
+        <v>128927821</v>
       </c>
       <c r="B34" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>430626</v>
+        <v>429994</v>
       </c>
       <c r="R34" t="n">
-        <v>6818202</v>
+        <v>6818158</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128927834</v>
+        <v>128927802</v>
       </c>
       <c r="B35" t="n">
-        <v>58093</v>
+        <v>78793</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430596</v>
+        <v>430567</v>
       </c>
       <c r="R35" t="n">
-        <v>6818184</v>
+        <v>6818243</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128927871</v>
+        <v>128927939</v>
       </c>
       <c r="B36" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>430145</v>
+        <v>429903</v>
       </c>
       <c r="R36" t="n">
-        <v>6817833</v>
+        <v>6818059</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128927939</v>
+        <v>128927871</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4528,21 +4528,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>429903</v>
+        <v>430145</v>
       </c>
       <c r="R39" t="n">
-        <v>6818059</v>
+        <v>6817833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4715,10 +4715,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128927813</v>
+        <v>128927743</v>
       </c>
       <c r="B41" t="n">
-        <v>78793</v>
+        <v>79625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,21 +4726,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430145</v>
+        <v>430211</v>
       </c>
       <c r="R41" t="n">
-        <v>6818165</v>
+        <v>6817980</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128927743</v>
+        <v>128927813</v>
       </c>
       <c r="B42" t="n">
-        <v>79625</v>
+        <v>78793</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,21 +4823,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>430211</v>
+        <v>430145</v>
       </c>
       <c r="R42" t="n">
-        <v>6817980</v>
+        <v>6818165</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128927938</v>
+        <v>128927842</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>429959</v>
+        <v>430596</v>
       </c>
       <c r="R47" t="n">
-        <v>6818128</v>
+        <v>6818186</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128927976</v>
+        <v>128927938</v>
       </c>
       <c r="B48" t="n">
         <v>79035</v>
@@ -5423,19 +5423,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430149</v>
+        <v>429959</v>
       </c>
       <c r="R48" t="n">
-        <v>6817860</v>
+        <v>6818128</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5476,7 +5473,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5495,7 +5491,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128927966</v>
+        <v>128927976</v>
       </c>
       <c r="B49" t="n">
         <v>79035</v>
@@ -5524,16 +5520,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430071</v>
+        <v>430149</v>
       </c>
       <c r="R49" t="n">
-        <v>6818124</v>
+        <v>6817860</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5574,6 +5573,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128927842</v>
+        <v>128927966</v>
       </c>
       <c r="B50" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430596</v>
+        <v>430071</v>
       </c>
       <c r="R50" t="n">
-        <v>6818186</v>
+        <v>6818124</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6187,10 +6187,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128927937</v>
+        <v>128927874</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>430011</v>
+        <v>430154</v>
       </c>
       <c r="R56" t="n">
-        <v>6818137</v>
+        <v>6817859</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128927874</v>
+        <v>128927970</v>
       </c>
       <c r="B57" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6295,21 +6295,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>430154</v>
+        <v>429900</v>
       </c>
       <c r="R57" t="n">
-        <v>6817859</v>
+        <v>6818098</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6355,6 +6355,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,7 +6386,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128927970</v>
+        <v>128927944</v>
       </c>
       <c r="B58" t="n">
         <v>79035</v>
@@ -6410,16 +6415,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>429900</v>
+        <v>430531</v>
       </c>
       <c r="R58" t="n">
-        <v>6818098</v>
+        <v>6818016</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6454,17 +6462,13 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6483,7 +6487,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927944</v>
+        <v>128927948</v>
       </c>
       <c r="B59" t="n">
         <v>79035</v>
@@ -6512,19 +6516,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430531</v>
+        <v>430655</v>
       </c>
       <c r="R59" t="n">
-        <v>6818016</v>
+        <v>6818216</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6565,7 +6566,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927948</v>
+        <v>128927735</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6595,21 +6595,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430655</v>
+        <v>430132</v>
       </c>
       <c r="R60" t="n">
-        <v>6818216</v>
+        <v>6817858</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6972,10 +6972,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128927815</v>
+        <v>128927937</v>
       </c>
       <c r="B64" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430061</v>
+        <v>430011</v>
       </c>
       <c r="R64" t="n">
-        <v>6818258</v>
+        <v>6818137</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128927735</v>
+        <v>128927815</v>
       </c>
       <c r="B65" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430132</v>
+        <v>430061</v>
       </c>
       <c r="R65" t="n">
-        <v>6817858</v>
+        <v>6818258</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128927790</v>
+        <v>128927825</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7177,42 +7177,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430130</v>
+        <v>430024</v>
       </c>
       <c r="R66" t="n">
-        <v>6817856</v>
+        <v>6818040</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,10 +7263,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128927893</v>
+        <v>128927790</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,34 +7274,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430286</v>
+        <v>430130</v>
       </c>
       <c r="R67" t="n">
-        <v>6818100</v>
+        <v>6817856</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,7 +7368,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128927974</v>
+        <v>128927893</v>
       </c>
       <c r="B68" t="n">
         <v>79035</v>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430091</v>
+        <v>430286</v>
       </c>
       <c r="R68" t="n">
-        <v>6818012</v>
+        <v>6818100</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7465,10 +7465,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128927751</v>
+        <v>128927974</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7476,42 +7476,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430337</v>
+        <v>430091</v>
       </c>
       <c r="R69" t="n">
-        <v>6818076</v>
+        <v>6818012</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,10 +7562,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128927825</v>
+        <v>128927751</v>
       </c>
       <c r="B70" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7581,34 +7573,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>430024</v>
+        <v>430337</v>
       </c>
       <c r="R70" t="n">
-        <v>6818040</v>
+        <v>6818076</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7667,10 +7667,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128927857</v>
+        <v>128927710</v>
       </c>
       <c r="B71" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,21 +7678,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430051</v>
+        <v>430610</v>
       </c>
       <c r="R71" t="n">
-        <v>6818114</v>
+        <v>6818230</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7764,10 +7764,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128927710</v>
+        <v>128927839</v>
       </c>
       <c r="B72" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7775,21 +7775,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>430610</v>
+        <v>430489</v>
       </c>
       <c r="R72" t="n">
-        <v>6818230</v>
+        <v>6818084</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7861,7 +7861,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128927839</v>
+        <v>128927857</v>
       </c>
       <c r="B73" t="n">
         <v>78792</v>
@@ -7896,10 +7896,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>430489</v>
+        <v>430051</v>
       </c>
       <c r="R73" t="n">
-        <v>6818084</v>
+        <v>6818114</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128927924</v>
+        <v>128927840</v>
       </c>
       <c r="B76" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8167,21 +8167,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430671</v>
+        <v>430407</v>
       </c>
       <c r="R76" t="n">
-        <v>6818266</v>
+        <v>6818114</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128927964</v>
+        <v>128927865</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430099</v>
+        <v>429935</v>
       </c>
       <c r="R77" t="n">
-        <v>6818174</v>
+        <v>6818065</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128927897</v>
+        <v>128927924</v>
       </c>
       <c r="B78" t="n">
         <v>79035</v>
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430386</v>
+        <v>430671</v>
       </c>
       <c r="R78" t="n">
-        <v>6818039</v>
+        <v>6818266</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8447,7 +8447,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128927955</v>
+        <v>128927964</v>
       </c>
       <c r="B79" t="n">
         <v>79035</v>
@@ -8476,19 +8476,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430129</v>
+        <v>430099</v>
       </c>
       <c r="R79" t="n">
-        <v>6818156</v>
+        <v>6818174</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8523,18 +8520,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30 m</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8553,7 +8544,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128927905</v>
+        <v>128927897</v>
       </c>
       <c r="B80" t="n">
         <v>79035</v>
@@ -8588,10 +8579,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430395</v>
+        <v>430386</v>
       </c>
       <c r="R80" t="n">
-        <v>6818138</v>
+        <v>6818039</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8650,7 +8641,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128927885</v>
+        <v>128927955</v>
       </c>
       <c r="B81" t="n">
         <v>79035</v>
@@ -8679,16 +8670,19 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430366</v>
+        <v>430129</v>
       </c>
       <c r="R81" t="n">
-        <v>6818264</v>
+        <v>6818156</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8723,12 +8717,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30 m</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8747,7 +8747,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128927947</v>
+        <v>128927905</v>
       </c>
       <c r="B82" t="n">
         <v>79035</v>
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430568</v>
+        <v>430395</v>
       </c>
       <c r="R82" t="n">
-        <v>6818235</v>
+        <v>6818138</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8818,11 +8818,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8849,10 +8844,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128927912</v>
+        <v>128927725</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8860,21 +8855,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8884,10 +8879,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430439</v>
+        <v>430040</v>
       </c>
       <c r="R83" t="n">
-        <v>6818230</v>
+        <v>6818029</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8946,10 +8941,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128927795</v>
+        <v>128927885</v>
       </c>
       <c r="B84" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8957,21 +8952,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8981,10 +8976,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430390</v>
+        <v>430366</v>
       </c>
       <c r="R84" t="n">
-        <v>6818205</v>
+        <v>6818264</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9043,10 +9038,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128927811</v>
+        <v>128927947</v>
       </c>
       <c r="B85" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9054,21 +9049,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9078,10 +9073,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>430176</v>
+        <v>430568</v>
       </c>
       <c r="R85" t="n">
-        <v>6818150</v>
+        <v>6818235</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9114,6 +9109,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9140,10 +9140,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128927832</v>
+        <v>128927912</v>
       </c>
       <c r="B86" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9151,21 +9151,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430153</v>
+        <v>430439</v>
       </c>
       <c r="R86" t="n">
-        <v>6817822</v>
+        <v>6818230</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9237,10 +9237,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128927840</v>
+        <v>128927795</v>
       </c>
       <c r="B87" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9248,21 +9248,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>430407</v>
+        <v>430390</v>
       </c>
       <c r="R87" t="n">
-        <v>6818114</v>
+        <v>6818205</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9334,10 +9334,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128927865</v>
+        <v>128927811</v>
       </c>
       <c r="B88" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9345,21 +9345,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>429935</v>
+        <v>430176</v>
       </c>
       <c r="R88" t="n">
-        <v>6818065</v>
+        <v>6818150</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128927725</v>
+        <v>128927832</v>
       </c>
       <c r="B89" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>430040</v>
+        <v>430153</v>
       </c>
       <c r="R89" t="n">
-        <v>6818029</v>
+        <v>6817822</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9528,32 +9528,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128927794</v>
+        <v>128927980</v>
       </c>
       <c r="B90" t="n">
-        <v>97530</v>
+        <v>78043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>6487</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>430535</v>
+        <v>430081</v>
       </c>
       <c r="R90" t="n">
-        <v>6818254</v>
+        <v>6818119</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128927980</v>
+        <v>128927891</v>
       </c>
       <c r="B91" t="n">
-        <v>78043</v>
+        <v>79035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9636,21 +9636,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430081</v>
+        <v>430336</v>
       </c>
       <c r="R91" t="n">
-        <v>6818119</v>
+        <v>6818151</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9722,7 +9722,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128927891</v>
+        <v>128927884</v>
       </c>
       <c r="B92" t="n">
         <v>79035</v>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430336</v>
+        <v>430423</v>
       </c>
       <c r="R92" t="n">
-        <v>6818151</v>
+        <v>6818270</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128927884</v>
+        <v>128927864</v>
       </c>
       <c r="B93" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9830,21 +9830,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430423</v>
+        <v>429975</v>
       </c>
       <c r="R93" t="n">
-        <v>6818270</v>
+        <v>6818158</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9916,10 +9916,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128927965</v>
+        <v>128927714</v>
       </c>
       <c r="B94" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9927,21 +9927,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9951,10 +9951,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430115</v>
+        <v>430630</v>
       </c>
       <c r="R94" t="n">
-        <v>6818177</v>
+        <v>6818207</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10013,7 +10013,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128927932</v>
+        <v>128927965</v>
       </c>
       <c r="B95" t="n">
         <v>79035</v>
@@ -10042,19 +10042,16 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430240</v>
+        <v>430115</v>
       </c>
       <c r="R95" t="n">
-        <v>6817987</v>
+        <v>6818177</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10089,18 +10086,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10119,7 +10110,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128927975</v>
+        <v>128927932</v>
       </c>
       <c r="B96" t="n">
         <v>79035</v>
@@ -10148,16 +10139,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430138</v>
+        <v>430240</v>
       </c>
       <c r="R96" t="n">
-        <v>6817903</v>
+        <v>6817987</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10192,12 +10186,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128927943</v>
+        <v>128927975</v>
       </c>
       <c r="B97" t="n">
         <v>79035</v>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430136</v>
+        <v>430138</v>
       </c>
       <c r="R97" t="n">
-        <v>6817849</v>
+        <v>6817903</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10313,10 +10313,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128927864</v>
+        <v>128927943</v>
       </c>
       <c r="B98" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10324,21 +10324,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>429975</v>
+        <v>430136</v>
       </c>
       <c r="R98" t="n">
-        <v>6818158</v>
+        <v>6817849</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10410,10 +10410,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128927714</v>
+        <v>128927851</v>
       </c>
       <c r="B99" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10421,21 +10421,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430630</v>
+        <v>430135</v>
       </c>
       <c r="R99" t="n">
-        <v>6818207</v>
+        <v>6818172</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10507,32 +10507,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128927851</v>
+        <v>128927794</v>
       </c>
       <c r="B100" t="n">
-        <v>78792</v>
+        <v>97530</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>430135</v>
+        <v>430535</v>
       </c>
       <c r="R100" t="n">
-        <v>6818172</v>
+        <v>6818254</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10798,10 +10798,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927899</v>
+        <v>128927793</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>58153</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430428</v>
+        <v>430104</v>
       </c>
       <c r="R103" t="n">
-        <v>6818038</v>
+        <v>6817933</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927954</v>
+        <v>128927827</v>
       </c>
       <c r="B104" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10906,37 +10906,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430166</v>
+        <v>430057</v>
       </c>
       <c r="R104" t="n">
-        <v>6818134</v>
+        <v>6818016</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10971,18 +10968,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11001,10 +10992,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927888</v>
+        <v>128927822</v>
       </c>
       <c r="B105" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11012,21 +11003,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11036,10 +11027,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430399</v>
+        <v>429973</v>
       </c>
       <c r="R105" t="n">
-        <v>6818238</v>
+        <v>6818162</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11098,10 +11089,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927971</v>
+        <v>128927826</v>
       </c>
       <c r="B106" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11109,21 +11100,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11133,10 +11124,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>429925</v>
+        <v>430018</v>
       </c>
       <c r="R106" t="n">
-        <v>6818065</v>
+        <v>6818046</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11195,10 +11186,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927949</v>
+        <v>128927796</v>
       </c>
       <c r="B107" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11206,21 +11197,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11230,10 +11221,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430653</v>
+        <v>430323</v>
       </c>
       <c r="R107" t="n">
-        <v>6818272</v>
+        <v>6818121</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11292,10 +11283,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927856</v>
+        <v>128927899</v>
       </c>
       <c r="B108" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11303,21 +11294,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11327,10 +11318,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430060</v>
+        <v>430428</v>
       </c>
       <c r="R108" t="n">
-        <v>6818160</v>
+        <v>6818038</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11389,10 +11380,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927793</v>
+        <v>128927954</v>
       </c>
       <c r="B109" t="n">
-        <v>58153</v>
+        <v>79035</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11400,34 +11391,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430104</v>
+        <v>430166</v>
       </c>
       <c r="R109" t="n">
-        <v>6817933</v>
+        <v>6818134</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11462,12 +11456,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11486,32 +11486,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128927836</v>
+        <v>128927888</v>
       </c>
       <c r="B110" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430147</v>
+        <v>430399</v>
       </c>
       <c r="R110" t="n">
-        <v>6817817</v>
+        <v>6818238</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11583,10 +11583,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927826</v>
+        <v>128927971</v>
       </c>
       <c r="B111" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11594,21 +11594,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430018</v>
+        <v>429925</v>
       </c>
       <c r="R111" t="n">
-        <v>6818046</v>
+        <v>6818065</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927796</v>
+        <v>128927949</v>
       </c>
       <c r="B112" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11691,21 +11691,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>430323</v>
+        <v>430653</v>
       </c>
       <c r="R112" t="n">
-        <v>6818121</v>
+        <v>6818272</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,10 +11777,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927827</v>
+        <v>128927856</v>
       </c>
       <c r="B113" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11788,21 +11788,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430057</v>
+        <v>430060</v>
       </c>
       <c r="R113" t="n">
-        <v>6818016</v>
+        <v>6818160</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,32 +11874,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927822</v>
+        <v>128927836</v>
       </c>
       <c r="B114" t="n">
-        <v>78793</v>
+        <v>58093</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>429973</v>
+        <v>430147</v>
       </c>
       <c r="R114" t="n">
-        <v>6818162</v>
+        <v>6817817</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128927740</v>
+        <v>128927873</v>
       </c>
       <c r="B117" t="n">
-        <v>79625</v>
+        <v>78792</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12176,21 +12176,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430401</v>
+        <v>429998</v>
       </c>
       <c r="R117" t="n">
-        <v>6818062</v>
+        <v>6818047</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12262,10 +12262,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128927873</v>
+        <v>128927901</v>
       </c>
       <c r="B118" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12273,21 +12273,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>429998</v>
+        <v>430501</v>
       </c>
       <c r="R118" t="n">
-        <v>6818047</v>
+        <v>6818013</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12359,7 +12359,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128927901</v>
+        <v>128927921</v>
       </c>
       <c r="B119" t="n">
         <v>79035</v>
@@ -12394,10 +12394,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>430501</v>
+        <v>430664</v>
       </c>
       <c r="R119" t="n">
-        <v>6818013</v>
+        <v>6818275</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12456,10 +12456,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128927921</v>
+        <v>128927740</v>
       </c>
       <c r="B120" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12467,21 +12467,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12491,10 +12491,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>430664</v>
+        <v>430401</v>
       </c>
       <c r="R120" t="n">
-        <v>6818275</v>
+        <v>6818062</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128927720</v>
+        <v>128927977</v>
       </c>
       <c r="B122" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12661,34 +12661,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>430112</v>
+        <v>430139</v>
       </c>
       <c r="R122" t="n">
-        <v>6818160</v>
+        <v>6817862</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12729,6 +12732,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12747,7 +12751,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128927853</v>
+        <v>128927869</v>
       </c>
       <c r="B123" t="n">
         <v>78792</v>
@@ -12782,10 +12786,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430073</v>
+        <v>430138</v>
       </c>
       <c r="R123" t="n">
-        <v>6818201</v>
+        <v>6817883</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12844,10 +12848,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128927777</v>
+        <v>128927720</v>
       </c>
       <c r="B124" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12855,42 +12859,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>429898</v>
+        <v>430112</v>
       </c>
       <c r="R124" t="n">
-        <v>6818099</v>
+        <v>6818160</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12949,10 +12945,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128927784</v>
+        <v>128927940</v>
       </c>
       <c r="B125" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12960,42 +12956,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>430201</v>
+        <v>429952</v>
       </c>
       <c r="R125" t="n">
-        <v>6818093</v>
+        <v>6818061</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13054,10 +13042,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128927769</v>
+        <v>128927853</v>
       </c>
       <c r="B126" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13065,42 +13053,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430485</v>
+        <v>430073</v>
       </c>
       <c r="R126" t="n">
-        <v>6818017</v>
+        <v>6818201</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13159,7 +13139,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128927953</v>
+        <v>128927918</v>
       </c>
       <c r="B127" t="n">
         <v>79035</v>
@@ -13188,19 +13168,16 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430242</v>
+        <v>430649</v>
       </c>
       <c r="R127" t="n">
-        <v>6818048</v>
+        <v>6818232</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13235,18 +13212,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13265,7 +13236,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128927907</v>
+        <v>128927878</v>
       </c>
       <c r="B128" t="n">
         <v>79035</v>
@@ -13300,10 +13271,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430394</v>
+        <v>430632</v>
       </c>
       <c r="R128" t="n">
-        <v>6818166</v>
+        <v>6818282</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13362,10 +13333,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128927977</v>
+        <v>128927777</v>
       </c>
       <c r="B129" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13373,26 +13344,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -13400,10 +13376,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430139</v>
+        <v>429898</v>
       </c>
       <c r="R129" t="n">
-        <v>6817862</v>
+        <v>6818099</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13444,7 +13420,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -13463,10 +13438,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128927869</v>
+        <v>128927784</v>
       </c>
       <c r="B130" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13474,34 +13449,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>430138</v>
+        <v>430201</v>
       </c>
       <c r="R130" t="n">
-        <v>6817883</v>
+        <v>6818093</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13560,10 +13543,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128927940</v>
+        <v>128927769</v>
       </c>
       <c r="B131" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13571,34 +13554,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>429952</v>
+        <v>430485</v>
       </c>
       <c r="R131" t="n">
-        <v>6818061</v>
+        <v>6818017</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13657,7 +13648,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128927918</v>
+        <v>128927953</v>
       </c>
       <c r="B132" t="n">
         <v>79035</v>
@@ -13686,16 +13677,19 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430649</v>
+        <v>430242</v>
       </c>
       <c r="R132" t="n">
-        <v>6818232</v>
+        <v>6818048</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13730,12 +13724,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13754,7 +13754,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128927878</v>
+        <v>128927907</v>
       </c>
       <c r="B133" t="n">
         <v>79035</v>
@@ -13789,10 +13789,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430632</v>
+        <v>430394</v>
       </c>
       <c r="R133" t="n">
-        <v>6818282</v>
+        <v>6818166</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14045,10 +14045,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128927894</v>
+        <v>128927824</v>
       </c>
       <c r="B136" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14056,37 +14056,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>430321</v>
+        <v>429941</v>
       </c>
       <c r="R136" t="n">
-        <v>6818095</v>
+        <v>6818056</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14121,18 +14118,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14151,10 +14142,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128927900</v>
+        <v>128927748</v>
       </c>
       <c r="B137" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14162,21 +14153,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14186,10 +14177,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430467</v>
+        <v>430202</v>
       </c>
       <c r="R137" t="n">
-        <v>6818020</v>
+        <v>6818084</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14248,45 +14239,54 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128927889</v>
+        <v>128927833</v>
       </c>
       <c r="B138" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430385</v>
+        <v>430204</v>
       </c>
       <c r="R138" t="n">
-        <v>6818203</v>
+        <v>6817811</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14327,6 +14327,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14345,10 +14346,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128927911</v>
+        <v>128927781</v>
       </c>
       <c r="B139" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14356,34 +14357,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430437</v>
+        <v>430480</v>
       </c>
       <c r="R139" t="n">
-        <v>6818227</v>
+        <v>6817997</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14442,10 +14451,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128927969</v>
+        <v>128927788</v>
       </c>
       <c r="B140" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14453,34 +14462,42 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>429947</v>
+        <v>430017</v>
       </c>
       <c r="R140" t="n">
-        <v>6818135</v>
+        <v>6818044</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14539,10 +14556,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128927956</v>
+        <v>128927775</v>
       </c>
       <c r="B141" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14550,34 +14567,42 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430119</v>
+        <v>430083</v>
       </c>
       <c r="R141" t="n">
-        <v>6818173</v>
+        <v>6818224</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14636,10 +14661,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128927925</v>
+        <v>128927792</v>
       </c>
       <c r="B142" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14647,34 +14672,42 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430683</v>
+        <v>430150</v>
       </c>
       <c r="R142" t="n">
-        <v>6818265</v>
+        <v>6817814</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14733,7 +14766,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128927972</v>
+        <v>128927894</v>
       </c>
       <c r="B143" t="n">
         <v>79035</v>
@@ -14771,10 +14804,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430018</v>
+        <v>430321</v>
       </c>
       <c r="R143" t="n">
-        <v>6818025</v>
+        <v>6818095</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14807,6 +14840,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -14834,7 +14872,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128927926</v>
+        <v>128927900</v>
       </c>
       <c r="B144" t="n">
         <v>79035</v>
@@ -14869,10 +14907,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430701</v>
+        <v>430467</v>
       </c>
       <c r="R144" t="n">
-        <v>6818261</v>
+        <v>6818020</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14931,10 +14969,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128927863</v>
+        <v>128927889</v>
       </c>
       <c r="B145" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14942,21 +14980,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14966,10 +15004,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>429970</v>
+        <v>430385</v>
       </c>
       <c r="R145" t="n">
-        <v>6818162</v>
+        <v>6818203</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15028,10 +15066,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128927709</v>
+        <v>128927863</v>
       </c>
       <c r="B146" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15039,21 +15077,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15063,10 +15101,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>430495</v>
+        <v>429970</v>
       </c>
       <c r="R146" t="n">
-        <v>6818056</v>
+        <v>6818162</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15125,10 +15163,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128927861</v>
+        <v>128927911</v>
       </c>
       <c r="B147" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15136,21 +15174,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15160,10 +15198,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>429989</v>
+        <v>430437</v>
       </c>
       <c r="R147" t="n">
-        <v>6818159</v>
+        <v>6818227</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15222,10 +15260,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927781</v>
+        <v>128927969</v>
       </c>
       <c r="B148" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15233,42 +15271,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430480</v>
+        <v>429947</v>
       </c>
       <c r="R148" t="n">
-        <v>6817997</v>
+        <v>6818135</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15327,10 +15357,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927788</v>
+        <v>128927709</v>
       </c>
       <c r="B149" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15338,42 +15368,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430017</v>
+        <v>430495</v>
       </c>
       <c r="R149" t="n">
-        <v>6818044</v>
+        <v>6818056</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15432,10 +15454,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927775</v>
+        <v>128927956</v>
       </c>
       <c r="B150" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15443,42 +15465,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430083</v>
+        <v>430119</v>
       </c>
       <c r="R150" t="n">
-        <v>6818224</v>
+        <v>6818173</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15537,10 +15551,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927792</v>
+        <v>128927925</v>
       </c>
       <c r="B151" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15548,42 +15562,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430150</v>
+        <v>430683</v>
       </c>
       <c r="R151" t="n">
-        <v>6817814</v>
+        <v>6818265</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15642,43 +15648,37 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128927833</v>
+        <v>128927972</v>
       </c>
       <c r="B152" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -15686,10 +15686,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430204</v>
+        <v>430018</v>
       </c>
       <c r="R152" t="n">
-        <v>6817811</v>
+        <v>6818025</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15749,10 +15749,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128927824</v>
+        <v>128927861</v>
       </c>
       <c r="B153" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15760,21 +15760,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15784,10 +15784,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>429941</v>
+        <v>429989</v>
       </c>
       <c r="R153" t="n">
-        <v>6818056</v>
+        <v>6818159</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15846,10 +15846,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128927748</v>
+        <v>128927926</v>
       </c>
       <c r="B154" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15857,21 +15857,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15881,10 +15881,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430202</v>
+        <v>430701</v>
       </c>
       <c r="R154" t="n">
-        <v>6818084</v>
+        <v>6818261</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15943,10 +15943,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128927917</v>
+        <v>128927798</v>
       </c>
       <c r="B155" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15954,21 +15954,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15978,10 +15978,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>430616</v>
+        <v>430315</v>
       </c>
       <c r="R155" t="n">
-        <v>6818194</v>
+        <v>6818095</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16040,10 +16040,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128927903</v>
+        <v>128927828</v>
       </c>
       <c r="B156" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16051,21 +16051,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16078,10 +16078,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>430437</v>
+        <v>430115</v>
       </c>
       <c r="R156" t="n">
-        <v>6818119</v>
+        <v>6817902</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16114,11 +16114,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Måttligt/rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16146,10 +16141,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128927875</v>
+        <v>128927779</v>
       </c>
       <c r="B157" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16157,34 +16152,42 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430127</v>
+        <v>430106</v>
       </c>
       <c r="R157" t="n">
-        <v>6817846</v>
+        <v>6817957</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16243,10 +16246,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128927920</v>
+        <v>128927783</v>
       </c>
       <c r="B158" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16254,34 +16257,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430637</v>
+        <v>430174</v>
       </c>
       <c r="R158" t="n">
-        <v>6818260</v>
+        <v>6817923</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16340,10 +16351,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128927838</v>
+        <v>128927917</v>
       </c>
       <c r="B159" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16351,21 +16362,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16375,10 +16386,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430439</v>
+        <v>430616</v>
       </c>
       <c r="R159" t="n">
-        <v>6818031</v>
+        <v>6818194</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16437,7 +16448,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128927951</v>
+        <v>128927903</v>
       </c>
       <c r="B160" t="n">
         <v>79035</v>
@@ -16475,10 +16486,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430191</v>
+        <v>430437</v>
       </c>
       <c r="R160" t="n">
-        <v>6817932</v>
+        <v>6818119</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16515,7 +16526,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Garnlav, måttligt inom en radie av 30m</t>
+          <t>Måttligt/rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16543,10 +16554,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128927958</v>
+        <v>128927875</v>
       </c>
       <c r="B161" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16554,21 +16565,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16578,10 +16589,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430048</v>
+        <v>430127</v>
       </c>
       <c r="R161" t="n">
-        <v>6818232</v>
+        <v>6817846</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16640,7 +16651,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128927902</v>
+        <v>128927920</v>
       </c>
       <c r="B162" t="n">
         <v>79035</v>
@@ -16675,10 +16686,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430530</v>
+        <v>430637</v>
       </c>
       <c r="R162" t="n">
-        <v>6818025</v>
+        <v>6818260</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16737,7 +16748,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128927837</v>
+        <v>128927838</v>
       </c>
       <c r="B163" t="n">
         <v>78792</v>
@@ -16772,10 +16783,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430360</v>
+        <v>430439</v>
       </c>
       <c r="R163" t="n">
-        <v>6818057</v>
+        <v>6818031</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16834,7 +16845,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128927846</v>
+        <v>128927837</v>
       </c>
       <c r="B164" t="n">
         <v>78792</v>
@@ -16869,10 +16880,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430241</v>
+        <v>430360</v>
       </c>
       <c r="R164" t="n">
-        <v>6818085</v>
+        <v>6818057</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16931,10 +16942,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128927779</v>
+        <v>128927951</v>
       </c>
       <c r="B165" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16942,31 +16953,26 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -16974,10 +16980,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430106</v>
+        <v>430191</v>
       </c>
       <c r="R165" t="n">
-        <v>6817957</v>
+        <v>6817932</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17012,12 +17018,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Garnlav, måttligt inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17036,10 +17048,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128927783</v>
+        <v>128927958</v>
       </c>
       <c r="B166" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17047,42 +17059,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>430174</v>
+        <v>430048</v>
       </c>
       <c r="R166" t="n">
-        <v>6817923</v>
+        <v>6818232</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17141,10 +17145,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128927798</v>
+        <v>128927846</v>
       </c>
       <c r="B167" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17152,21 +17156,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17176,10 +17180,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430315</v>
+        <v>430241</v>
       </c>
       <c r="R167" t="n">
-        <v>6818095</v>
+        <v>6818085</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17238,10 +17242,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128927828</v>
+        <v>128927902</v>
       </c>
       <c r="B168" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17249,37 +17253,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430115</v>
+        <v>430530</v>
       </c>
       <c r="R168" t="n">
-        <v>6817902</v>
+        <v>6818025</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17320,7 +17321,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17436,48 +17436,45 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128927933</v>
+        <v>128927835</v>
       </c>
       <c r="B170" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430220</v>
+        <v>430104</v>
       </c>
       <c r="R170" t="n">
-        <v>6818148</v>
+        <v>6817960</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17512,18 +17509,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -17542,7 +17533,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128927904</v>
+        <v>128927933</v>
       </c>
       <c r="B171" t="n">
         <v>79035</v>
@@ -17571,16 +17562,19 @@
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430405</v>
+        <v>430220</v>
       </c>
       <c r="R171" t="n">
-        <v>6818117</v>
+        <v>6818148</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17615,12 +17609,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -17740,10 +17740,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128927712</v>
+        <v>128927904</v>
       </c>
       <c r="B173" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17751,21 +17751,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17775,10 +17775,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430596</v>
+        <v>430405</v>
       </c>
       <c r="R173" t="n">
-        <v>6818190</v>
+        <v>6818117</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17837,10 +17837,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128927829</v>
+        <v>128927712</v>
       </c>
       <c r="B174" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17848,21 +17848,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17872,10 +17872,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430138</v>
+        <v>430596</v>
       </c>
       <c r="R174" t="n">
-        <v>6817883</v>
+        <v>6818190</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17934,32 +17934,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128927835</v>
+        <v>128927829</v>
       </c>
       <c r="B175" t="n">
-        <v>58093</v>
+        <v>78793</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17969,10 +17969,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430104</v>
+        <v>430138</v>
       </c>
       <c r="R175" t="n">
-        <v>6817960</v>
+        <v>6817883</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18031,53 +18031,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128927762</v>
+        <v>128927750</v>
       </c>
       <c r="B176" t="n">
-        <v>56913</v>
+        <v>79625</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430394</v>
+        <v>430140</v>
       </c>
       <c r="R176" t="n">
-        <v>6818168</v>
+        <v>6817881</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18136,53 +18128,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128927760</v>
+        <v>128927741</v>
       </c>
       <c r="B177" t="n">
-        <v>56913</v>
+        <v>79625</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430663</v>
+        <v>430600</v>
       </c>
       <c r="R177" t="n">
-        <v>6818259</v>
+        <v>6818203</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18241,10 +18225,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128927750</v>
+        <v>128927812</v>
       </c>
       <c r="B178" t="n">
-        <v>79625</v>
+        <v>78793</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18252,21 +18236,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18276,10 +18260,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430140</v>
+        <v>430157</v>
       </c>
       <c r="R178" t="n">
-        <v>6817881</v>
+        <v>6818149</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18338,10 +18322,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128927741</v>
+        <v>128927898</v>
       </c>
       <c r="B179" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18349,21 +18333,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18373,10 +18357,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430600</v>
+        <v>430384</v>
       </c>
       <c r="R179" t="n">
-        <v>6818203</v>
+        <v>6818048</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18435,10 +18419,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128927898</v>
+        <v>128927723</v>
       </c>
       <c r="B180" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18446,21 +18430,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18470,10 +18454,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>430384</v>
+        <v>429993</v>
       </c>
       <c r="R180" t="n">
-        <v>6818048</v>
+        <v>6818157</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18532,10 +18516,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128927968</v>
+        <v>128927848</v>
       </c>
       <c r="B181" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18543,21 +18527,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18567,10 +18551,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430067</v>
+        <v>430174</v>
       </c>
       <c r="R181" t="n">
-        <v>6818139</v>
+        <v>6818156</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18629,7 +18613,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128927952</v>
+        <v>128927968</v>
       </c>
       <c r="B182" t="n">
         <v>79035</v>
@@ -18664,10 +18648,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430190</v>
+        <v>430067</v>
       </c>
       <c r="R182" t="n">
-        <v>6817925</v>
+        <v>6818139</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18726,7 +18710,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128927945</v>
+        <v>128927952</v>
       </c>
       <c r="B183" t="n">
         <v>79035</v>
@@ -18761,10 +18745,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430404</v>
+        <v>430190</v>
       </c>
       <c r="R183" t="n">
-        <v>6818178</v>
+        <v>6817925</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18823,10 +18807,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128927723</v>
+        <v>128927945</v>
       </c>
       <c r="B184" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18834,21 +18818,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18858,10 +18842,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>429993</v>
+        <v>430404</v>
       </c>
       <c r="R184" t="n">
-        <v>6818157</v>
+        <v>6818178</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18920,45 +18904,53 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128927848</v>
+        <v>128927760</v>
       </c>
       <c r="B185" t="n">
-        <v>78792</v>
+        <v>56913</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430174</v>
+        <v>430663</v>
       </c>
       <c r="R185" t="n">
-        <v>6818156</v>
+        <v>6818259</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19017,45 +19009,53 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128927812</v>
+        <v>128927762</v>
       </c>
       <c r="B186" t="n">
-        <v>78793</v>
+        <v>56913</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430157</v>
+        <v>430394</v>
       </c>
       <c r="R186" t="n">
-        <v>6818149</v>
+        <v>6818168</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19114,10 +19114,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128927910</v>
+        <v>128927789</v>
       </c>
       <c r="B187" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19125,34 +19125,42 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430430</v>
+        <v>430089</v>
       </c>
       <c r="R187" t="n">
-        <v>6818202</v>
+        <v>6817965</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19185,6 +19193,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19211,10 +19224,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128927847</v>
+        <v>128927820</v>
       </c>
       <c r="B188" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19222,21 +19235,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19246,10 +19259,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430227</v>
+        <v>430014</v>
       </c>
       <c r="R188" t="n">
-        <v>6818154</v>
+        <v>6818142</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19308,10 +19321,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128927892</v>
+        <v>128927818</v>
       </c>
       <c r="B189" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19319,21 +19332,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19343,10 +19356,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430304</v>
+        <v>430048</v>
       </c>
       <c r="R189" t="n">
-        <v>6818124</v>
+        <v>6818123</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19405,7 +19418,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128927906</v>
+        <v>128927910</v>
       </c>
       <c r="B190" t="n">
         <v>79035</v>
@@ -19434,19 +19447,16 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430401</v>
+        <v>430430</v>
       </c>
       <c r="R190" t="n">
-        <v>6818157</v>
+        <v>6818202</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19481,18 +19491,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
-        </is>
-      </c>
       <c r="AD190" t="b">
         <v>0</v>
       </c>
       <c r="AE190" t="b">
         <v>0</v>
       </c>
-      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
@@ -19511,10 +19515,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128927922</v>
+        <v>128927731</v>
       </c>
       <c r="B191" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19522,21 +19526,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19546,10 +19550,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430668</v>
+        <v>430056</v>
       </c>
       <c r="R191" t="n">
-        <v>6818241</v>
+        <v>6818017</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19608,10 +19612,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128927962</v>
+        <v>128927847</v>
       </c>
       <c r="B192" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19619,21 +19623,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19643,10 +19647,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430069</v>
+        <v>430227</v>
       </c>
       <c r="R192" t="n">
-        <v>6818225</v>
+        <v>6818154</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19705,10 +19709,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128927731</v>
+        <v>128927892</v>
       </c>
       <c r="B193" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19716,21 +19720,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19740,10 +19744,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430056</v>
+        <v>430304</v>
       </c>
       <c r="R193" t="n">
-        <v>6818017</v>
+        <v>6818124</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19996,10 +20000,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128927820</v>
+        <v>128927906</v>
       </c>
       <c r="B196" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20007,34 +20011,37 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430014</v>
+        <v>430401</v>
       </c>
       <c r="R196" t="n">
-        <v>6818142</v>
+        <v>6818157</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20069,12 +20076,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
+        </is>
+      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20093,10 +20106,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128927818</v>
+        <v>128927922</v>
       </c>
       <c r="B197" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20104,21 +20117,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20128,10 +20141,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430048</v>
+        <v>430668</v>
       </c>
       <c r="R197" t="n">
-        <v>6818123</v>
+        <v>6818241</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20190,10 +20203,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128927789</v>
+        <v>128927962</v>
       </c>
       <c r="B198" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20201,42 +20214,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430089</v>
+        <v>430069</v>
       </c>
       <c r="R198" t="n">
-        <v>6817965</v>
+        <v>6818225</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20269,11 +20274,6 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -20300,10 +20300,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128927913</v>
+        <v>128927755</v>
       </c>
       <c r="B199" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20311,34 +20311,42 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430484</v>
+        <v>430480</v>
       </c>
       <c r="R199" t="n">
-        <v>6818253</v>
+        <v>6818068</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20397,10 +20405,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128927841</v>
+        <v>128927913</v>
       </c>
       <c r="B200" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20408,21 +20416,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20432,10 +20440,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430569</v>
+        <v>430484</v>
       </c>
       <c r="R200" t="n">
-        <v>6818243</v>
+        <v>6818253</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20494,10 +20502,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128927936</v>
+        <v>128927841</v>
       </c>
       <c r="B201" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20505,21 +20513,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20529,10 +20537,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430084</v>
+        <v>430569</v>
       </c>
       <c r="R201" t="n">
-        <v>6818157</v>
+        <v>6818243</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20591,7 +20599,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128927942</v>
+        <v>128927936</v>
       </c>
       <c r="B202" t="n">
         <v>79035</v>
@@ -20626,10 +20634,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430087</v>
+        <v>430084</v>
       </c>
       <c r="R202" t="n">
-        <v>6817971</v>
+        <v>6818157</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20882,10 +20890,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128927755</v>
+        <v>128927961</v>
       </c>
       <c r="B205" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20893,42 +20901,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430480</v>
+        <v>430086</v>
       </c>
       <c r="R205" t="n">
-        <v>6818068</v>
+        <v>6818236</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20987,7 +20987,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128927961</v>
+        <v>128927942</v>
       </c>
       <c r="B206" t="n">
         <v>79035</v>
@@ -21022,10 +21022,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430086</v>
+        <v>430087</v>
       </c>
       <c r="R206" t="n">
-        <v>6818236</v>
+        <v>6817971</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21375,10 +21375,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128927830</v>
+        <v>128927860</v>
       </c>
       <c r="B210" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21386,21 +21386,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21410,10 +21410,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430167</v>
+        <v>430013</v>
       </c>
       <c r="R210" t="n">
-        <v>6817850</v>
+        <v>6818142</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21472,10 +21472,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128927808</v>
+        <v>128927941</v>
       </c>
       <c r="B211" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21483,21 +21483,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21507,10 +21507,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>430669</v>
+        <v>430078</v>
       </c>
       <c r="R211" t="n">
-        <v>6818242</v>
+        <v>6817995</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21569,10 +21569,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128927817</v>
+        <v>128927960</v>
       </c>
       <c r="B212" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21580,21 +21580,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21604,10 +21604,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430068</v>
+        <v>430089</v>
       </c>
       <c r="R212" t="n">
-        <v>6818152</v>
+        <v>6818238</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21666,10 +21666,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128927746</v>
+        <v>128927866</v>
       </c>
       <c r="B213" t="n">
-        <v>79625</v>
+        <v>78792</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21677,21 +21677,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21701,10 +21701,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>430232</v>
+        <v>429950</v>
       </c>
       <c r="R213" t="n">
-        <v>6818068</v>
+        <v>6818057</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21763,10 +21763,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128927860</v>
+        <v>128927753</v>
       </c>
       <c r="B214" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21774,34 +21774,42 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>430013</v>
+        <v>430514</v>
       </c>
       <c r="R214" t="n">
-        <v>6818142</v>
+        <v>6818047</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21860,10 +21868,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128927941</v>
+        <v>128927830</v>
       </c>
       <c r="B215" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21871,21 +21879,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21895,10 +21903,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>430078</v>
+        <v>430167</v>
       </c>
       <c r="R215" t="n">
-        <v>6817995</v>
+        <v>6817850</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21957,10 +21965,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128927960</v>
+        <v>128927808</v>
       </c>
       <c r="B216" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21968,21 +21976,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -21992,10 +22000,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>430089</v>
+        <v>430669</v>
       </c>
       <c r="R216" t="n">
-        <v>6818238</v>
+        <v>6818242</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22054,10 +22062,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128927866</v>
+        <v>128927817</v>
       </c>
       <c r="B217" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22065,21 +22073,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22089,10 +22097,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>429950</v>
+        <v>430068</v>
       </c>
       <c r="R217" t="n">
-        <v>6818057</v>
+        <v>6818152</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22151,10 +22159,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128927753</v>
+        <v>128927746</v>
       </c>
       <c r="B218" t="n">
-        <v>57723</v>
+        <v>79625</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22162,42 +22170,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>430514</v>
+        <v>430232</v>
       </c>
       <c r="R218" t="n">
-        <v>6818047</v>
+        <v>6818068</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22256,10 +22256,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128927967</v>
+        <v>128927800</v>
       </c>
       <c r="B219" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22267,34 +22267,37 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430084</v>
+        <v>430487</v>
       </c>
       <c r="R219" t="n">
-        <v>6818144</v>
+        <v>6818080</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22335,6 +22338,7 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -22353,10 +22357,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128927881</v>
+        <v>128927771</v>
       </c>
       <c r="B220" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22364,34 +22368,42 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430536</v>
+        <v>430658</v>
       </c>
       <c r="R220" t="n">
-        <v>6818208</v>
+        <v>6818274</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22450,7 +22462,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128927916</v>
+        <v>128927967</v>
       </c>
       <c r="B221" t="n">
         <v>79035</v>
@@ -22485,10 +22497,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430580</v>
+        <v>430084</v>
       </c>
       <c r="R221" t="n">
-        <v>6818221</v>
+        <v>6818144</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22644,10 +22656,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128927771</v>
+        <v>128927881</v>
       </c>
       <c r="B223" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22655,42 +22667,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430658</v>
+        <v>430536</v>
       </c>
       <c r="R223" t="n">
-        <v>6818274</v>
+        <v>6818208</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22749,10 +22753,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128927800</v>
+        <v>128927916</v>
       </c>
       <c r="B224" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22760,37 +22764,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430487</v>
+        <v>430580</v>
       </c>
       <c r="R224" t="n">
-        <v>6818080</v>
+        <v>6818221</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22831,7 +22832,6 @@
       <c r="AE224" t="b">
         <v>0</v>
       </c>
-      <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
       </c>
@@ -22850,10 +22850,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128927890</v>
+        <v>128927850</v>
       </c>
       <c r="B225" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22861,21 +22861,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -22885,10 +22885,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>430348</v>
+        <v>430159</v>
       </c>
       <c r="R225" t="n">
-        <v>6818167</v>
+        <v>6818161</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -22947,7 +22947,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128927915</v>
+        <v>128927890</v>
       </c>
       <c r="B226" t="n">
         <v>79035</v>
@@ -22976,19 +22976,16 @@
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430575</v>
+        <v>430348</v>
       </c>
       <c r="R226" t="n">
-        <v>6818234</v>
+        <v>6818167</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23029,7 +23026,6 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
-      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
@@ -23048,10 +23044,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128927923</v>
+        <v>128927730</v>
       </c>
       <c r="B227" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23059,21 +23055,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23083,10 +23079,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430670</v>
+        <v>430075</v>
       </c>
       <c r="R227" t="n">
-        <v>6818263</v>
+        <v>6818213</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23145,10 +23141,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128927850</v>
+        <v>128927915</v>
       </c>
       <c r="B228" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -23156,34 +23152,37 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>430159</v>
+        <v>430575</v>
       </c>
       <c r="R228" t="n">
-        <v>6818161</v>
+        <v>6818234</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23224,6 +23223,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -23242,10 +23242,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128927730</v>
+        <v>128927923</v>
       </c>
       <c r="B229" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23253,21 +23253,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23277,10 +23277,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>430075</v>
+        <v>430670</v>
       </c>
       <c r="R229" t="n">
-        <v>6818213</v>
+        <v>6818263</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128927732</v>
+        <v>128927821</v>
       </c>
       <c r="B22" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430138</v>
+        <v>429994</v>
       </c>
       <c r="R22" t="n">
-        <v>6817883</v>
+        <v>6818158</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927950</v>
+        <v>128927802</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430233</v>
+        <v>430567</v>
       </c>
       <c r="R23" t="n">
-        <v>6817831</v>
+        <v>6818243</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927880</v>
+        <v>128927732</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430577</v>
+        <v>430138</v>
       </c>
       <c r="R24" t="n">
-        <v>6818221</v>
+        <v>6817883</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927868</v>
+        <v>128927950</v>
       </c>
       <c r="B25" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,21 +3153,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430089</v>
+        <v>430233</v>
       </c>
       <c r="R25" t="n">
-        <v>6817984</v>
+        <v>6817831</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,7 +3239,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927978</v>
+        <v>128927880</v>
       </c>
       <c r="B26" t="n">
         <v>79035</v>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430082</v>
+        <v>430577</v>
       </c>
       <c r="R26" t="n">
-        <v>6818210</v>
+        <v>6818221</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3318,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3337,7 +3336,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927843</v>
+        <v>128927868</v>
       </c>
       <c r="B27" t="n">
         <v>78792</v>
@@ -3372,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430626</v>
+        <v>430089</v>
       </c>
       <c r="R27" t="n">
-        <v>6818202</v>
+        <v>6817984</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927721</v>
+        <v>128927978</v>
       </c>
       <c r="B28" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3445,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3469,10 +3468,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430060</v>
+        <v>430082</v>
       </c>
       <c r="R28" t="n">
-        <v>6818156</v>
+        <v>6818210</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,6 +3512,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927935</v>
+        <v>128927843</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,21 +3542,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430099</v>
+        <v>430626</v>
       </c>
       <c r="R29" t="n">
-        <v>6818154</v>
+        <v>6818202</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927726</v>
+        <v>128927721</v>
       </c>
       <c r="B30" t="n">
         <v>79654</v>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430114</v>
+        <v>430060</v>
       </c>
       <c r="R30" t="n">
-        <v>6817912</v>
+        <v>6818156</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,32 +3725,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927834</v>
+        <v>128927935</v>
       </c>
       <c r="B31" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430596</v>
+        <v>430099</v>
       </c>
       <c r="R31" t="n">
-        <v>6818184</v>
+        <v>6818154</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128927770</v>
+        <v>128927726</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3833,42 +3833,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430455</v>
+        <v>430114</v>
       </c>
       <c r="R32" t="n">
-        <v>6818246</v>
+        <v>6817912</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,32 +3919,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128927963</v>
+        <v>128927834</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3962,10 +3954,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>430064</v>
+        <v>430596</v>
       </c>
       <c r="R33" t="n">
-        <v>6818190</v>
+        <v>6818184</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4024,10 +4016,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128927821</v>
+        <v>128927770</v>
       </c>
       <c r="B34" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,34 +4027,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>429994</v>
+        <v>430455</v>
       </c>
       <c r="R34" t="n">
-        <v>6818158</v>
+        <v>6818246</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128927802</v>
+        <v>128927963</v>
       </c>
       <c r="B35" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4132,21 +4132,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430567</v>
+        <v>430064</v>
       </c>
       <c r="R35" t="n">
-        <v>6818243</v>
+        <v>6818190</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128927845</v>
+        <v>128927786</v>
       </c>
       <c r="B43" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,34 +4920,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430669</v>
+        <v>430078</v>
       </c>
       <c r="R43" t="n">
-        <v>6818249</v>
+        <v>6818213</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4980,6 +4988,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5006,10 +5019,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128927930</v>
+        <v>128927845</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5041,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430205</v>
+        <v>430669</v>
       </c>
       <c r="R44" t="n">
-        <v>6817961</v>
+        <v>6818249</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,7 +5116,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128927928</v>
+        <v>128927930</v>
       </c>
       <c r="B45" t="n">
         <v>79035</v>
@@ -5138,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430293</v>
+        <v>430205</v>
       </c>
       <c r="R45" t="n">
-        <v>6817871</v>
+        <v>6817961</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5200,7 +5213,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128927934</v>
+        <v>128927928</v>
       </c>
       <c r="B46" t="n">
         <v>79035</v>
@@ -5235,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430088</v>
+        <v>430293</v>
       </c>
       <c r="R46" t="n">
-        <v>6818186</v>
+        <v>6817871</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,10 +5310,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128927842</v>
+        <v>128927934</v>
       </c>
       <c r="B47" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5308,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5332,7 +5345,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430596</v>
+        <v>430088</v>
       </c>
       <c r="R47" t="n">
         <v>6818186</v>
@@ -5394,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128927938</v>
+        <v>128927842</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5405,21 +5418,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5429,10 +5442,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>429959</v>
+        <v>430596</v>
       </c>
       <c r="R48" t="n">
-        <v>6818128</v>
+        <v>6818186</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5491,7 +5504,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128927976</v>
+        <v>128927938</v>
       </c>
       <c r="B49" t="n">
         <v>79035</v>
@@ -5520,19 +5533,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430149</v>
+        <v>429959</v>
       </c>
       <c r="R49" t="n">
-        <v>6817860</v>
+        <v>6818128</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5573,7 +5583,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5592,7 +5601,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128927966</v>
+        <v>128927976</v>
       </c>
       <c r="B50" t="n">
         <v>79035</v>
@@ -5621,16 +5630,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430071</v>
+        <v>430149</v>
       </c>
       <c r="R50" t="n">
-        <v>6818124</v>
+        <v>6817860</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5671,6 +5683,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5702,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128927786</v>
+        <v>128927966</v>
       </c>
       <c r="B51" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,42 +5713,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430078</v>
+        <v>430071</v>
       </c>
       <c r="R51" t="n">
-        <v>6818213</v>
+        <v>6818124</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5768,11 +5773,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6187,10 +6187,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128927874</v>
+        <v>128927815</v>
       </c>
       <c r="B56" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>430154</v>
+        <v>430061</v>
       </c>
       <c r="R56" t="n">
-        <v>6817859</v>
+        <v>6818258</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128927970</v>
+        <v>128927937</v>
       </c>
       <c r="B57" t="n">
         <v>79035</v>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>429900</v>
+        <v>430011</v>
       </c>
       <c r="R57" t="n">
-        <v>6818098</v>
+        <v>6818137</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6355,11 +6355,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6386,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128927944</v>
+        <v>128927874</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6397,37 +6392,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>430531</v>
+        <v>430154</v>
       </c>
       <c r="R58" t="n">
-        <v>6818016</v>
+        <v>6817859</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6468,7 +6460,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6487,7 +6478,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927948</v>
+        <v>128927970</v>
       </c>
       <c r="B59" t="n">
         <v>79035</v>
@@ -6522,10 +6513,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430655</v>
+        <v>429900</v>
       </c>
       <c r="R59" t="n">
-        <v>6818216</v>
+        <v>6818098</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6558,6 +6549,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6584,10 +6580,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927735</v>
+        <v>128927944</v>
       </c>
       <c r="B60" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6595,34 +6591,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430132</v>
+        <v>430531</v>
       </c>
       <c r="R60" t="n">
-        <v>6817858</v>
+        <v>6818016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6663,6 +6662,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128927882</v>
+        <v>128927948</v>
       </c>
       <c r="B61" t="n">
         <v>79035</v>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430526</v>
+        <v>430655</v>
       </c>
       <c r="R61" t="n">
-        <v>6818232</v>
+        <v>6818216</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128927929</v>
+        <v>128927735</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430208</v>
+        <v>430132</v>
       </c>
       <c r="R62" t="n">
-        <v>6817816</v>
+        <v>6817858</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6875,10 +6875,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128927855</v>
+        <v>128927882</v>
       </c>
       <c r="B63" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6886,21 +6886,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>430113</v>
+        <v>430526</v>
       </c>
       <c r="R63" t="n">
-        <v>6818160</v>
+        <v>6818232</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6972,7 +6972,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128927937</v>
+        <v>128927929</v>
       </c>
       <c r="B64" t="n">
         <v>79035</v>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>430011</v>
+        <v>430208</v>
       </c>
       <c r="R64" t="n">
-        <v>6818137</v>
+        <v>6817816</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128927815</v>
+        <v>128927855</v>
       </c>
       <c r="B65" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430061</v>
+        <v>430113</v>
       </c>
       <c r="R65" t="n">
-        <v>6818258</v>
+        <v>6818160</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7368,10 +7368,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128927893</v>
+        <v>128927751</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7379,34 +7379,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430286</v>
+        <v>430337</v>
       </c>
       <c r="R68" t="n">
-        <v>6818100</v>
+        <v>6818076</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7465,7 +7473,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128927974</v>
+        <v>128927893</v>
       </c>
       <c r="B69" t="n">
         <v>79035</v>
@@ -7500,10 +7508,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430091</v>
+        <v>430286</v>
       </c>
       <c r="R69" t="n">
-        <v>6818012</v>
+        <v>6818100</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7562,10 +7570,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128927751</v>
+        <v>128927974</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7573,42 +7581,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>430337</v>
+        <v>430091</v>
       </c>
       <c r="R70" t="n">
-        <v>6818076</v>
+        <v>6818012</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -10798,10 +10798,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927793</v>
+        <v>128927899</v>
       </c>
       <c r="B103" t="n">
-        <v>58153</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430104</v>
+        <v>430428</v>
       </c>
       <c r="R103" t="n">
-        <v>6817933</v>
+        <v>6818038</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,10 +10895,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927827</v>
+        <v>128927954</v>
       </c>
       <c r="B104" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10906,34 +10906,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430057</v>
+        <v>430166</v>
       </c>
       <c r="R104" t="n">
-        <v>6818016</v>
+        <v>6818134</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10968,12 +10971,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -10992,10 +11001,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927822</v>
+        <v>128927888</v>
       </c>
       <c r="B105" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11003,21 +11012,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11027,10 +11036,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>429973</v>
+        <v>430399</v>
       </c>
       <c r="R105" t="n">
-        <v>6818162</v>
+        <v>6818238</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11089,10 +11098,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927826</v>
+        <v>128927971</v>
       </c>
       <c r="B106" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11100,21 +11109,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11124,10 +11133,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430018</v>
+        <v>429925</v>
       </c>
       <c r="R106" t="n">
-        <v>6818046</v>
+        <v>6818065</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11186,10 +11195,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927796</v>
+        <v>128927949</v>
       </c>
       <c r="B107" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11197,21 +11206,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11221,10 +11230,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430323</v>
+        <v>430653</v>
       </c>
       <c r="R107" t="n">
-        <v>6818121</v>
+        <v>6818272</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11283,10 +11292,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927899</v>
+        <v>128927856</v>
       </c>
       <c r="B108" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11294,21 +11303,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11318,10 +11327,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430428</v>
+        <v>430060</v>
       </c>
       <c r="R108" t="n">
-        <v>6818038</v>
+        <v>6818160</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11380,48 +11389,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927954</v>
+        <v>128927836</v>
       </c>
       <c r="B109" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430166</v>
+        <v>430147</v>
       </c>
       <c r="R109" t="n">
-        <v>6818134</v>
+        <v>6817817</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11456,18 +11462,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11486,10 +11486,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128927888</v>
+        <v>128927793</v>
       </c>
       <c r="B110" t="n">
-        <v>79035</v>
+        <v>58153</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11497,21 +11497,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430399</v>
+        <v>430104</v>
       </c>
       <c r="R110" t="n">
-        <v>6818238</v>
+        <v>6817933</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11583,10 +11583,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927971</v>
+        <v>128927827</v>
       </c>
       <c r="B111" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11594,21 +11594,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11618,10 +11618,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>429925</v>
+        <v>430057</v>
       </c>
       <c r="R111" t="n">
-        <v>6818065</v>
+        <v>6818016</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927949</v>
+        <v>128927822</v>
       </c>
       <c r="B112" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11691,21 +11691,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>430653</v>
+        <v>429973</v>
       </c>
       <c r="R112" t="n">
-        <v>6818272</v>
+        <v>6818162</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,10 +11777,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927856</v>
+        <v>128927826</v>
       </c>
       <c r="B113" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11788,21 +11788,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430060</v>
+        <v>430018</v>
       </c>
       <c r="R113" t="n">
-        <v>6818160</v>
+        <v>6818046</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,32 +11874,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927836</v>
+        <v>128927796</v>
       </c>
       <c r="B114" t="n">
-        <v>58093</v>
+        <v>78793</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430147</v>
+        <v>430323</v>
       </c>
       <c r="R114" t="n">
-        <v>6817817</v>
+        <v>6818121</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128927977</v>
+        <v>128927777</v>
       </c>
       <c r="B122" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12661,26 +12661,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -12688,10 +12693,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>430139</v>
+        <v>429898</v>
       </c>
       <c r="R122" t="n">
-        <v>6817862</v>
+        <v>6818099</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12732,7 +12737,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12751,10 +12755,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128927869</v>
+        <v>128927784</v>
       </c>
       <c r="B123" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12762,34 +12766,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430138</v>
+        <v>430201</v>
       </c>
       <c r="R123" t="n">
-        <v>6817883</v>
+        <v>6818093</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12848,10 +12860,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128927720</v>
+        <v>128927769</v>
       </c>
       <c r="B124" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12859,34 +12871,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430112</v>
+        <v>430485</v>
       </c>
       <c r="R124" t="n">
-        <v>6818160</v>
+        <v>6818017</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12945,7 +12965,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128927940</v>
+        <v>128927953</v>
       </c>
       <c r="B125" t="n">
         <v>79035</v>
@@ -12974,16 +12994,19 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>429952</v>
+        <v>430242</v>
       </c>
       <c r="R125" t="n">
-        <v>6818061</v>
+        <v>6818048</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13018,12 +13041,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13042,10 +13071,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128927853</v>
+        <v>128927907</v>
       </c>
       <c r="B126" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13053,21 +13082,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13077,10 +13106,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430073</v>
+        <v>430394</v>
       </c>
       <c r="R126" t="n">
-        <v>6818201</v>
+        <v>6818166</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13139,7 +13168,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128927918</v>
+        <v>128927977</v>
       </c>
       <c r="B127" t="n">
         <v>79035</v>
@@ -13168,16 +13197,19 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430649</v>
+        <v>430139</v>
       </c>
       <c r="R127" t="n">
-        <v>6818232</v>
+        <v>6817862</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13218,6 +13250,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13236,10 +13269,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128927878</v>
+        <v>128927869</v>
       </c>
       <c r="B128" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13247,21 +13280,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13271,10 +13304,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430632</v>
+        <v>430138</v>
       </c>
       <c r="R128" t="n">
-        <v>6818282</v>
+        <v>6817883</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13333,10 +13366,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128927777</v>
+        <v>128927720</v>
       </c>
       <c r="B129" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13344,42 +13377,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>429898</v>
+        <v>430112</v>
       </c>
       <c r="R129" t="n">
-        <v>6818099</v>
+        <v>6818160</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13438,10 +13463,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128927784</v>
+        <v>128927940</v>
       </c>
       <c r="B130" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13449,42 +13474,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>430201</v>
+        <v>429952</v>
       </c>
       <c r="R130" t="n">
-        <v>6818093</v>
+        <v>6818061</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13543,10 +13560,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128927769</v>
+        <v>128927853</v>
       </c>
       <c r="B131" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13554,42 +13571,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430485</v>
+        <v>430073</v>
       </c>
       <c r="R131" t="n">
-        <v>6818017</v>
+        <v>6818201</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13648,7 +13657,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128927953</v>
+        <v>128927918</v>
       </c>
       <c r="B132" t="n">
         <v>79035</v>
@@ -13677,19 +13686,16 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430242</v>
+        <v>430649</v>
       </c>
       <c r="R132" t="n">
-        <v>6818048</v>
+        <v>6818232</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13724,18 +13730,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13754,7 +13754,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128927907</v>
+        <v>128927878</v>
       </c>
       <c r="B133" t="n">
         <v>79035</v>
@@ -13789,10 +13789,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430394</v>
+        <v>430632</v>
       </c>
       <c r="R133" t="n">
-        <v>6818166</v>
+        <v>6818282</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -19114,10 +19114,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128927789</v>
+        <v>128927820</v>
       </c>
       <c r="B187" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19125,42 +19125,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430089</v>
+        <v>430014</v>
       </c>
       <c r="R187" t="n">
-        <v>6817965</v>
+        <v>6818142</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19193,11 +19185,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19224,7 +19211,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128927820</v>
+        <v>128927818</v>
       </c>
       <c r="B188" t="n">
         <v>78793</v>
@@ -19259,10 +19246,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430014</v>
+        <v>430048</v>
       </c>
       <c r="R188" t="n">
-        <v>6818142</v>
+        <v>6818123</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19321,10 +19308,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128927818</v>
+        <v>128927789</v>
       </c>
       <c r="B189" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19332,34 +19319,42 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430048</v>
+        <v>430089</v>
       </c>
       <c r="R189" t="n">
-        <v>6818123</v>
+        <v>6817965</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19392,6 +19387,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20300,10 +20300,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128927755</v>
+        <v>128927913</v>
       </c>
       <c r="B199" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20311,42 +20311,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430480</v>
+        <v>430484</v>
       </c>
       <c r="R199" t="n">
-        <v>6818068</v>
+        <v>6818253</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20405,10 +20397,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128927913</v>
+        <v>128927841</v>
       </c>
       <c r="B200" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20416,21 +20408,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20440,10 +20432,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430484</v>
+        <v>430569</v>
       </c>
       <c r="R200" t="n">
-        <v>6818253</v>
+        <v>6818243</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20502,10 +20494,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128927841</v>
+        <v>128927936</v>
       </c>
       <c r="B201" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20513,21 +20505,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20537,10 +20529,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430569</v>
+        <v>430084</v>
       </c>
       <c r="R201" t="n">
-        <v>6818243</v>
+        <v>6818157</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20599,10 +20591,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128927936</v>
+        <v>128927717</v>
       </c>
       <c r="B202" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20610,21 +20602,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20634,10 +20626,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>430084</v>
+        <v>430214</v>
       </c>
       <c r="R202" t="n">
-        <v>6818157</v>
+        <v>6817971</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -20696,7 +20688,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128927717</v>
+        <v>128927715</v>
       </c>
       <c r="B203" t="n">
         <v>79654</v>
@@ -20731,10 +20723,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430214</v>
+        <v>430650</v>
       </c>
       <c r="R203" t="n">
-        <v>6817971</v>
+        <v>6818249</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20793,10 +20785,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128927715</v>
+        <v>128927961</v>
       </c>
       <c r="B204" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20804,21 +20796,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20828,10 +20820,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430650</v>
+        <v>430086</v>
       </c>
       <c r="R204" t="n">
-        <v>6818249</v>
+        <v>6818236</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20890,7 +20882,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128927961</v>
+        <v>128927942</v>
       </c>
       <c r="B205" t="n">
         <v>79035</v>
@@ -20925,10 +20917,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430086</v>
+        <v>430087</v>
       </c>
       <c r="R205" t="n">
-        <v>6818236</v>
+        <v>6817971</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20987,10 +20979,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128927942</v>
+        <v>128927809</v>
       </c>
       <c r="B206" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20998,21 +20990,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21022,10 +21014,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430087</v>
+        <v>430222</v>
       </c>
       <c r="R206" t="n">
-        <v>6817971</v>
+        <v>6818155</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21084,7 +21076,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128927809</v>
+        <v>128927814</v>
       </c>
       <c r="B207" t="n">
         <v>78793</v>
@@ -21119,10 +21111,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>430222</v>
+        <v>430138</v>
       </c>
       <c r="R207" t="n">
-        <v>6818155</v>
+        <v>6818171</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21181,7 +21173,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128927814</v>
+        <v>128927816</v>
       </c>
       <c r="B208" t="n">
         <v>78793</v>
@@ -21216,10 +21208,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>430138</v>
+        <v>430086</v>
       </c>
       <c r="R208" t="n">
-        <v>6818171</v>
+        <v>6818278</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21278,10 +21270,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128927816</v>
+        <v>128927755</v>
       </c>
       <c r="B209" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21289,34 +21281,42 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>430086</v>
+        <v>430480</v>
       </c>
       <c r="R209" t="n">
-        <v>6818278</v>
+        <v>6818068</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927950</v>
+        <v>128927721</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,21 +3153,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430233</v>
+        <v>430060</v>
       </c>
       <c r="R25" t="n">
-        <v>6817831</v>
+        <v>6818156</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927880</v>
+        <v>128927868</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430577</v>
+        <v>430089</v>
       </c>
       <c r="R26" t="n">
-        <v>6818221</v>
+        <v>6817984</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,7 +3336,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927868</v>
+        <v>128927843</v>
       </c>
       <c r="B27" t="n">
         <v>78792</v>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430089</v>
+        <v>430626</v>
       </c>
       <c r="R27" t="n">
-        <v>6817984</v>
+        <v>6818202</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927978</v>
+        <v>128927726</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3444,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430082</v>
+        <v>430114</v>
       </c>
       <c r="R28" t="n">
-        <v>6818210</v>
+        <v>6817912</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3512,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3531,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927843</v>
+        <v>128927950</v>
       </c>
       <c r="B29" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,21 +3541,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3566,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430626</v>
+        <v>430233</v>
       </c>
       <c r="R29" t="n">
-        <v>6818202</v>
+        <v>6817831</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,10 +3627,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927721</v>
+        <v>128927880</v>
       </c>
       <c r="B30" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3639,21 +3638,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3663,10 +3662,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430060</v>
+        <v>430577</v>
       </c>
       <c r="R30" t="n">
-        <v>6818156</v>
+        <v>6818221</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,7 +3724,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927935</v>
+        <v>128927978</v>
       </c>
       <c r="B31" t="n">
         <v>79035</v>
@@ -3760,10 +3759,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430099</v>
+        <v>430082</v>
       </c>
       <c r="R31" t="n">
-        <v>6818154</v>
+        <v>6818210</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3804,6 +3803,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128927726</v>
+        <v>128927935</v>
       </c>
       <c r="B32" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3833,21 +3833,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430114</v>
+        <v>430099</v>
       </c>
       <c r="R32" t="n">
-        <v>6817912</v>
+        <v>6818154</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3919,32 +3919,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128927834</v>
+        <v>128927963</v>
       </c>
       <c r="B33" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>430596</v>
+        <v>430064</v>
       </c>
       <c r="R33" t="n">
-        <v>6818184</v>
+        <v>6818190</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128927963</v>
+        <v>128927834</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430064</v>
+        <v>430596</v>
       </c>
       <c r="R35" t="n">
-        <v>6818190</v>
+        <v>6818184</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128927939</v>
+        <v>128927743</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>429903</v>
+        <v>430211</v>
       </c>
       <c r="R36" t="n">
-        <v>6818059</v>
+        <v>6817980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128927773</v>
+        <v>128927813</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4326,42 +4326,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>430251</v>
+        <v>430145</v>
       </c>
       <c r="R37" t="n">
-        <v>6818033</v>
+        <v>6818165</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4420,10 +4412,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128927895</v>
+        <v>128927871</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4431,21 +4423,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4455,10 +4447,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430350</v>
+        <v>430145</v>
       </c>
       <c r="R38" t="n">
-        <v>6818053</v>
+        <v>6817833</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4517,10 +4509,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128927871</v>
+        <v>128927895</v>
       </c>
       <c r="B39" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4528,21 +4520,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4552,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430145</v>
+        <v>430350</v>
       </c>
       <c r="R39" t="n">
-        <v>6817833</v>
+        <v>6818053</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4614,7 +4606,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128927973</v>
+        <v>128927939</v>
       </c>
       <c r="B40" t="n">
         <v>79035</v>
@@ -4643,19 +4635,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>430073</v>
+        <v>429903</v>
       </c>
       <c r="R40" t="n">
-        <v>6818021</v>
+        <v>6818059</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4696,7 +4685,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4715,10 +4703,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128927743</v>
+        <v>128927973</v>
       </c>
       <c r="B41" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,34 +4714,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>430211</v>
+        <v>430073</v>
       </c>
       <c r="R41" t="n">
-        <v>6817980</v>
+        <v>6818021</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4794,6 +4785,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4812,10 +4804,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128927813</v>
+        <v>128927773</v>
       </c>
       <c r="B42" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4823,34 +4815,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>430145</v>
+        <v>430251</v>
       </c>
       <c r="R42" t="n">
-        <v>6818165</v>
+        <v>6818033</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128927786</v>
+        <v>128927930</v>
       </c>
       <c r="B43" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,42 +4920,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430078</v>
+        <v>430205</v>
       </c>
       <c r="R43" t="n">
-        <v>6818213</v>
+        <v>6817961</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4988,11 +4980,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5019,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128927845</v>
+        <v>128927928</v>
       </c>
       <c r="B44" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5030,21 +5017,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5054,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430669</v>
+        <v>430293</v>
       </c>
       <c r="R44" t="n">
-        <v>6818249</v>
+        <v>6817871</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,7 +5103,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128927930</v>
+        <v>128927934</v>
       </c>
       <c r="B45" t="n">
         <v>79035</v>
@@ -5151,10 +5138,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430205</v>
+        <v>430088</v>
       </c>
       <c r="R45" t="n">
-        <v>6817961</v>
+        <v>6818186</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,7 +5200,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128927928</v>
+        <v>128927938</v>
       </c>
       <c r="B46" t="n">
         <v>79035</v>
@@ -5248,10 +5235,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>430293</v>
+        <v>429959</v>
       </c>
       <c r="R46" t="n">
-        <v>6817871</v>
+        <v>6818128</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5310,7 +5297,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128927934</v>
+        <v>128927976</v>
       </c>
       <c r="B47" t="n">
         <v>79035</v>
@@ -5339,16 +5326,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430088</v>
+        <v>430149</v>
       </c>
       <c r="R47" t="n">
-        <v>6818186</v>
+        <v>6817860</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,6 +5379,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5407,10 +5398,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128927842</v>
+        <v>128927966</v>
       </c>
       <c r="B48" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5418,21 +5409,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5442,10 +5433,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430596</v>
+        <v>430071</v>
       </c>
       <c r="R48" t="n">
-        <v>6818186</v>
+        <v>6818124</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5504,10 +5495,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128927938</v>
+        <v>128927786</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5515,34 +5506,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>429959</v>
+        <v>430078</v>
       </c>
       <c r="R49" t="n">
-        <v>6818128</v>
+        <v>6818213</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5575,6 +5574,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5601,10 +5605,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128927976</v>
+        <v>128927845</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5612,37 +5616,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430149</v>
+        <v>430669</v>
       </c>
       <c r="R50" t="n">
-        <v>6817860</v>
+        <v>6818249</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5683,7 +5684,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5702,10 +5702,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128927966</v>
+        <v>128927842</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430071</v>
+        <v>430596</v>
       </c>
       <c r="R51" t="n">
-        <v>6818124</v>
+        <v>6818186</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5896,7 +5896,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128927819</v>
+        <v>128927799</v>
       </c>
       <c r="B53" t="n">
         <v>78793</v>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>430033</v>
+        <v>430396</v>
       </c>
       <c r="R53" t="n">
-        <v>6818116</v>
+        <v>6818052</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5993,7 +5993,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128927799</v>
+        <v>128927806</v>
       </c>
       <c r="B54" t="n">
         <v>78793</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>430396</v>
+        <v>430655</v>
       </c>
       <c r="R54" t="n">
-        <v>6818052</v>
+        <v>6818264</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128927806</v>
+        <v>128927819</v>
       </c>
       <c r="B55" t="n">
         <v>78793</v>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>430655</v>
+        <v>430033</v>
       </c>
       <c r="R55" t="n">
-        <v>6818264</v>
+        <v>6818116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6187,10 +6187,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128927815</v>
+        <v>128927735</v>
       </c>
       <c r="B56" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>430061</v>
+        <v>430132</v>
       </c>
       <c r="R56" t="n">
-        <v>6818258</v>
+        <v>6817858</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128927937</v>
+        <v>128927855</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6295,21 +6295,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>430011</v>
+        <v>430113</v>
       </c>
       <c r="R57" t="n">
-        <v>6818137</v>
+        <v>6818160</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927970</v>
+        <v>128927937</v>
       </c>
       <c r="B59" t="n">
         <v>79035</v>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>429900</v>
+        <v>430011</v>
       </c>
       <c r="R59" t="n">
-        <v>6818098</v>
+        <v>6818137</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6549,11 +6549,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6580,7 +6575,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927944</v>
+        <v>128927970</v>
       </c>
       <c r="B60" t="n">
         <v>79035</v>
@@ -6609,19 +6604,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>430531</v>
+        <v>429900</v>
       </c>
       <c r="R60" t="n">
-        <v>6818016</v>
+        <v>6818098</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6656,13 +6648,17 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6681,7 +6677,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128927948</v>
+        <v>128927944</v>
       </c>
       <c r="B61" t="n">
         <v>79035</v>
@@ -6710,16 +6706,19 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430655</v>
+        <v>430531</v>
       </c>
       <c r="R61" t="n">
-        <v>6818216</v>
+        <v>6818016</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6760,6 +6759,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128927735</v>
+        <v>128927948</v>
       </c>
       <c r="B62" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430132</v>
+        <v>430655</v>
       </c>
       <c r="R62" t="n">
-        <v>6817858</v>
+        <v>6818216</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128927855</v>
+        <v>128927815</v>
       </c>
       <c r="B65" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430113</v>
+        <v>430061</v>
       </c>
       <c r="R65" t="n">
-        <v>6818160</v>
+        <v>6818258</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128927825</v>
+        <v>128927790</v>
       </c>
       <c r="B66" t="n">
-        <v>78793</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7177,34 +7177,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430024</v>
+        <v>430130</v>
       </c>
       <c r="R66" t="n">
-        <v>6818040</v>
+        <v>6817856</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7263,10 +7271,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128927790</v>
+        <v>128927751</v>
       </c>
       <c r="B67" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7274,16 +7282,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7296,7 +7304,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7306,10 +7314,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430130</v>
+        <v>430337</v>
       </c>
       <c r="R67" t="n">
-        <v>6817856</v>
+        <v>6818076</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,10 +7376,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128927751</v>
+        <v>128927893</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7379,42 +7387,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>430337</v>
+        <v>430286</v>
       </c>
       <c r="R68" t="n">
-        <v>6818076</v>
+        <v>6818100</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7473,7 +7473,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128927893</v>
+        <v>128927974</v>
       </c>
       <c r="B69" t="n">
         <v>79035</v>
@@ -7508,10 +7508,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430286</v>
+        <v>430091</v>
       </c>
       <c r="R69" t="n">
-        <v>6818100</v>
+        <v>6818012</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,10 +7570,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128927974</v>
+        <v>128927825</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7581,21 +7581,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>430091</v>
+        <v>430024</v>
       </c>
       <c r="R70" t="n">
-        <v>6818012</v>
+        <v>6818040</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7667,10 +7667,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128927710</v>
+        <v>128927831</v>
       </c>
       <c r="B71" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,34 +7678,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430610</v>
+        <v>430126</v>
       </c>
       <c r="R71" t="n">
-        <v>6818230</v>
+        <v>6817835</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7746,6 +7749,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7764,7 +7768,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128927839</v>
+        <v>128927857</v>
       </c>
       <c r="B72" t="n">
         <v>78792</v>
@@ -7799,10 +7803,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>430489</v>
+        <v>430051</v>
       </c>
       <c r="R72" t="n">
-        <v>6818084</v>
+        <v>6818114</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7861,10 +7865,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128927857</v>
+        <v>128927710</v>
       </c>
       <c r="B73" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7872,21 +7876,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7896,10 +7900,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>430051</v>
+        <v>430610</v>
       </c>
       <c r="R73" t="n">
-        <v>6818114</v>
+        <v>6818230</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7958,7 +7962,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128927852</v>
+        <v>128927839</v>
       </c>
       <c r="B74" t="n">
         <v>78792</v>
@@ -7993,10 +7997,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>430086</v>
+        <v>430489</v>
       </c>
       <c r="R74" t="n">
-        <v>6818279</v>
+        <v>6818084</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8055,10 +8059,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128927831</v>
+        <v>128927852</v>
       </c>
       <c r="B75" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8066,37 +8070,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>430126</v>
+        <v>430086</v>
       </c>
       <c r="R75" t="n">
-        <v>6817835</v>
+        <v>6818279</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8137,7 +8138,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128927865</v>
+        <v>128927725</v>
       </c>
       <c r="B77" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>429935</v>
+        <v>430040</v>
       </c>
       <c r="R77" t="n">
-        <v>6818065</v>
+        <v>6818029</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8350,10 +8350,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128927924</v>
+        <v>128927865</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8361,21 +8361,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430671</v>
+        <v>429935</v>
       </c>
       <c r="R78" t="n">
-        <v>6818266</v>
+        <v>6818065</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8447,7 +8447,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128927964</v>
+        <v>128927924</v>
       </c>
       <c r="B79" t="n">
         <v>79035</v>
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430099</v>
+        <v>430671</v>
       </c>
       <c r="R79" t="n">
-        <v>6818174</v>
+        <v>6818266</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8544,7 +8544,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128927897</v>
+        <v>128927964</v>
       </c>
       <c r="B80" t="n">
         <v>79035</v>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430386</v>
+        <v>430099</v>
       </c>
       <c r="R80" t="n">
-        <v>6818039</v>
+        <v>6818174</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8641,7 +8641,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128927955</v>
+        <v>128927897</v>
       </c>
       <c r="B81" t="n">
         <v>79035</v>
@@ -8670,19 +8670,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430129</v>
+        <v>430386</v>
       </c>
       <c r="R81" t="n">
-        <v>6818156</v>
+        <v>6818039</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8717,18 +8714,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30 m</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8747,7 +8738,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128927905</v>
+        <v>128927955</v>
       </c>
       <c r="B82" t="n">
         <v>79035</v>
@@ -8776,16 +8767,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430395</v>
+        <v>430129</v>
       </c>
       <c r="R82" t="n">
-        <v>6818138</v>
+        <v>6818156</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8820,12 +8814,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30 m</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8844,10 +8844,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128927725</v>
+        <v>128927905</v>
       </c>
       <c r="B83" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8855,21 +8855,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8879,10 +8879,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430040</v>
+        <v>430395</v>
       </c>
       <c r="R83" t="n">
-        <v>6818029</v>
+        <v>6818138</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128927811</v>
+        <v>128927832</v>
       </c>
       <c r="B88" t="n">
         <v>78793</v>
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>430176</v>
+        <v>430153</v>
       </c>
       <c r="R88" t="n">
-        <v>6818150</v>
+        <v>6817822</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9431,7 +9431,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128927832</v>
+        <v>128927811</v>
       </c>
       <c r="B89" t="n">
         <v>78793</v>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>430153</v>
+        <v>430176</v>
       </c>
       <c r="R89" t="n">
-        <v>6817822</v>
+        <v>6818150</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128927891</v>
+        <v>128927714</v>
       </c>
       <c r="B91" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9636,21 +9636,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430336</v>
+        <v>430630</v>
       </c>
       <c r="R91" t="n">
-        <v>6818151</v>
+        <v>6818207</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128927884</v>
+        <v>128927864</v>
       </c>
       <c r="B92" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9733,21 +9733,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>430423</v>
+        <v>429975</v>
       </c>
       <c r="R92" t="n">
-        <v>6818270</v>
+        <v>6818158</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9819,7 +9819,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128927864</v>
+        <v>128927851</v>
       </c>
       <c r="B93" t="n">
         <v>78792</v>
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>429975</v>
+        <v>430135</v>
       </c>
       <c r="R93" t="n">
-        <v>6818158</v>
+        <v>6818172</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9916,10 +9916,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128927714</v>
+        <v>128927891</v>
       </c>
       <c r="B94" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9927,21 +9927,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9951,10 +9951,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430630</v>
+        <v>430336</v>
       </c>
       <c r="R94" t="n">
-        <v>6818207</v>
+        <v>6818151</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10013,7 +10013,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128927965</v>
+        <v>128927884</v>
       </c>
       <c r="B95" t="n">
         <v>79035</v>
@@ -10048,10 +10048,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430115</v>
+        <v>430423</v>
       </c>
       <c r="R95" t="n">
-        <v>6818177</v>
+        <v>6818270</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10110,7 +10110,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128927932</v>
+        <v>128927965</v>
       </c>
       <c r="B96" t="n">
         <v>79035</v>
@@ -10139,19 +10139,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430240</v>
+        <v>430115</v>
       </c>
       <c r="R96" t="n">
-        <v>6817987</v>
+        <v>6818177</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10186,18 +10183,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10216,7 +10207,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128927975</v>
+        <v>128927932</v>
       </c>
       <c r="B97" t="n">
         <v>79035</v>
@@ -10245,16 +10236,19 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430138</v>
+        <v>430240</v>
       </c>
       <c r="R97" t="n">
-        <v>6817903</v>
+        <v>6817987</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10289,12 +10283,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128927943</v>
+        <v>128927975</v>
       </c>
       <c r="B98" t="n">
         <v>79035</v>
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430136</v>
+        <v>430138</v>
       </c>
       <c r="R98" t="n">
-        <v>6817849</v>
+        <v>6817903</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10410,10 +10410,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128927851</v>
+        <v>128927943</v>
       </c>
       <c r="B99" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10421,21 +10421,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430135</v>
+        <v>430136</v>
       </c>
       <c r="R99" t="n">
-        <v>6818172</v>
+        <v>6817849</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10798,10 +10798,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927899</v>
+        <v>128927856</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430428</v>
+        <v>430060</v>
       </c>
       <c r="R103" t="n">
-        <v>6818038</v>
+        <v>6818160</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,48 +10895,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927954</v>
+        <v>128927836</v>
       </c>
       <c r="B104" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430166</v>
+        <v>430147</v>
       </c>
       <c r="R104" t="n">
-        <v>6818134</v>
+        <v>6817817</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10971,18 +10968,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11001,10 +10992,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927888</v>
+        <v>128927826</v>
       </c>
       <c r="B105" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11012,21 +11003,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11036,10 +11027,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430399</v>
+        <v>430018</v>
       </c>
       <c r="R105" t="n">
-        <v>6818238</v>
+        <v>6818046</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11098,10 +11089,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927971</v>
+        <v>128927796</v>
       </c>
       <c r="B106" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11109,21 +11100,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11133,10 +11124,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>429925</v>
+        <v>430323</v>
       </c>
       <c r="R106" t="n">
-        <v>6818065</v>
+        <v>6818121</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11195,10 +11186,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927949</v>
+        <v>128927793</v>
       </c>
       <c r="B107" t="n">
-        <v>79035</v>
+        <v>58153</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11206,21 +11197,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11230,10 +11221,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430653</v>
+        <v>430104</v>
       </c>
       <c r="R107" t="n">
-        <v>6818272</v>
+        <v>6817933</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11292,10 +11283,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927856</v>
+        <v>128927827</v>
       </c>
       <c r="B108" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11303,21 +11294,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11327,10 +11318,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430060</v>
+        <v>430057</v>
       </c>
       <c r="R108" t="n">
-        <v>6818160</v>
+        <v>6818016</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11389,32 +11380,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927836</v>
+        <v>128927822</v>
       </c>
       <c r="B109" t="n">
-        <v>58093</v>
+        <v>78793</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11424,10 +11415,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>430147</v>
+        <v>429973</v>
       </c>
       <c r="R109" t="n">
-        <v>6817817</v>
+        <v>6818162</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11486,10 +11477,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128927793</v>
+        <v>128927899</v>
       </c>
       <c r="B110" t="n">
-        <v>58153</v>
+        <v>79035</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11497,21 +11488,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11521,10 +11512,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>430104</v>
+        <v>430428</v>
       </c>
       <c r="R110" t="n">
-        <v>6817933</v>
+        <v>6818038</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11583,10 +11574,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927827</v>
+        <v>128927954</v>
       </c>
       <c r="B111" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11594,34 +11585,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430057</v>
+        <v>430166</v>
       </c>
       <c r="R111" t="n">
-        <v>6818016</v>
+        <v>6818134</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11656,12 +11650,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927822</v>
+        <v>128927888</v>
       </c>
       <c r="B112" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11691,21 +11691,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>429973</v>
+        <v>430399</v>
       </c>
       <c r="R112" t="n">
-        <v>6818162</v>
+        <v>6818238</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,10 +11777,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927826</v>
+        <v>128927971</v>
       </c>
       <c r="B113" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11788,21 +11788,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>430018</v>
+        <v>429925</v>
       </c>
       <c r="R113" t="n">
-        <v>6818046</v>
+        <v>6818065</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927796</v>
+        <v>128927949</v>
       </c>
       <c r="B114" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430323</v>
+        <v>430653</v>
       </c>
       <c r="R114" t="n">
-        <v>6818121</v>
+        <v>6818272</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11971,7 +11971,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128927870</v>
+        <v>128927858</v>
       </c>
       <c r="B115" t="n">
         <v>78792</v>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>430164</v>
+        <v>430034</v>
       </c>
       <c r="R115" t="n">
-        <v>6817854</v>
+        <v>6818117</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12068,7 +12068,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128927858</v>
+        <v>128927873</v>
       </c>
       <c r="B116" t="n">
         <v>78792</v>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>430034</v>
+        <v>429998</v>
       </c>
       <c r="R116" t="n">
-        <v>6818117</v>
+        <v>6818047</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12165,7 +12165,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128927873</v>
+        <v>128927870</v>
       </c>
       <c r="B117" t="n">
         <v>78792</v>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>429998</v>
+        <v>430164</v>
       </c>
       <c r="R117" t="n">
-        <v>6818047</v>
+        <v>6817854</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12965,7 +12965,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128927953</v>
+        <v>128927918</v>
       </c>
       <c r="B125" t="n">
         <v>79035</v>
@@ -12994,19 +12994,16 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>430242</v>
+        <v>430649</v>
       </c>
       <c r="R125" t="n">
-        <v>6818048</v>
+        <v>6818232</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13041,18 +13038,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13071,7 +13062,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128927907</v>
+        <v>128927878</v>
       </c>
       <c r="B126" t="n">
         <v>79035</v>
@@ -13106,10 +13097,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430394</v>
+        <v>430632</v>
       </c>
       <c r="R126" t="n">
-        <v>6818166</v>
+        <v>6818282</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13168,7 +13159,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128927977</v>
+        <v>128927908</v>
       </c>
       <c r="B127" t="n">
         <v>79035</v>
@@ -13197,19 +13188,16 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430139</v>
+        <v>430425</v>
       </c>
       <c r="R127" t="n">
-        <v>6817862</v>
+        <v>6818197</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13250,7 +13238,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13269,10 +13256,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128927869</v>
+        <v>128927886</v>
       </c>
       <c r="B128" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13280,21 +13267,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13304,10 +13291,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430138</v>
+        <v>430424</v>
       </c>
       <c r="R128" t="n">
-        <v>6817883</v>
+        <v>6818252</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13366,10 +13353,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128927720</v>
+        <v>128927853</v>
       </c>
       <c r="B129" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13377,21 +13364,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13401,10 +13388,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430112</v>
+        <v>430073</v>
       </c>
       <c r="R129" t="n">
-        <v>6818160</v>
+        <v>6818201</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13463,10 +13450,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128927940</v>
+        <v>128927720</v>
       </c>
       <c r="B130" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13474,21 +13461,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13498,10 +13485,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>429952</v>
+        <v>430112</v>
       </c>
       <c r="R130" t="n">
-        <v>6818061</v>
+        <v>6818160</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13560,7 +13547,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128927853</v>
+        <v>128927869</v>
       </c>
       <c r="B131" t="n">
         <v>78792</v>
@@ -13595,10 +13582,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430073</v>
+        <v>430138</v>
       </c>
       <c r="R131" t="n">
-        <v>6818201</v>
+        <v>6817883</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13657,7 +13644,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128927918</v>
+        <v>128927953</v>
       </c>
       <c r="B132" t="n">
         <v>79035</v>
@@ -13686,16 +13673,19 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430649</v>
+        <v>430242</v>
       </c>
       <c r="R132" t="n">
-        <v>6818232</v>
+        <v>6818048</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13730,12 +13720,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13754,7 +13750,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128927878</v>
+        <v>128927907</v>
       </c>
       <c r="B133" t="n">
         <v>79035</v>
@@ -13789,10 +13785,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430632</v>
+        <v>430394</v>
       </c>
       <c r="R133" t="n">
-        <v>6818282</v>
+        <v>6818166</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13851,7 +13847,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128927908</v>
+        <v>128927977</v>
       </c>
       <c r="B134" t="n">
         <v>79035</v>
@@ -13880,16 +13876,19 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430425</v>
+        <v>430139</v>
       </c>
       <c r="R134" t="n">
-        <v>6818197</v>
+        <v>6817862</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13930,6 +13929,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -13948,7 +13948,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128927886</v>
+        <v>128927940</v>
       </c>
       <c r="B135" t="n">
         <v>79035</v>
@@ -13983,10 +13983,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>430424</v>
+        <v>429952</v>
       </c>
       <c r="R135" t="n">
-        <v>6818252</v>
+        <v>6818061</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14045,10 +14045,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128927824</v>
+        <v>128927863</v>
       </c>
       <c r="B136" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14056,21 +14056,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14080,10 +14080,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>429941</v>
+        <v>429970</v>
       </c>
       <c r="R136" t="n">
-        <v>6818056</v>
+        <v>6818162</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14142,10 +14142,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128927748</v>
+        <v>128927861</v>
       </c>
       <c r="B137" t="n">
-        <v>79625</v>
+        <v>78792</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14153,21 +14153,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14177,10 +14177,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>430202</v>
+        <v>429989</v>
       </c>
       <c r="R137" t="n">
-        <v>6818084</v>
+        <v>6818159</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14239,54 +14239,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128927833</v>
+        <v>128927709</v>
       </c>
       <c r="B138" t="n">
-        <v>8450</v>
+        <v>79654</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430204</v>
+        <v>430495</v>
       </c>
       <c r="R138" t="n">
-        <v>6817811</v>
+        <v>6818056</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14327,7 +14318,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14346,40 +14336,41 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128927781</v>
+        <v>128927833</v>
       </c>
       <c r="B139" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
@@ -14389,10 +14380,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430480</v>
+        <v>430204</v>
       </c>
       <c r="R139" t="n">
-        <v>6817997</v>
+        <v>6817811</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14433,6 +14424,7 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14451,10 +14443,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128927788</v>
+        <v>128927748</v>
       </c>
       <c r="B140" t="n">
-        <v>57720</v>
+        <v>79625</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14462,42 +14454,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430017</v>
+        <v>430202</v>
       </c>
       <c r="R140" t="n">
-        <v>6818044</v>
+        <v>6818084</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14556,10 +14540,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128927775</v>
+        <v>128927824</v>
       </c>
       <c r="B141" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14567,42 +14551,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>430083</v>
+        <v>429941</v>
       </c>
       <c r="R141" t="n">
-        <v>6818224</v>
+        <v>6818056</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14661,10 +14637,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128927792</v>
+        <v>128927894</v>
       </c>
       <c r="B142" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14672,31 +14648,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -14704,10 +14675,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430150</v>
+        <v>430321</v>
       </c>
       <c r="R142" t="n">
-        <v>6817814</v>
+        <v>6818095</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14742,12 +14713,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -14766,7 +14743,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128927894</v>
+        <v>128927900</v>
       </c>
       <c r="B143" t="n">
         <v>79035</v>
@@ -14795,19 +14772,16 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430321</v>
+        <v>430467</v>
       </c>
       <c r="R143" t="n">
-        <v>6818095</v>
+        <v>6818020</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14842,18 +14816,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -14872,7 +14840,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128927900</v>
+        <v>128927889</v>
       </c>
       <c r="B144" t="n">
         <v>79035</v>
@@ -14907,10 +14875,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430467</v>
+        <v>430385</v>
       </c>
       <c r="R144" t="n">
-        <v>6818020</v>
+        <v>6818203</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14969,7 +14937,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128927889</v>
+        <v>128927911</v>
       </c>
       <c r="B145" t="n">
         <v>79035</v>
@@ -15004,10 +14972,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430385</v>
+        <v>430437</v>
       </c>
       <c r="R145" t="n">
-        <v>6818203</v>
+        <v>6818227</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15066,10 +15034,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128927863</v>
+        <v>128927969</v>
       </c>
       <c r="B146" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15077,21 +15045,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15101,10 +15069,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>429970</v>
+        <v>429947</v>
       </c>
       <c r="R146" t="n">
-        <v>6818162</v>
+        <v>6818135</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15163,7 +15131,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128927911</v>
+        <v>128927956</v>
       </c>
       <c r="B147" t="n">
         <v>79035</v>
@@ -15198,10 +15166,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430437</v>
+        <v>430119</v>
       </c>
       <c r="R147" t="n">
-        <v>6818227</v>
+        <v>6818173</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15260,7 +15228,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927969</v>
+        <v>128927925</v>
       </c>
       <c r="B148" t="n">
         <v>79035</v>
@@ -15295,10 +15263,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>429947</v>
+        <v>430683</v>
       </c>
       <c r="R148" t="n">
-        <v>6818135</v>
+        <v>6818265</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15357,10 +15325,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927709</v>
+        <v>128927972</v>
       </c>
       <c r="B149" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15368,34 +15336,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430495</v>
+        <v>430018</v>
       </c>
       <c r="R149" t="n">
-        <v>6818056</v>
+        <v>6818025</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15436,6 +15407,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15454,7 +15426,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927956</v>
+        <v>128927926</v>
       </c>
       <c r="B150" t="n">
         <v>79035</v>
@@ -15489,10 +15461,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430119</v>
+        <v>430701</v>
       </c>
       <c r="R150" t="n">
-        <v>6818173</v>
+        <v>6818261</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15551,10 +15523,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927925</v>
+        <v>128927781</v>
       </c>
       <c r="B151" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15562,34 +15534,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430683</v>
+        <v>430480</v>
       </c>
       <c r="R151" t="n">
-        <v>6818265</v>
+        <v>6817997</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15648,10 +15628,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128927972</v>
+        <v>128927788</v>
       </c>
       <c r="B152" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15659,26 +15639,31 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -15686,10 +15671,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430018</v>
+        <v>430017</v>
       </c>
       <c r="R152" t="n">
-        <v>6818025</v>
+        <v>6818044</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15730,7 +15715,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15749,10 +15733,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128927861</v>
+        <v>128927775</v>
       </c>
       <c r="B153" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15760,34 +15744,42 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>429989</v>
+        <v>430083</v>
       </c>
       <c r="R153" t="n">
-        <v>6818159</v>
+        <v>6818224</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15846,10 +15838,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128927926</v>
+        <v>128927792</v>
       </c>
       <c r="B154" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15857,34 +15849,42 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430701</v>
+        <v>430150</v>
       </c>
       <c r="R154" t="n">
-        <v>6818261</v>
+        <v>6817814</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15943,10 +15943,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128927798</v>
+        <v>128927917</v>
       </c>
       <c r="B155" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15954,21 +15954,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15978,10 +15978,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>430315</v>
+        <v>430616</v>
       </c>
       <c r="R155" t="n">
-        <v>6818095</v>
+        <v>6818194</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16040,10 +16040,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128927828</v>
+        <v>128927903</v>
       </c>
       <c r="B156" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16051,21 +16051,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16078,10 +16078,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>430115</v>
+        <v>430437</v>
       </c>
       <c r="R156" t="n">
-        <v>6817902</v>
+        <v>6818119</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16114,6 +16114,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Måttligt/rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16141,10 +16146,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128927779</v>
+        <v>128927920</v>
       </c>
       <c r="B157" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16152,42 +16157,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430106</v>
+        <v>430637</v>
       </c>
       <c r="R157" t="n">
-        <v>6817957</v>
+        <v>6818260</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16246,10 +16243,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128927783</v>
+        <v>128927951</v>
       </c>
       <c r="B158" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16257,31 +16254,26 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -16289,10 +16281,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430174</v>
+        <v>430191</v>
       </c>
       <c r="R158" t="n">
-        <v>6817923</v>
+        <v>6817932</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16327,12 +16319,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Garnlav, måttligt inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -16351,7 +16349,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128927917</v>
+        <v>128927958</v>
       </c>
       <c r="B159" t="n">
         <v>79035</v>
@@ -16386,10 +16384,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430616</v>
+        <v>430048</v>
       </c>
       <c r="R159" t="n">
-        <v>6818194</v>
+        <v>6818232</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16448,7 +16446,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128927903</v>
+        <v>128927902</v>
       </c>
       <c r="B160" t="n">
         <v>79035</v>
@@ -16477,19 +16475,16 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430437</v>
+        <v>430530</v>
       </c>
       <c r="R160" t="n">
-        <v>6818119</v>
+        <v>6818025</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16524,18 +16519,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Måttligt/rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -16554,10 +16543,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128927875</v>
+        <v>128927779</v>
       </c>
       <c r="B161" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16565,34 +16554,42 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430127</v>
+        <v>430106</v>
       </c>
       <c r="R161" t="n">
-        <v>6817846</v>
+        <v>6817957</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16651,10 +16648,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128927920</v>
+        <v>128927783</v>
       </c>
       <c r="B162" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16662,34 +16659,42 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430637</v>
+        <v>430174</v>
       </c>
       <c r="R162" t="n">
-        <v>6818260</v>
+        <v>6817923</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16748,7 +16753,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128927838</v>
+        <v>128927837</v>
       </c>
       <c r="B163" t="n">
         <v>78792</v>
@@ -16783,10 +16788,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430439</v>
+        <v>430360</v>
       </c>
       <c r="R163" t="n">
-        <v>6818031</v>
+        <v>6818057</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16845,7 +16850,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128927837</v>
+        <v>128927838</v>
       </c>
       <c r="B164" t="n">
         <v>78792</v>
@@ -16880,10 +16885,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430360</v>
+        <v>430439</v>
       </c>
       <c r="R164" t="n">
-        <v>6818057</v>
+        <v>6818031</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16942,10 +16947,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128927951</v>
+        <v>128927846</v>
       </c>
       <c r="B165" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16953,37 +16958,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430191</v>
+        <v>430241</v>
       </c>
       <c r="R165" t="n">
-        <v>6817932</v>
+        <v>6818085</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17018,18 +17020,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Garnlav, måttligt inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -17048,10 +17044,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128927958</v>
+        <v>128927875</v>
       </c>
       <c r="B166" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17059,21 +17055,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17083,10 +17079,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>430048</v>
+        <v>430127</v>
       </c>
       <c r="R166" t="n">
-        <v>6818232</v>
+        <v>6817846</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17145,10 +17141,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128927846</v>
+        <v>128927828</v>
       </c>
       <c r="B167" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17156,34 +17152,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430241</v>
+        <v>430115</v>
       </c>
       <c r="R167" t="n">
-        <v>6818085</v>
+        <v>6817902</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17224,6 +17223,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17242,10 +17242,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128927902</v>
+        <v>128927798</v>
       </c>
       <c r="B168" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17253,21 +17253,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17277,10 +17277,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430530</v>
+        <v>430315</v>
       </c>
       <c r="R168" t="n">
-        <v>6818025</v>
+        <v>6818095</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17436,32 +17436,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128927835</v>
+        <v>128927712</v>
       </c>
       <c r="B170" t="n">
-        <v>58093</v>
+        <v>79654</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17471,10 +17471,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430104</v>
+        <v>430596</v>
       </c>
       <c r="R170" t="n">
-        <v>6817960</v>
+        <v>6818190</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17533,10 +17533,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128927933</v>
+        <v>128927737</v>
       </c>
       <c r="B171" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17544,21 +17544,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17571,10 +17571,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430220</v>
+        <v>430143</v>
       </c>
       <c r="R171" t="n">
-        <v>6818148</v>
+        <v>6817831</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17607,11 +17607,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -17639,48 +17634,45 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128927737</v>
+        <v>128927835</v>
       </c>
       <c r="B172" t="n">
-        <v>79654</v>
+        <v>58093</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430143</v>
+        <v>430104</v>
       </c>
       <c r="R172" t="n">
-        <v>6817831</v>
+        <v>6817960</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17721,7 +17713,6 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -17740,10 +17731,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128927904</v>
+        <v>128927829</v>
       </c>
       <c r="B173" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17751,21 +17742,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17775,10 +17766,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430405</v>
+        <v>430138</v>
       </c>
       <c r="R173" t="n">
-        <v>6818117</v>
+        <v>6817883</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17837,10 +17828,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128927712</v>
+        <v>128927933</v>
       </c>
       <c r="B174" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17848,34 +17839,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430596</v>
+        <v>430220</v>
       </c>
       <c r="R174" t="n">
-        <v>6818190</v>
+        <v>6818148</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17910,12 +17904,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -17934,10 +17934,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128927829</v>
+        <v>128927904</v>
       </c>
       <c r="B175" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17945,21 +17945,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17969,10 +17969,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430138</v>
+        <v>430405</v>
       </c>
       <c r="R175" t="n">
-        <v>6817883</v>
+        <v>6818117</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18031,10 +18031,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128927750</v>
+        <v>128927898</v>
       </c>
       <c r="B176" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18042,21 +18042,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18066,10 +18066,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430140</v>
+        <v>430384</v>
       </c>
       <c r="R176" t="n">
-        <v>6817881</v>
+        <v>6818048</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18128,10 +18128,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128927741</v>
+        <v>128927968</v>
       </c>
       <c r="B177" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18139,21 +18139,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18163,10 +18163,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430600</v>
+        <v>430067</v>
       </c>
       <c r="R177" t="n">
-        <v>6818203</v>
+        <v>6818139</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18225,10 +18225,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128927812</v>
+        <v>128927952</v>
       </c>
       <c r="B178" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18236,21 +18236,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18260,10 +18260,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430157</v>
+        <v>430190</v>
       </c>
       <c r="R178" t="n">
-        <v>6818149</v>
+        <v>6817925</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18322,7 +18322,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128927898</v>
+        <v>128927945</v>
       </c>
       <c r="B179" t="n">
         <v>79035</v>
@@ -18357,10 +18357,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430384</v>
+        <v>430404</v>
       </c>
       <c r="R179" t="n">
-        <v>6818048</v>
+        <v>6818178</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18419,10 +18419,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128927723</v>
+        <v>128927848</v>
       </c>
       <c r="B180" t="n">
-        <v>79654</v>
+        <v>78792</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18430,21 +18430,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18454,10 +18454,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>429993</v>
+        <v>430174</v>
       </c>
       <c r="R180" t="n">
-        <v>6818157</v>
+        <v>6818156</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18516,10 +18516,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128927848</v>
+        <v>128927723</v>
       </c>
       <c r="B181" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18527,21 +18527,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18551,10 +18551,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>430174</v>
+        <v>429993</v>
       </c>
       <c r="R181" t="n">
-        <v>6818156</v>
+        <v>6818157</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18613,45 +18613,53 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128927968</v>
+        <v>128927760</v>
       </c>
       <c r="B182" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430067</v>
+        <v>430663</v>
       </c>
       <c r="R182" t="n">
-        <v>6818139</v>
+        <v>6818259</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18710,45 +18718,53 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128927952</v>
+        <v>128927762</v>
       </c>
       <c r="B183" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430190</v>
+        <v>430394</v>
       </c>
       <c r="R183" t="n">
-        <v>6817925</v>
+        <v>6818168</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18807,10 +18823,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128927945</v>
+        <v>128927750</v>
       </c>
       <c r="B184" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18818,21 +18834,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18842,10 +18858,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>430404</v>
+        <v>430140</v>
       </c>
       <c r="R184" t="n">
-        <v>6818178</v>
+        <v>6817881</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -18904,53 +18920,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128927760</v>
+        <v>128927741</v>
       </c>
       <c r="B185" t="n">
-        <v>56913</v>
+        <v>79625</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>430663</v>
+        <v>430600</v>
       </c>
       <c r="R185" t="n">
-        <v>6818259</v>
+        <v>6818203</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19009,53 +19017,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128927762</v>
+        <v>128927812</v>
       </c>
       <c r="B186" t="n">
-        <v>56913</v>
+        <v>78793</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>430394</v>
+        <v>430157</v>
       </c>
       <c r="R186" t="n">
-        <v>6818168</v>
+        <v>6818149</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19114,10 +19114,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128927820</v>
+        <v>128927872</v>
       </c>
       <c r="B187" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19125,21 +19125,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19149,10 +19149,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430014</v>
+        <v>430227</v>
       </c>
       <c r="R187" t="n">
-        <v>6818142</v>
+        <v>6818015</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19211,10 +19211,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128927818</v>
+        <v>128927728</v>
       </c>
       <c r="B188" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19222,21 +19222,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19246,10 +19246,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430048</v>
+        <v>430232</v>
       </c>
       <c r="R188" t="n">
-        <v>6818123</v>
+        <v>6818068</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19308,10 +19308,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128927789</v>
+        <v>128927731</v>
       </c>
       <c r="B189" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19319,42 +19319,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430089</v>
+        <v>430056</v>
       </c>
       <c r="R189" t="n">
-        <v>6817965</v>
+        <v>6818017</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19387,11 +19379,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -19418,10 +19405,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128927910</v>
+        <v>128927847</v>
       </c>
       <c r="B190" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19429,21 +19416,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19453,10 +19440,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430430</v>
+        <v>430227</v>
       </c>
       <c r="R190" t="n">
-        <v>6818202</v>
+        <v>6818154</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19515,10 +19502,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128927731</v>
+        <v>128927910</v>
       </c>
       <c r="B191" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19526,21 +19513,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19550,10 +19537,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430056</v>
+        <v>430430</v>
       </c>
       <c r="R191" t="n">
-        <v>6818017</v>
+        <v>6818202</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19612,10 +19599,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128927847</v>
+        <v>128927892</v>
       </c>
       <c r="B192" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19623,21 +19610,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19647,10 +19634,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430227</v>
+        <v>430304</v>
       </c>
       <c r="R192" t="n">
-        <v>6818154</v>
+        <v>6818124</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19709,7 +19696,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128927892</v>
+        <v>128927906</v>
       </c>
       <c r="B193" t="n">
         <v>79035</v>
@@ -19738,16 +19725,19 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>430304</v>
+        <v>430401</v>
       </c>
       <c r="R193" t="n">
-        <v>6818124</v>
+        <v>6818157</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19782,12 +19772,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -19806,10 +19802,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128927872</v>
+        <v>128927922</v>
       </c>
       <c r="B194" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19817,21 +19813,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19841,10 +19837,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>430227</v>
+        <v>430668</v>
       </c>
       <c r="R194" t="n">
-        <v>6818015</v>
+        <v>6818241</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -19903,10 +19899,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128927728</v>
+        <v>128927962</v>
       </c>
       <c r="B195" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19914,21 +19910,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19938,10 +19934,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>430232</v>
+        <v>430069</v>
       </c>
       <c r="R195" t="n">
-        <v>6818068</v>
+        <v>6818225</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20000,10 +19996,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128927906</v>
+        <v>128927789</v>
       </c>
       <c r="B196" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20011,26 +20007,31 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
@@ -20038,10 +20039,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>430401</v>
+        <v>430089</v>
       </c>
       <c r="R196" t="n">
-        <v>6818157</v>
+        <v>6817965</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20078,7 +20079,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Garnlav förekommer på de flesta granar och tallar inom en radie av 40 m</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20087,7 +20088,6 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20106,10 +20106,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128927922</v>
+        <v>128927820</v>
       </c>
       <c r="B197" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20117,21 +20117,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20141,10 +20141,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>430668</v>
+        <v>430014</v>
       </c>
       <c r="R197" t="n">
-        <v>6818241</v>
+        <v>6818142</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20203,10 +20203,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128927962</v>
+        <v>128927818</v>
       </c>
       <c r="B198" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20214,21 +20214,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20238,10 +20238,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>430069</v>
+        <v>430048</v>
       </c>
       <c r="R198" t="n">
-        <v>6818225</v>
+        <v>6818123</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20300,10 +20300,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128927913</v>
+        <v>128927715</v>
       </c>
       <c r="B199" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20311,21 +20311,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20335,10 +20335,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>430484</v>
+        <v>430650</v>
       </c>
       <c r="R199" t="n">
-        <v>6818253</v>
+        <v>6818249</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20397,10 +20397,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128927841</v>
+        <v>128927755</v>
       </c>
       <c r="B200" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20408,34 +20408,42 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>430569</v>
+        <v>430480</v>
       </c>
       <c r="R200" t="n">
-        <v>6818243</v>
+        <v>6818068</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20494,10 +20502,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128927936</v>
+        <v>128927841</v>
       </c>
       <c r="B201" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20505,21 +20513,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20529,10 +20537,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>430084</v>
+        <v>430569</v>
       </c>
       <c r="R201" t="n">
-        <v>6818157</v>
+        <v>6818243</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20688,10 +20696,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128927715</v>
+        <v>128927913</v>
       </c>
       <c r="B203" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20699,21 +20707,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20723,10 +20731,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>430650</v>
+        <v>430484</v>
       </c>
       <c r="R203" t="n">
-        <v>6818249</v>
+        <v>6818253</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -20785,7 +20793,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128927961</v>
+        <v>128927936</v>
       </c>
       <c r="B204" t="n">
         <v>79035</v>
@@ -20820,10 +20828,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>430086</v>
+        <v>430084</v>
       </c>
       <c r="R204" t="n">
-        <v>6818236</v>
+        <v>6818157</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -20882,7 +20890,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128927942</v>
+        <v>128927961</v>
       </c>
       <c r="B205" t="n">
         <v>79035</v>
@@ -20917,10 +20925,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>430087</v>
+        <v>430086</v>
       </c>
       <c r="R205" t="n">
-        <v>6817971</v>
+        <v>6818236</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -20979,10 +20987,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128927809</v>
+        <v>128927942</v>
       </c>
       <c r="B206" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20990,21 +20998,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21014,10 +21022,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>430222</v>
+        <v>430087</v>
       </c>
       <c r="R206" t="n">
-        <v>6818155</v>
+        <v>6817971</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21076,7 +21084,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128927814</v>
+        <v>128927809</v>
       </c>
       <c r="B207" t="n">
         <v>78793</v>
@@ -21111,10 +21119,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>430138</v>
+        <v>430222</v>
       </c>
       <c r="R207" t="n">
-        <v>6818171</v>
+        <v>6818155</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21173,7 +21181,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128927816</v>
+        <v>128927814</v>
       </c>
       <c r="B208" t="n">
         <v>78793</v>
@@ -21208,10 +21216,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>430086</v>
+        <v>430138</v>
       </c>
       <c r="R208" t="n">
-        <v>6818278</v>
+        <v>6818171</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21270,10 +21278,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128927755</v>
+        <v>128927816</v>
       </c>
       <c r="B209" t="n">
-        <v>57723</v>
+        <v>78793</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -21281,42 +21289,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>430480</v>
+        <v>430086</v>
       </c>
       <c r="R209" t="n">
-        <v>6818068</v>
+        <v>6818278</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21375,10 +21375,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128927860</v>
+        <v>128927753</v>
       </c>
       <c r="B210" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -21386,34 +21386,42 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>430013</v>
+        <v>430514</v>
       </c>
       <c r="R210" t="n">
-        <v>6818142</v>
+        <v>6818047</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -21472,10 +21480,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128927941</v>
+        <v>128927860</v>
       </c>
       <c r="B211" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21483,21 +21491,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21507,10 +21515,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>430078</v>
+        <v>430013</v>
       </c>
       <c r="R211" t="n">
-        <v>6817995</v>
+        <v>6818142</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -21569,10 +21577,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128927960</v>
+        <v>128927866</v>
       </c>
       <c r="B212" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -21580,21 +21588,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21604,10 +21612,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>430089</v>
+        <v>429950</v>
       </c>
       <c r="R212" t="n">
-        <v>6818238</v>
+        <v>6818057</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21666,10 +21674,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128927866</v>
+        <v>128927941</v>
       </c>
       <c r="B213" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21677,21 +21685,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21701,10 +21709,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>429950</v>
+        <v>430078</v>
       </c>
       <c r="R213" t="n">
-        <v>6818057</v>
+        <v>6817995</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21763,10 +21771,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128927753</v>
+        <v>128927960</v>
       </c>
       <c r="B214" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21774,42 +21782,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>430514</v>
+        <v>430089</v>
       </c>
       <c r="R214" t="n">
-        <v>6818047</v>
+        <v>6818238</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -21868,10 +21868,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128927830</v>
+        <v>128927746</v>
       </c>
       <c r="B215" t="n">
-        <v>78793</v>
+        <v>79625</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21879,21 +21879,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21903,10 +21903,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>430167</v>
+        <v>430232</v>
       </c>
       <c r="R215" t="n">
-        <v>6817850</v>
+        <v>6818068</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21965,7 +21965,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128927808</v>
+        <v>128927830</v>
       </c>
       <c r="B216" t="n">
         <v>78793</v>
@@ -22000,10 +22000,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>430669</v>
+        <v>430167</v>
       </c>
       <c r="R216" t="n">
-        <v>6818242</v>
+        <v>6817850</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22062,7 +22062,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128927817</v>
+        <v>128927808</v>
       </c>
       <c r="B217" t="n">
         <v>78793</v>
@@ -22097,10 +22097,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>430068</v>
+        <v>430669</v>
       </c>
       <c r="R217" t="n">
-        <v>6818152</v>
+        <v>6818242</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22159,10 +22159,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128927746</v>
+        <v>128927817</v>
       </c>
       <c r="B218" t="n">
-        <v>79625</v>
+        <v>78793</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22170,21 +22170,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22194,10 +22194,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>430232</v>
+        <v>430068</v>
       </c>
       <c r="R218" t="n">
-        <v>6818068</v>
+        <v>6818152</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22256,10 +22256,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128927800</v>
+        <v>128927967</v>
       </c>
       <c r="B219" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22267,37 +22267,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>430487</v>
+        <v>430084</v>
       </c>
       <c r="R219" t="n">
-        <v>6818080</v>
+        <v>6818144</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22338,7 +22335,6 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -22357,10 +22353,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128927771</v>
+        <v>128927881</v>
       </c>
       <c r="B220" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22368,42 +22364,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>430658</v>
+        <v>430536</v>
       </c>
       <c r="R220" t="n">
-        <v>6818274</v>
+        <v>6818208</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -22462,7 +22450,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128927967</v>
+        <v>128927916</v>
       </c>
       <c r="B221" t="n">
         <v>79035</v>
@@ -22497,10 +22485,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>430084</v>
+        <v>430580</v>
       </c>
       <c r="R221" t="n">
-        <v>6818144</v>
+        <v>6818221</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -22559,10 +22547,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128927867</v>
+        <v>128927771</v>
       </c>
       <c r="B222" t="n">
-        <v>78792</v>
+        <v>57720</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -22570,34 +22558,42 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>430006</v>
+        <v>430658</v>
       </c>
       <c r="R222" t="n">
-        <v>6818034</v>
+        <v>6818274</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -22656,10 +22652,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128927881</v>
+        <v>128927867</v>
       </c>
       <c r="B223" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -22667,21 +22663,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -22691,10 +22687,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>430536</v>
+        <v>430006</v>
       </c>
       <c r="R223" t="n">
-        <v>6818208</v>
+        <v>6818034</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -22753,10 +22749,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128927916</v>
+        <v>128927800</v>
       </c>
       <c r="B224" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22764,34 +22760,37 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>430580</v>
+        <v>430487</v>
       </c>
       <c r="R224" t="n">
-        <v>6818221</v>
+        <v>6818080</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -22832,6 +22831,7 @@
       <c r="AE224" t="b">
         <v>0</v>
       </c>
+      <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
         <v>0</v>
       </c>
@@ -22947,10 +22947,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128927890</v>
+        <v>128927730</v>
       </c>
       <c r="B226" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22958,21 +22958,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -22982,10 +22982,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>430348</v>
+        <v>430075</v>
       </c>
       <c r="R226" t="n">
-        <v>6818167</v>
+        <v>6818213</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23044,10 +23044,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128927730</v>
+        <v>128927890</v>
       </c>
       <c r="B227" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -23055,21 +23055,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23079,10 +23079,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>430075</v>
+        <v>430348</v>
       </c>
       <c r="R227" t="n">
-        <v>6818213</v>
+        <v>6818167</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>

--- a/artfynd/A 41639-2025 artfynd.xlsx
+++ b/artfynd/A 41639-2025 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128927821</v>
+        <v>128927770</v>
       </c>
       <c r="B22" t="n">
-        <v>78793</v>
+        <v>57722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,34 +2862,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>429994</v>
+        <v>430455</v>
       </c>
       <c r="R22" t="n">
-        <v>6818158</v>
+        <v>6818246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2948,10 +2956,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128927802</v>
+        <v>128927950</v>
       </c>
       <c r="B23" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,21 +2967,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,10 +2991,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>430567</v>
+        <v>430233</v>
       </c>
       <c r="R23" t="n">
-        <v>6818243</v>
+        <v>6817831</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,10 +3053,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128927732</v>
+        <v>128927868</v>
       </c>
       <c r="B24" t="n">
-        <v>79654</v>
+        <v>78796</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,21 +3064,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3088,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430138</v>
+        <v>430089</v>
       </c>
       <c r="R24" t="n">
-        <v>6817883</v>
+        <v>6817984</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128927721</v>
+        <v>128927978</v>
       </c>
       <c r="B25" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,21 +3161,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3177,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430060</v>
+        <v>430082</v>
       </c>
       <c r="R25" t="n">
-        <v>6818156</v>
+        <v>6818210</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,6 +3229,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3239,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128927868</v>
+        <v>128927843</v>
       </c>
       <c r="B26" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3274,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430089</v>
+        <v>430626</v>
       </c>
       <c r="R26" t="n">
-        <v>6817984</v>
+        <v>6818202</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128927843</v>
+        <v>128927721</v>
       </c>
       <c r="B27" t="n">
-        <v>78792</v>
+        <v>79658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3347,21 +3356,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3371,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430626</v>
+        <v>430060</v>
       </c>
       <c r="R27" t="n">
-        <v>6818202</v>
+        <v>6818156</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128927726</v>
+        <v>128927935</v>
       </c>
       <c r="B28" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3444,21 +3453,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3468,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430114</v>
+        <v>430099</v>
       </c>
       <c r="R28" t="n">
-        <v>6817912</v>
+        <v>6818154</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128927950</v>
+        <v>128927726</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3541,21 +3550,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3565,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430233</v>
+        <v>430114</v>
       </c>
       <c r="R29" t="n">
-        <v>6817831</v>
+        <v>6817912</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3627,32 +3636,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128927880</v>
+        <v>128927834</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>58095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3662,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>430577</v>
+        <v>430596</v>
       </c>
       <c r="R30" t="n">
-        <v>6818221</v>
+        <v>6818184</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3724,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128927978</v>
+        <v>128927821</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3735,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3759,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>430082</v>
+        <v>429994</v>
       </c>
       <c r="R31" t="n">
-        <v>6818210</v>
+        <v>6818158</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3803,7 +3812,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3822,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128927935</v>
+        <v>128927802</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3833,21 +3841,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3857,10 +3865,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>430099</v>
+        <v>430567</v>
       </c>
       <c r="R32" t="n">
-        <v>6818154</v>
+        <v>6818243</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3919,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128927963</v>
+        <v>128927880</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,10 +3962,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>430064</v>
+        <v>430577</v>
       </c>
       <c r="R33" t="n">
-        <v>6818190</v>
+        <v>6818221</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4016,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128927770</v>
+        <v>128927963</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4027,42 +4035,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>430455</v>
+        <v>430064</v>
       </c>
       <c r="R34" t="n">
-        <v>6818246</v>
+        <v>6818190</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128927834</v>
+        <v>128927732</v>
       </c>
       <c r="B35" t="n">
-        <v>58093</v>
+        <v>79658</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>430596</v>
+        <v>430138</v>
       </c>
       <c r="R35" t="n">
-        <v>6818184</v>
+        <v>6817883</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4221,7 +4221,7 @@
         <v>128927743</v>
       </c>
       <c r="B36" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>128927813</v>
       </c>
       <c r="B37" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128927871</v>
+        <v>128927895</v>
       </c>
       <c r="B38" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4423,21 +4423,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4447,10 +4447,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>430145</v>
+        <v>430350</v>
       </c>
       <c r="R38" t="n">
-        <v>6817833</v>
+        <v>6818053</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4509,10 +4509,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128927895</v>
+        <v>128927871</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4520,21 +4520,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>430350</v>
+        <v>430145</v>
       </c>
       <c r="R39" t="n">
-        <v>6818053</v>
+        <v>6817833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4609,7 +4609,7 @@
         <v>128927939</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>128927973</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>128927773</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128927930</v>
+        <v>128927845</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>430205</v>
+        <v>430669</v>
       </c>
       <c r="R43" t="n">
-        <v>6817961</v>
+        <v>6818249</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5006,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128927928</v>
+        <v>128927930</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>430293</v>
+        <v>430205</v>
       </c>
       <c r="R44" t="n">
-        <v>6817871</v>
+        <v>6817961</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,10 +5103,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128927934</v>
+        <v>128927928</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>430088</v>
+        <v>430293</v>
       </c>
       <c r="R45" t="n">
-        <v>6818186</v>
+        <v>6817871</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5200,10 +5200,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128927938</v>
+        <v>128927934</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>429959</v>
+        <v>430088</v>
       </c>
       <c r="R46" t="n">
-        <v>6818128</v>
+        <v>6818186</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,10 +5297,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128927976</v>
+        <v>128927842</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5308,37 +5308,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>430149</v>
+        <v>430596</v>
       </c>
       <c r="R47" t="n">
-        <v>6817860</v>
+        <v>6818186</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5379,7 +5376,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5398,10 +5394,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128927966</v>
+        <v>128927938</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5433,10 +5429,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>430071</v>
+        <v>429959</v>
       </c>
       <c r="R48" t="n">
-        <v>6818124</v>
+        <v>6818128</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5495,10 +5491,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128927786</v>
+        <v>128927976</v>
       </c>
       <c r="B49" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5506,31 +5502,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5538,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>430078</v>
+        <v>430149</v>
       </c>
       <c r="R49" t="n">
-        <v>6818213</v>
+        <v>6817860</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5576,17 +5567,13 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gammalt bo?</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5605,10 +5592,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128927845</v>
+        <v>128927966</v>
       </c>
       <c r="B50" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5616,21 +5603,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5640,10 +5627,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>430669</v>
+        <v>430071</v>
       </c>
       <c r="R50" t="n">
-        <v>6818249</v>
+        <v>6818124</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5702,10 +5689,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128927842</v>
+        <v>128927786</v>
       </c>
       <c r="B51" t="n">
-        <v>78792</v>
+        <v>57722</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,34 +5700,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>430596</v>
+        <v>430078</v>
       </c>
       <c r="R51" t="n">
-        <v>6818186</v>
+        <v>6818213</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5773,6 +5768,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gammalt bo?</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5802,7 +5802,7 @@
         <v>128927805</v>
       </c>
       <c r="B52" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128927799</v>
+        <v>128927819</v>
       </c>
       <c r="B53" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>430396</v>
+        <v>430033</v>
       </c>
       <c r="R53" t="n">
-        <v>6818052</v>
+        <v>6818116</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5993,10 +5993,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128927806</v>
+        <v>128927799</v>
       </c>
       <c r="B54" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>430655</v>
+        <v>430396</v>
       </c>
       <c r="R54" t="n">
-        <v>6818264</v>
+        <v>6818052</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,10 +6090,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128927819</v>
+        <v>128927806</v>
       </c>
       <c r="B55" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>430033</v>
+        <v>430655</v>
       </c>
       <c r="R55" t="n">
-        <v>6818116</v>
+        <v>6818264</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6187,10 +6187,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128927735</v>
+        <v>128927815</v>
       </c>
       <c r="B56" t="n">
-        <v>79654</v>
+        <v>78797</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>430132</v>
+        <v>430061</v>
       </c>
       <c r="R56" t="n">
-        <v>6817858</v>
+        <v>6818258</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6284,10 +6284,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128927855</v>
+        <v>128927937</v>
       </c>
       <c r="B57" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6295,21 +6295,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>430113</v>
+        <v>430011</v>
       </c>
       <c r="R57" t="n">
-        <v>6818160</v>
+        <v>6818137</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6384,7 +6384,7 @@
         <v>128927874</v>
       </c>
       <c r="B58" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6478,10 +6478,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128927937</v>
+        <v>128927970</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>430011</v>
+        <v>429900</v>
       </c>
       <c r="R59" t="n">
-        <v>6818137</v>
+        <v>6818098</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6549,6 +6549,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Foto 11.06 miljöbild</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6575,10 +6580,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128927970</v>
+        <v>128927944</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6604,16 +6609,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>429900</v>
+        <v>430531</v>
       </c>
       <c r="R60" t="n">
-        <v>6818098</v>
+        <v>6818016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6648,17 +6656,13 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Foto 11.06 miljöbild</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6677,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128927944</v>
+        <v>128927948</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6706,19 +6710,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>430531</v>
+        <v>430655</v>
       </c>
       <c r="R61" t="n">
-        <v>6818016</v>
+        <v>6818216</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6759,7 +6760,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128927948</v>
+        <v>128927735</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6789,21 +6789,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>430655</v>
+        <v>430132</v>
       </c>
       <c r="R62" t="n">
-        <v>6818216</v>
+        <v>6817858</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6878,7 +6878,7 @@
         <v>128927882</v>
       </c>
       <c r="B63" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>128927929</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128927815</v>
+        <v>128927855</v>
       </c>
       <c r="B65" t="n">
-        <v>78793</v>
+        <v>78796</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430061</v>
+        <v>430113</v>
       </c>
       <c r="R65" t="n">
-        <v>6818258</v>
+        <v>6818160</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128927790</v>
+        <v>128927825</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>78797</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7177,42 +7177,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430130</v>
+        <v>430024</v>
       </c>
       <c r="R66" t="n">
-        <v>6817856</v>
+        <v>6818040</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,10 +7263,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128927751</v>
+        <v>128927790</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>57722</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7282,16 +7274,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7304,7 +7296,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7314,10 +7306,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>430337</v>
+        <v>430130</v>
       </c>
       <c r="R67" t="n">
-        <v>6818076</v>
+        <v>6817856</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7379,7 +7371,7 @@
         <v>128927893</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7476,7 +7468,7 @@
         <v>128927974</v>
       </c>
       <c r="B69" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7570,10 +7562,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128927825</v>
+        <v>128927751</v>
       </c>
       <c r="B70" t="n">
-        <v>78793</v>
+        <v>57725</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7581,34 +7573,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>430024</v>
+        <v>430337</v>
       </c>
       <c r="R70" t="n">
-        <v>6818040</v>
+        <v>6818076</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7667,10 +7667,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128927831</v>
+        <v>128927857</v>
       </c>
       <c r="B71" t="n">
-        <v>78793</v>
+        <v>78796</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7678,37 +7678,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430126</v>
+        <v>430051</v>
       </c>
       <c r="R71" t="n">
-        <v>6817835</v>
+        <v>6818114</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7749,7 +7746,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7768,10 +7764,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128927857</v>
+        <v>128927852</v>
       </c>
       <c r="B72" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7803,10 +7799,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>430051</v>
+        <v>430086</v>
       </c>
       <c r="R72" t="n">
-        <v>6818114</v>
+        <v>6818279</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7868,7 +7864,7 @@
         <v>128927710</v>
       </c>
       <c r="B73" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7965,7 +7961,7 @@
         <v>128927839</v>
       </c>
       <c r="B74" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8059,10 +8055,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128927852</v>
+        <v>128927831</v>
       </c>
       <c r="B75" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8070,34 +8066,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>430086</v>
+        <v>430126</v>
       </c>
       <c r="R75" t="n">
-        <v>6818279</v>
+        <v>6817835</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8138,6 +8137,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8159,7 +8159,7 @@
         <v>128927840</v>
       </c>
       <c r="B76" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128927725</v>
+        <v>128927924</v>
       </c>
       <c r="B77" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430040</v>
+        <v>430671</v>
       </c>
       <c r="R77" t="n">
-        <v>6818029</v>
+        <v>6818266</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8350,10 +8350,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128927865</v>
+        <v>128927964</v>
       </c>
       <c r="B78" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8361,21 +8361,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>429935</v>
+        <v>430099</v>
       </c>
       <c r="R78" t="n">
-        <v>6818065</v>
+        <v>6818174</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128927924</v>
+        <v>128927897</v>
       </c>
       <c r="B79" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430671</v>
+        <v>430386</v>
       </c>
       <c r="R79" t="n">
-        <v>6818266</v>
+        <v>6818039</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8544,10 +8544,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128927964</v>
+        <v>128927955</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8573,16 +8573,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430099</v>
+        <v>430129</v>
       </c>
       <c r="R80" t="n">
-        <v>6818174</v>
+        <v>6818156</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8617,12 +8620,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30 m</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8641,10 +8650,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128927897</v>
+        <v>128927905</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8676,10 +8685,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430386</v>
+        <v>430395</v>
       </c>
       <c r="R81" t="n">
-        <v>6818039</v>
+        <v>6818138</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8738,10 +8747,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128927955</v>
+        <v>128927725</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8749,37 +8758,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>430129</v>
+        <v>430040</v>
       </c>
       <c r="R82" t="n">
-        <v>6818156</v>
+        <v>6818029</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8814,18 +8820,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30 m</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8844,10 +8844,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128927905</v>
+        <v>128927947</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8879,10 +8879,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>430395</v>
+        <v>430568</v>
       </c>
       <c r="R83" t="n">
-        <v>6818138</v>
+        <v>6818235</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8915,6 +8915,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8941,10 +8946,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128927885</v>
+        <v>128927795</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8952,21 +8957,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8976,10 +8981,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>430366</v>
+        <v>430390</v>
       </c>
       <c r="R84" t="n">
-        <v>6818264</v>
+        <v>6818205</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9038,10 +9043,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128927947</v>
+        <v>128927811</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9049,21 +9054,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9073,10 +9078,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>430568</v>
+        <v>430176</v>
       </c>
       <c r="R85" t="n">
-        <v>6818235</v>
+        <v>6818150</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9109,11 +9114,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Måttligt inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9140,10 +9140,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128927912</v>
+        <v>128927832</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9151,21 +9151,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>430439</v>
+        <v>430153</v>
       </c>
       <c r="R86" t="n">
-        <v>6818230</v>
+        <v>6817822</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9237,10 +9237,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128927795</v>
+        <v>128927865</v>
       </c>
       <c r="B87" t="n">
-        <v>78793</v>
+        <v>78796</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9248,21 +9248,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>430390</v>
+        <v>429935</v>
       </c>
       <c r="R87" t="n">
-        <v>6818205</v>
+        <v>6818065</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9334,10 +9334,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128927832</v>
+        <v>128927885</v>
       </c>
       <c r="B88" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9345,21 +9345,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>430153</v>
+        <v>430366</v>
       </c>
       <c r="R88" t="n">
-        <v>6817822</v>
+        <v>6818264</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9431,10 +9431,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128927811</v>
+        <v>128927912</v>
       </c>
       <c r="B89" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9442,21 +9442,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>430176</v>
+        <v>430439</v>
       </c>
       <c r="R89" t="n">
-        <v>6818150</v>
+        <v>6818230</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9531,7 +9531,7 @@
         <v>128927980</v>
       </c>
       <c r="B90" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128927714</v>
+        <v>128927891</v>
       </c>
       <c r="B91" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9636,21 +9636,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>430630</v>
+        <v>430336</v>
       </c>
       <c r="R91" t="n">
-        <v>6818207</v>
+        <v>6818151</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9722,10 +9722,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128927864</v>
+        <v>128927884</v>
       </c>
       <c r="B92" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9733,21 +9733,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>429975</v>
+        <v>430423</v>
       </c>
       <c r="R92" t="n">
-        <v>6818158</v>
+        <v>6818270</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128927851</v>
+        <v>128927864</v>
       </c>
       <c r="B93" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>430135</v>
+        <v>429975</v>
       </c>
       <c r="R93" t="n">
-        <v>6818172</v>
+        <v>6818158</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9916,10 +9916,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128927891</v>
+        <v>128927714</v>
       </c>
       <c r="B94" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9927,21 +9927,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9951,10 +9951,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>430336</v>
+        <v>430630</v>
       </c>
       <c r="R94" t="n">
-        <v>6818151</v>
+        <v>6818207</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10013,10 +10013,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128927884</v>
+        <v>128927965</v>
       </c>
       <c r="B95" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>430423</v>
+        <v>430115</v>
       </c>
       <c r="R95" t="n">
-        <v>6818270</v>
+        <v>6818177</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10110,10 +10110,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128927965</v>
+        <v>128927932</v>
       </c>
       <c r="B96" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10139,16 +10139,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>430115</v>
+        <v>430240</v>
       </c>
       <c r="R96" t="n">
-        <v>6818177</v>
+        <v>6817987</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10183,12 +10186,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Garnlav i de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10207,10 +10216,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128927932</v>
+        <v>128927975</v>
       </c>
       <c r="B97" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10236,19 +10245,16 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>430240</v>
+        <v>430138</v>
       </c>
       <c r="R97" t="n">
-        <v>6817987</v>
+        <v>6817903</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10283,18 +10289,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Garnlav i de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10313,10 +10313,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128927975</v>
+        <v>128927943</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10348,10 +10348,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>430138</v>
+        <v>430136</v>
       </c>
       <c r="R98" t="n">
-        <v>6817903</v>
+        <v>6817849</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10410,10 +10410,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128927943</v>
+        <v>128927851</v>
       </c>
       <c r="B99" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10421,21 +10421,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>430136</v>
+        <v>430135</v>
       </c>
       <c r="R99" t="n">
-        <v>6817849</v>
+        <v>6818172</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10510,7 +10510,7 @@
         <v>128927794</v>
       </c>
       <c r="B100" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>128927810</v>
       </c>
       <c r="B101" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>128927803</v>
       </c>
       <c r="B102" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128927856</v>
+        <v>128927793</v>
       </c>
       <c r="B103" t="n">
-        <v>78792</v>
+        <v>58155</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10809,21 +10809,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>103001</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10833,10 +10833,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>430060</v>
+        <v>430104</v>
       </c>
       <c r="R103" t="n">
-        <v>6818160</v>
+        <v>6817933</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10895,32 +10895,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128927836</v>
+        <v>128927827</v>
       </c>
       <c r="B104" t="n">
-        <v>58093</v>
+        <v>78797</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>430147</v>
+        <v>430057</v>
       </c>
       <c r="R104" t="n">
-        <v>6817817</v>
+        <v>6818016</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10992,10 +10992,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128927826</v>
+        <v>128927822</v>
       </c>
       <c r="B105" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>430018</v>
+        <v>429973</v>
       </c>
       <c r="R105" t="n">
-        <v>6818046</v>
+        <v>6818162</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11089,10 +11089,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128927796</v>
+        <v>128927826</v>
       </c>
       <c r="B106" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>430323</v>
+        <v>430018</v>
       </c>
       <c r="R106" t="n">
-        <v>6818121</v>
+        <v>6818046</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11186,10 +11186,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128927793</v>
+        <v>128927796</v>
       </c>
       <c r="B107" t="n">
-        <v>58153</v>
+        <v>78797</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11197,21 +11197,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103001</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>430104</v>
+        <v>430323</v>
       </c>
       <c r="R107" t="n">
-        <v>6817933</v>
+        <v>6818121</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11283,10 +11283,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128927827</v>
+        <v>128927954</v>
       </c>
       <c r="B108" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11294,34 +11294,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>430057</v>
+        <v>430166</v>
       </c>
       <c r="R108" t="n">
-        <v>6818016</v>
+        <v>6818134</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11356,12 +11359,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träden inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11380,32 +11389,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128927822</v>
+        <v>128927836</v>
       </c>
       <c r="B109" t="n">
-        <v>78793</v>
+        <v>58095</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11415,10 +11424,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>429973</v>
+        <v>430147</v>
       </c>
       <c r="R109" t="n">
-        <v>6818162</v>
+        <v>6817817</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11480,7 +11489,7 @@
         <v>128927899</v>
       </c>
       <c r="B110" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11574,10 +11583,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128927954</v>
+        <v>128927888</v>
       </c>
       <c r="B111" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11603,19 +11612,16 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>430166</v>
+        <v>430399</v>
       </c>
       <c r="R111" t="n">
-        <v>6818134</v>
+        <v>6818238</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11650,18 +11656,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träden inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128927888</v>
+        <v>128927971</v>
       </c>
       <c r="B112" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>430399</v>
+        <v>429925</v>
       </c>
       <c r="R112" t="n">
-        <v>6818238</v>
+        <v>6818065</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11777,10 +11777,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128927971</v>
+        <v>128927949</v>
       </c>
       <c r="B113" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>429925</v>
+        <v>430653</v>
       </c>
       <c r="R113" t="n">
-        <v>6818065</v>
+        <v>6818272</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128927949</v>
+        <v>128927856</v>
       </c>
       <c r="B114" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>430653</v>
+        <v>430060</v>
       </c>
       <c r="R114" t="n">
-        <v>6818272</v>
+        <v>6818160</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128927858</v>
+        <v>128927870</v>
       </c>
       <c r="B115" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>430034</v>
+        <v>430164</v>
       </c>
       <c r="R115" t="n">
-        <v>6818117</v>
+        <v>6817854</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12068,10 +12068,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128927873</v>
+        <v>128927858</v>
       </c>
       <c r="B116" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>429998</v>
+        <v>430034</v>
       </c>
       <c r="R116" t="n">
-        <v>6818047</v>
+        <v>6818117</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12165,10 +12165,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128927870</v>
+        <v>128927873</v>
       </c>
       <c r="B117" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>430164</v>
+        <v>429998</v>
       </c>
       <c r="R117" t="n">
-        <v>6817854</v>
+        <v>6818047</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12265,7 +12265,7 @@
         <v>128927901</v>
       </c>
       <c r="B118" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>128927921</v>
       </c>
       <c r="B119" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>128927740</v>
       </c>
       <c r="B120" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>128927823</v>
       </c>
       <c r="B121" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128927777</v>
+        <v>128927953</v>
       </c>
       <c r="B122" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12661,31 +12661,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
@@ -12693,10 +12688,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>429898</v>
+        <v>430242</v>
       </c>
       <c r="R122" t="n">
-        <v>6818099</v>
+        <v>6818048</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12731,12 +12726,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Garnlav på de flesta träd inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12755,10 +12756,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128927784</v>
+        <v>128927907</v>
       </c>
       <c r="B123" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12766,42 +12767,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>430201</v>
+        <v>430394</v>
       </c>
       <c r="R123" t="n">
-        <v>6818093</v>
+        <v>6818166</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12860,10 +12853,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128927769</v>
+        <v>128927977</v>
       </c>
       <c r="B124" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12871,31 +12864,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -12903,10 +12891,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>430485</v>
+        <v>430139</v>
       </c>
       <c r="R124" t="n">
-        <v>6818017</v>
+        <v>6817862</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12947,6 +12935,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -12965,10 +12954,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128927918</v>
+        <v>128927869</v>
       </c>
       <c r="B125" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12976,21 +12965,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13000,10 +12989,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>430649</v>
+        <v>430138</v>
       </c>
       <c r="R125" t="n">
-        <v>6818232</v>
+        <v>6817883</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13062,10 +13051,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128927878</v>
+        <v>128927720</v>
       </c>
       <c r="B126" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13073,21 +13062,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13097,10 +13086,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>430632</v>
+        <v>430112</v>
       </c>
       <c r="R126" t="n">
-        <v>6818282</v>
+        <v>6818160</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13159,10 +13148,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128927908</v>
+        <v>128927940</v>
       </c>
       <c r="B127" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13194,10 +13183,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>430425</v>
+        <v>429952</v>
       </c>
       <c r="R127" t="n">
-        <v>6818197</v>
+        <v>6818061</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13256,10 +13245,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128927886</v>
+        <v>128927853</v>
       </c>
       <c r="B128" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13267,21 +13256,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13291,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>430424</v>
+        <v>430073</v>
       </c>
       <c r="R128" t="n">
-        <v>6818252</v>
+        <v>6818201</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13353,10 +13342,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128927853</v>
+        <v>128927918</v>
       </c>
       <c r="B129" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13364,21 +13353,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13388,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>430073</v>
+        <v>430649</v>
       </c>
       <c r="R129" t="n">
-        <v>6818201</v>
+        <v>6818232</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13450,10 +13439,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128927720</v>
+        <v>128927878</v>
       </c>
       <c r="B130" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13461,21 +13450,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13485,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>430112</v>
+        <v>430632</v>
       </c>
       <c r="R130" t="n">
-        <v>6818160</v>
+        <v>6818282</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13547,10 +13536,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128927869</v>
+        <v>128927908</v>
       </c>
       <c r="B131" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13558,21 +13547,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13582,10 +13571,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>430138</v>
+        <v>430425</v>
       </c>
       <c r="R131" t="n">
-        <v>6817883</v>
+        <v>6818197</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13644,10 +13633,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128927953</v>
+        <v>128927886</v>
       </c>
       <c r="B132" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13673,19 +13662,16 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>430242</v>
+        <v>430424</v>
       </c>
       <c r="R132" t="n">
-        <v>6818048</v>
+        <v>6818252</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13720,18 +13706,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Garnlav på de flesta träd inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -13750,10 +13730,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128927907</v>
+        <v>128927777</v>
       </c>
       <c r="B133" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13761,34 +13741,42 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>430394</v>
+        <v>429898</v>
       </c>
       <c r="R133" t="n">
-        <v>6818166</v>
+        <v>6818099</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13847,10 +13835,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128927977</v>
+        <v>128927784</v>
       </c>
       <c r="B134" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13858,26 +13846,31 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -13885,10 +13878,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>430139</v>
+        <v>430201</v>
       </c>
       <c r="R134" t="n">
-        <v>6817862</v>
+        <v>6818093</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13929,7 +13922,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -13948,10 +13940,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128927940</v>
+        <v>128927769</v>
       </c>
       <c r="B135" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13959,34 +13951,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>429952</v>
+        <v>430485</v>
       </c>
       <c r="R135" t="n">
-        <v>6818061</v>
+        <v>6818017</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14045,10 +14045,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128927863</v>
+        <v>128927894</v>
       </c>
       <c r="B136" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14056,34 +14056,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>429970</v>
+        <v>430321</v>
       </c>
       <c r="R136" t="n">
-        <v>6818162</v>
+        <v>6818095</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14118,12 +14121,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -14142,10 +14151,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128927861</v>
+        <v>128927900</v>
       </c>
       <c r="B137" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14153,21 +14162,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14177,10 +14186,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>429989</v>
+        <v>430467</v>
       </c>
       <c r="R137" t="n">
-        <v>6818159</v>
+        <v>6818020</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14239,10 +14248,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128927709</v>
+        <v>128927911</v>
       </c>
       <c r="B138" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14250,21 +14259,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14274,10 +14283,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>430495</v>
+        <v>430437</v>
       </c>
       <c r="R138" t="n">
-        <v>6818056</v>
+        <v>6818227</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14336,54 +14345,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128927833</v>
+        <v>128927709</v>
       </c>
       <c r="B139" t="n">
-        <v>8450</v>
+        <v>79658</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>430204</v>
+        <v>430495</v>
       </c>
       <c r="R139" t="n">
-        <v>6817811</v>
+        <v>6818056</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14424,7 +14424,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14443,10 +14442,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128927748</v>
+        <v>128927956</v>
       </c>
       <c r="B140" t="n">
-        <v>79625</v>
+        <v>79039</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14454,21 +14453,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14478,10 +14477,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>430202</v>
+        <v>430119</v>
       </c>
       <c r="R140" t="n">
-        <v>6818084</v>
+        <v>6818173</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14540,10 +14539,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128927824</v>
+        <v>128927925</v>
       </c>
       <c r="B141" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14551,21 +14550,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14575,10 +14574,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>429941</v>
+        <v>430683</v>
       </c>
       <c r="R141" t="n">
-        <v>6818056</v>
+        <v>6818265</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14637,10 +14636,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128927894</v>
+        <v>128927972</v>
       </c>
       <c r="B142" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14675,10 +14674,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>430321</v>
+        <v>430018</v>
       </c>
       <c r="R142" t="n">
-        <v>6818095</v>
+        <v>6818025</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14711,11 +14710,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Garnlav på flertalet träd inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14743,10 +14737,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128927900</v>
+        <v>128927861</v>
       </c>
       <c r="B143" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14754,21 +14748,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14778,10 +14772,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>430467</v>
+        <v>429989</v>
       </c>
       <c r="R143" t="n">
-        <v>6818020</v>
+        <v>6818159</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14840,10 +14834,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128927889</v>
+        <v>128927926</v>
       </c>
       <c r="B144" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14875,10 +14869,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>430385</v>
+        <v>430701</v>
       </c>
       <c r="R144" t="n">
-        <v>6818203</v>
+        <v>6818261</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -14937,10 +14931,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128927911</v>
+        <v>128927781</v>
       </c>
       <c r="B145" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14948,34 +14942,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>430437</v>
+        <v>430480</v>
       </c>
       <c r="R145" t="n">
-        <v>6818227</v>
+        <v>6817997</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15034,10 +15036,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128927969</v>
+        <v>128927788</v>
       </c>
       <c r="B146" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15045,34 +15047,42 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>429947</v>
+        <v>430017</v>
       </c>
       <c r="R146" t="n">
-        <v>6818135</v>
+        <v>6818044</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15131,10 +15141,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128927956</v>
+        <v>128927775</v>
       </c>
       <c r="B147" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15142,34 +15152,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>430119</v>
+        <v>430083</v>
       </c>
       <c r="R147" t="n">
-        <v>6818173</v>
+        <v>6818224</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15228,10 +15246,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128927925</v>
+        <v>128927792</v>
       </c>
       <c r="B148" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15239,34 +15257,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>430683</v>
+        <v>430150</v>
       </c>
       <c r="R148" t="n">
-        <v>6818265</v>
+        <v>6817814</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15325,10 +15351,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128927972</v>
+        <v>128927889</v>
       </c>
       <c r="B149" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15354,19 +15380,16 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>430018</v>
+        <v>430385</v>
       </c>
       <c r="R149" t="n">
-        <v>6818025</v>
+        <v>6818203</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15407,7 +15430,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -15426,10 +15448,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128927926</v>
+        <v>128927863</v>
       </c>
       <c r="B150" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15437,21 +15459,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15461,10 +15483,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>430701</v>
+        <v>429970</v>
       </c>
       <c r="R150" t="n">
-        <v>6818261</v>
+        <v>6818162</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15523,10 +15545,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128927781</v>
+        <v>128927969</v>
       </c>
       <c r="B151" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15534,42 +15556,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>430480</v>
+        <v>429947</v>
       </c>
       <c r="R151" t="n">
-        <v>6817997</v>
+        <v>6818135</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15628,40 +15642,41 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128927788</v>
+        <v>128927833</v>
       </c>
       <c r="B152" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -15671,10 +15686,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>430017</v>
+        <v>430204</v>
       </c>
       <c r="R152" t="n">
-        <v>6818044</v>
+        <v>6817811</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15715,6 +15730,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -15733,10 +15749,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128927775</v>
+        <v>128927824</v>
       </c>
       <c r="B153" t="n">
-        <v>57720</v>
+        <v>78797</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15744,42 +15760,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>430083</v>
+        <v>429941</v>
       </c>
       <c r="R153" t="n">
-        <v>6818224</v>
+        <v>6818056</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15838,10 +15846,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128927792</v>
+        <v>128927748</v>
       </c>
       <c r="B154" t="n">
-        <v>57720</v>
+        <v>79629</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15849,42 +15857,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>430150</v>
+        <v>430202</v>
       </c>
       <c r="R154" t="n">
-        <v>6817814</v>
+        <v>6818084</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15946,7 +15946,7 @@
         <v>128927917</v>
       </c>
       <c r="B155" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>128927903</v>
       </c>
       <c r="B156" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16146,10 +16146,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128927920</v>
+        <v>128927875</v>
       </c>
       <c r="B157" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16157,21 +16157,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16181,10 +16181,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>430637</v>
+        <v>430127</v>
       </c>
       <c r="R157" t="n">
-        <v>6818260</v>
+        <v>6817846</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16243,10 +16243,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128927951</v>
+        <v>128927920</v>
       </c>
       <c r="B158" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16272,19 +16272,16 @@
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>430191</v>
+        <v>430637</v>
       </c>
       <c r="R158" t="n">
-        <v>6817932</v>
+        <v>6818260</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16319,18 +16316,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Garnlav, måttligt inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -16349,10 +16340,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128927958</v>
+        <v>128927838</v>
       </c>
       <c r="B159" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16360,21 +16351,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16384,10 +16375,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>430048</v>
+        <v>430439</v>
       </c>
       <c r="R159" t="n">
-        <v>6818232</v>
+        <v>6818031</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16446,10 +16437,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128927902</v>
+        <v>128927837</v>
       </c>
       <c r="B160" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16457,21 +16448,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16481,10 +16472,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>430530</v>
+        <v>430360</v>
       </c>
       <c r="R160" t="n">
-        <v>6818025</v>
+        <v>6818057</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16543,10 +16534,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128927779</v>
+        <v>128927951</v>
       </c>
       <c r="B161" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16554,31 +16545,26 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -16586,10 +16572,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>430106</v>
+        <v>430191</v>
       </c>
       <c r="R161" t="n">
-        <v>6817957</v>
+        <v>6817932</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16624,12 +16610,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Garnlav, måttligt inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -16648,10 +16640,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128927783</v>
+        <v>128927958</v>
       </c>
       <c r="B162" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16659,42 +16651,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>430174</v>
+        <v>430048</v>
       </c>
       <c r="R162" t="n">
-        <v>6817923</v>
+        <v>6818232</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16753,10 +16737,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128927837</v>
+        <v>128927846</v>
       </c>
       <c r="B163" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16788,10 +16772,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>430360</v>
+        <v>430241</v>
       </c>
       <c r="R163" t="n">
-        <v>6818057</v>
+        <v>6818085</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16850,10 +16834,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128927838</v>
+        <v>128927902</v>
       </c>
       <c r="B164" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16861,21 +16845,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16885,10 +16869,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>430439</v>
+        <v>430530</v>
       </c>
       <c r="R164" t="n">
-        <v>6818031</v>
+        <v>6818025</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -16947,10 +16931,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128927846</v>
+        <v>128927798</v>
       </c>
       <c r="B165" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16958,21 +16942,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -16982,10 +16966,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>430241</v>
+        <v>430315</v>
       </c>
       <c r="R165" t="n">
-        <v>6818085</v>
+        <v>6818095</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17044,10 +17028,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128927875</v>
+        <v>128927828</v>
       </c>
       <c r="B166" t="n">
-        <v>78792</v>
+        <v>78797</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17055,34 +17039,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>430127</v>
+        <v>430115</v>
       </c>
       <c r="R166" t="n">
-        <v>6817846</v>
+        <v>6817902</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17123,6 +17110,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -17141,10 +17129,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128927828</v>
+        <v>128927779</v>
       </c>
       <c r="B167" t="n">
-        <v>78793</v>
+        <v>57722</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17152,26 +17140,31 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
@@ -17179,10 +17172,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>430115</v>
+        <v>430106</v>
       </c>
       <c r="R167" t="n">
-        <v>6817902</v>
+        <v>6817957</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17223,7 +17216,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -17242,10 +17234,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128927798</v>
+        <v>128927783</v>
       </c>
       <c r="B168" t="n">
-        <v>78793</v>
+        <v>57722</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17253,34 +17245,42 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>430315</v>
+        <v>430174</v>
       </c>
       <c r="R168" t="n">
-        <v>6818095</v>
+        <v>6817923</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17342,7 +17342,7 @@
         <v>128927981</v>
       </c>
       <c r="B169" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17436,32 +17436,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128927712</v>
+        <v>128927835</v>
       </c>
       <c r="B170" t="n">
-        <v>79654</v>
+        <v>58095</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17471,10 +17471,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>430596</v>
+        <v>430104</v>
       </c>
       <c r="R170" t="n">
-        <v>6818190</v>
+        <v>6817960</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17533,10 +17533,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128927737</v>
+        <v>128927829</v>
       </c>
       <c r="B171" t="n">
-        <v>79654</v>
+        <v>78797</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17544,37 +17544,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>430143</v>
+        <v>430138</v>
       </c>
       <c r="R171" t="n">
-        <v>6817831</v>
+        <v>6817883</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17615,7 +17612,6 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -17634,45 +17630,48 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128927835</v>
+        <v>128927933</v>
       </c>
       <c r="B172" t="n">
-        <v>58093</v>
+        <v>79039</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>430104</v>
+        <v>430220</v>
       </c>
       <c r="R172" t="n">
-        <v>6817960</v>
+        <v>6818148</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17707,12 +17706,18 @@
           <t>2025-10-05</t>
         </is>
       </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -17731,10 +17736,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128927829</v>
+        <v>128927737</v>
       </c>
       <c r="B173" t="n">
-        <v>78793</v>
+        <v>79658</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17742,34 +17747,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>430138</v>
+        <v>430143</v>
       </c>
       <c r="R173" t="n">
-        <v>6817883</v>
+        <v>6817831</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -17810,6 +17818,7 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -17828,10 +17837,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128927933</v>
+        <v>128927904</v>
       </c>
       <c r="B174" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17857,19 +17866,16 @@
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>430220</v>
+        <v>430405</v>
       </c>
       <c r="R174" t="n">
-        <v>6818148</v>
+        <v>6818117</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -17904,18 +17910,12 @@
           <t>2025-10-05</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -17934,10 +17934,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128927904</v>
+        <v>128927712</v>
       </c>
       <c r="B175" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17945,21 +17945,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17969,10 +17969,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>430405</v>
+        <v>430596</v>
       </c>
       <c r="R175" t="n">
-        <v>6818117</v>
+        <v>6818190</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18031,45 +18031,53 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128927898</v>
+        <v>128927762</v>
       </c>
       <c r="B176" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>430384</v>
+        <v>430394</v>
       </c>
       <c r="R176" t="n">
-        <v>6818048</v>
+        <v>6818168</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18128,45 +18136,53 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128927968</v>
+        <v>128927760</v>
       </c>
       <c r="B177" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>430067</v>
+        <v>430663</v>
       </c>
       <c r="R177" t="n">
-        <v>6818139</v>
+        <v>6818259</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18225,10 +18241,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128927952</v>
+        <v>128927898</v>
       </c>
       <c r="B178" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18260,10 +18276,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>430190</v>
+        <v>430384</v>
       </c>
       <c r="R178" t="n">
-        <v>6817925</v>
+        <v>6818048</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18322,10 +18338,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128927945</v>
+        <v>128927723</v>
       </c>
       <c r="B179" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18333,21 +18349,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18357,10 +18373,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>430404</v>
+        <v>429993</v>
       </c>
       <c r="R179" t="n">
-        <v>6818178</v>
+        <v>6818157</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18422,7 +18438,7 @@
         <v>128927848</v>
       </c>
       <c r="B180" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18516,10 +18532,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128927723</v>
+        <v>128927968</v>
       </c>
       <c r="B181" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18527,21 +18543,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18551,10 +18567,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>429993</v>
+        <v>430067</v>
       </c>
       <c r="R181" t="n">
-        <v>6818157</v>
+        <v>6818139</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18613,53 +18629,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128927760</v>
+        <v>128927952</v>
       </c>
       <c r="B182" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>430663</v>
+        <v>430190</v>
       </c>
       <c r="R182" t="n">
-        <v>6818259</v>
+        <v>6817925</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18718,53 +18726,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128927762</v>
+        <v>128927945</v>
       </c>
       <c r="B183" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Rivsjövasslen, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>430394</v>
+        <v>430404</v>
       </c>
       <c r="R183" t="n">
-        <v>6818168</v>
+        <v>6818178</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -18826,7 +18826,7 @@
         <v>128927750</v>
       </c>
       <c r="B184" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>128927741</v>
       </c>
       <c r="B185" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>128927812</v>
       </c>
       <c r="B186" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19114,10 +19114,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128927872</v>
+        <v>128927910</v>
       </c>
       <c r="B187" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19125,21 +19125,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19149,10 +19149,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>430227</v>
+        <v>430430</v>
       </c>
       <c r="R187" t="n">
-        <v>6818015</v>
+        <v>6818202</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19211,10 +19211,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128927728</v>
+        <v>128927731</v>
       </c>
       <c r="B188" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19246,10 +19246,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>430232</v>
+        <v>430056</v>
       </c>
       <c r="R188" t="n">
-        <v>6818068</v>
+        <v>6818017</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19308,10 +19308,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128927731</v>
+        <v>128927847</v>
       </c>
       <c r="B189" t="n">
-        <v>79654</v>
+        <v>78796</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19319,21 +19319,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19343,10 +19343,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>430056</v>
+        <v>430227</v>
       </c>
       <c r="R189" t="n">
-        <v>6818017</v>
+        <v>6818154</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19405,10 +19405,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128927847</v>
+        <v>128927892</v>
       </c>
       <c r="B190" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19416,21 +19416,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19440,10 +19440,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>430227</v>
+        <v>430304</v>
       </c>
       <c r="R190" t="n">
-        <v>6818154</v>
+        <v>6818124</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19502,10 +19502,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128927910</v>
+        <v>128927872</v>
       </c>
       <c r="B191" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19513,21 +19513,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19537,10 +19537,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>430430</v>
+        <v>430227</v>
       </c>
       <c r="R191" t="n">
-        <v>6818202</v>
+        <v>6818015</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19599,10 +19599,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128927892</v>
+        <v>128927728</v>
       </c>
       <c r="B192" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19610,21 +19610,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19634,10 +19634,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>430304</v>
+        <v>430232</v>
       </c>
       <c r="R192" t="n">
-        <v>6818124</v>
+        <v>6818068</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19699,7 +19699,7 @@
         <v>128927906</v>
       </c>
       <c r="B193" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>128927922</v>
       </c>
       <c r="B194" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>128927962</v>
       </c>
       <c r="B195" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>128927789</v>
       </c>
       <c r="B196" t="n">
-        <v>57720</v>
+  